--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="290">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1245,7 +1245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4051,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ14">
         <v>1.4</v>
@@ -4672,7 +4672,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ17">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -7350,7 +7350,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ30">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR30">
         <v>1.33</v>
@@ -8377,7 +8377,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ35">
         <v>2.22</v>
@@ -11055,7 +11055,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ48">
         <v>1.44</v>
@@ -12088,7 +12088,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ53">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR53">
         <v>1.6</v>
@@ -14766,7 +14766,7 @@
         <v>2</v>
       </c>
       <c r="AQ66">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR66">
         <v>1.24</v>
@@ -15381,7 +15381,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ69">
         <v>1.33</v>
@@ -15999,7 +15999,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ72">
         <v>1.1</v>
@@ -19092,7 +19092,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ87">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR87">
         <v>1.38</v>
@@ -20737,7 +20737,7 @@
         <v>0.4</v>
       </c>
       <c r="AP95">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ95">
         <v>0.3</v>
@@ -22182,7 +22182,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ102">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR102">
         <v>1.5</v>
@@ -24857,7 +24857,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ115">
         <v>1.2</v>
@@ -26302,7 +26302,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ122">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR122">
         <v>1.24</v>
@@ -28565,7 +28565,7 @@
         <v>1.29</v>
       </c>
       <c r="AP133">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ133">
         <v>1.5</v>
@@ -30422,7 +30422,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ142">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR142">
         <v>1.66</v>
@@ -31449,7 +31449,7 @@
         <v>1.5</v>
       </c>
       <c r="AP147">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ147">
         <v>1.2</v>
@@ -33100,7 +33100,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ155">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR155">
         <v>1.55</v>
@@ -34333,7 +34333,7 @@
         <v>0.75</v>
       </c>
       <c r="AP161">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ161">
         <v>0.67</v>
@@ -36678,6 +36678,212 @@
       </c>
       <c r="BP172">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7502783</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45688.625</v>
+      </c>
+      <c r="F173">
+        <v>20</v>
+      </c>
+      <c r="G173" t="s">
+        <v>82</v>
+      </c>
+      <c r="H173" t="s">
+        <v>72</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>0</v>
+      </c>
+      <c r="O173" t="s">
+        <v>89</v>
+      </c>
+      <c r="P173" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q173">
+        <v>3.1</v>
+      </c>
+      <c r="R173">
+        <v>1.93</v>
+      </c>
+      <c r="S173">
+        <v>3.5</v>
+      </c>
+      <c r="T173">
+        <v>1.51</v>
+      </c>
+      <c r="U173">
+        <v>2.37</v>
+      </c>
+      <c r="V173">
+        <v>3.3</v>
+      </c>
+      <c r="W173">
+        <v>1.28</v>
+      </c>
+      <c r="X173">
+        <v>9.5</v>
+      </c>
+      <c r="Y173">
+        <v>1.05</v>
+      </c>
+      <c r="Z173">
+        <v>2.46</v>
+      </c>
+      <c r="AA173">
+        <v>3</v>
+      </c>
+      <c r="AB173">
+        <v>3.07</v>
+      </c>
+      <c r="AC173">
+        <v>1.09</v>
+      </c>
+      <c r="AD173">
+        <v>6.5</v>
+      </c>
+      <c r="AE173">
+        <v>1.45</v>
+      </c>
+      <c r="AF173">
+        <v>2.62</v>
+      </c>
+      <c r="AG173">
+        <v>2.35</v>
+      </c>
+      <c r="AH173">
+        <v>1.57</v>
+      </c>
+      <c r="AI173">
+        <v>2</v>
+      </c>
+      <c r="AJ173">
+        <v>1.7</v>
+      </c>
+      <c r="AK173">
+        <v>1.39</v>
+      </c>
+      <c r="AL173">
+        <v>1.35</v>
+      </c>
+      <c r="AM173">
+        <v>1.5</v>
+      </c>
+      <c r="AN173">
+        <v>1.1</v>
+      </c>
+      <c r="AO173">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP173">
+        <v>1.09</v>
+      </c>
+      <c r="AQ173">
+        <v>0.6</v>
+      </c>
+      <c r="AR173">
+        <v>1.71</v>
+      </c>
+      <c r="AS173">
+        <v>1.27</v>
+      </c>
+      <c r="AT173">
+        <v>2.98</v>
+      </c>
+      <c r="AU173">
+        <v>6</v>
+      </c>
+      <c r="AV173">
+        <v>2</v>
+      </c>
+      <c r="AW173">
+        <v>12</v>
+      </c>
+      <c r="AX173">
+        <v>4</v>
+      </c>
+      <c r="AY173">
+        <v>18</v>
+      </c>
+      <c r="AZ173">
+        <v>6</v>
+      </c>
+      <c r="BA173">
+        <v>5</v>
+      </c>
+      <c r="BB173">
+        <v>6</v>
+      </c>
+      <c r="BC173">
+        <v>11</v>
+      </c>
+      <c r="BD173">
+        <v>1.85</v>
+      </c>
+      <c r="BE173">
+        <v>8</v>
+      </c>
+      <c r="BF173">
+        <v>2.28</v>
+      </c>
+      <c r="BG173">
+        <v>1.18</v>
+      </c>
+      <c r="BH173">
+        <v>4.5</v>
+      </c>
+      <c r="BI173">
+        <v>1.34</v>
+      </c>
+      <c r="BJ173">
+        <v>3.1</v>
+      </c>
+      <c r="BK173">
+        <v>1.58</v>
+      </c>
+      <c r="BL173">
+        <v>2.29</v>
+      </c>
+      <c r="BM173">
+        <v>2</v>
+      </c>
+      <c r="BN173">
+        <v>1.8</v>
+      </c>
+      <c r="BO173">
+        <v>2.44</v>
+      </c>
+      <c r="BP173">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="296">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -616,6 +616,18 @@
     <t>['28']</t>
   </si>
   <si>
+    <t>['2', '45+4', '51']</t>
+  </si>
+  <si>
+    <t>['63', '75']</t>
+  </si>
+  <si>
+    <t>['1', '12', '77']</t>
+  </si>
+  <si>
+    <t>['37', '70']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -884,6 +896,12 @@
   </si>
   <si>
     <t>['80']</t>
+  </si>
+  <si>
+    <t>['7', '64']</t>
+  </si>
+  <si>
+    <t>['39', '84']</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP173"/>
+  <dimension ref="A1:BP180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1501,7 +1519,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1707,7 +1725,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1913,7 +1931,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -1994,7 +2012,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ4">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2325,7 +2343,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2531,7 +2549,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2815,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ8">
         <v>1.5</v>
@@ -2943,7 +2961,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3355,7 +3373,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3436,7 +3454,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ11">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3639,10 +3657,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ12">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3767,7 +3785,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3845,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ13">
         <v>1.6</v>
@@ -3973,7 +3991,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4054,7 +4072,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ14">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4179,7 +4197,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4257,10 +4275,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ15">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4385,7 +4403,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4463,10 +4481,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ16">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4669,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ17">
         <v>0.6</v>
@@ -4878,7 +4896,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ18">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5003,7 +5021,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5081,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ19">
         <v>0.3</v>
@@ -5209,7 +5227,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5827,7 +5845,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6239,7 +6257,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6651,7 +6669,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7063,7 +7081,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7144,7 +7162,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ29">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR29">
         <v>1.08</v>
@@ -7269,7 +7287,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7347,7 +7365,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ30">
         <v>0.6</v>
@@ -7553,10 +7571,10 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ31">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR31">
         <v>1.31</v>
@@ -7681,7 +7699,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7759,10 +7777,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ32">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR32">
         <v>2.27</v>
@@ -7965,10 +7983,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ33">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR33">
         <v>1.04</v>
@@ -8093,7 +8111,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8171,10 +8189,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ34">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR34">
         <v>1.57</v>
@@ -8299,7 +8317,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8380,7 +8398,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ35">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AR35">
         <v>1.95</v>
@@ -8505,7 +8523,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8583,10 +8601,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ36">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR36">
         <v>0.91</v>
@@ -8789,7 +8807,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ37">
         <v>1.6</v>
@@ -8917,7 +8935,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9123,7 +9141,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9535,7 +9553,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9741,7 +9759,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10153,7 +10171,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10359,7 +10377,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10643,7 +10661,7 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ46">
         <v>1.22</v>
@@ -10771,7 +10789,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10849,10 +10867,10 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ47">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR47">
         <v>1.36</v>
@@ -10977,7 +10995,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11058,7 +11076,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ48">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR48">
         <v>1.74</v>
@@ -11183,7 +11201,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11261,10 +11279,10 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ49">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AR49">
         <v>1.23</v>
@@ -11467,10 +11485,10 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ50">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR50">
         <v>1.2</v>
@@ -11595,7 +11613,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -11673,10 +11691,10 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ51">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR51">
         <v>1.12</v>
@@ -11879,7 +11897,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ52">
         <v>0.78</v>
@@ -12213,7 +12231,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12294,7 +12312,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR54">
         <v>1.11</v>
@@ -12497,10 +12515,10 @@
         <v>2</v>
       </c>
       <c r="AP55">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ55">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR55">
         <v>1.78</v>
@@ -12625,7 +12643,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12831,7 +12849,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -12912,7 +12930,7 @@
         <v>1</v>
       </c>
       <c r="AQ57">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR57">
         <v>1.67</v>
@@ -13243,7 +13261,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13321,7 +13339,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ59">
         <v>1.22</v>
@@ -13733,7 +13751,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ61">
         <v>1.1</v>
@@ -14479,7 +14497,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14560,7 +14578,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ65">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR65">
         <v>1.18</v>
@@ -14763,7 +14781,7 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ66">
         <v>0.6</v>
@@ -14891,7 +14909,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -14972,7 +14990,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ67">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AR67">
         <v>1.38</v>
@@ -15097,7 +15115,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15178,7 +15196,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ68">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR68">
         <v>1.55</v>
@@ -15384,7 +15402,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ69">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR69">
         <v>1.69</v>
@@ -15587,7 +15605,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ70">
         <v>0.78</v>
@@ -15793,10 +15811,10 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ71">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR71">
         <v>0.8</v>
@@ -16127,7 +16145,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16208,7 +16226,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ73">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR73">
         <v>1.18</v>
@@ -16333,7 +16351,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16411,7 +16429,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ74">
         <v>1.5</v>
@@ -16539,7 +16557,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16617,7 +16635,7 @@
         <v>0.5</v>
       </c>
       <c r="AP75">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ75">
         <v>1.2</v>
@@ -16745,7 +16763,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17157,7 +17175,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17238,7 +17256,7 @@
         <v>1</v>
       </c>
       <c r="AQ78">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR78">
         <v>1.7</v>
@@ -17569,7 +17587,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -18059,7 +18077,7 @@
         <v>1.6</v>
       </c>
       <c r="AP82">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ82">
         <v>1.1</v>
@@ -18187,7 +18205,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18268,7 +18286,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ83">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AR83">
         <v>1.45</v>
@@ -18471,7 +18489,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ84">
         <v>1.22</v>
@@ -18680,7 +18698,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ85">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18805,7 +18823,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -18886,7 +18904,7 @@
         <v>1</v>
       </c>
       <c r="AQ86">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR86">
         <v>1.78</v>
@@ -19217,7 +19235,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19295,10 +19313,10 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ88">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR88">
         <v>1.05</v>
@@ -19501,7 +19519,7 @@
         <v>0.33</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ89">
         <v>0.67</v>
@@ -19629,7 +19647,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19707,7 +19725,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ90">
         <v>1.5</v>
@@ -19835,7 +19853,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -19916,7 +19934,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ91">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR91">
         <v>1.19</v>
@@ -20041,7 +20059,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20119,7 +20137,7 @@
         <v>0.6</v>
       </c>
       <c r="AP92">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ92">
         <v>1.2</v>
@@ -20247,7 +20265,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20328,7 +20346,7 @@
         <v>1</v>
       </c>
       <c r="AQ93">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR93">
         <v>1.22</v>
@@ -20453,7 +20471,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20531,7 +20549,7 @@
         <v>2.2</v>
       </c>
       <c r="AP94">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ94">
         <v>1.6</v>
@@ -20659,7 +20677,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -20946,7 +20964,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ96">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR96">
         <v>1.37</v>
@@ -21071,7 +21089,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21277,7 +21295,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21483,7 +21501,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -21561,10 +21579,10 @@
         <v>1.75</v>
       </c>
       <c r="AP99">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ99">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR99">
         <v>1.34</v>
@@ -21767,10 +21785,10 @@
         <v>1.67</v>
       </c>
       <c r="AP100">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ100">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR100">
         <v>1.7</v>
@@ -21973,7 +21991,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ101">
         <v>0.67</v>
@@ -22307,7 +22325,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22388,7 +22406,7 @@
         <v>1</v>
       </c>
       <c r="AQ103">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR103">
         <v>1.71</v>
@@ -22719,7 +22737,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22797,7 +22815,7 @@
         <v>1.67</v>
       </c>
       <c r="AP105">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ105">
         <v>1.5</v>
@@ -22925,7 +22943,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23131,7 +23149,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23212,7 +23230,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ107">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR107">
         <v>1.21</v>
@@ -23337,7 +23355,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23415,7 +23433,7 @@
         <v>1.4</v>
       </c>
       <c r="AP108">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ108">
         <v>1.22</v>
@@ -23543,7 +23561,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -23621,7 +23639,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ109">
         <v>0.67</v>
@@ -23830,7 +23848,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ110">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR110">
         <v>1.51</v>
@@ -24033,10 +24051,10 @@
         <v>2.6</v>
       </c>
       <c r="AP111">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ111">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AR111">
         <v>1.61</v>
@@ -24242,7 +24260,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ112">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR112">
         <v>1.41</v>
@@ -24367,7 +24385,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24573,7 +24591,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -24654,7 +24672,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ114">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR114">
         <v>1.37</v>
@@ -24985,7 +25003,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25063,7 +25081,7 @@
         <v>1</v>
       </c>
       <c r="AP116">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ116">
         <v>1.5</v>
@@ -25191,7 +25209,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25272,7 +25290,7 @@
         <v>1</v>
       </c>
       <c r="AQ117">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR117">
         <v>1.26</v>
@@ -25397,7 +25415,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25475,7 +25493,7 @@
         <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ118">
         <v>0.3</v>
@@ -25681,7 +25699,7 @@
         <v>2</v>
       </c>
       <c r="AP119">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ119">
         <v>1.6</v>
@@ -26221,7 +26239,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26508,7 +26526,7 @@
         <v>1</v>
       </c>
       <c r="AQ123">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR123">
         <v>1.21</v>
@@ -26633,7 +26651,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -26917,7 +26935,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ125">
         <v>1.2</v>
@@ -27045,7 +27063,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27126,7 +27144,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ126">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -27329,7 +27347,7 @@
         <v>0.83</v>
       </c>
       <c r="AP127">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ127">
         <v>0.78</v>
@@ -27457,7 +27475,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27744,7 +27762,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ129">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR129">
         <v>1.3</v>
@@ -27869,7 +27887,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -27947,7 +27965,7 @@
         <v>0.43</v>
       </c>
       <c r="AP130">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ130">
         <v>0.3</v>
@@ -28153,10 +28171,10 @@
         <v>1.57</v>
       </c>
       <c r="AP131">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ131">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -28281,7 +28299,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28359,7 +28377,7 @@
         <v>1.86</v>
       </c>
       <c r="AP132">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ132">
         <v>1.6</v>
@@ -28487,7 +28505,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28693,7 +28711,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -28771,7 +28789,7 @@
         <v>1.43</v>
       </c>
       <c r="AP134">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ134">
         <v>1.6</v>
@@ -28980,7 +28998,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ135">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AR135">
         <v>1.3</v>
@@ -29186,7 +29204,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ136">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR136">
         <v>1.47</v>
@@ -29311,7 +29329,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29392,7 +29410,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ137">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR137">
         <v>1.18</v>
@@ -29723,7 +29741,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30007,7 +30025,7 @@
         <v>1.5</v>
       </c>
       <c r="AP140">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ140">
         <v>1.5</v>
@@ -30135,7 +30153,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30213,10 +30231,10 @@
         <v>2.29</v>
       </c>
       <c r="AP141">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ141">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AR141">
         <v>1.36</v>
@@ -30419,7 +30437,7 @@
         <v>0.71</v>
       </c>
       <c r="AP142">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ142">
         <v>0.6</v>
@@ -30547,7 +30565,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30625,7 +30643,7 @@
         <v>1.63</v>
       </c>
       <c r="AP143">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ143">
         <v>1.6</v>
@@ -30753,7 +30771,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -30831,10 +30849,10 @@
         <v>1.29</v>
       </c>
       <c r="AP144">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ144">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR144">
         <v>1.17</v>
@@ -31040,7 +31058,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ145">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR145">
         <v>1.33</v>
@@ -31165,7 +31183,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31243,10 +31261,10 @@
         <v>1.63</v>
       </c>
       <c r="AP146">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ146">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR146">
         <v>1.64</v>
@@ -31371,7 +31389,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31452,7 +31470,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ147">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR147">
         <v>1.68</v>
@@ -31577,7 +31595,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32195,7 +32213,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32273,7 +32291,7 @@
         <v>1.13</v>
       </c>
       <c r="AP151">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ151">
         <v>1.2</v>
@@ -32401,7 +32419,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32482,7 +32500,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ152">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR152">
         <v>1.34</v>
@@ -32607,7 +32625,7 @@
         <v>140</v>
       </c>
       <c r="P153" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q153">
         <v>2.96</v>
@@ -32813,7 +32831,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33303,10 +33321,10 @@
         <v>1.33</v>
       </c>
       <c r="AP156">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ156">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR156">
         <v>1.49</v>
@@ -33637,7 +33655,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -33715,10 +33733,10 @@
         <v>1.5</v>
       </c>
       <c r="AP158">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ158">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR158">
         <v>1.37</v>
@@ -33921,10 +33939,10 @@
         <v>1.38</v>
       </c>
       <c r="AP159">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ159">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR159">
         <v>1.72</v>
@@ -34127,7 +34145,7 @@
         <v>1.78</v>
       </c>
       <c r="AP160">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ160">
         <v>1.6</v>
@@ -34255,7 +34273,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34336,7 +34354,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ161">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR161">
         <v>1.7</v>
@@ -34539,10 +34557,10 @@
         <v>1.44</v>
       </c>
       <c r="AP162">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ162">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR162">
         <v>1.69</v>
@@ -34667,7 +34685,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34745,10 +34763,10 @@
         <v>2.38</v>
       </c>
       <c r="AP163">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ163">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AR163">
         <v>1.12</v>
@@ -34873,7 +34891,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35079,7 +35097,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35491,7 +35509,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -36315,7 +36333,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36393,7 +36411,7 @@
         <v>1.67</v>
       </c>
       <c r="AP171">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ171">
         <v>1.6</v>
@@ -36521,7 +36539,7 @@
         <v>199</v>
       </c>
       <c r="P172" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q172">
         <v>3.1</v>
@@ -36602,7 +36620,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ172">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR172">
         <v>1.3</v>
@@ -36884,6 +36902,1448 @@
       </c>
       <c r="BP173">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7502775</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45689.33333333334</v>
+      </c>
+      <c r="F174">
+        <v>20</v>
+      </c>
+      <c r="G174" t="s">
+        <v>83</v>
+      </c>
+      <c r="H174" t="s">
+        <v>78</v>
+      </c>
+      <c r="I174">
+        <v>2</v>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="K174">
+        <v>3</v>
+      </c>
+      <c r="L174">
+        <v>3</v>
+      </c>
+      <c r="M174">
+        <v>2</v>
+      </c>
+      <c r="N174">
+        <v>5</v>
+      </c>
+      <c r="O174" t="s">
+        <v>200</v>
+      </c>
+      <c r="P174" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q174">
+        <v>3.32</v>
+      </c>
+      <c r="R174">
+        <v>1.96</v>
+      </c>
+      <c r="S174">
+        <v>3.42</v>
+      </c>
+      <c r="T174">
+        <v>1.48</v>
+      </c>
+      <c r="U174">
+        <v>2.54</v>
+      </c>
+      <c r="V174">
+        <v>3.34</v>
+      </c>
+      <c r="W174">
+        <v>1.3</v>
+      </c>
+      <c r="X174">
+        <v>9.9</v>
+      </c>
+      <c r="Y174">
+        <v>1.03</v>
+      </c>
+      <c r="Z174">
+        <v>2.75</v>
+      </c>
+      <c r="AA174">
+        <v>2.9</v>
+      </c>
+      <c r="AB174">
+        <v>2.62</v>
+      </c>
+      <c r="AC174">
+        <v>1.02</v>
+      </c>
+      <c r="AD174">
+        <v>7.9</v>
+      </c>
+      <c r="AE174">
+        <v>1.36</v>
+      </c>
+      <c r="AF174">
+        <v>2.71</v>
+      </c>
+      <c r="AG174">
+        <v>2.2</v>
+      </c>
+      <c r="AH174">
+        <v>1.55</v>
+      </c>
+      <c r="AI174">
+        <v>1.92</v>
+      </c>
+      <c r="AJ174">
+        <v>1.79</v>
+      </c>
+      <c r="AK174">
+        <v>1.44</v>
+      </c>
+      <c r="AL174">
+        <v>1.33</v>
+      </c>
+      <c r="AM174">
+        <v>1.46</v>
+      </c>
+      <c r="AN174">
+        <v>1.7</v>
+      </c>
+      <c r="AO174">
+        <v>1.33</v>
+      </c>
+      <c r="AP174">
+        <v>1.82</v>
+      </c>
+      <c r="AQ174">
+        <v>1.2</v>
+      </c>
+      <c r="AR174">
+        <v>1.73</v>
+      </c>
+      <c r="AS174">
+        <v>1.51</v>
+      </c>
+      <c r="AT174">
+        <v>3.24</v>
+      </c>
+      <c r="AU174">
+        <v>6</v>
+      </c>
+      <c r="AV174">
+        <v>6</v>
+      </c>
+      <c r="AW174">
+        <v>6</v>
+      </c>
+      <c r="AX174">
+        <v>8</v>
+      </c>
+      <c r="AY174">
+        <v>12</v>
+      </c>
+      <c r="AZ174">
+        <v>14</v>
+      </c>
+      <c r="BA174">
+        <v>-1</v>
+      </c>
+      <c r="BB174">
+        <v>-1</v>
+      </c>
+      <c r="BC174">
+        <v>-1</v>
+      </c>
+      <c r="BD174">
+        <v>2.54</v>
+      </c>
+      <c r="BE174">
+        <v>8</v>
+      </c>
+      <c r="BF174">
+        <v>1.69</v>
+      </c>
+      <c r="BG174">
+        <v>1.2</v>
+      </c>
+      <c r="BH174">
+        <v>4.2</v>
+      </c>
+      <c r="BI174">
+        <v>1.38</v>
+      </c>
+      <c r="BJ174">
+        <v>2.88</v>
+      </c>
+      <c r="BK174">
+        <v>1.63</v>
+      </c>
+      <c r="BL174">
+        <v>2.18</v>
+      </c>
+      <c r="BM174">
+        <v>2.02</v>
+      </c>
+      <c r="BN174">
+        <v>1.74</v>
+      </c>
+      <c r="BO174">
+        <v>2.57</v>
+      </c>
+      <c r="BP174">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7502781</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45689.45833333334</v>
+      </c>
+      <c r="F175">
+        <v>20</v>
+      </c>
+      <c r="G175" t="s">
+        <v>87</v>
+      </c>
+      <c r="H175" t="s">
+        <v>74</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="L175">
+        <v>2</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+      <c r="N175">
+        <v>2</v>
+      </c>
+      <c r="O175" t="s">
+        <v>201</v>
+      </c>
+      <c r="P175" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q175">
+        <v>2.52</v>
+      </c>
+      <c r="R175">
+        <v>2.03</v>
+      </c>
+      <c r="S175">
+        <v>4.65</v>
+      </c>
+      <c r="T175">
+        <v>1.44</v>
+      </c>
+      <c r="U175">
+        <v>2.67</v>
+      </c>
+      <c r="V175">
+        <v>3.15</v>
+      </c>
+      <c r="W175">
+        <v>1.33</v>
+      </c>
+      <c r="X175">
+        <v>9</v>
+      </c>
+      <c r="Y175">
+        <v>1.04</v>
+      </c>
+      <c r="Z175">
+        <v>1.87</v>
+      </c>
+      <c r="AA175">
+        <v>3.1</v>
+      </c>
+      <c r="AB175">
+        <v>4.2</v>
+      </c>
+      <c r="AC175">
+        <v>1.01</v>
+      </c>
+      <c r="AD175">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE175">
+        <v>1.32</v>
+      </c>
+      <c r="AF175">
+        <v>2.88</v>
+      </c>
+      <c r="AG175">
+        <v>2.05</v>
+      </c>
+      <c r="AH175">
+        <v>1.61</v>
+      </c>
+      <c r="AI175">
+        <v>1.93</v>
+      </c>
+      <c r="AJ175">
+        <v>1.78</v>
+      </c>
+      <c r="AK175">
+        <v>1.22</v>
+      </c>
+      <c r="AL175">
+        <v>1.29</v>
+      </c>
+      <c r="AM175">
+        <v>1.86</v>
+      </c>
+      <c r="AN175">
+        <v>2</v>
+      </c>
+      <c r="AO175">
+        <v>2.22</v>
+      </c>
+      <c r="AP175">
+        <v>2.1</v>
+      </c>
+      <c r="AQ175">
+        <v>2</v>
+      </c>
+      <c r="AR175">
+        <v>1.61</v>
+      </c>
+      <c r="AS175">
+        <v>1.42</v>
+      </c>
+      <c r="AT175">
+        <v>3.03</v>
+      </c>
+      <c r="AU175">
+        <v>5</v>
+      </c>
+      <c r="AV175">
+        <v>0</v>
+      </c>
+      <c r="AW175">
+        <v>7</v>
+      </c>
+      <c r="AX175">
+        <v>4</v>
+      </c>
+      <c r="AY175">
+        <v>12</v>
+      </c>
+      <c r="AZ175">
+        <v>4</v>
+      </c>
+      <c r="BA175">
+        <v>-1</v>
+      </c>
+      <c r="BB175">
+        <v>-1</v>
+      </c>
+      <c r="BC175">
+        <v>-1</v>
+      </c>
+      <c r="BD175">
+        <v>1.45</v>
+      </c>
+      <c r="BE175">
+        <v>9</v>
+      </c>
+      <c r="BF175">
+        <v>3.32</v>
+      </c>
+      <c r="BG175">
+        <v>1.17</v>
+      </c>
+      <c r="BH175">
+        <v>4.7</v>
+      </c>
+      <c r="BI175">
+        <v>1.31</v>
+      </c>
+      <c r="BJ175">
+        <v>3.25</v>
+      </c>
+      <c r="BK175">
+        <v>1.54</v>
+      </c>
+      <c r="BL175">
+        <v>2.38</v>
+      </c>
+      <c r="BM175">
+        <v>1.92</v>
+      </c>
+      <c r="BN175">
+        <v>1.88</v>
+      </c>
+      <c r="BO175">
+        <v>2.35</v>
+      </c>
+      <c r="BP175">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7502779</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45689.52083333334</v>
+      </c>
+      <c r="F176">
+        <v>20</v>
+      </c>
+      <c r="G176" t="s">
+        <v>84</v>
+      </c>
+      <c r="H176" t="s">
+        <v>86</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>1</v>
+      </c>
+      <c r="O176" t="s">
+        <v>179</v>
+      </c>
+      <c r="P176" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q176">
+        <v>2.75</v>
+      </c>
+      <c r="R176">
+        <v>2.1</v>
+      </c>
+      <c r="S176">
+        <v>4</v>
+      </c>
+      <c r="T176">
+        <v>1.4</v>
+      </c>
+      <c r="U176">
+        <v>2.75</v>
+      </c>
+      <c r="V176">
+        <v>3</v>
+      </c>
+      <c r="W176">
+        <v>1.36</v>
+      </c>
+      <c r="X176">
+        <v>8</v>
+      </c>
+      <c r="Y176">
+        <v>1.08</v>
+      </c>
+      <c r="Z176">
+        <v>2.1</v>
+      </c>
+      <c r="AA176">
+        <v>3.3</v>
+      </c>
+      <c r="AB176">
+        <v>3.25</v>
+      </c>
+      <c r="AC176">
+        <v>1.05</v>
+      </c>
+      <c r="AD176">
+        <v>8.5</v>
+      </c>
+      <c r="AE176">
+        <v>1.3</v>
+      </c>
+      <c r="AF176">
+        <v>3.3</v>
+      </c>
+      <c r="AG176">
+        <v>1.91</v>
+      </c>
+      <c r="AH176">
+        <v>1.75</v>
+      </c>
+      <c r="AI176">
+        <v>1.8</v>
+      </c>
+      <c r="AJ176">
+        <v>1.91</v>
+      </c>
+      <c r="AK176">
+        <v>1.32</v>
+      </c>
+      <c r="AL176">
+        <v>1.29</v>
+      </c>
+      <c r="AM176">
+        <v>1.68</v>
+      </c>
+      <c r="AN176">
+        <v>1.56</v>
+      </c>
+      <c r="AO176">
+        <v>1.44</v>
+      </c>
+      <c r="AP176">
+        <v>1.7</v>
+      </c>
+      <c r="AQ176">
+        <v>1.3</v>
+      </c>
+      <c r="AR176">
+        <v>1.68</v>
+      </c>
+      <c r="AS176">
+        <v>1.54</v>
+      </c>
+      <c r="AT176">
+        <v>3.22</v>
+      </c>
+      <c r="AU176">
+        <v>6</v>
+      </c>
+      <c r="AV176">
+        <v>2</v>
+      </c>
+      <c r="AW176">
+        <v>5</v>
+      </c>
+      <c r="AX176">
+        <v>9</v>
+      </c>
+      <c r="AY176">
+        <v>11</v>
+      </c>
+      <c r="AZ176">
+        <v>11</v>
+      </c>
+      <c r="BA176">
+        <v>-1</v>
+      </c>
+      <c r="BB176">
+        <v>-1</v>
+      </c>
+      <c r="BC176">
+        <v>-1</v>
+      </c>
+      <c r="BD176">
+        <v>1.59</v>
+      </c>
+      <c r="BE176">
+        <v>8.5</v>
+      </c>
+      <c r="BF176">
+        <v>2.78</v>
+      </c>
+      <c r="BG176">
+        <v>1.18</v>
+      </c>
+      <c r="BH176">
+        <v>4.5</v>
+      </c>
+      <c r="BI176">
+        <v>1.34</v>
+      </c>
+      <c r="BJ176">
+        <v>3.1</v>
+      </c>
+      <c r="BK176">
+        <v>1.58</v>
+      </c>
+      <c r="BL176">
+        <v>2.29</v>
+      </c>
+      <c r="BM176">
+        <v>1.93</v>
+      </c>
+      <c r="BN176">
+        <v>1.82</v>
+      </c>
+      <c r="BO176">
+        <v>2.44</v>
+      </c>
+      <c r="BP176">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7502780</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45689.52083333334</v>
+      </c>
+      <c r="F177">
+        <v>20</v>
+      </c>
+      <c r="G177" t="s">
+        <v>76</v>
+      </c>
+      <c r="H177" t="s">
+        <v>73</v>
+      </c>
+      <c r="I177">
+        <v>2</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="K177">
+        <v>3</v>
+      </c>
+      <c r="L177">
+        <v>3</v>
+      </c>
+      <c r="M177">
+        <v>2</v>
+      </c>
+      <c r="N177">
+        <v>5</v>
+      </c>
+      <c r="O177" t="s">
+        <v>202</v>
+      </c>
+      <c r="P177" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q177">
+        <v>3.2</v>
+      </c>
+      <c r="R177">
+        <v>2.06</v>
+      </c>
+      <c r="S177">
+        <v>3.28</v>
+      </c>
+      <c r="T177">
+        <v>1.41</v>
+      </c>
+      <c r="U177">
+        <v>2.78</v>
+      </c>
+      <c r="V177">
+        <v>2.99</v>
+      </c>
+      <c r="W177">
+        <v>1.36</v>
+      </c>
+      <c r="X177">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y177">
+        <v>1.06</v>
+      </c>
+      <c r="Z177">
+        <v>2.55</v>
+      </c>
+      <c r="AA177">
+        <v>3.25</v>
+      </c>
+      <c r="AB177">
+        <v>2.6</v>
+      </c>
+      <c r="AC177">
+        <v>1.02</v>
+      </c>
+      <c r="AD177">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE177">
+        <v>1.28</v>
+      </c>
+      <c r="AF177">
+        <v>3.1</v>
+      </c>
+      <c r="AG177">
+        <v>1.91</v>
+      </c>
+      <c r="AH177">
+        <v>1.73</v>
+      </c>
+      <c r="AI177">
+        <v>1.76</v>
+      </c>
+      <c r="AJ177">
+        <v>1.95</v>
+      </c>
+      <c r="AK177">
+        <v>1.46</v>
+      </c>
+      <c r="AL177">
+        <v>1.31</v>
+      </c>
+      <c r="AM177">
+        <v>1.47</v>
+      </c>
+      <c r="AN177">
+        <v>1.22</v>
+      </c>
+      <c r="AO177">
+        <v>1.2</v>
+      </c>
+      <c r="AP177">
+        <v>1.4</v>
+      </c>
+      <c r="AQ177">
+        <v>1.09</v>
+      </c>
+      <c r="AR177">
+        <v>1.06</v>
+      </c>
+      <c r="AS177">
+        <v>1.29</v>
+      </c>
+      <c r="AT177">
+        <v>2.35</v>
+      </c>
+      <c r="AU177">
+        <v>5</v>
+      </c>
+      <c r="AV177">
+        <v>5</v>
+      </c>
+      <c r="AW177">
+        <v>4</v>
+      </c>
+      <c r="AX177">
+        <v>6</v>
+      </c>
+      <c r="AY177">
+        <v>9</v>
+      </c>
+      <c r="AZ177">
+        <v>11</v>
+      </c>
+      <c r="BA177">
+        <v>-1</v>
+      </c>
+      <c r="BB177">
+        <v>-1</v>
+      </c>
+      <c r="BC177">
+        <v>-1</v>
+      </c>
+      <c r="BD177">
+        <v>1.75</v>
+      </c>
+      <c r="BE177">
+        <v>8.5</v>
+      </c>
+      <c r="BF177">
+        <v>2.43</v>
+      </c>
+      <c r="BG177">
+        <v>1.18</v>
+      </c>
+      <c r="BH177">
+        <v>4.5</v>
+      </c>
+      <c r="BI177">
+        <v>1.34</v>
+      </c>
+      <c r="BJ177">
+        <v>3.1</v>
+      </c>
+      <c r="BK177">
+        <v>1.58</v>
+      </c>
+      <c r="BL177">
+        <v>2.29</v>
+      </c>
+      <c r="BM177">
+        <v>2</v>
+      </c>
+      <c r="BN177">
+        <v>1.8</v>
+      </c>
+      <c r="BO177">
+        <v>2.44</v>
+      </c>
+      <c r="BP177">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7502782</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45689.625</v>
+      </c>
+      <c r="F178">
+        <v>20</v>
+      </c>
+      <c r="G178" t="s">
+        <v>81</v>
+      </c>
+      <c r="H178" t="s">
+        <v>71</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="L178">
+        <v>2</v>
+      </c>
+      <c r="M178">
+        <v>0</v>
+      </c>
+      <c r="N178">
+        <v>2</v>
+      </c>
+      <c r="O178" t="s">
+        <v>203</v>
+      </c>
+      <c r="P178" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q178">
+        <v>3.02</v>
+      </c>
+      <c r="R178">
+        <v>1.99</v>
+      </c>
+      <c r="S178">
+        <v>3.7</v>
+      </c>
+      <c r="T178">
+        <v>1.47</v>
+      </c>
+      <c r="U178">
+        <v>2.57</v>
+      </c>
+      <c r="V178">
+        <v>3.2</v>
+      </c>
+      <c r="W178">
+        <v>1.32</v>
+      </c>
+      <c r="X178">
+        <v>8.5</v>
+      </c>
+      <c r="Y178">
+        <v>1.05</v>
+      </c>
+      <c r="Z178">
+        <v>2.4</v>
+      </c>
+      <c r="AA178">
+        <v>3.1</v>
+      </c>
+      <c r="AB178">
+        <v>2.9</v>
+      </c>
+      <c r="AC178">
+        <v>1.03</v>
+      </c>
+      <c r="AD178">
+        <v>7.3</v>
+      </c>
+      <c r="AE178">
+        <v>1.36</v>
+      </c>
+      <c r="AF178">
+        <v>2.71</v>
+      </c>
+      <c r="AG178">
+        <v>2.1</v>
+      </c>
+      <c r="AH178">
+        <v>1.6</v>
+      </c>
+      <c r="AI178">
+        <v>1.89</v>
+      </c>
+      <c r="AJ178">
+        <v>1.81</v>
+      </c>
+      <c r="AK178">
+        <v>1.37</v>
+      </c>
+      <c r="AL178">
+        <v>1.33</v>
+      </c>
+      <c r="AM178">
+        <v>1.55</v>
+      </c>
+      <c r="AN178">
+        <v>1.22</v>
+      </c>
+      <c r="AO178">
+        <v>0.67</v>
+      </c>
+      <c r="AP178">
+        <v>1.4</v>
+      </c>
+      <c r="AQ178">
+        <v>0.6</v>
+      </c>
+      <c r="AR178">
+        <v>1.35</v>
+      </c>
+      <c r="AS178">
+        <v>1.22</v>
+      </c>
+      <c r="AT178">
+        <v>2.57</v>
+      </c>
+      <c r="AU178">
+        <v>5</v>
+      </c>
+      <c r="AV178">
+        <v>3</v>
+      </c>
+      <c r="AW178">
+        <v>2</v>
+      </c>
+      <c r="AX178">
+        <v>5</v>
+      </c>
+      <c r="AY178">
+        <v>7</v>
+      </c>
+      <c r="AZ178">
+        <v>8</v>
+      </c>
+      <c r="BA178">
+        <v>-1</v>
+      </c>
+      <c r="BB178">
+        <v>-1</v>
+      </c>
+      <c r="BC178">
+        <v>-1</v>
+      </c>
+      <c r="BD178">
+        <v>2.05</v>
+      </c>
+      <c r="BE178">
+        <v>8</v>
+      </c>
+      <c r="BF178">
+        <v>1.95</v>
+      </c>
+      <c r="BG178">
+        <v>1.18</v>
+      </c>
+      <c r="BH178">
+        <v>4.5</v>
+      </c>
+      <c r="BI178">
+        <v>1.34</v>
+      </c>
+      <c r="BJ178">
+        <v>3.1</v>
+      </c>
+      <c r="BK178">
+        <v>1.58</v>
+      </c>
+      <c r="BL178">
+        <v>2.29</v>
+      </c>
+      <c r="BM178">
+        <v>2</v>
+      </c>
+      <c r="BN178">
+        <v>1.8</v>
+      </c>
+      <c r="BO178">
+        <v>2.44</v>
+      </c>
+      <c r="BP178">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7502777</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45690.33333333334</v>
+      </c>
+      <c r="F179">
+        <v>20</v>
+      </c>
+      <c r="G179" t="s">
+        <v>80</v>
+      </c>
+      <c r="H179" t="s">
+        <v>75</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179" t="s">
+        <v>89</v>
+      </c>
+      <c r="P179" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q179">
+        <v>4.33</v>
+      </c>
+      <c r="R179">
+        <v>2.05</v>
+      </c>
+      <c r="S179">
+        <v>2.75</v>
+      </c>
+      <c r="T179">
+        <v>1.44</v>
+      </c>
+      <c r="U179">
+        <v>2.63</v>
+      </c>
+      <c r="V179">
+        <v>3.25</v>
+      </c>
+      <c r="W179">
+        <v>1.33</v>
+      </c>
+      <c r="X179">
+        <v>9</v>
+      </c>
+      <c r="Y179">
+        <v>1.07</v>
+      </c>
+      <c r="Z179">
+        <v>3.3</v>
+      </c>
+      <c r="AA179">
+        <v>3.2</v>
+      </c>
+      <c r="AB179">
+        <v>2.1</v>
+      </c>
+      <c r="AC179">
+        <v>1.06</v>
+      </c>
+      <c r="AD179">
+        <v>8</v>
+      </c>
+      <c r="AE179">
+        <v>1.36</v>
+      </c>
+      <c r="AF179">
+        <v>3</v>
+      </c>
+      <c r="AG179">
+        <v>2</v>
+      </c>
+      <c r="AH179">
+        <v>1.67</v>
+      </c>
+      <c r="AI179">
+        <v>1.83</v>
+      </c>
+      <c r="AJ179">
+        <v>1.83</v>
+      </c>
+      <c r="AK179">
+        <v>1.72</v>
+      </c>
+      <c r="AL179">
+        <v>1.31</v>
+      </c>
+      <c r="AM179">
+        <v>1.29</v>
+      </c>
+      <c r="AN179">
+        <v>0.5</v>
+      </c>
+      <c r="AO179">
+        <v>1.33</v>
+      </c>
+      <c r="AP179">
+        <v>0.55</v>
+      </c>
+      <c r="AQ179">
+        <v>1.3</v>
+      </c>
+      <c r="AR179">
+        <v>1.25</v>
+      </c>
+      <c r="AS179">
+        <v>1.37</v>
+      </c>
+      <c r="AT179">
+        <v>2.62</v>
+      </c>
+      <c r="AU179">
+        <v>8</v>
+      </c>
+      <c r="AV179">
+        <v>3</v>
+      </c>
+      <c r="AW179">
+        <v>5</v>
+      </c>
+      <c r="AX179">
+        <v>8</v>
+      </c>
+      <c r="AY179">
+        <v>13</v>
+      </c>
+      <c r="AZ179">
+        <v>11</v>
+      </c>
+      <c r="BA179">
+        <v>-1</v>
+      </c>
+      <c r="BB179">
+        <v>-1</v>
+      </c>
+      <c r="BC179">
+        <v>-1</v>
+      </c>
+      <c r="BD179">
+        <v>2.32</v>
+      </c>
+      <c r="BE179">
+        <v>8.5</v>
+      </c>
+      <c r="BF179">
+        <v>1.82</v>
+      </c>
+      <c r="BG179">
+        <v>1.17</v>
+      </c>
+      <c r="BH179">
+        <v>4.6</v>
+      </c>
+      <c r="BI179">
+        <v>1.32</v>
+      </c>
+      <c r="BJ179">
+        <v>3.2</v>
+      </c>
+      <c r="BK179">
+        <v>1.55</v>
+      </c>
+      <c r="BL179">
+        <v>2.35</v>
+      </c>
+      <c r="BM179">
+        <v>1.9</v>
+      </c>
+      <c r="BN179">
+        <v>1.9</v>
+      </c>
+      <c r="BO179">
+        <v>2.38</v>
+      </c>
+      <c r="BP179">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7502776</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45690.45833333334</v>
+      </c>
+      <c r="F180">
+        <v>20</v>
+      </c>
+      <c r="G180" t="s">
+        <v>85</v>
+      </c>
+      <c r="H180" t="s">
+        <v>70</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>1</v>
+      </c>
+      <c r="M180">
+        <v>1</v>
+      </c>
+      <c r="N180">
+        <v>2</v>
+      </c>
+      <c r="O180" t="s">
+        <v>179</v>
+      </c>
+      <c r="P180" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q180">
+        <v>2.97</v>
+      </c>
+      <c r="R180">
+        <v>1.99</v>
+      </c>
+      <c r="S180">
+        <v>3.76</v>
+      </c>
+      <c r="T180">
+        <v>1.44</v>
+      </c>
+      <c r="U180">
+        <v>2.65</v>
+      </c>
+      <c r="V180">
+        <v>3.2</v>
+      </c>
+      <c r="W180">
+        <v>1.32</v>
+      </c>
+      <c r="X180">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y180">
+        <v>1.03</v>
+      </c>
+      <c r="Z180">
+        <v>2.3</v>
+      </c>
+      <c r="AA180">
+        <v>3.1</v>
+      </c>
+      <c r="AB180">
+        <v>3</v>
+      </c>
+      <c r="AC180">
+        <v>1</v>
+      </c>
+      <c r="AD180">
+        <v>9.1</v>
+      </c>
+      <c r="AE180">
+        <v>1.32</v>
+      </c>
+      <c r="AF180">
+        <v>2.88</v>
+      </c>
+      <c r="AG180">
+        <v>2.1</v>
+      </c>
+      <c r="AH180">
+        <v>1.61</v>
+      </c>
+      <c r="AI180">
+        <v>1.86</v>
+      </c>
+      <c r="AJ180">
+        <v>1.84</v>
+      </c>
+      <c r="AK180">
+        <v>1.35</v>
+      </c>
+      <c r="AL180">
+        <v>1.32</v>
+      </c>
+      <c r="AM180">
+        <v>1.58</v>
+      </c>
+      <c r="AN180">
+        <v>1.67</v>
+      </c>
+      <c r="AO180">
+        <v>1.4</v>
+      </c>
+      <c r="AP180">
+        <v>1.6</v>
+      </c>
+      <c r="AQ180">
+        <v>1.36</v>
+      </c>
+      <c r="AR180">
+        <v>1.51</v>
+      </c>
+      <c r="AS180">
+        <v>1.38</v>
+      </c>
+      <c r="AT180">
+        <v>2.89</v>
+      </c>
+      <c r="AU180">
+        <v>4</v>
+      </c>
+      <c r="AV180">
+        <v>5</v>
+      </c>
+      <c r="AW180">
+        <v>5</v>
+      </c>
+      <c r="AX180">
+        <v>6</v>
+      </c>
+      <c r="AY180">
+        <v>9</v>
+      </c>
+      <c r="AZ180">
+        <v>11</v>
+      </c>
+      <c r="BA180">
+        <v>-1</v>
+      </c>
+      <c r="BB180">
+        <v>-1</v>
+      </c>
+      <c r="BC180">
+        <v>-1</v>
+      </c>
+      <c r="BD180">
+        <v>1.91</v>
+      </c>
+      <c r="BE180">
+        <v>8</v>
+      </c>
+      <c r="BF180">
+        <v>2.1</v>
+      </c>
+      <c r="BG180">
+        <v>1.23</v>
+      </c>
+      <c r="BH180">
+        <v>3.85</v>
+      </c>
+      <c r="BI180">
+        <v>1.43</v>
+      </c>
+      <c r="BJ180">
+        <v>2.68</v>
+      </c>
+      <c r="BK180">
+        <v>1.71</v>
+      </c>
+      <c r="BL180">
+        <v>2.06</v>
+      </c>
+      <c r="BM180">
+        <v>2.14</v>
+      </c>
+      <c r="BN180">
+        <v>1.66</v>
+      </c>
+      <c r="BO180">
+        <v>2.77</v>
+      </c>
+      <c r="BP180">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="297">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -626,6 +626,9 @@
   </si>
   <si>
     <t>['37', '70']</t>
+  </si>
+  <si>
+    <t>['25', '83']</t>
   </si>
   <si>
     <t>['24', '27']</t>
@@ -1263,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP180"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1519,7 +1522,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1725,7 +1728,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1931,7 +1934,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2343,7 +2346,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2549,7 +2552,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2961,7 +2964,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3373,7 +3376,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3451,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ11">
         <v>1.2</v>
@@ -3785,7 +3788,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3866,7 +3869,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ13">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3991,7 +3994,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4197,7 +4200,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4403,7 +4406,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -5021,7 +5024,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5227,7 +5230,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5845,7 +5848,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6257,7 +6260,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6669,7 +6672,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7081,7 +7084,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7159,7 +7162,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ29">
         <v>1.09</v>
@@ -7287,7 +7290,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7699,7 +7702,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8111,7 +8114,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8317,7 +8320,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8523,7 +8526,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8810,7 +8813,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ37">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR37">
         <v>0.82</v>
@@ -8935,7 +8938,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9141,7 +9144,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9428,7 +9431,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ40">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR40">
         <v>1.4</v>
@@ -9553,7 +9556,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9759,7 +9762,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10171,7 +10174,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10377,7 +10380,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10789,7 +10792,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10995,7 +10998,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11201,7 +11204,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11613,7 +11616,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12103,7 +12106,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ53">
         <v>0.6</v>
@@ -12231,7 +12234,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12643,7 +12646,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12849,7 +12852,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13261,7 +13264,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13960,7 +13963,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ62">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR62">
         <v>1.41</v>
@@ -14497,7 +14500,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14909,7 +14912,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -14987,7 +14990,7 @@
         <v>3</v>
       </c>
       <c r="AP67">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ67">
         <v>2</v>
@@ -15115,7 +15118,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -16145,7 +16148,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16351,7 +16354,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16557,7 +16560,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16763,7 +16766,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17175,7 +17178,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17587,7 +17590,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17668,7 +17671,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR80">
         <v>1.09</v>
@@ -17871,7 +17874,7 @@
         <v>1.25</v>
       </c>
       <c r="AP81">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ81">
         <v>0.78</v>
@@ -18205,7 +18208,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18823,7 +18826,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19235,7 +19238,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19647,7 +19650,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19853,7 +19856,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20059,7 +20062,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20265,7 +20268,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20471,7 +20474,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20677,7 +20680,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21089,7 +21092,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21295,7 +21298,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21376,7 +21379,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ98">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21501,7 +21504,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22325,7 +22328,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22737,7 +22740,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22943,7 +22946,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23021,7 +23024,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ106">
         <v>1.1</v>
@@ -23149,7 +23152,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23355,7 +23358,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23561,7 +23564,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24385,7 +24388,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24466,7 +24469,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ113">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24591,7 +24594,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25003,7 +25006,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25209,7 +25212,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25415,7 +25418,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -26111,7 +26114,7 @@
         <v>1.86</v>
       </c>
       <c r="AP121">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ121">
         <v>1.5</v>
@@ -26239,7 +26242,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26651,7 +26654,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27063,7 +27066,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27475,7 +27478,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27887,7 +27890,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28299,7 +28302,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28505,7 +28508,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28711,7 +28714,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -28792,7 +28795,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ134">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR134">
         <v>1.14</v>
@@ -29329,7 +29332,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29741,7 +29744,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30153,7 +30156,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30565,7 +30568,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30646,7 +30649,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ143">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR143">
         <v>1.64</v>
@@ -30771,7 +30774,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31183,7 +31186,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31389,7 +31392,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31595,7 +31598,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32213,7 +32216,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32419,7 +32422,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32625,7 +32628,7 @@
         <v>140</v>
       </c>
       <c r="P153" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q153">
         <v>2.96</v>
@@ -32831,7 +32834,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -32909,7 +32912,7 @@
         <v>1.75</v>
       </c>
       <c r="AP154">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ154">
         <v>1.6</v>
@@ -33527,7 +33530,7 @@
         <v>0.33</v>
       </c>
       <c r="AP157">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ157">
         <v>0.3</v>
@@ -33655,7 +33658,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34148,7 +34151,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ160">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR160">
         <v>1.7</v>
@@ -34273,7 +34276,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34685,7 +34688,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34891,7 +34894,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35097,7 +35100,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35509,7 +35512,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -36333,7 +36336,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36539,7 +36542,7 @@
         <v>199</v>
       </c>
       <c r="P172" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q172">
         <v>3.1</v>
@@ -36951,7 +36954,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37062,13 +37065,13 @@
         <v>14</v>
       </c>
       <c r="BA174">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB174">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC174">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BD174">
         <v>2.54</v>
@@ -37268,13 +37271,13 @@
         <v>4</v>
       </c>
       <c r="BA175">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB175">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC175">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BD175">
         <v>1.45</v>
@@ -37474,13 +37477,13 @@
         <v>11</v>
       </c>
       <c r="BA176">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB176">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC176">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BD176">
         <v>1.59</v>
@@ -37569,7 +37572,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -37680,13 +37683,13 @@
         <v>11</v>
       </c>
       <c r="BA177">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB177">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BC177">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BD177">
         <v>1.75</v>
@@ -37886,13 +37889,13 @@
         <v>8</v>
       </c>
       <c r="BA178">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB178">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC178">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BD178">
         <v>2.05</v>
@@ -38092,13 +38095,13 @@
         <v>11</v>
       </c>
       <c r="BA179">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BB179">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC179">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD179">
         <v>2.32</v>
@@ -38187,7 +38190,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38298,13 +38301,13 @@
         <v>11</v>
       </c>
       <c r="BA180">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB180">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC180">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD180">
         <v>1.91</v>
@@ -38344,6 +38347,212 @@
       </c>
       <c r="BP180">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7502778</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45690.52083333334</v>
+      </c>
+      <c r="F181">
+        <v>20</v>
+      </c>
+      <c r="G181" t="s">
+        <v>79</v>
+      </c>
+      <c r="H181" t="s">
+        <v>77</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>1</v>
+      </c>
+      <c r="L181">
+        <v>2</v>
+      </c>
+      <c r="M181">
+        <v>1</v>
+      </c>
+      <c r="N181">
+        <v>3</v>
+      </c>
+      <c r="O181" t="s">
+        <v>204</v>
+      </c>
+      <c r="P181" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q181">
+        <v>2.88</v>
+      </c>
+      <c r="R181">
+        <v>2</v>
+      </c>
+      <c r="S181">
+        <v>3.88</v>
+      </c>
+      <c r="T181">
+        <v>1.47</v>
+      </c>
+      <c r="U181">
+        <v>2.57</v>
+      </c>
+      <c r="V181">
+        <v>3.2</v>
+      </c>
+      <c r="W181">
+        <v>1.32</v>
+      </c>
+      <c r="X181">
+        <v>8.5</v>
+      </c>
+      <c r="Y181">
+        <v>1.05</v>
+      </c>
+      <c r="Z181">
+        <v>2.25</v>
+      </c>
+      <c r="AA181">
+        <v>3.1</v>
+      </c>
+      <c r="AB181">
+        <v>3.1</v>
+      </c>
+      <c r="AC181">
+        <v>1.03</v>
+      </c>
+      <c r="AD181">
+        <v>7.3</v>
+      </c>
+      <c r="AE181">
+        <v>1.35</v>
+      </c>
+      <c r="AF181">
+        <v>2.75</v>
+      </c>
+      <c r="AG181">
+        <v>2.15</v>
+      </c>
+      <c r="AH181">
+        <v>1.6</v>
+      </c>
+      <c r="AI181">
+        <v>1.89</v>
+      </c>
+      <c r="AJ181">
+        <v>1.81</v>
+      </c>
+      <c r="AK181">
+        <v>1.33</v>
+      </c>
+      <c r="AL181">
+        <v>1.32</v>
+      </c>
+      <c r="AM181">
+        <v>1.61</v>
+      </c>
+      <c r="AN181">
+        <v>1.78</v>
+      </c>
+      <c r="AO181">
+        <v>1.6</v>
+      </c>
+      <c r="AP181">
+        <v>1.9</v>
+      </c>
+      <c r="AQ181">
+        <v>1.45</v>
+      </c>
+      <c r="AR181">
+        <v>1.63</v>
+      </c>
+      <c r="AS181">
+        <v>1.4</v>
+      </c>
+      <c r="AT181">
+        <v>3.03</v>
+      </c>
+      <c r="AU181">
+        <v>4</v>
+      </c>
+      <c r="AV181">
+        <v>5</v>
+      </c>
+      <c r="AW181">
+        <v>9</v>
+      </c>
+      <c r="AX181">
+        <v>4</v>
+      </c>
+      <c r="AY181">
+        <v>13</v>
+      </c>
+      <c r="AZ181">
+        <v>9</v>
+      </c>
+      <c r="BA181">
+        <v>1</v>
+      </c>
+      <c r="BB181">
+        <v>5</v>
+      </c>
+      <c r="BC181">
+        <v>6</v>
+      </c>
+      <c r="BD181">
+        <v>1.82</v>
+      </c>
+      <c r="BE181">
+        <v>8.5</v>
+      </c>
+      <c r="BF181">
+        <v>2.32</v>
+      </c>
+      <c r="BG181">
+        <v>1.17</v>
+      </c>
+      <c r="BH181">
+        <v>4.7</v>
+      </c>
+      <c r="BI181">
+        <v>1.32</v>
+      </c>
+      <c r="BJ181">
+        <v>3.22</v>
+      </c>
+      <c r="BK181">
+        <v>1.54</v>
+      </c>
+      <c r="BL181">
+        <v>2.37</v>
+      </c>
+      <c r="BM181">
+        <v>1.98</v>
+      </c>
+      <c r="BN181">
+        <v>1.82</v>
+      </c>
+      <c r="BO181">
+        <v>2.36</v>
+      </c>
+      <c r="BP181">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="297">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP182"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2633,7 +2633,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ7">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -4896,7 +4896,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ18">
         <v>1.3</v>
@@ -5517,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="AQ21">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR21">
         <v>1.84</v>
@@ -6956,7 +6956,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ28">
         <v>1.1</v>
@@ -10252,7 +10252,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
         <v>0.67</v>
@@ -11903,7 +11903,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ52">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR52">
         <v>1.2</v>
@@ -14372,7 +14372,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ64">
         <v>1.5</v>
@@ -15611,7 +15611,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ70">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR70">
         <v>1.47</v>
@@ -16844,7 +16844,7 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ76">
         <v>1.6</v>
@@ -17877,7 +17877,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ81">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -21170,7 +21170,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
         <v>1.5</v>
@@ -22615,7 +22615,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ104">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR104">
         <v>1.44</v>
@@ -24466,7 +24466,7 @@
         <v>1.17</v>
       </c>
       <c r="AP113">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ113">
         <v>1.45</v>
@@ -27353,7 +27353,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ127">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR127">
         <v>0.99</v>
@@ -29204,7 +29204,7 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ136">
         <v>1.2</v>
@@ -29619,7 +29619,7 @@
         <v>1</v>
       </c>
       <c r="AQ138">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR138">
         <v>1.22</v>
@@ -31676,7 +31676,7 @@
         <v>0.38</v>
       </c>
       <c r="AP148">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ148">
         <v>0.3</v>
@@ -33118,7 +33118,7 @@
         <v>0.63</v>
       </c>
       <c r="AP155">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ155">
         <v>0.6</v>
@@ -34975,7 +34975,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ164">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR164">
         <v>1.48</v>
@@ -38553,6 +38553,212 @@
       </c>
       <c r="BP181">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7502786</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45695.625</v>
+      </c>
+      <c r="F182">
+        <v>21</v>
+      </c>
+      <c r="G182" t="s">
+        <v>86</v>
+      </c>
+      <c r="H182" t="s">
+        <v>83</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182">
+        <v>1</v>
+      </c>
+      <c r="O182" t="s">
+        <v>89</v>
+      </c>
+      <c r="P182" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q182">
+        <v>2.65</v>
+      </c>
+      <c r="R182">
+        <v>2.18</v>
+      </c>
+      <c r="S182">
+        <v>4.44</v>
+      </c>
+      <c r="T182">
+        <v>1.41</v>
+      </c>
+      <c r="U182">
+        <v>2.84</v>
+      </c>
+      <c r="V182">
+        <v>3.1</v>
+      </c>
+      <c r="W182">
+        <v>1.36</v>
+      </c>
+      <c r="X182">
+        <v>7.8</v>
+      </c>
+      <c r="Y182">
+        <v>1.06</v>
+      </c>
+      <c r="Z182">
+        <v>1.91</v>
+      </c>
+      <c r="AA182">
+        <v>3.25</v>
+      </c>
+      <c r="AB182">
+        <v>3.5</v>
+      </c>
+      <c r="AC182">
+        <v>1.06</v>
+      </c>
+      <c r="AD182">
+        <v>8</v>
+      </c>
+      <c r="AE182">
+        <v>1.33</v>
+      </c>
+      <c r="AF182">
+        <v>3.1</v>
+      </c>
+      <c r="AG182">
+        <v>1.95</v>
+      </c>
+      <c r="AH182">
+        <v>1.7</v>
+      </c>
+      <c r="AI182">
+        <v>1.85</v>
+      </c>
+      <c r="AJ182">
+        <v>1.91</v>
+      </c>
+      <c r="AK182">
+        <v>1.26</v>
+      </c>
+      <c r="AL182">
+        <v>1.28</v>
+      </c>
+      <c r="AM182">
+        <v>1.79</v>
+      </c>
+      <c r="AN182">
+        <v>2.2</v>
+      </c>
+      <c r="AO182">
+        <v>0.78</v>
+      </c>
+      <c r="AP182">
+        <v>2</v>
+      </c>
+      <c r="AQ182">
+        <v>1</v>
+      </c>
+      <c r="AR182">
+        <v>1.54</v>
+      </c>
+      <c r="AS182">
+        <v>1.34</v>
+      </c>
+      <c r="AT182">
+        <v>2.88</v>
+      </c>
+      <c r="AU182">
+        <v>3</v>
+      </c>
+      <c r="AV182">
+        <v>6</v>
+      </c>
+      <c r="AW182">
+        <v>9</v>
+      </c>
+      <c r="AX182">
+        <v>6</v>
+      </c>
+      <c r="AY182">
+        <v>12</v>
+      </c>
+      <c r="AZ182">
+        <v>12</v>
+      </c>
+      <c r="BA182">
+        <v>4</v>
+      </c>
+      <c r="BB182">
+        <v>4</v>
+      </c>
+      <c r="BC182">
+        <v>8</v>
+      </c>
+      <c r="BD182">
+        <v>1.59</v>
+      </c>
+      <c r="BE182">
+        <v>8.5</v>
+      </c>
+      <c r="BF182">
+        <v>2.78</v>
+      </c>
+      <c r="BG182">
+        <v>1.25</v>
+      </c>
+      <c r="BH182">
+        <v>3.75</v>
+      </c>
+      <c r="BI182">
+        <v>1.45</v>
+      </c>
+      <c r="BJ182">
+        <v>2.63</v>
+      </c>
+      <c r="BK182">
+        <v>1.74</v>
+      </c>
+      <c r="BL182">
+        <v>2.02</v>
+      </c>
+      <c r="BM182">
+        <v>2.19</v>
+      </c>
+      <c r="BN182">
+        <v>1.63</v>
+      </c>
+      <c r="BO182">
+        <v>2.82</v>
+      </c>
+      <c r="BP182">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="298">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -631,6 +631,9 @@
     <t>['25', '83']</t>
   </si>
   <si>
+    <t>['52']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -761,9 +764,6 @@
   </si>
   <si>
     <t>['9', '11', '76']</t>
-  </si>
-  <si>
-    <t>['52']</t>
   </si>
   <si>
     <t>['31', '61']</t>
@@ -905,6 +905,9 @@
   </si>
   <si>
     <t>['39', '84']</t>
+  </si>
+  <si>
+    <t>['9', '45+1']</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP182"/>
+  <dimension ref="A1:BP183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1522,7 +1525,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1728,7 +1731,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1934,7 +1937,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2012,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ4">
         <v>1.3</v>
@@ -2346,7 +2349,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2427,7 +2430,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ6">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2552,7 +2555,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2964,7 +2967,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3376,7 +3379,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3788,7 +3791,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3994,7 +3997,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4200,7 +4203,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4406,7 +4409,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -5024,7 +5027,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5230,7 +5233,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5723,7 +5726,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ22">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR22">
         <v>1.3</v>
@@ -5848,7 +5851,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -5926,7 +5929,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ23">
         <v>1.22</v>
@@ -6260,7 +6263,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6672,7 +6675,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7084,7 +7087,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7290,7 +7293,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7702,7 +7705,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8114,7 +8117,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8320,7 +8323,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8526,7 +8529,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8938,7 +8941,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9144,7 +9147,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9556,7 +9559,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9762,7 +9765,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10174,7 +10177,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10255,7 +10258,7 @@
         <v>2</v>
       </c>
       <c r="AQ44">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR44">
         <v>1.61</v>
@@ -10380,7 +10383,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10458,7 +10461,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ45">
         <v>1.1</v>
@@ -10792,7 +10795,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10998,7 +11001,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11204,7 +11207,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11616,7 +11619,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12234,7 +12237,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12646,7 +12649,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12852,7 +12855,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13264,7 +13267,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13548,7 +13551,7 @@
         <v>0.67</v>
       </c>
       <c r="AP60">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ60">
         <v>1.2</v>
@@ -14500,7 +14503,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14912,7 +14915,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15118,7 +15121,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -16148,7 +16151,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16354,7 +16357,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16560,7 +16563,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16766,7 +16769,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17178,7 +17181,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17462,7 +17465,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ79">
         <v>0.3</v>
@@ -17590,7 +17593,7 @@
         <v>139</v>
       </c>
       <c r="P80" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -19525,7 +19528,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ89">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR89">
         <v>1.48</v>
@@ -19856,7 +19859,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20474,7 +20477,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20964,7 +20967,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ96">
         <v>1.36</v>
@@ -21092,7 +21095,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21997,7 +22000,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ101">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR101">
         <v>1.6</v>
@@ -23152,7 +23155,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23645,7 +23648,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ109">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR109">
         <v>1.09</v>
@@ -24672,7 +24675,7 @@
         <v>1.6</v>
       </c>
       <c r="AP114">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ114">
         <v>1.2</v>
@@ -27559,7 +27562,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ128">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR128">
         <v>1.46</v>
@@ -27762,7 +27765,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ129">
         <v>0.6</v>
@@ -29825,7 +29828,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ139">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR139">
         <v>1.54</v>
@@ -32500,7 +32503,7 @@
         <v>1.43</v>
       </c>
       <c r="AP152">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ152">
         <v>1.3</v>
@@ -32628,7 +32631,7 @@
         <v>140</v>
       </c>
       <c r="P153" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="Q153">
         <v>2.96</v>
@@ -35384,7 +35387,7 @@
         <v>1.56</v>
       </c>
       <c r="AP166">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ166">
         <v>1.5</v>
@@ -36005,7 +36008,7 @@
         <v>1</v>
       </c>
       <c r="AQ169">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR169">
         <v>1.26</v>
@@ -38759,6 +38762,212 @@
       </c>
       <c r="BP182">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7502787</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45696.33333333334</v>
+      </c>
+      <c r="F183">
+        <v>21</v>
+      </c>
+      <c r="G183" t="s">
+        <v>72</v>
+      </c>
+      <c r="H183" t="s">
+        <v>80</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>2</v>
+      </c>
+      <c r="K183">
+        <v>2</v>
+      </c>
+      <c r="L183">
+        <v>1</v>
+      </c>
+      <c r="M183">
+        <v>2</v>
+      </c>
+      <c r="N183">
+        <v>3</v>
+      </c>
+      <c r="O183" t="s">
+        <v>205</v>
+      </c>
+      <c r="P183" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q183">
+        <v>2.27</v>
+      </c>
+      <c r="R183">
+        <v>2.09</v>
+      </c>
+      <c r="S183">
+        <v>5.35</v>
+      </c>
+      <c r="T183">
+        <v>1.41</v>
+      </c>
+      <c r="U183">
+        <v>2.78</v>
+      </c>
+      <c r="V183">
+        <v>3.1</v>
+      </c>
+      <c r="W183">
+        <v>1.34</v>
+      </c>
+      <c r="X183">
+        <v>9</v>
+      </c>
+      <c r="Y183">
+        <v>1.04</v>
+      </c>
+      <c r="Z183">
+        <v>1.67</v>
+      </c>
+      <c r="AA183">
+        <v>3.4</v>
+      </c>
+      <c r="AB183">
+        <v>4.4</v>
+      </c>
+      <c r="AC183">
+        <v>1.02</v>
+      </c>
+      <c r="AD183">
+        <v>7.8</v>
+      </c>
+      <c r="AE183">
+        <v>1.28</v>
+      </c>
+      <c r="AF183">
+        <v>3.08</v>
+      </c>
+      <c r="AG183">
+        <v>2</v>
+      </c>
+      <c r="AH183">
+        <v>1.67</v>
+      </c>
+      <c r="AI183">
+        <v>1.96</v>
+      </c>
+      <c r="AJ183">
+        <v>1.75</v>
+      </c>
+      <c r="AK183">
+        <v>1.15</v>
+      </c>
+      <c r="AL183">
+        <v>1.26</v>
+      </c>
+      <c r="AM183">
+        <v>2.11</v>
+      </c>
+      <c r="AN183">
+        <v>1.9</v>
+      </c>
+      <c r="AO183">
+        <v>0.67</v>
+      </c>
+      <c r="AP183">
+        <v>1.73</v>
+      </c>
+      <c r="AQ183">
+        <v>0.9</v>
+      </c>
+      <c r="AR183">
+        <v>1.33</v>
+      </c>
+      <c r="AS183">
+        <v>1.13</v>
+      </c>
+      <c r="AT183">
+        <v>2.46</v>
+      </c>
+      <c r="AU183">
+        <v>6</v>
+      </c>
+      <c r="AV183">
+        <v>5</v>
+      </c>
+      <c r="AW183">
+        <v>12</v>
+      </c>
+      <c r="AX183">
+        <v>2</v>
+      </c>
+      <c r="AY183">
+        <v>18</v>
+      </c>
+      <c r="AZ183">
+        <v>7</v>
+      </c>
+      <c r="BA183">
+        <v>12</v>
+      </c>
+      <c r="BB183">
+        <v>8</v>
+      </c>
+      <c r="BC183">
+        <v>20</v>
+      </c>
+      <c r="BD183">
+        <v>1.45</v>
+      </c>
+      <c r="BE183">
+        <v>9</v>
+      </c>
+      <c r="BF183">
+        <v>3.19</v>
+      </c>
+      <c r="BG183">
+        <v>1.23</v>
+      </c>
+      <c r="BH183">
+        <v>3.92</v>
+      </c>
+      <c r="BI183">
+        <v>1.42</v>
+      </c>
+      <c r="BJ183">
+        <v>2.73</v>
+      </c>
+      <c r="BK183">
+        <v>1.69</v>
+      </c>
+      <c r="BL183">
+        <v>2.09</v>
+      </c>
+      <c r="BM183">
+        <v>2.11</v>
+      </c>
+      <c r="BN183">
+        <v>1.68</v>
+      </c>
+      <c r="BO183">
+        <v>2.72</v>
+      </c>
+      <c r="BP183">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="300">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -634,6 +634,9 @@
     <t>['52']</t>
   </si>
   <si>
+    <t>['12', '67']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -908,6 +911,9 @@
   </si>
   <si>
     <t>['9', '45+1']</t>
+  </si>
+  <si>
+    <t>['3', '31']</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP183"/>
+  <dimension ref="A1:BP186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1525,7 +1531,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1603,10 +1609,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ2">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1731,7 +1737,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1812,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1937,7 +1943,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2349,7 +2355,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2427,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ6">
         <v>0.9</v>
@@ -2555,7 +2561,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2967,7 +2973,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3251,10 +3257,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ10">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3379,7 +3385,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3791,7 +3797,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3997,7 +4003,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4203,7 +4209,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4409,7 +4415,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -5027,7 +5033,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5233,7 +5239,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5517,7 +5523,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ21">
         <v>1</v>
@@ -5851,7 +5857,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -5932,7 +5938,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ23">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR23">
         <v>1.93</v>
@@ -6263,7 +6269,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6341,10 +6347,10 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ25">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR25">
         <v>1.23</v>
@@ -6547,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ26">
         <v>1.5</v>
@@ -6675,7 +6681,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -6756,7 +6762,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR27">
         <v>1.33</v>
@@ -7087,7 +7093,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7293,7 +7299,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7705,7 +7711,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8117,7 +8123,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8323,7 +8329,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8529,7 +8535,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8941,7 +8947,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9022,7 +9028,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ38">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR38">
         <v>1.5</v>
@@ -9147,7 +9153,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9225,7 +9231,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ39">
         <v>1.5</v>
@@ -9559,7 +9565,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9637,7 +9643,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
         <v>1.5</v>
@@ -9765,7 +9771,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9846,7 +9852,7 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR42">
         <v>1.42</v>
@@ -10049,7 +10055,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ43">
         <v>0.3</v>
@@ -10177,7 +10183,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10383,7 +10389,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10670,7 +10676,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ46">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR46">
         <v>1.7</v>
@@ -10795,7 +10801,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11001,7 +11007,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11207,7 +11213,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11619,7 +11625,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12237,7 +12243,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12649,7 +12655,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12730,7 +12736,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ56">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR56">
         <v>1.67</v>
@@ -12855,7 +12861,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -12933,7 +12939,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ57">
         <v>1.09</v>
@@ -13139,7 +13145,7 @@
         <v>0.67</v>
       </c>
       <c r="AP58">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ58">
         <v>0.3</v>
@@ -13267,7 +13273,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13348,7 +13354,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ59">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR59">
         <v>1.13</v>
@@ -13554,7 +13560,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ60">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR60">
         <v>1.51</v>
@@ -13963,7 +13969,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ62">
         <v>1.45</v>
@@ -14503,7 +14509,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14915,7 +14921,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15121,7 +15127,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -16151,7 +16157,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16229,7 +16235,7 @@
         <v>1.25</v>
       </c>
       <c r="AP73">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ73">
         <v>1.09</v>
@@ -16357,7 +16363,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16563,7 +16569,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16644,7 +16650,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ75">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR75">
         <v>1.62</v>
@@ -16769,7 +16775,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -16850,7 +16856,7 @@
         <v>2</v>
       </c>
       <c r="AQ76">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR76">
         <v>1.55</v>
@@ -17181,7 +17187,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17259,7 +17265,7 @@
         <v>1.75</v>
       </c>
       <c r="AP78">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ78">
         <v>1.36</v>
@@ -18211,7 +18217,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18289,7 +18295,7 @@
         <v>2.5</v>
       </c>
       <c r="AP83">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ83">
         <v>2</v>
@@ -18498,7 +18504,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ84">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR84">
         <v>1.48</v>
@@ -18829,7 +18835,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -18907,7 +18913,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ86">
         <v>0.6</v>
@@ -19241,7 +19247,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19653,7 +19659,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19859,7 +19865,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -19937,7 +19943,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ91">
         <v>1.2</v>
@@ -20065,7 +20071,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20146,7 +20152,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ92">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR92">
         <v>1.19</v>
@@ -20271,7 +20277,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20477,7 +20483,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20558,7 +20564,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ94">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR94">
         <v>1.74</v>
@@ -20683,7 +20689,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21095,7 +21101,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21301,7 +21307,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21507,7 +21513,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22331,7 +22337,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22409,7 +22415,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ103">
         <v>1.3</v>
@@ -22743,7 +22749,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22949,7 +22955,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23155,7 +23161,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23233,7 +23239,7 @@
         <v>1</v>
       </c>
       <c r="AP107">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ107">
         <v>0.6</v>
@@ -23361,7 +23367,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23442,7 +23448,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ108">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR108">
         <v>1.57</v>
@@ -23567,7 +23573,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -23851,7 +23857,7 @@
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ110">
         <v>1.3</v>
@@ -24391,7 +24397,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24597,7 +24603,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -24884,7 +24890,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ115">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR115">
         <v>1.59</v>
@@ -25009,7 +25015,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25215,7 +25221,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25421,7 +25427,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25708,7 +25714,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ119">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR119">
         <v>1.64</v>
@@ -25914,7 +25920,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ120">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR120">
         <v>1.47</v>
@@ -26245,7 +26251,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26323,7 +26329,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ122">
         <v>0.6</v>
@@ -26657,7 +26663,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -26735,7 +26741,7 @@
         <v>1.29</v>
       </c>
       <c r="AP124">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ124">
         <v>1.1</v>
@@ -26944,7 +26950,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ125">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR125">
         <v>1.63</v>
@@ -27069,7 +27075,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27147,7 +27153,7 @@
         <v>1.17</v>
       </c>
       <c r="AP126">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ126">
         <v>1.3</v>
@@ -27481,7 +27487,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27893,7 +27899,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28305,7 +28311,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28386,7 +28392,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ132">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR132">
         <v>1.39</v>
@@ -28511,7 +28517,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28717,7 +28723,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29335,7 +29341,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29413,7 +29419,7 @@
         <v>1.57</v>
       </c>
       <c r="AP137">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ137">
         <v>1.3</v>
@@ -29747,7 +29753,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -29825,7 +29831,7 @@
         <v>0.29</v>
       </c>
       <c r="AP139">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ139">
         <v>0.9</v>
@@ -30159,7 +30165,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30571,7 +30577,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30777,7 +30783,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31189,7 +31195,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31395,7 +31401,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31601,7 +31607,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32091,10 +32097,10 @@
         <v>1.43</v>
       </c>
       <c r="AP150">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ150">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR150">
         <v>1.63</v>
@@ -32219,7 +32225,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32300,7 +32306,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ151">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR151">
         <v>1.02</v>
@@ -32425,7 +32431,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32837,7 +32843,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -32918,7 +32924,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ154">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR154">
         <v>1.58</v>
@@ -33661,7 +33667,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34279,7 +34285,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34691,7 +34697,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34897,7 +34903,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35103,7 +35109,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35181,7 +35187,7 @@
         <v>1.33</v>
       </c>
       <c r="AP165">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ165">
         <v>1.5</v>
@@ -35515,7 +35521,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -35593,10 +35599,10 @@
         <v>1.25</v>
       </c>
       <c r="AP167">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ167">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR167">
         <v>1.71</v>
@@ -35799,7 +35805,7 @@
         <v>1.11</v>
       </c>
       <c r="AP168">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AQ168">
         <v>1.1</v>
@@ -36214,7 +36220,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ170">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR170">
         <v>1.53</v>
@@ -36339,7 +36345,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36420,7 +36426,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ171">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR171">
         <v>1.04</v>
@@ -36545,7 +36551,7 @@
         <v>199</v>
       </c>
       <c r="P172" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q172">
         <v>3.1</v>
@@ -36957,7 +36963,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37575,7 +37581,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -38193,7 +38199,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38605,7 +38611,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38811,7 +38817,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -38968,6 +38974,624 @@
       </c>
       <c r="BP183">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7502792</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45696.45833333334</v>
+      </c>
+      <c r="F184">
+        <v>21</v>
+      </c>
+      <c r="G184" t="s">
+        <v>78</v>
+      </c>
+      <c r="H184" t="s">
+        <v>87</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>1</v>
+      </c>
+      <c r="M184">
+        <v>0</v>
+      </c>
+      <c r="N184">
+        <v>1</v>
+      </c>
+      <c r="O184" t="s">
+        <v>109</v>
+      </c>
+      <c r="P184" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q184">
+        <v>3.45</v>
+      </c>
+      <c r="R184">
+        <v>1.97</v>
+      </c>
+      <c r="S184">
+        <v>3.25</v>
+      </c>
+      <c r="T184">
+        <v>1.49</v>
+      </c>
+      <c r="U184">
+        <v>2.51</v>
+      </c>
+      <c r="V184">
+        <v>3.28</v>
+      </c>
+      <c r="W184">
+        <v>1.31</v>
+      </c>
+      <c r="X184">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y184">
+        <v>1.05</v>
+      </c>
+      <c r="Z184">
+        <v>2.5</v>
+      </c>
+      <c r="AA184">
+        <v>3.1</v>
+      </c>
+      <c r="AB184">
+        <v>2.5</v>
+      </c>
+      <c r="AC184">
+        <v>1.04</v>
+      </c>
+      <c r="AD184">
+        <v>7.1</v>
+      </c>
+      <c r="AE184">
+        <v>1.37</v>
+      </c>
+      <c r="AF184">
+        <v>2.67</v>
+      </c>
+      <c r="AG184">
+        <v>2.1</v>
+      </c>
+      <c r="AH184">
+        <v>1.6</v>
+      </c>
+      <c r="AI184">
+        <v>1.92</v>
+      </c>
+      <c r="AJ184">
+        <v>1.79</v>
+      </c>
+      <c r="AK184">
+        <v>1.47</v>
+      </c>
+      <c r="AL184">
+        <v>1.33</v>
+      </c>
+      <c r="AM184">
+        <v>1.43</v>
+      </c>
+      <c r="AN184">
+        <v>1</v>
+      </c>
+      <c r="AO184">
+        <v>1.6</v>
+      </c>
+      <c r="AP184">
+        <v>1.18</v>
+      </c>
+      <c r="AQ184">
+        <v>1.45</v>
+      </c>
+      <c r="AR184">
+        <v>1.54</v>
+      </c>
+      <c r="AS184">
+        <v>1.36</v>
+      </c>
+      <c r="AT184">
+        <v>2.9</v>
+      </c>
+      <c r="AU184">
+        <v>2</v>
+      </c>
+      <c r="AV184">
+        <v>2</v>
+      </c>
+      <c r="AW184">
+        <v>11</v>
+      </c>
+      <c r="AX184">
+        <v>12</v>
+      </c>
+      <c r="AY184">
+        <v>13</v>
+      </c>
+      <c r="AZ184">
+        <v>14</v>
+      </c>
+      <c r="BA184">
+        <v>-1</v>
+      </c>
+      <c r="BB184">
+        <v>-1</v>
+      </c>
+      <c r="BC184">
+        <v>-1</v>
+      </c>
+      <c r="BD184">
+        <v>1.75</v>
+      </c>
+      <c r="BE184">
+        <v>8</v>
+      </c>
+      <c r="BF184">
+        <v>2.52</v>
+      </c>
+      <c r="BG184">
+        <v>1.2</v>
+      </c>
+      <c r="BH184">
+        <v>4.2</v>
+      </c>
+      <c r="BI184">
+        <v>1.38</v>
+      </c>
+      <c r="BJ184">
+        <v>2.88</v>
+      </c>
+      <c r="BK184">
+        <v>1.63</v>
+      </c>
+      <c r="BL184">
+        <v>2.18</v>
+      </c>
+      <c r="BM184">
+        <v>2.02</v>
+      </c>
+      <c r="BN184">
+        <v>1.74</v>
+      </c>
+      <c r="BO184">
+        <v>2.57</v>
+      </c>
+      <c r="BP184">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7502784</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45696.52083333334</v>
+      </c>
+      <c r="F185">
+        <v>21</v>
+      </c>
+      <c r="G185" t="s">
+        <v>70</v>
+      </c>
+      <c r="H185" t="s">
+        <v>81</v>
+      </c>
+      <c r="I185">
+        <v>1</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>1</v>
+      </c>
+      <c r="L185">
+        <v>2</v>
+      </c>
+      <c r="M185">
+        <v>0</v>
+      </c>
+      <c r="N185">
+        <v>2</v>
+      </c>
+      <c r="O185" t="s">
+        <v>206</v>
+      </c>
+      <c r="P185" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q185">
+        <v>2.53</v>
+      </c>
+      <c r="R185">
+        <v>2.05</v>
+      </c>
+      <c r="S185">
+        <v>4.5</v>
+      </c>
+      <c r="T185">
+        <v>1.44</v>
+      </c>
+      <c r="U185">
+        <v>2.67</v>
+      </c>
+      <c r="V185">
+        <v>3.1</v>
+      </c>
+      <c r="W185">
+        <v>1.34</v>
+      </c>
+      <c r="X185">
+        <v>8.4</v>
+      </c>
+      <c r="Y185">
+        <v>1.05</v>
+      </c>
+      <c r="Z185">
+        <v>1.75</v>
+      </c>
+      <c r="AA185">
+        <v>3.3</v>
+      </c>
+      <c r="AB185">
+        <v>4</v>
+      </c>
+      <c r="AC185">
+        <v>1.01</v>
+      </c>
+      <c r="AD185">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE185">
+        <v>1.31</v>
+      </c>
+      <c r="AF185">
+        <v>2.93</v>
+      </c>
+      <c r="AG185">
+        <v>2.05</v>
+      </c>
+      <c r="AH185">
+        <v>1.61</v>
+      </c>
+      <c r="AI185">
+        <v>1.89</v>
+      </c>
+      <c r="AJ185">
+        <v>1.81</v>
+      </c>
+      <c r="AK185">
+        <v>1.24</v>
+      </c>
+      <c r="AL185">
+        <v>1.28</v>
+      </c>
+      <c r="AM185">
+        <v>1.83</v>
+      </c>
+      <c r="AN185">
+        <v>0.78</v>
+      </c>
+      <c r="AO185">
+        <v>1.2</v>
+      </c>
+      <c r="AP185">
+        <v>1</v>
+      </c>
+      <c r="AQ185">
+        <v>1.09</v>
+      </c>
+      <c r="AR185">
+        <v>1.68</v>
+      </c>
+      <c r="AS185">
+        <v>1.16</v>
+      </c>
+      <c r="AT185">
+        <v>2.84</v>
+      </c>
+      <c r="AU185">
+        <v>3</v>
+      </c>
+      <c r="AV185">
+        <v>2</v>
+      </c>
+      <c r="AW185">
+        <v>15</v>
+      </c>
+      <c r="AX185">
+        <v>13</v>
+      </c>
+      <c r="AY185">
+        <v>18</v>
+      </c>
+      <c r="AZ185">
+        <v>15</v>
+      </c>
+      <c r="BA185">
+        <v>-1</v>
+      </c>
+      <c r="BB185">
+        <v>-1</v>
+      </c>
+      <c r="BC185">
+        <v>-1</v>
+      </c>
+      <c r="BD185">
+        <v>1.34</v>
+      </c>
+      <c r="BE185">
+        <v>9.5</v>
+      </c>
+      <c r="BF185">
+        <v>4.07</v>
+      </c>
+      <c r="BG185">
+        <v>1.23</v>
+      </c>
+      <c r="BH185">
+        <v>3.92</v>
+      </c>
+      <c r="BI185">
+        <v>1.42</v>
+      </c>
+      <c r="BJ185">
+        <v>2.73</v>
+      </c>
+      <c r="BK185">
+        <v>1.69</v>
+      </c>
+      <c r="BL185">
+        <v>2.09</v>
+      </c>
+      <c r="BM185">
+        <v>2.11</v>
+      </c>
+      <c r="BN185">
+        <v>1.68</v>
+      </c>
+      <c r="BO185">
+        <v>2.72</v>
+      </c>
+      <c r="BP185">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7502789</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45696.625</v>
+      </c>
+      <c r="F186">
+        <v>21</v>
+      </c>
+      <c r="G186" t="s">
+        <v>74</v>
+      </c>
+      <c r="H186" t="s">
+        <v>82</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186">
+        <v>2</v>
+      </c>
+      <c r="K186">
+        <v>3</v>
+      </c>
+      <c r="L186">
+        <v>1</v>
+      </c>
+      <c r="M186">
+        <v>2</v>
+      </c>
+      <c r="N186">
+        <v>3</v>
+      </c>
+      <c r="O186" t="s">
+        <v>141</v>
+      </c>
+      <c r="P186" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q186">
+        <v>3.14</v>
+      </c>
+      <c r="R186">
+        <v>1.87</v>
+      </c>
+      <c r="S186">
+        <v>3.98</v>
+      </c>
+      <c r="T186">
+        <v>1.53</v>
+      </c>
+      <c r="U186">
+        <v>2.41</v>
+      </c>
+      <c r="V186">
+        <v>3.1</v>
+      </c>
+      <c r="W186">
+        <v>1.34</v>
+      </c>
+      <c r="X186">
+        <v>8.1</v>
+      </c>
+      <c r="Y186">
+        <v>1.06</v>
+      </c>
+      <c r="Z186">
+        <v>2.3</v>
+      </c>
+      <c r="AA186">
+        <v>3.1</v>
+      </c>
+      <c r="AB186">
+        <v>2.8</v>
+      </c>
+      <c r="AC186">
+        <v>1.05</v>
+      </c>
+      <c r="AD186">
+        <v>6.5</v>
+      </c>
+      <c r="AE186">
+        <v>1.33</v>
+      </c>
+      <c r="AF186">
+        <v>2.84</v>
+      </c>
+      <c r="AG186">
+        <v>2</v>
+      </c>
+      <c r="AH186">
+        <v>1.67</v>
+      </c>
+      <c r="AI186">
+        <v>1.81</v>
+      </c>
+      <c r="AJ186">
+        <v>1.89</v>
+      </c>
+      <c r="AK186">
+        <v>1.33</v>
+      </c>
+      <c r="AL186">
+        <v>1.39</v>
+      </c>
+      <c r="AM186">
+        <v>1.52</v>
+      </c>
+      <c r="AN186">
+        <v>1.7</v>
+      </c>
+      <c r="AO186">
+        <v>1.22</v>
+      </c>
+      <c r="AP186">
+        <v>1.55</v>
+      </c>
+      <c r="AQ186">
+        <v>1.4</v>
+      </c>
+      <c r="AR186">
+        <v>1.18</v>
+      </c>
+      <c r="AS186">
+        <v>1.3</v>
+      </c>
+      <c r="AT186">
+        <v>2.48</v>
+      </c>
+      <c r="AU186">
+        <v>5</v>
+      </c>
+      <c r="AV186">
+        <v>8</v>
+      </c>
+      <c r="AW186">
+        <v>10</v>
+      </c>
+      <c r="AX186">
+        <v>3</v>
+      </c>
+      <c r="AY186">
+        <v>15</v>
+      </c>
+      <c r="AZ186">
+        <v>11</v>
+      </c>
+      <c r="BA186">
+        <v>-1</v>
+      </c>
+      <c r="BB186">
+        <v>-1</v>
+      </c>
+      <c r="BC186">
+        <v>-1</v>
+      </c>
+      <c r="BD186">
+        <v>2.28</v>
+      </c>
+      <c r="BE186">
+        <v>8.5</v>
+      </c>
+      <c r="BF186">
+        <v>1.82</v>
+      </c>
+      <c r="BG186">
+        <v>0</v>
+      </c>
+      <c r="BH186">
+        <v>0</v>
+      </c>
+      <c r="BI186">
+        <v>0</v>
+      </c>
+      <c r="BJ186">
+        <v>0</v>
+      </c>
+      <c r="BK186">
+        <v>0</v>
+      </c>
+      <c r="BL186">
+        <v>0</v>
+      </c>
+      <c r="BM186">
+        <v>1.95</v>
+      </c>
+      <c r="BN186">
+        <v>1.85</v>
+      </c>
+      <c r="BO186">
+        <v>0</v>
+      </c>
+      <c r="BP186">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="302">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -637,6 +637,9 @@
     <t>['12', '67']</t>
   </si>
   <si>
+    <t>['10', '26']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -914,6 +917,9 @@
   </si>
   <si>
     <t>['3', '31']</t>
+  </si>
+  <si>
+    <t>['19', '67']</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP186"/>
+  <dimension ref="A1:BP189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1531,7 +1537,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1737,7 +1743,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1943,7 +1949,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2227,10 +2233,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2355,7 +2361,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2561,7 +2567,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2848,7 +2854,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ8">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2973,7 +2979,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3051,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ9">
         <v>1.1</v>
@@ -3385,7 +3391,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3797,7 +3803,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4003,7 +4009,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4209,7 +4215,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4415,7 +4421,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -5033,7 +5039,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5114,7 +5120,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ19">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5239,7 +5245,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5317,10 +5323,10 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ20">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR20">
         <v>1.01</v>
@@ -5857,7 +5863,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6141,10 +6147,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ24">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR24">
         <v>1.31</v>
@@ -6269,7 +6275,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6556,7 +6562,7 @@
         <v>1</v>
       </c>
       <c r="AQ26">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR26">
         <v>1.66</v>
@@ -6681,7 +6687,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7093,7 +7099,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7299,7 +7305,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7711,7 +7717,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8123,7 +8129,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8329,7 +8335,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8535,7 +8541,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8947,7 +8953,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9153,7 +9159,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9234,7 +9240,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ39">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR39">
         <v>1.92</v>
@@ -9437,7 +9443,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ40">
         <v>1.45</v>
@@ -9565,7 +9571,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9646,7 +9652,7 @@
         <v>1</v>
       </c>
       <c r="AQ41">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR41">
         <v>1.49</v>
@@ -9771,7 +9777,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10058,7 +10064,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ43">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR43">
         <v>1.55</v>
@@ -10183,7 +10189,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10389,7 +10395,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10801,7 +10807,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11007,7 +11013,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11213,7 +11219,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11625,7 +11631,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12243,7 +12249,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12321,7 +12327,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ54">
         <v>1.36</v>
@@ -12655,7 +12661,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12861,7 +12867,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13148,7 +13154,7 @@
         <v>1</v>
       </c>
       <c r="AQ58">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR58">
         <v>1.6</v>
@@ -13273,7 +13279,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -14178,7 +14184,7 @@
         <v>1</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR63">
         <v>1.24</v>
@@ -14384,7 +14390,7 @@
         <v>2</v>
       </c>
       <c r="AQ64">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR64">
         <v>1.67</v>
@@ -14509,7 +14515,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14587,7 +14593,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ65">
         <v>1.2</v>
@@ -14921,7 +14927,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15127,7 +15133,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15205,7 +15211,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ68">
         <v>1.36</v>
@@ -16157,7 +16163,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16363,7 +16369,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16444,7 +16450,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ74">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR74">
         <v>1.25</v>
@@ -16569,7 +16575,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16775,7 +16781,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17062,7 +17068,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ77">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR77">
         <v>1.55</v>
@@ -17187,7 +17193,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17474,7 +17480,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ79">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR79">
         <v>1.3</v>
@@ -18217,7 +18223,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18707,7 +18713,7 @@
         <v>2</v>
       </c>
       <c r="AP85">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ85">
         <v>1.3</v>
@@ -18835,7 +18841,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19119,7 +19125,7 @@
         <v>1.25</v>
       </c>
       <c r="AP87">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ87">
         <v>0.6</v>
@@ -19247,7 +19253,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19659,7 +19665,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19740,7 +19746,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ90">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR90">
         <v>1.65</v>
@@ -19865,7 +19871,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20071,7 +20077,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20277,7 +20283,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20483,7 +20489,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20689,7 +20695,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -20770,7 +20776,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ95">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR95">
         <v>1.56</v>
@@ -21101,7 +21107,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21182,7 +21188,7 @@
         <v>2</v>
       </c>
       <c r="AQ97">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR97">
         <v>1.52</v>
@@ -21307,7 +21313,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21513,7 +21519,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22209,7 +22215,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ102">
         <v>0.6</v>
@@ -22337,7 +22343,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22621,7 +22627,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ104">
         <v>1</v>
@@ -22749,7 +22755,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22830,7 +22836,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ105">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR105">
         <v>1.39</v>
@@ -22955,7 +22961,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23161,7 +23167,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23367,7 +23373,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23573,7 +23579,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24397,7 +24403,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24603,7 +24609,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25015,7 +25021,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25096,7 +25102,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ116">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR116">
         <v>1.1</v>
@@ -25221,7 +25227,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25427,7 +25433,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25508,7 +25514,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ118">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR118">
         <v>1.48</v>
@@ -25917,7 +25923,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ120">
         <v>1.4</v>
@@ -26126,7 +26132,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ121">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR121">
         <v>1.6</v>
@@ -26251,7 +26257,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26663,7 +26669,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27075,7 +27081,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27487,7 +27493,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27565,7 +27571,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ128">
         <v>0.9</v>
@@ -27899,7 +27905,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -27980,7 +27986,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ130">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR130">
         <v>1.55</v>
@@ -28311,7 +28317,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28517,7 +28523,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28598,7 +28604,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ133">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR133">
         <v>1.63</v>
@@ -28723,7 +28729,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29341,7 +29347,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29753,7 +29759,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30040,7 +30046,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ140">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR140">
         <v>1.48</v>
@@ -30165,7 +30171,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30577,7 +30583,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30783,7 +30789,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31195,7 +31201,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31401,7 +31407,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31607,7 +31613,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -31688,7 +31694,7 @@
         <v>2</v>
       </c>
       <c r="AQ148">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR148">
         <v>1.62</v>
@@ -31891,7 +31897,7 @@
         <v>1.13</v>
       </c>
       <c r="AP149">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ149">
         <v>1.1</v>
@@ -32225,7 +32231,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32431,7 +32437,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32715,10 +32721,10 @@
         <v>1.63</v>
       </c>
       <c r="AP153">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ153">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR153">
         <v>1.48</v>
@@ -32843,7 +32849,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33542,7 +33548,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ157">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR157">
         <v>1.59</v>
@@ -33667,7 +33673,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34285,7 +34291,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34697,7 +34703,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34903,7 +34909,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -34981,7 +34987,7 @@
         <v>0.88</v>
       </c>
       <c r="AP164">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ164">
         <v>1</v>
@@ -35109,7 +35115,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35190,7 +35196,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ165">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR165">
         <v>1.57</v>
@@ -35396,7 +35402,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ166">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR166">
         <v>1.36</v>
@@ -35521,7 +35527,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -36217,7 +36223,7 @@
         <v>1.33</v>
       </c>
       <c r="AP170">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ170">
         <v>1.09</v>
@@ -36345,7 +36351,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36551,7 +36557,7 @@
         <v>199</v>
       </c>
       <c r="P172" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q172">
         <v>3.1</v>
@@ -36963,7 +36969,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37581,7 +37587,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -38199,7 +38205,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38611,7 +38617,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38817,7 +38823,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39134,13 +39140,13 @@
         <v>14</v>
       </c>
       <c r="BA184">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB184">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC184">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BD184">
         <v>1.75</v>
@@ -39340,13 +39346,13 @@
         <v>15</v>
       </c>
       <c r="BA185">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BB185">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC185">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD185">
         <v>1.34</v>
@@ -39435,7 +39441,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39546,13 +39552,13 @@
         <v>11</v>
       </c>
       <c r="BA186">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB186">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC186">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BD186">
         <v>2.28</v>
@@ -39592,6 +39598,624 @@
       </c>
       <c r="BP186">
         <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7502791</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45697.33333333334</v>
+      </c>
+      <c r="F187">
+        <v>21</v>
+      </c>
+      <c r="G187" t="s">
+        <v>71</v>
+      </c>
+      <c r="H187" t="s">
+        <v>85</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <v>0</v>
+      </c>
+      <c r="N187">
+        <v>0</v>
+      </c>
+      <c r="O187" t="s">
+        <v>89</v>
+      </c>
+      <c r="P187" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q187">
+        <v>3.75</v>
+      </c>
+      <c r="R187">
+        <v>1.95</v>
+      </c>
+      <c r="S187">
+        <v>3.4</v>
+      </c>
+      <c r="T187">
+        <v>1.53</v>
+      </c>
+      <c r="U187">
+        <v>2.38</v>
+      </c>
+      <c r="V187">
+        <v>3.5</v>
+      </c>
+      <c r="W187">
+        <v>1.29</v>
+      </c>
+      <c r="X187">
+        <v>11</v>
+      </c>
+      <c r="Y187">
+        <v>1.05</v>
+      </c>
+      <c r="Z187">
+        <v>2.88</v>
+      </c>
+      <c r="AA187">
+        <v>3</v>
+      </c>
+      <c r="AB187">
+        <v>2.5</v>
+      </c>
+      <c r="AC187">
+        <v>1.09</v>
+      </c>
+      <c r="AD187">
+        <v>6.5</v>
+      </c>
+      <c r="AE187">
+        <v>1.43</v>
+      </c>
+      <c r="AF187">
+        <v>2.55</v>
+      </c>
+      <c r="AG187">
+        <v>2.25</v>
+      </c>
+      <c r="AH187">
+        <v>1.53</v>
+      </c>
+      <c r="AI187">
+        <v>2</v>
+      </c>
+      <c r="AJ187">
+        <v>1.73</v>
+      </c>
+      <c r="AK187">
+        <v>1.5</v>
+      </c>
+      <c r="AL187">
+        <v>1.35</v>
+      </c>
+      <c r="AM187">
+        <v>1.39</v>
+      </c>
+      <c r="AN187">
+        <v>1</v>
+      </c>
+      <c r="AO187">
+        <v>1.5</v>
+      </c>
+      <c r="AP187">
+        <v>1</v>
+      </c>
+      <c r="AQ187">
+        <v>1.45</v>
+      </c>
+      <c r="AR187">
+        <v>1.28</v>
+      </c>
+      <c r="AS187">
+        <v>1.45</v>
+      </c>
+      <c r="AT187">
+        <v>2.73</v>
+      </c>
+      <c r="AU187">
+        <v>2</v>
+      </c>
+      <c r="AV187">
+        <v>3</v>
+      </c>
+      <c r="AW187">
+        <v>8</v>
+      </c>
+      <c r="AX187">
+        <v>11</v>
+      </c>
+      <c r="AY187">
+        <v>10</v>
+      </c>
+      <c r="AZ187">
+        <v>14</v>
+      </c>
+      <c r="BA187">
+        <v>-1</v>
+      </c>
+      <c r="BB187">
+        <v>-1</v>
+      </c>
+      <c r="BC187">
+        <v>-1</v>
+      </c>
+      <c r="BD187">
+        <v>2.2</v>
+      </c>
+      <c r="BE187">
+        <v>8</v>
+      </c>
+      <c r="BF187">
+        <v>1.83</v>
+      </c>
+      <c r="BG187">
+        <v>1.31</v>
+      </c>
+      <c r="BH187">
+        <v>3.2</v>
+      </c>
+      <c r="BI187">
+        <v>1.56</v>
+      </c>
+      <c r="BJ187">
+        <v>2.33</v>
+      </c>
+      <c r="BK187">
+        <v>1.92</v>
+      </c>
+      <c r="BL187">
+        <v>1.82</v>
+      </c>
+      <c r="BM187">
+        <v>2.42</v>
+      </c>
+      <c r="BN187">
+        <v>1.5</v>
+      </c>
+      <c r="BO187">
+        <v>3.2</v>
+      </c>
+      <c r="BP187">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7502790</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45697.45833333334</v>
+      </c>
+      <c r="F188">
+        <v>21</v>
+      </c>
+      <c r="G188" t="s">
+        <v>73</v>
+      </c>
+      <c r="H188" t="s">
+        <v>79</v>
+      </c>
+      <c r="I188">
+        <v>2</v>
+      </c>
+      <c r="J188">
+        <v>1</v>
+      </c>
+      <c r="K188">
+        <v>3</v>
+      </c>
+      <c r="L188">
+        <v>2</v>
+      </c>
+      <c r="M188">
+        <v>2</v>
+      </c>
+      <c r="N188">
+        <v>4</v>
+      </c>
+      <c r="O188" t="s">
+        <v>207</v>
+      </c>
+      <c r="P188" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q188">
+        <v>3.25</v>
+      </c>
+      <c r="R188">
+        <v>2</v>
+      </c>
+      <c r="S188">
+        <v>3.6</v>
+      </c>
+      <c r="T188">
+        <v>1.5</v>
+      </c>
+      <c r="U188">
+        <v>2.5</v>
+      </c>
+      <c r="V188">
+        <v>3.4</v>
+      </c>
+      <c r="W188">
+        <v>1.3</v>
+      </c>
+      <c r="X188">
+        <v>10</v>
+      </c>
+      <c r="Y188">
+        <v>1.06</v>
+      </c>
+      <c r="Z188">
+        <v>2.45</v>
+      </c>
+      <c r="AA188">
+        <v>3</v>
+      </c>
+      <c r="AB188">
+        <v>2.9</v>
+      </c>
+      <c r="AC188">
+        <v>1.07</v>
+      </c>
+      <c r="AD188">
+        <v>7.5</v>
+      </c>
+      <c r="AE188">
+        <v>1.38</v>
+      </c>
+      <c r="AF188">
+        <v>2.8</v>
+      </c>
+      <c r="AG188">
+        <v>2.05</v>
+      </c>
+      <c r="AH188">
+        <v>1.61</v>
+      </c>
+      <c r="AI188">
+        <v>1.83</v>
+      </c>
+      <c r="AJ188">
+        <v>1.83</v>
+      </c>
+      <c r="AK188">
+        <v>1.41</v>
+      </c>
+      <c r="AL188">
+        <v>1.33</v>
+      </c>
+      <c r="AM188">
+        <v>1.51</v>
+      </c>
+      <c r="AN188">
+        <v>1.89</v>
+      </c>
+      <c r="AO188">
+        <v>1.5</v>
+      </c>
+      <c r="AP188">
+        <v>1.8</v>
+      </c>
+      <c r="AQ188">
+        <v>1.45</v>
+      </c>
+      <c r="AR188">
+        <v>1.43</v>
+      </c>
+      <c r="AS188">
+        <v>1.16</v>
+      </c>
+      <c r="AT188">
+        <v>2.59</v>
+      </c>
+      <c r="AU188">
+        <v>3</v>
+      </c>
+      <c r="AV188">
+        <v>5</v>
+      </c>
+      <c r="AW188">
+        <v>7</v>
+      </c>
+      <c r="AX188">
+        <v>5</v>
+      </c>
+      <c r="AY188">
+        <v>10</v>
+      </c>
+      <c r="AZ188">
+        <v>10</v>
+      </c>
+      <c r="BA188">
+        <v>-1</v>
+      </c>
+      <c r="BB188">
+        <v>-1</v>
+      </c>
+      <c r="BC188">
+        <v>-1</v>
+      </c>
+      <c r="BD188">
+        <v>2.05</v>
+      </c>
+      <c r="BE188">
+        <v>8</v>
+      </c>
+      <c r="BF188">
+        <v>1.95</v>
+      </c>
+      <c r="BG188">
+        <v>1.17</v>
+      </c>
+      <c r="BH188">
+        <v>4.2</v>
+      </c>
+      <c r="BI188">
+        <v>1.33</v>
+      </c>
+      <c r="BJ188">
+        <v>3.02</v>
+      </c>
+      <c r="BK188">
+        <v>1.59</v>
+      </c>
+      <c r="BL188">
+        <v>2.28</v>
+      </c>
+      <c r="BM188">
+        <v>1.94</v>
+      </c>
+      <c r="BN188">
+        <v>1.8</v>
+      </c>
+      <c r="BO188">
+        <v>2.42</v>
+      </c>
+      <c r="BP188">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7502788</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45697.52083333334</v>
+      </c>
+      <c r="F189">
+        <v>21</v>
+      </c>
+      <c r="G189" t="s">
+        <v>77</v>
+      </c>
+      <c r="H189" t="s">
+        <v>76</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>0</v>
+      </c>
+      <c r="M189">
+        <v>0</v>
+      </c>
+      <c r="N189">
+        <v>0</v>
+      </c>
+      <c r="O189" t="s">
+        <v>89</v>
+      </c>
+      <c r="P189" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q189">
+        <v>2.5</v>
+      </c>
+      <c r="R189">
+        <v>2.2</v>
+      </c>
+      <c r="S189">
+        <v>4.5</v>
+      </c>
+      <c r="T189">
+        <v>1.4</v>
+      </c>
+      <c r="U189">
+        <v>2.75</v>
+      </c>
+      <c r="V189">
+        <v>3</v>
+      </c>
+      <c r="W189">
+        <v>1.36</v>
+      </c>
+      <c r="X189">
+        <v>8</v>
+      </c>
+      <c r="Y189">
+        <v>1.08</v>
+      </c>
+      <c r="Z189">
+        <v>1.8</v>
+      </c>
+      <c r="AA189">
+        <v>3.5</v>
+      </c>
+      <c r="AB189">
+        <v>4</v>
+      </c>
+      <c r="AC189">
+        <v>1.05</v>
+      </c>
+      <c r="AD189">
+        <v>8.5</v>
+      </c>
+      <c r="AE189">
+        <v>1.3</v>
+      </c>
+      <c r="AF189">
+        <v>3.25</v>
+      </c>
+      <c r="AG189">
+        <v>1.85</v>
+      </c>
+      <c r="AH189">
+        <v>1.8</v>
+      </c>
+      <c r="AI189">
+        <v>1.83</v>
+      </c>
+      <c r="AJ189">
+        <v>1.83</v>
+      </c>
+      <c r="AK189">
+        <v>1.23</v>
+      </c>
+      <c r="AL189">
+        <v>1.28</v>
+      </c>
+      <c r="AM189">
+        <v>1.88</v>
+      </c>
+      <c r="AN189">
+        <v>1.33</v>
+      </c>
+      <c r="AO189">
+        <v>0.3</v>
+      </c>
+      <c r="AP189">
+        <v>1.3</v>
+      </c>
+      <c r="AQ189">
+        <v>0.36</v>
+      </c>
+      <c r="AR189">
+        <v>1.67</v>
+      </c>
+      <c r="AS189">
+        <v>1.56</v>
+      </c>
+      <c r="AT189">
+        <v>3.23</v>
+      </c>
+      <c r="AU189">
+        <v>6</v>
+      </c>
+      <c r="AV189">
+        <v>7</v>
+      </c>
+      <c r="AW189">
+        <v>11</v>
+      </c>
+      <c r="AX189">
+        <v>5</v>
+      </c>
+      <c r="AY189">
+        <v>17</v>
+      </c>
+      <c r="AZ189">
+        <v>12</v>
+      </c>
+      <c r="BA189">
+        <v>-1</v>
+      </c>
+      <c r="BB189">
+        <v>-1</v>
+      </c>
+      <c r="BC189">
+        <v>-1</v>
+      </c>
+      <c r="BD189">
+        <v>1.82</v>
+      </c>
+      <c r="BE189">
+        <v>8</v>
+      </c>
+      <c r="BF189">
+        <v>2.39</v>
+      </c>
+      <c r="BG189">
+        <v>1.17</v>
+      </c>
+      <c r="BH189">
+        <v>4.15</v>
+      </c>
+      <c r="BI189">
+        <v>1.34</v>
+      </c>
+      <c r="BJ189">
+        <v>3</v>
+      </c>
+      <c r="BK189">
+        <v>1.6</v>
+      </c>
+      <c r="BL189">
+        <v>2.26</v>
+      </c>
+      <c r="BM189">
+        <v>1.96</v>
+      </c>
+      <c r="BN189">
+        <v>1.79</v>
+      </c>
+      <c r="BO189">
+        <v>2.45</v>
+      </c>
+      <c r="BP189">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="304">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -640,6 +640,9 @@
     <t>['10', '26']</t>
   </si>
   <si>
+    <t>['59', '78']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -920,6 +923,9 @@
   </si>
   <si>
     <t>['19', '67']</t>
+  </si>
+  <si>
+    <t>['54', '63', '81', '90+2']</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP189"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1537,7 +1543,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1743,7 +1749,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1949,7 +1955,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2361,7 +2367,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2567,7 +2573,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2645,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -2979,7 +2985,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3060,7 +3066,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ9">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3391,7 +3397,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3803,7 +3809,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4009,7 +4015,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4215,7 +4221,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4421,7 +4427,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -5039,7 +5045,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5245,7 +5251,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5735,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ22">
         <v>0.9</v>
@@ -5863,7 +5869,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6275,7 +6281,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6687,7 +6693,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -6974,7 +6980,7 @@
         <v>2</v>
       </c>
       <c r="AQ28">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR28">
         <v>1.62</v>
@@ -7099,7 +7105,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7305,7 +7311,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7717,7 +7723,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8129,7 +8135,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8335,7 +8341,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8541,7 +8547,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8953,7 +8959,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9031,7 +9037,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ38">
         <v>1.09</v>
@@ -9159,7 +9165,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9571,7 +9577,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9777,7 +9783,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10189,7 +10195,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10395,7 +10401,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10476,7 +10482,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ45">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR45">
         <v>1.58</v>
@@ -10807,7 +10813,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11013,7 +11019,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11219,7 +11225,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11631,7 +11637,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12249,7 +12255,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12661,7 +12667,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12739,7 +12745,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ56">
         <v>1.45</v>
@@ -12867,7 +12873,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13279,7 +13285,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13772,7 +13778,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ61">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR61">
         <v>1.62</v>
@@ -14515,7 +14521,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14927,7 +14933,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15133,7 +15139,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -16038,7 +16044,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ72">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR72">
         <v>1.62</v>
@@ -16163,7 +16169,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16369,7 +16375,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16575,7 +16581,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16781,7 +16787,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17065,7 +17071,7 @@
         <v>1.5</v>
       </c>
       <c r="AP77">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ77">
         <v>1.45</v>
@@ -17193,7 +17199,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -18098,7 +18104,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ82">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR82">
         <v>1.36</v>
@@ -18223,7 +18229,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18841,7 +18847,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19253,7 +19259,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19665,7 +19671,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19871,7 +19877,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20077,7 +20083,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20283,7 +20289,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20489,7 +20495,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20695,7 +20701,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21107,7 +21113,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21313,7 +21319,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21391,7 +21397,7 @@
         <v>1.4</v>
       </c>
       <c r="AP98">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ98">
         <v>1.45</v>
@@ -21519,7 +21525,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22343,7 +22349,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22755,7 +22761,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22961,7 +22967,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23042,7 +23048,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ106">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR106">
         <v>1.65</v>
@@ -23167,7 +23173,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23373,7 +23379,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23579,7 +23585,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24275,7 +24281,7 @@
         <v>1.83</v>
       </c>
       <c r="AP112">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ112">
         <v>1.09</v>
@@ -24403,7 +24409,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24609,7 +24615,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25021,7 +25027,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25227,7 +25233,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25433,7 +25439,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -26257,7 +26263,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26669,7 +26675,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -26750,7 +26756,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ124">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR124">
         <v>1.69</v>
@@ -27081,7 +27087,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27493,7 +27499,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27905,7 +27911,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28317,7 +28323,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28523,7 +28529,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28729,7 +28735,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29013,7 +29019,7 @@
         <v>2.17</v>
       </c>
       <c r="AP135">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ135">
         <v>2</v>
@@ -29347,7 +29353,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29759,7 +29765,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30171,7 +30177,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30583,7 +30589,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30789,7 +30795,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31073,7 +31079,7 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ145">
         <v>0.6</v>
@@ -31201,7 +31207,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31407,7 +31413,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31613,7 +31619,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -31900,7 +31906,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ149">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR149">
         <v>1.55</v>
@@ -32231,7 +32237,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32437,7 +32443,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32849,7 +32855,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33673,7 +33679,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34291,7 +34297,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34703,7 +34709,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34909,7 +34915,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35115,7 +35121,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35527,7 +35533,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -35814,7 +35820,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ168">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR168">
         <v>1.2</v>
@@ -36351,7 +36357,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36557,7 +36563,7 @@
         <v>199</v>
       </c>
       <c r="P172" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q172">
         <v>3.1</v>
@@ -36635,7 +36641,7 @@
         <v>1.5</v>
       </c>
       <c r="AP172">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ172">
         <v>1.3</v>
@@ -36969,7 +36975,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37587,7 +37593,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -38205,7 +38211,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38617,7 +38623,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38823,7 +38829,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39441,7 +39447,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39758,13 +39764,13 @@
         <v>14</v>
       </c>
       <c r="BA187">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB187">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC187">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BD187">
         <v>2.2</v>
@@ -39853,7 +39859,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -39964,13 +39970,13 @@
         <v>10</v>
       </c>
       <c r="BA188">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BB188">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC188">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BD188">
         <v>2.05</v>
@@ -40170,13 +40176,13 @@
         <v>12</v>
       </c>
       <c r="BA189">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB189">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC189">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD189">
         <v>1.82</v>
@@ -40216,6 +40222,212 @@
       </c>
       <c r="BP189">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7502785</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45698.625</v>
+      </c>
+      <c r="F190">
+        <v>21</v>
+      </c>
+      <c r="G190" t="s">
+        <v>75</v>
+      </c>
+      <c r="H190" t="s">
+        <v>84</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>2</v>
+      </c>
+      <c r="M190">
+        <v>4</v>
+      </c>
+      <c r="N190">
+        <v>6</v>
+      </c>
+      <c r="O190" t="s">
+        <v>208</v>
+      </c>
+      <c r="P190" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q190">
+        <v>3.6</v>
+      </c>
+      <c r="R190">
+        <v>1.95</v>
+      </c>
+      <c r="S190">
+        <v>3.4</v>
+      </c>
+      <c r="T190">
+        <v>1.53</v>
+      </c>
+      <c r="U190">
+        <v>2.38</v>
+      </c>
+      <c r="V190">
+        <v>3.5</v>
+      </c>
+      <c r="W190">
+        <v>1.29</v>
+      </c>
+      <c r="X190">
+        <v>11</v>
+      </c>
+      <c r="Y190">
+        <v>1.05</v>
+      </c>
+      <c r="Z190">
+        <v>2.9</v>
+      </c>
+      <c r="AA190">
+        <v>3</v>
+      </c>
+      <c r="AB190">
+        <v>2.45</v>
+      </c>
+      <c r="AC190">
+        <v>1.04</v>
+      </c>
+      <c r="AD190">
+        <v>7.1</v>
+      </c>
+      <c r="AE190">
+        <v>1.43</v>
+      </c>
+      <c r="AF190">
+        <v>2.55</v>
+      </c>
+      <c r="AG190">
+        <v>2.3</v>
+      </c>
+      <c r="AH190">
+        <v>1.5</v>
+      </c>
+      <c r="AI190">
+        <v>2</v>
+      </c>
+      <c r="AJ190">
+        <v>1.73</v>
+      </c>
+      <c r="AK190">
+        <v>1.47</v>
+      </c>
+      <c r="AL190">
+        <v>1.34</v>
+      </c>
+      <c r="AM190">
+        <v>1.41</v>
+      </c>
+      <c r="AN190">
+        <v>1.9</v>
+      </c>
+      <c r="AO190">
+        <v>1.1</v>
+      </c>
+      <c r="AP190">
+        <v>1.73</v>
+      </c>
+      <c r="AQ190">
+        <v>1.27</v>
+      </c>
+      <c r="AR190">
+        <v>1.31</v>
+      </c>
+      <c r="AS190">
+        <v>1.38</v>
+      </c>
+      <c r="AT190">
+        <v>2.69</v>
+      </c>
+      <c r="AU190">
+        <v>6</v>
+      </c>
+      <c r="AV190">
+        <v>8</v>
+      </c>
+      <c r="AW190">
+        <v>6</v>
+      </c>
+      <c r="AX190">
+        <v>7</v>
+      </c>
+      <c r="AY190">
+        <v>12</v>
+      </c>
+      <c r="AZ190">
+        <v>15</v>
+      </c>
+      <c r="BA190">
+        <v>-1</v>
+      </c>
+      <c r="BB190">
+        <v>-1</v>
+      </c>
+      <c r="BC190">
+        <v>-1</v>
+      </c>
+      <c r="BD190">
+        <v>2.1</v>
+      </c>
+      <c r="BE190">
+        <v>8</v>
+      </c>
+      <c r="BF190">
+        <v>1.95</v>
+      </c>
+      <c r="BG190">
+        <v>1.18</v>
+      </c>
+      <c r="BH190">
+        <v>3.85</v>
+      </c>
+      <c r="BI190">
+        <v>1.38</v>
+      </c>
+      <c r="BJ190">
+        <v>2.71</v>
+      </c>
+      <c r="BK190">
+        <v>1.69</v>
+      </c>
+      <c r="BL190">
+        <v>2.04</v>
+      </c>
+      <c r="BM190">
+        <v>1.95</v>
+      </c>
+      <c r="BN190">
+        <v>1.85</v>
+      </c>
+      <c r="BO190">
+        <v>2.74</v>
+      </c>
+      <c r="BP190">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -40382,13 +40382,13 @@
         <v>15</v>
       </c>
       <c r="BA190">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB190">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC190">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD190">
         <v>2.1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="306">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -643,6 +643,9 @@
     <t>['59', '78']</t>
   </si>
   <si>
+    <t>['78', '79']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -926,6 +929,9 @@
   </si>
   <si>
     <t>['54', '63', '81', '90+2']</t>
+  </si>
+  <si>
+    <t>['19', '41']</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1543,7 +1549,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1749,7 +1755,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1955,7 +1961,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2367,7 +2373,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2573,7 +2579,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2654,7 +2660,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2985,7 +2991,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3397,7 +3403,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3478,7 +3484,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ11">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3684,7 +3690,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ12">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3809,7 +3815,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4015,7 +4021,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4093,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ14">
         <v>1.36</v>
@@ -4221,7 +4227,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4427,7 +4433,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4711,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ17">
         <v>0.6</v>
@@ -5045,7 +5051,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5123,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ19">
         <v>0.36</v>
@@ -5251,7 +5257,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5538,7 +5544,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ21">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR21">
         <v>1.84</v>
@@ -5869,7 +5875,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6281,7 +6287,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6693,7 +6699,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7105,7 +7111,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7311,7 +7317,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7595,10 +7601,10 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ31">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR31">
         <v>1.31</v>
@@ -7723,7 +7729,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8135,7 +8141,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8341,7 +8347,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8419,7 +8425,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ35">
         <v>2</v>
@@ -8547,7 +8553,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8625,10 +8631,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ36">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR36">
         <v>0.91</v>
@@ -8959,7 +8965,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9165,7 +9171,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9577,7 +9583,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9783,7 +9789,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10195,7 +10201,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10401,7 +10407,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10813,7 +10819,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10891,7 +10897,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ47">
         <v>1.3</v>
@@ -11019,7 +11025,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11097,7 +11103,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ48">
         <v>1.3</v>
@@ -11225,7 +11231,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11509,7 +11515,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ50">
         <v>1.09</v>
@@ -11637,7 +11643,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -11718,7 +11724,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ51">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR51">
         <v>1.12</v>
@@ -11924,7 +11930,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ52">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR52">
         <v>1.2</v>
@@ -12255,7 +12261,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12542,7 +12548,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ55">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR55">
         <v>1.78</v>
@@ -12667,7 +12673,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12873,7 +12879,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13285,7 +13291,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -14521,7 +14527,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14602,7 +14608,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ65">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR65">
         <v>1.18</v>
@@ -14805,7 +14811,7 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ66">
         <v>0.6</v>
@@ -14933,7 +14939,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15139,7 +15145,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15423,7 +15429,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ69">
         <v>1.3</v>
@@ -15629,10 +15635,10 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR70">
         <v>1.47</v>
@@ -15838,7 +15844,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ71">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR71">
         <v>0.8</v>
@@ -16041,7 +16047,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ72">
         <v>1.27</v>
@@ -16169,7 +16175,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16375,7 +16381,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16581,7 +16587,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16787,7 +16793,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17199,7 +17205,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17898,7 +17904,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -18229,7 +18235,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18513,7 +18519,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ84">
         <v>1.4</v>
@@ -18847,7 +18853,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -18928,7 +18934,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ86">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR86">
         <v>1.78</v>
@@ -19259,7 +19265,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19543,7 +19549,7 @@
         <v>0.33</v>
       </c>
       <c r="AP89">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ89">
         <v>0.9</v>
@@ -19671,7 +19677,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19877,7 +19883,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -19958,7 +19964,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ91">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR91">
         <v>1.19</v>
@@ -20083,7 +20089,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20289,7 +20295,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20495,7 +20501,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20701,7 +20707,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -20779,7 +20785,7 @@
         <v>0.4</v>
       </c>
       <c r="AP95">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ95">
         <v>0.36</v>
@@ -21113,7 +21119,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21319,7 +21325,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21525,7 +21531,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22349,7 +22355,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22636,7 +22642,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ104">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR104">
         <v>1.44</v>
@@ -22761,7 +22767,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22967,7 +22973,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23173,7 +23179,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23254,7 +23260,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ107">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR107">
         <v>1.21</v>
@@ -23379,7 +23385,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23457,7 +23463,7 @@
         <v>1.4</v>
       </c>
       <c r="AP108">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ108">
         <v>1.4</v>
@@ -23585,7 +23591,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24409,7 +24415,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24615,7 +24621,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -24696,7 +24702,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ114">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR114">
         <v>1.37</v>
@@ -24899,7 +24905,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ115">
         <v>1.09</v>
@@ -25027,7 +25033,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25233,7 +25239,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25439,7 +25445,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25517,7 +25523,7 @@
         <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ118">
         <v>0.36</v>
@@ -26263,7 +26269,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26675,7 +26681,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -26959,7 +26965,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ125">
         <v>1.09</v>
@@ -27087,7 +27093,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27374,7 +27380,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ127">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR127">
         <v>0.99</v>
@@ -27499,7 +27505,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27786,7 +27792,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ129">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR129">
         <v>1.3</v>
@@ -27911,7 +27917,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28323,7 +28329,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28401,7 +28407,7 @@
         <v>1.86</v>
       </c>
       <c r="AP132">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ132">
         <v>1.45</v>
@@ -28529,7 +28535,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28607,7 +28613,7 @@
         <v>1.29</v>
       </c>
       <c r="AP133">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ133">
         <v>1.45</v>
@@ -28735,7 +28741,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29228,7 +29234,7 @@
         <v>2</v>
       </c>
       <c r="AQ136">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR136">
         <v>1.47</v>
@@ -29353,7 +29359,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29640,7 +29646,7 @@
         <v>1</v>
       </c>
       <c r="AQ138">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR138">
         <v>1.22</v>
@@ -29765,7 +29771,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30177,7 +30183,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30255,7 +30261,7 @@
         <v>2.29</v>
       </c>
       <c r="AP141">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ141">
         <v>2</v>
@@ -30589,7 +30595,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30667,7 +30673,7 @@
         <v>1.63</v>
       </c>
       <c r="AP143">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ143">
         <v>1.45</v>
@@ -30795,7 +30801,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -30876,7 +30882,7 @@
         <v>0.55</v>
       </c>
       <c r="AQ144">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR144">
         <v>1.17</v>
@@ -31082,7 +31088,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ145">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR145">
         <v>1.33</v>
@@ -31207,7 +31213,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31413,7 +31419,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31491,7 +31497,7 @@
         <v>1.5</v>
       </c>
       <c r="AP147">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ147">
         <v>1.09</v>
@@ -31619,7 +31625,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32237,7 +32243,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32443,7 +32449,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32855,7 +32861,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33345,7 +33351,7 @@
         <v>1.33</v>
       </c>
       <c r="AP156">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ156">
         <v>1.09</v>
@@ -33679,7 +33685,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -33760,7 +33766,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ158">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR158">
         <v>1.37</v>
@@ -34297,7 +34303,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34375,10 +34381,10 @@
         <v>0.75</v>
       </c>
       <c r="AP161">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ161">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR161">
         <v>1.7</v>
@@ -34581,7 +34587,7 @@
         <v>1.44</v>
       </c>
       <c r="AP162">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ162">
         <v>1.36</v>
@@ -34709,7 +34715,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34915,7 +34921,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -34996,7 +35002,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ164">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR164">
         <v>1.48</v>
@@ -35121,7 +35127,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35533,7 +35539,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -36357,7 +36363,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36563,7 +36569,7 @@
         <v>199</v>
       </c>
       <c r="P172" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q172">
         <v>3.1</v>
@@ -36847,7 +36853,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP173">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ173">
         <v>0.6</v>
@@ -36975,7 +36981,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37056,7 +37062,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ174">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR174">
         <v>1.73</v>
@@ -37259,7 +37265,7 @@
         <v>2.22</v>
       </c>
       <c r="AP175">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ175">
         <v>2</v>
@@ -37593,7 +37599,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -37880,7 +37886,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ178">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR178">
         <v>1.35</v>
@@ -38211,7 +38217,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38289,7 +38295,7 @@
         <v>1.4</v>
       </c>
       <c r="AP180">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ180">
         <v>1.36</v>
@@ -38623,7 +38629,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38704,7 +38710,7 @@
         <v>2</v>
       </c>
       <c r="AQ182">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR182">
         <v>1.54</v>
@@ -38829,7 +38835,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39447,7 +39453,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39859,7 +39865,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40271,7 +40277,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40427,6 +40433,624 @@
         <v>2.74</v>
       </c>
       <c r="BP190">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7502794</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45703.33333333334</v>
+      </c>
+      <c r="F191">
+        <v>22</v>
+      </c>
+      <c r="G191" t="s">
+        <v>85</v>
+      </c>
+      <c r="H191" t="s">
+        <v>78</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>2</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
+      </c>
+      <c r="N191">
+        <v>2</v>
+      </c>
+      <c r="O191" t="s">
+        <v>209</v>
+      </c>
+      <c r="P191" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q191">
+        <v>2.95</v>
+      </c>
+      <c r="R191">
+        <v>2.02</v>
+      </c>
+      <c r="S191">
+        <v>4</v>
+      </c>
+      <c r="T191">
+        <v>1.51</v>
+      </c>
+      <c r="U191">
+        <v>2.4</v>
+      </c>
+      <c r="V191">
+        <v>3.2</v>
+      </c>
+      <c r="W191">
+        <v>1.31</v>
+      </c>
+      <c r="X191">
+        <v>8.5</v>
+      </c>
+      <c r="Y191">
+        <v>1.02</v>
+      </c>
+      <c r="Z191">
+        <v>2.15</v>
+      </c>
+      <c r="AA191">
+        <v>3.2</v>
+      </c>
+      <c r="AB191">
+        <v>3.25</v>
+      </c>
+      <c r="AC191">
+        <v>1.03</v>
+      </c>
+      <c r="AD191">
+        <v>7.6</v>
+      </c>
+      <c r="AE191">
+        <v>1.41</v>
+      </c>
+      <c r="AF191">
+        <v>2.65</v>
+      </c>
+      <c r="AG191">
+        <v>2.05</v>
+      </c>
+      <c r="AH191">
+        <v>1.61</v>
+      </c>
+      <c r="AI191">
+        <v>1.95</v>
+      </c>
+      <c r="AJ191">
+        <v>1.77</v>
+      </c>
+      <c r="AK191">
+        <v>1.33</v>
+      </c>
+      <c r="AL191">
+        <v>1.31</v>
+      </c>
+      <c r="AM191">
+        <v>1.61</v>
+      </c>
+      <c r="AN191">
+        <v>1.6</v>
+      </c>
+      <c r="AO191">
+        <v>1.2</v>
+      </c>
+      <c r="AP191">
+        <v>1.73</v>
+      </c>
+      <c r="AQ191">
+        <v>1.09</v>
+      </c>
+      <c r="AR191">
+        <v>1.47</v>
+      </c>
+      <c r="AS191">
+        <v>1.54</v>
+      </c>
+      <c r="AT191">
+        <v>3.01</v>
+      </c>
+      <c r="AU191">
+        <v>6</v>
+      </c>
+      <c r="AV191">
+        <v>5</v>
+      </c>
+      <c r="AW191">
+        <v>13</v>
+      </c>
+      <c r="AX191">
+        <v>6</v>
+      </c>
+      <c r="AY191">
+        <v>19</v>
+      </c>
+      <c r="AZ191">
+        <v>11</v>
+      </c>
+      <c r="BA191">
+        <v>9</v>
+      </c>
+      <c r="BB191">
+        <v>2</v>
+      </c>
+      <c r="BC191">
+        <v>11</v>
+      </c>
+      <c r="BD191">
+        <v>1.95</v>
+      </c>
+      <c r="BE191">
+        <v>8</v>
+      </c>
+      <c r="BF191">
+        <v>2.1</v>
+      </c>
+      <c r="BG191">
+        <v>1.19</v>
+      </c>
+      <c r="BH191">
+        <v>3.98</v>
+      </c>
+      <c r="BI191">
+        <v>1.38</v>
+      </c>
+      <c r="BJ191">
+        <v>2.82</v>
+      </c>
+      <c r="BK191">
+        <v>1.63</v>
+      </c>
+      <c r="BL191">
+        <v>2.18</v>
+      </c>
+      <c r="BM191">
+        <v>2.02</v>
+      </c>
+      <c r="BN191">
+        <v>1.74</v>
+      </c>
+      <c r="BO191">
+        <v>2.53</v>
+      </c>
+      <c r="BP191">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7502800</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45703.45833333334</v>
+      </c>
+      <c r="F192">
+        <v>22</v>
+      </c>
+      <c r="G192" t="s">
+        <v>82</v>
+      </c>
+      <c r="H192" t="s">
+        <v>83</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>2</v>
+      </c>
+      <c r="K192">
+        <v>2</v>
+      </c>
+      <c r="L192">
+        <v>1</v>
+      </c>
+      <c r="M192">
+        <v>2</v>
+      </c>
+      <c r="N192">
+        <v>3</v>
+      </c>
+      <c r="O192" t="s">
+        <v>123</v>
+      </c>
+      <c r="P192" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q192">
+        <v>2.95</v>
+      </c>
+      <c r="R192">
+        <v>2.04</v>
+      </c>
+      <c r="S192">
+        <v>4</v>
+      </c>
+      <c r="T192">
+        <v>1.49</v>
+      </c>
+      <c r="U192">
+        <v>2.45</v>
+      </c>
+      <c r="V192">
+        <v>3.15</v>
+      </c>
+      <c r="W192">
+        <v>1.32</v>
+      </c>
+      <c r="X192">
+        <v>9.4</v>
+      </c>
+      <c r="Y192">
+        <v>1.01</v>
+      </c>
+      <c r="Z192">
+        <v>2.1</v>
+      </c>
+      <c r="AA192">
+        <v>3.1</v>
+      </c>
+      <c r="AB192">
+        <v>3.4</v>
+      </c>
+      <c r="AC192">
+        <v>1.01</v>
+      </c>
+      <c r="AD192">
+        <v>9</v>
+      </c>
+      <c r="AE192">
+        <v>1.39</v>
+      </c>
+      <c r="AF192">
+        <v>2.7</v>
+      </c>
+      <c r="AG192">
+        <v>2.1</v>
+      </c>
+      <c r="AH192">
+        <v>1.6</v>
+      </c>
+      <c r="AI192">
+        <v>1.91</v>
+      </c>
+      <c r="AJ192">
+        <v>1.81</v>
+      </c>
+      <c r="AK192">
+        <v>1.32</v>
+      </c>
+      <c r="AL192">
+        <v>1.32</v>
+      </c>
+      <c r="AM192">
+        <v>1.61</v>
+      </c>
+      <c r="AN192">
+        <v>1.09</v>
+      </c>
+      <c r="AO192">
+        <v>1</v>
+      </c>
+      <c r="AP192">
+        <v>1</v>
+      </c>
+      <c r="AQ192">
+        <v>1.18</v>
+      </c>
+      <c r="AR192">
+        <v>1.73</v>
+      </c>
+      <c r="AS192">
+        <v>1.37</v>
+      </c>
+      <c r="AT192">
+        <v>3.1</v>
+      </c>
+      <c r="AU192">
+        <v>7</v>
+      </c>
+      <c r="AV192">
+        <v>4</v>
+      </c>
+      <c r="AW192">
+        <v>13</v>
+      </c>
+      <c r="AX192">
+        <v>9</v>
+      </c>
+      <c r="AY192">
+        <v>20</v>
+      </c>
+      <c r="AZ192">
+        <v>13</v>
+      </c>
+      <c r="BA192">
+        <v>-1</v>
+      </c>
+      <c r="BB192">
+        <v>-1</v>
+      </c>
+      <c r="BC192">
+        <v>-1</v>
+      </c>
+      <c r="BD192">
+        <v>1.69</v>
+      </c>
+      <c r="BE192">
+        <v>8.5</v>
+      </c>
+      <c r="BF192">
+        <v>2.62</v>
+      </c>
+      <c r="BG192">
+        <v>1.17</v>
+      </c>
+      <c r="BH192">
+        <v>4.25</v>
+      </c>
+      <c r="BI192">
+        <v>1.33</v>
+      </c>
+      <c r="BJ192">
+        <v>3.05</v>
+      </c>
+      <c r="BK192">
+        <v>1.58</v>
+      </c>
+      <c r="BL192">
+        <v>2.29</v>
+      </c>
+      <c r="BM192">
+        <v>2</v>
+      </c>
+      <c r="BN192">
+        <v>1.8</v>
+      </c>
+      <c r="BO192">
+        <v>2.4</v>
+      </c>
+      <c r="BP192">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7502799</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45703.52083333334</v>
+      </c>
+      <c r="F193">
+        <v>22</v>
+      </c>
+      <c r="G193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H193" t="s">
+        <v>71</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>1</v>
+      </c>
+      <c r="M193">
+        <v>0</v>
+      </c>
+      <c r="N193">
+        <v>1</v>
+      </c>
+      <c r="O193" t="s">
+        <v>123</v>
+      </c>
+      <c r="P193" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q193">
+        <v>2.45</v>
+      </c>
+      <c r="R193">
+        <v>2.09</v>
+      </c>
+      <c r="S193">
+        <v>5</v>
+      </c>
+      <c r="T193">
+        <v>1.48</v>
+      </c>
+      <c r="U193">
+        <v>2.5</v>
+      </c>
+      <c r="V193">
+        <v>3.1</v>
+      </c>
+      <c r="W193">
+        <v>1.33</v>
+      </c>
+      <c r="X193">
+        <v>8.9</v>
+      </c>
+      <c r="Y193">
+        <v>1.01</v>
+      </c>
+      <c r="Z193">
+        <v>1.8</v>
+      </c>
+      <c r="AA193">
+        <v>3.3</v>
+      </c>
+      <c r="AB193">
+        <v>4.4</v>
+      </c>
+      <c r="AC193">
+        <v>1.01</v>
+      </c>
+      <c r="AD193">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE193">
+        <v>1.39</v>
+      </c>
+      <c r="AF193">
+        <v>2.75</v>
+      </c>
+      <c r="AG193">
+        <v>2.05</v>
+      </c>
+      <c r="AH193">
+        <v>1.61</v>
+      </c>
+      <c r="AI193">
+        <v>2</v>
+      </c>
+      <c r="AJ193">
+        <v>1.73</v>
+      </c>
+      <c r="AK193">
+        <v>1.21</v>
+      </c>
+      <c r="AL193">
+        <v>1.28</v>
+      </c>
+      <c r="AM193">
+        <v>1.89</v>
+      </c>
+      <c r="AN193">
+        <v>2.1</v>
+      </c>
+      <c r="AO193">
+        <v>0.6</v>
+      </c>
+      <c r="AP193">
+        <v>2.18</v>
+      </c>
+      <c r="AQ193">
+        <v>0.55</v>
+      </c>
+      <c r="AR193">
+        <v>1.6</v>
+      </c>
+      <c r="AS193">
+        <v>1.22</v>
+      </c>
+      <c r="AT193">
+        <v>2.82</v>
+      </c>
+      <c r="AU193">
+        <v>4</v>
+      </c>
+      <c r="AV193">
+        <v>4</v>
+      </c>
+      <c r="AW193">
+        <v>11</v>
+      </c>
+      <c r="AX193">
+        <v>4</v>
+      </c>
+      <c r="AY193">
+        <v>15</v>
+      </c>
+      <c r="AZ193">
+        <v>8</v>
+      </c>
+      <c r="BA193">
+        <v>-1</v>
+      </c>
+      <c r="BB193">
+        <v>-1</v>
+      </c>
+      <c r="BC193">
+        <v>-1</v>
+      </c>
+      <c r="BD193">
+        <v>1.59</v>
+      </c>
+      <c r="BE193">
+        <v>8.5</v>
+      </c>
+      <c r="BF193">
+        <v>2.89</v>
+      </c>
+      <c r="BG193">
+        <v>1.26</v>
+      </c>
+      <c r="BH193">
+        <v>3.38</v>
+      </c>
+      <c r="BI193">
+        <v>1.48</v>
+      </c>
+      <c r="BJ193">
+        <v>2.45</v>
+      </c>
+      <c r="BK193">
+        <v>1.82</v>
+      </c>
+      <c r="BL193">
+        <v>1.98</v>
+      </c>
+      <c r="BM193">
+        <v>2.3</v>
+      </c>
+      <c r="BN193">
+        <v>1.57</v>
+      </c>
+      <c r="BO193">
+        <v>2.93</v>
+      </c>
+      <c r="BP193">
         <v>1.35</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="313">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -646,6 +646,18 @@
     <t>['78', '79']</t>
   </si>
   <si>
+    <t>['28', '39', '58']</t>
+  </si>
+  <si>
+    <t>['90+10']</t>
+  </si>
+  <si>
+    <t>['46', '52', '54']</t>
+  </si>
+  <si>
+    <t>['6', '20', '34', '52', '61']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -932,6 +944,15 @@
   </si>
   <si>
     <t>['19', '41']</t>
+  </si>
+  <si>
+    <t>['36', '38']</t>
+  </si>
+  <si>
+    <t>['81', '90+3']</t>
+  </si>
+  <si>
+    <t>['69', '90+8']</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP193"/>
+  <dimension ref="A1:BP198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1549,7 +1570,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1755,7 +1776,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1961,7 +1982,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2042,7 +2063,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ4">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2373,7 +2394,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2579,7 +2600,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2863,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ8">
         <v>1.45</v>
@@ -2991,7 +3012,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3403,7 +3424,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3481,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>1.09</v>
@@ -3687,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ12">
         <v>0.55</v>
@@ -3815,7 +3836,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3893,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ13">
         <v>1.45</v>
@@ -4021,7 +4042,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4102,7 +4123,7 @@
         <v>1</v>
       </c>
       <c r="AQ14">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4227,7 +4248,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4433,7 +4454,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4511,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4720,7 +4741,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ17">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4926,7 +4947,7 @@
         <v>2</v>
       </c>
       <c r="AQ18">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5051,7 +5072,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5257,7 +5278,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5875,7 +5896,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6287,7 +6308,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6699,7 +6720,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7111,7 +7132,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7189,7 +7210,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
         <v>1.09</v>
@@ -7317,7 +7338,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7395,10 +7416,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ30">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR30">
         <v>1.33</v>
@@ -7729,7 +7750,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7807,10 +7828,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ32">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR32">
         <v>2.27</v>
@@ -8013,10 +8034,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ33">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR33">
         <v>1.04</v>
@@ -8141,7 +8162,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8222,7 +8243,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ34">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR34">
         <v>1.57</v>
@@ -8347,7 +8368,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8428,7 +8449,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR35">
         <v>1.95</v>
@@ -8553,7 +8574,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8837,7 +8858,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ37">
         <v>1.45</v>
@@ -8965,7 +8986,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9171,7 +9192,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9583,7 +9604,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9789,7 +9810,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10201,7 +10222,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10407,7 +10428,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10819,7 +10840,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10900,7 +10921,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ47">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR47">
         <v>1.36</v>
@@ -11025,7 +11046,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11106,7 +11127,7 @@
         <v>1</v>
       </c>
       <c r="AQ48">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR48">
         <v>1.74</v>
@@ -11231,7 +11252,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11309,10 +11330,10 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ49">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR49">
         <v>1.23</v>
@@ -11643,7 +11664,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -11721,7 +11742,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ51">
         <v>1.09</v>
@@ -11927,7 +11948,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ52">
         <v>1.18</v>
@@ -12133,10 +12154,10 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ53">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR53">
         <v>1.6</v>
@@ -12261,7 +12282,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12342,7 +12363,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ54">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR54">
         <v>1.11</v>
@@ -12545,7 +12566,7 @@
         <v>2</v>
       </c>
       <c r="AP55">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ55">
         <v>0.55</v>
@@ -12673,7 +12694,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12879,7 +12900,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13291,7 +13312,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13369,7 +13390,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ59">
         <v>1.4</v>
@@ -14527,7 +14548,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14814,7 +14835,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ66">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR66">
         <v>1.24</v>
@@ -14939,7 +14960,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15017,10 +15038,10 @@
         <v>3</v>
       </c>
       <c r="AP67">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR67">
         <v>1.38</v>
@@ -15145,7 +15166,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15226,7 +15247,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ68">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR68">
         <v>1.55</v>
@@ -15432,7 +15453,7 @@
         <v>1</v>
       </c>
       <c r="AQ69">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR69">
         <v>1.69</v>
@@ -15841,7 +15862,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ71">
         <v>0.55</v>
@@ -16175,7 +16196,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16381,7 +16402,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16459,7 +16480,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ74">
         <v>1.45</v>
@@ -16587,7 +16608,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16793,7 +16814,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17205,7 +17226,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17286,7 +17307,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ78">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR78">
         <v>1.7</v>
@@ -17901,7 +17922,7 @@
         <v>1.25</v>
       </c>
       <c r="AP81">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ81">
         <v>1.18</v>
@@ -18107,7 +18128,7 @@
         <v>1.6</v>
       </c>
       <c r="AP82">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ82">
         <v>1.27</v>
@@ -18235,7 +18256,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18316,7 +18337,7 @@
         <v>1</v>
       </c>
       <c r="AQ83">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR83">
         <v>1.45</v>
@@ -18728,7 +18749,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ85">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18853,7 +18874,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19140,7 +19161,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ87">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR87">
         <v>1.38</v>
@@ -19265,7 +19286,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19343,10 +19364,10 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ88">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR88">
         <v>1.05</v>
@@ -19677,7 +19698,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19755,7 +19776,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ90">
         <v>1.45</v>
@@ -19883,7 +19904,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20089,7 +20110,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20167,7 +20188,7 @@
         <v>0.6</v>
       </c>
       <c r="AP92">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ92">
         <v>1.09</v>
@@ -20295,7 +20316,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20501,7 +20522,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20707,7 +20728,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -20994,7 +21015,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ96">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR96">
         <v>1.37</v>
@@ -21119,7 +21140,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21325,7 +21346,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21531,7 +21552,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -21609,10 +21630,10 @@
         <v>1.75</v>
       </c>
       <c r="AP99">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ99">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR99">
         <v>1.34</v>
@@ -21818,7 +21839,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ100">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR100">
         <v>1.7</v>
@@ -22021,7 +22042,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ101">
         <v>0.9</v>
@@ -22230,7 +22251,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ102">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR102">
         <v>1.5</v>
@@ -22355,7 +22376,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22436,7 +22457,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ103">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR103">
         <v>1.71</v>
@@ -22767,7 +22788,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22845,7 +22866,7 @@
         <v>1.67</v>
       </c>
       <c r="AP105">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ105">
         <v>1.45</v>
@@ -22973,7 +22994,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23051,7 +23072,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
         <v>1.27</v>
@@ -23179,7 +23200,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23385,7 +23406,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23591,7 +23612,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -23669,7 +23690,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ109">
         <v>0.9</v>
@@ -23878,7 +23899,7 @@
         <v>1</v>
       </c>
       <c r="AQ110">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR110">
         <v>1.51</v>
@@ -24084,7 +24105,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ111">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR111">
         <v>1.61</v>
@@ -24415,7 +24436,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24621,7 +24642,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25033,7 +25054,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25111,7 +25132,7 @@
         <v>1</v>
       </c>
       <c r="AP116">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ116">
         <v>1.45</v>
@@ -25239,7 +25260,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25320,7 +25341,7 @@
         <v>1</v>
       </c>
       <c r="AQ117">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR117">
         <v>1.26</v>
@@ -25445,7 +25466,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25729,7 +25750,7 @@
         <v>2</v>
       </c>
       <c r="AP119">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ119">
         <v>1.45</v>
@@ -26141,7 +26162,7 @@
         <v>1.86</v>
       </c>
       <c r="AP121">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ121">
         <v>1.45</v>
@@ -26269,7 +26290,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26350,7 +26371,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ122">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR122">
         <v>1.24</v>
@@ -26556,7 +26577,7 @@
         <v>1</v>
       </c>
       <c r="AQ123">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR123">
         <v>1.21</v>
@@ -26681,7 +26702,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27093,7 +27114,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27174,7 +27195,7 @@
         <v>1</v>
       </c>
       <c r="AQ126">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -27377,7 +27398,7 @@
         <v>0.83</v>
       </c>
       <c r="AP127">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ127">
         <v>1.18</v>
@@ -27505,7 +27526,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27917,7 +27938,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -27995,7 +28016,7 @@
         <v>0.43</v>
       </c>
       <c r="AP130">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ130">
         <v>0.36</v>
@@ -28201,7 +28222,7 @@
         <v>1.57</v>
       </c>
       <c r="AP131">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ131">
         <v>1.09</v>
@@ -28329,7 +28350,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28535,7 +28556,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28741,7 +28762,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -28819,7 +28840,7 @@
         <v>1.43</v>
       </c>
       <c r="AP134">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ134">
         <v>1.45</v>
@@ -29028,7 +29049,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ135">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR135">
         <v>1.3</v>
@@ -29359,7 +29380,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29440,7 +29461,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ137">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR137">
         <v>1.18</v>
@@ -29771,7 +29792,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30055,7 +30076,7 @@
         <v>1.5</v>
       </c>
       <c r="AP140">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ140">
         <v>1.45</v>
@@ -30183,7 +30204,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30264,7 +30285,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ141">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR141">
         <v>1.36</v>
@@ -30470,7 +30491,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ142">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR142">
         <v>1.66</v>
@@ -30595,7 +30616,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30801,7 +30822,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -30879,7 +30900,7 @@
         <v>1.29</v>
       </c>
       <c r="AP144">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ144">
         <v>1.09</v>
@@ -31213,7 +31234,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31291,10 +31312,10 @@
         <v>1.63</v>
       </c>
       <c r="AP146">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ146">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR146">
         <v>1.64</v>
@@ -31419,7 +31440,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31625,7 +31646,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32243,7 +32264,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32321,7 +32342,7 @@
         <v>1.13</v>
       </c>
       <c r="AP151">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ151">
         <v>1.09</v>
@@ -32449,7 +32470,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32530,7 +32551,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ152">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR152">
         <v>1.34</v>
@@ -32861,7 +32882,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -32939,7 +32960,7 @@
         <v>1.75</v>
       </c>
       <c r="AP154">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ154">
         <v>1.45</v>
@@ -33148,7 +33169,7 @@
         <v>2</v>
       </c>
       <c r="AQ155">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR155">
         <v>1.55</v>
@@ -33557,7 +33578,7 @@
         <v>0.33</v>
       </c>
       <c r="AP157">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ157">
         <v>0.36</v>
@@ -33685,7 +33706,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -33763,7 +33784,7 @@
         <v>1.5</v>
       </c>
       <c r="AP158">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ158">
         <v>1.09</v>
@@ -33972,7 +33993,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ159">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR159">
         <v>1.72</v>
@@ -34175,7 +34196,7 @@
         <v>1.78</v>
       </c>
       <c r="AP160">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ160">
         <v>1.45</v>
@@ -34303,7 +34324,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34590,7 +34611,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ162">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR162">
         <v>1.69</v>
@@ -34715,7 +34736,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34793,10 +34814,10 @@
         <v>2.38</v>
       </c>
       <c r="AP163">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ163">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR163">
         <v>1.12</v>
@@ -34921,7 +34942,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35127,7 +35148,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35539,7 +35560,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -36363,7 +36384,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36441,7 +36462,7 @@
         <v>1.67</v>
       </c>
       <c r="AP171">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ171">
         <v>1.45</v>
@@ -36569,7 +36590,7 @@
         <v>199</v>
       </c>
       <c r="P172" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q172">
         <v>3.1</v>
@@ -36650,7 +36671,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ172">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR172">
         <v>1.3</v>
@@ -36856,7 +36877,7 @@
         <v>1</v>
       </c>
       <c r="AQ173">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR173">
         <v>1.71</v>
@@ -36981,7 +37002,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37268,7 +37289,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ175">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AR175">
         <v>1.61</v>
@@ -37471,10 +37492,10 @@
         <v>1.44</v>
       </c>
       <c r="AP176">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ176">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR176">
         <v>1.68</v>
@@ -37599,7 +37620,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -37677,7 +37698,7 @@
         <v>1.2</v>
       </c>
       <c r="AP177">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ177">
         <v>1.09</v>
@@ -37883,7 +37904,7 @@
         <v>0.67</v>
       </c>
       <c r="AP178">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ178">
         <v>0.55</v>
@@ -38089,10 +38110,10 @@
         <v>1.33</v>
       </c>
       <c r="AP179">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ179">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR179">
         <v>1.25</v>
@@ -38217,7 +38238,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38298,7 +38319,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ180">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR180">
         <v>1.51</v>
@@ -38501,7 +38522,7 @@
         <v>1.6</v>
       </c>
       <c r="AP181">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ181">
         <v>1.45</v>
@@ -38629,7 +38650,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38835,7 +38856,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39453,7 +39474,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39865,7 +39886,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40277,7 +40298,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40689,7 +40710,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41052,6 +41073,1036 @@
       </c>
       <c r="BP193">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7502796</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45704.33333333334</v>
+      </c>
+      <c r="F194">
+        <v>22</v>
+      </c>
+      <c r="G194" t="s">
+        <v>80</v>
+      </c>
+      <c r="H194" t="s">
+        <v>86</v>
+      </c>
+      <c r="I194">
+        <v>2</v>
+      </c>
+      <c r="J194">
+        <v>2</v>
+      </c>
+      <c r="K194">
+        <v>4</v>
+      </c>
+      <c r="L194">
+        <v>3</v>
+      </c>
+      <c r="M194">
+        <v>2</v>
+      </c>
+      <c r="N194">
+        <v>5</v>
+      </c>
+      <c r="O194" t="s">
+        <v>210</v>
+      </c>
+      <c r="P194" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q194">
+        <v>4.2</v>
+      </c>
+      <c r="R194">
+        <v>2.24</v>
+      </c>
+      <c r="S194">
+        <v>2.49</v>
+      </c>
+      <c r="T194">
+        <v>1.37</v>
+      </c>
+      <c r="U194">
+        <v>2.85</v>
+      </c>
+      <c r="V194">
+        <v>2.6</v>
+      </c>
+      <c r="W194">
+        <v>1.44</v>
+      </c>
+      <c r="X194">
+        <v>6.3</v>
+      </c>
+      <c r="Y194">
+        <v>1.09</v>
+      </c>
+      <c r="Z194">
+        <v>3.5</v>
+      </c>
+      <c r="AA194">
+        <v>3.6</v>
+      </c>
+      <c r="AB194">
+        <v>1.91</v>
+      </c>
+      <c r="AC194">
+        <v>1</v>
+      </c>
+      <c r="AD194">
+        <v>9</v>
+      </c>
+      <c r="AE194">
+        <v>1.26</v>
+      </c>
+      <c r="AF194">
+        <v>3.45</v>
+      </c>
+      <c r="AG194">
+        <v>1.75</v>
+      </c>
+      <c r="AH194">
+        <v>1.85</v>
+      </c>
+      <c r="AI194">
+        <v>1.7</v>
+      </c>
+      <c r="AJ194">
+        <v>2.03</v>
+      </c>
+      <c r="AK194">
+        <v>1.79</v>
+      </c>
+      <c r="AL194">
+        <v>1.27</v>
+      </c>
+      <c r="AM194">
+        <v>1.27</v>
+      </c>
+      <c r="AN194">
+        <v>0.55</v>
+      </c>
+      <c r="AO194">
+        <v>1.3</v>
+      </c>
+      <c r="AP194">
+        <v>0.75</v>
+      </c>
+      <c r="AQ194">
+        <v>1.18</v>
+      </c>
+      <c r="AR194">
+        <v>1.3</v>
+      </c>
+      <c r="AS194">
+        <v>1.49</v>
+      </c>
+      <c r="AT194">
+        <v>2.79</v>
+      </c>
+      <c r="AU194">
+        <v>10</v>
+      </c>
+      <c r="AV194">
+        <v>4</v>
+      </c>
+      <c r="AW194">
+        <v>4</v>
+      </c>
+      <c r="AX194">
+        <v>8</v>
+      </c>
+      <c r="AY194">
+        <v>14</v>
+      </c>
+      <c r="AZ194">
+        <v>12</v>
+      </c>
+      <c r="BA194">
+        <v>2</v>
+      </c>
+      <c r="BB194">
+        <v>3</v>
+      </c>
+      <c r="BC194">
+        <v>5</v>
+      </c>
+      <c r="BD194">
+        <v>2.41</v>
+      </c>
+      <c r="BE194">
+        <v>8.5</v>
+      </c>
+      <c r="BF194">
+        <v>1.75</v>
+      </c>
+      <c r="BG194">
+        <v>1.12</v>
+      </c>
+      <c r="BH194">
+        <v>4.95</v>
+      </c>
+      <c r="BI194">
+        <v>1.24</v>
+      </c>
+      <c r="BJ194">
+        <v>3.45</v>
+      </c>
+      <c r="BK194">
+        <v>1.45</v>
+      </c>
+      <c r="BL194">
+        <v>2.55</v>
+      </c>
+      <c r="BM194">
+        <v>1.74</v>
+      </c>
+      <c r="BN194">
+        <v>2.02</v>
+      </c>
+      <c r="BO194">
+        <v>2.16</v>
+      </c>
+      <c r="BP194">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7502797</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45704.33333333334</v>
+      </c>
+      <c r="F195">
+        <v>22</v>
+      </c>
+      <c r="G195" t="s">
+        <v>84</v>
+      </c>
+      <c r="H195" t="s">
+        <v>72</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>0</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>0</v>
+      </c>
+      <c r="O195" t="s">
+        <v>89</v>
+      </c>
+      <c r="P195" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q195">
+        <v>2.4</v>
+      </c>
+      <c r="R195">
+        <v>2.05</v>
+      </c>
+      <c r="S195">
+        <v>5.5</v>
+      </c>
+      <c r="T195">
+        <v>1.5</v>
+      </c>
+      <c r="U195">
+        <v>2.5</v>
+      </c>
+      <c r="V195">
+        <v>3.4</v>
+      </c>
+      <c r="W195">
+        <v>1.3</v>
+      </c>
+      <c r="X195">
+        <v>10</v>
+      </c>
+      <c r="Y195">
+        <v>1.06</v>
+      </c>
+      <c r="Z195">
+        <v>1.67</v>
+      </c>
+      <c r="AA195">
+        <v>3.25</v>
+      </c>
+      <c r="AB195">
+        <v>5.5</v>
+      </c>
+      <c r="AC195">
+        <v>1.04</v>
+      </c>
+      <c r="AD195">
+        <v>7.1</v>
+      </c>
+      <c r="AE195">
+        <v>1.41</v>
+      </c>
+      <c r="AF195">
+        <v>2.65</v>
+      </c>
+      <c r="AG195">
+        <v>2.15</v>
+      </c>
+      <c r="AH195">
+        <v>1.57</v>
+      </c>
+      <c r="AI195">
+        <v>2.1</v>
+      </c>
+      <c r="AJ195">
+        <v>1.67</v>
+      </c>
+      <c r="AK195">
+        <v>1.21</v>
+      </c>
+      <c r="AL195">
+        <v>1.3</v>
+      </c>
+      <c r="AM195">
+        <v>1.84</v>
+      </c>
+      <c r="AN195">
+        <v>1.7</v>
+      </c>
+      <c r="AO195">
+        <v>0.6</v>
+      </c>
+      <c r="AP195">
+        <v>1.64</v>
+      </c>
+      <c r="AQ195">
+        <v>0.64</v>
+      </c>
+      <c r="AR195">
+        <v>1.64</v>
+      </c>
+      <c r="AS195">
+        <v>1.24</v>
+      </c>
+      <c r="AT195">
+        <v>2.88</v>
+      </c>
+      <c r="AU195">
+        <v>8</v>
+      </c>
+      <c r="AV195">
+        <v>4</v>
+      </c>
+      <c r="AW195">
+        <v>20</v>
+      </c>
+      <c r="AX195">
+        <v>7</v>
+      </c>
+      <c r="AY195">
+        <v>28</v>
+      </c>
+      <c r="AZ195">
+        <v>11</v>
+      </c>
+      <c r="BA195">
+        <v>-1</v>
+      </c>
+      <c r="BB195">
+        <v>-1</v>
+      </c>
+      <c r="BC195">
+        <v>-1</v>
+      </c>
+      <c r="BD195">
+        <v>1.45</v>
+      </c>
+      <c r="BE195">
+        <v>9</v>
+      </c>
+      <c r="BF195">
+        <v>3.32</v>
+      </c>
+      <c r="BG195">
+        <v>1.26</v>
+      </c>
+      <c r="BH195">
+        <v>3.38</v>
+      </c>
+      <c r="BI195">
+        <v>1.48</v>
+      </c>
+      <c r="BJ195">
+        <v>2.45</v>
+      </c>
+      <c r="BK195">
+        <v>1.8</v>
+      </c>
+      <c r="BL195">
+        <v>2</v>
+      </c>
+      <c r="BM195">
+        <v>2.3</v>
+      </c>
+      <c r="BN195">
+        <v>1.57</v>
+      </c>
+      <c r="BO195">
+        <v>2.93</v>
+      </c>
+      <c r="BP195">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7502795</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F196">
+        <v>22</v>
+      </c>
+      <c r="G196" t="s">
+        <v>81</v>
+      </c>
+      <c r="H196" t="s">
+        <v>75</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <v>1</v>
+      </c>
+      <c r="M196">
+        <v>2</v>
+      </c>
+      <c r="N196">
+        <v>3</v>
+      </c>
+      <c r="O196" t="s">
+        <v>211</v>
+      </c>
+      <c r="P196" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q196">
+        <v>3.2</v>
+      </c>
+      <c r="R196">
+        <v>2.05</v>
+      </c>
+      <c r="S196">
+        <v>3.6</v>
+      </c>
+      <c r="T196">
+        <v>1.44</v>
+      </c>
+      <c r="U196">
+        <v>2.63</v>
+      </c>
+      <c r="V196">
+        <v>3.4</v>
+      </c>
+      <c r="W196">
+        <v>1.3</v>
+      </c>
+      <c r="X196">
+        <v>10</v>
+      </c>
+      <c r="Y196">
+        <v>1.06</v>
+      </c>
+      <c r="Z196">
+        <v>2.5</v>
+      </c>
+      <c r="AA196">
+        <v>3.25</v>
+      </c>
+      <c r="AB196">
+        <v>2.62</v>
+      </c>
+      <c r="AC196">
+        <v>1.02</v>
+      </c>
+      <c r="AD196">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE196">
+        <v>1.37</v>
+      </c>
+      <c r="AF196">
+        <v>2.85</v>
+      </c>
+      <c r="AG196">
+        <v>2.05</v>
+      </c>
+      <c r="AH196">
+        <v>1.65</v>
+      </c>
+      <c r="AI196">
+        <v>1.83</v>
+      </c>
+      <c r="AJ196">
+        <v>1.83</v>
+      </c>
+      <c r="AK196">
+        <v>1.4</v>
+      </c>
+      <c r="AL196">
+        <v>1.31</v>
+      </c>
+      <c r="AM196">
+        <v>1.52</v>
+      </c>
+      <c r="AN196">
+        <v>1.4</v>
+      </c>
+      <c r="AO196">
+        <v>1.3</v>
+      </c>
+      <c r="AP196">
+        <v>1.27</v>
+      </c>
+      <c r="AQ196">
+        <v>1.45</v>
+      </c>
+      <c r="AR196">
+        <v>1.34</v>
+      </c>
+      <c r="AS196">
+        <v>1.37</v>
+      </c>
+      <c r="AT196">
+        <v>2.71</v>
+      </c>
+      <c r="AU196">
+        <v>7</v>
+      </c>
+      <c r="AV196">
+        <v>5</v>
+      </c>
+      <c r="AW196">
+        <v>10</v>
+      </c>
+      <c r="AX196">
+        <v>10</v>
+      </c>
+      <c r="AY196">
+        <v>17</v>
+      </c>
+      <c r="AZ196">
+        <v>15</v>
+      </c>
+      <c r="BA196">
+        <v>-1</v>
+      </c>
+      <c r="BB196">
+        <v>-1</v>
+      </c>
+      <c r="BC196">
+        <v>-1</v>
+      </c>
+      <c r="BD196">
+        <v>2.1</v>
+      </c>
+      <c r="BE196">
+        <v>8.5</v>
+      </c>
+      <c r="BF196">
+        <v>1.91</v>
+      </c>
+      <c r="BG196">
+        <v>1.15</v>
+      </c>
+      <c r="BH196">
+        <v>4.45</v>
+      </c>
+      <c r="BI196">
+        <v>1.29</v>
+      </c>
+      <c r="BJ196">
+        <v>3.12</v>
+      </c>
+      <c r="BK196">
+        <v>1.53</v>
+      </c>
+      <c r="BL196">
+        <v>2.34</v>
+      </c>
+      <c r="BM196">
+        <v>1.9</v>
+      </c>
+      <c r="BN196">
+        <v>1.9</v>
+      </c>
+      <c r="BO196">
+        <v>2.35</v>
+      </c>
+      <c r="BP196">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7502801</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45704.52083333334</v>
+      </c>
+      <c r="F197">
+        <v>22</v>
+      </c>
+      <c r="G197" t="s">
+        <v>76</v>
+      </c>
+      <c r="H197" t="s">
+        <v>74</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>3</v>
+      </c>
+      <c r="M197">
+        <v>2</v>
+      </c>
+      <c r="N197">
+        <v>5</v>
+      </c>
+      <c r="O197" t="s">
+        <v>212</v>
+      </c>
+      <c r="P197" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q197">
+        <v>3</v>
+      </c>
+      <c r="R197">
+        <v>2.16</v>
+      </c>
+      <c r="S197">
+        <v>3.5</v>
+      </c>
+      <c r="T197">
+        <v>1.4</v>
+      </c>
+      <c r="U197">
+        <v>2.75</v>
+      </c>
+      <c r="V197">
+        <v>2.75</v>
+      </c>
+      <c r="W197">
+        <v>1.4</v>
+      </c>
+      <c r="X197">
+        <v>7.1</v>
+      </c>
+      <c r="Y197">
+        <v>1.04</v>
+      </c>
+      <c r="Z197">
+        <v>2.2</v>
+      </c>
+      <c r="AA197">
+        <v>3.25</v>
+      </c>
+      <c r="AB197">
+        <v>3.1</v>
+      </c>
+      <c r="AC197">
+        <v>1</v>
+      </c>
+      <c r="AD197">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE197">
+        <v>1.29</v>
+      </c>
+      <c r="AF197">
+        <v>3.25</v>
+      </c>
+      <c r="AG197">
+        <v>1.85</v>
+      </c>
+      <c r="AH197">
+        <v>1.8</v>
+      </c>
+      <c r="AI197">
+        <v>1.71</v>
+      </c>
+      <c r="AJ197">
+        <v>2.02</v>
+      </c>
+      <c r="AK197">
+        <v>1.39</v>
+      </c>
+      <c r="AL197">
+        <v>1.3</v>
+      </c>
+      <c r="AM197">
+        <v>1.54</v>
+      </c>
+      <c r="AN197">
+        <v>1.4</v>
+      </c>
+      <c r="AO197">
+        <v>2</v>
+      </c>
+      <c r="AP197">
+        <v>1.55</v>
+      </c>
+      <c r="AQ197">
+        <v>1.82</v>
+      </c>
+      <c r="AR197">
+        <v>1.07</v>
+      </c>
+      <c r="AS197">
+        <v>1.34</v>
+      </c>
+      <c r="AT197">
+        <v>2.41</v>
+      </c>
+      <c r="AU197">
+        <v>7</v>
+      </c>
+      <c r="AV197">
+        <v>5</v>
+      </c>
+      <c r="AW197">
+        <v>10</v>
+      </c>
+      <c r="AX197">
+        <v>6</v>
+      </c>
+      <c r="AY197">
+        <v>17</v>
+      </c>
+      <c r="AZ197">
+        <v>11</v>
+      </c>
+      <c r="BA197">
+        <v>-1</v>
+      </c>
+      <c r="BB197">
+        <v>-1</v>
+      </c>
+      <c r="BC197">
+        <v>-1</v>
+      </c>
+      <c r="BD197">
+        <v>1.51</v>
+      </c>
+      <c r="BE197">
+        <v>9</v>
+      </c>
+      <c r="BF197">
+        <v>3.06</v>
+      </c>
+      <c r="BG197">
+        <v>1.12</v>
+      </c>
+      <c r="BH197">
+        <v>4.95</v>
+      </c>
+      <c r="BI197">
+        <v>1.24</v>
+      </c>
+      <c r="BJ197">
+        <v>3.45</v>
+      </c>
+      <c r="BK197">
+        <v>1.45</v>
+      </c>
+      <c r="BL197">
+        <v>2.55</v>
+      </c>
+      <c r="BM197">
+        <v>1.74</v>
+      </c>
+      <c r="BN197">
+        <v>2.02</v>
+      </c>
+      <c r="BO197">
+        <v>2.16</v>
+      </c>
+      <c r="BP197">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7502793</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45704.58333333334</v>
+      </c>
+      <c r="F198">
+        <v>22</v>
+      </c>
+      <c r="G198" t="s">
+        <v>79</v>
+      </c>
+      <c r="H198" t="s">
+        <v>70</v>
+      </c>
+      <c r="I198">
+        <v>3</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>3</v>
+      </c>
+      <c r="L198">
+        <v>5</v>
+      </c>
+      <c r="M198">
+        <v>0</v>
+      </c>
+      <c r="N198">
+        <v>5</v>
+      </c>
+      <c r="O198" t="s">
+        <v>213</v>
+      </c>
+      <c r="P198" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q198">
+        <v>3.1</v>
+      </c>
+      <c r="R198">
+        <v>2.05</v>
+      </c>
+      <c r="S198">
+        <v>3.75</v>
+      </c>
+      <c r="T198">
+        <v>1.5</v>
+      </c>
+      <c r="U198">
+        <v>2.5</v>
+      </c>
+      <c r="V198">
+        <v>3.4</v>
+      </c>
+      <c r="W198">
+        <v>1.3</v>
+      </c>
+      <c r="X198">
+        <v>10</v>
+      </c>
+      <c r="Y198">
+        <v>1.06</v>
+      </c>
+      <c r="Z198">
+        <v>2.3</v>
+      </c>
+      <c r="AA198">
+        <v>3</v>
+      </c>
+      <c r="AB198">
+        <v>3.1</v>
+      </c>
+      <c r="AC198">
+        <v>1.01</v>
+      </c>
+      <c r="AD198">
+        <v>8.9</v>
+      </c>
+      <c r="AE198">
+        <v>1.38</v>
+      </c>
+      <c r="AF198">
+        <v>2.75</v>
+      </c>
+      <c r="AG198">
+        <v>2.1</v>
+      </c>
+      <c r="AH198">
+        <v>1.6</v>
+      </c>
+      <c r="AI198">
+        <v>1.83</v>
+      </c>
+      <c r="AJ198">
+        <v>1.83</v>
+      </c>
+      <c r="AK198">
+        <v>1.34</v>
+      </c>
+      <c r="AL198">
+        <v>1.33</v>
+      </c>
+      <c r="AM198">
+        <v>1.56</v>
+      </c>
+      <c r="AN198">
+        <v>1.9</v>
+      </c>
+      <c r="AO198">
+        <v>1.36</v>
+      </c>
+      <c r="AP198">
+        <v>2</v>
+      </c>
+      <c r="AQ198">
+        <v>1.25</v>
+      </c>
+      <c r="AR198">
+        <v>1.61</v>
+      </c>
+      <c r="AS198">
+        <v>1.38</v>
+      </c>
+      <c r="AT198">
+        <v>2.99</v>
+      </c>
+      <c r="AU198">
+        <v>7</v>
+      </c>
+      <c r="AV198">
+        <v>4</v>
+      </c>
+      <c r="AW198">
+        <v>1</v>
+      </c>
+      <c r="AX198">
+        <v>9</v>
+      </c>
+      <c r="AY198">
+        <v>8</v>
+      </c>
+      <c r="AZ198">
+        <v>13</v>
+      </c>
+      <c r="BA198">
+        <v>-1</v>
+      </c>
+      <c r="BB198">
+        <v>-1</v>
+      </c>
+      <c r="BC198">
+        <v>-1</v>
+      </c>
+      <c r="BD198">
+        <v>2.1</v>
+      </c>
+      <c r="BE198">
+        <v>8</v>
+      </c>
+      <c r="BF198">
+        <v>1.95</v>
+      </c>
+      <c r="BG198">
+        <v>1.23</v>
+      </c>
+      <c r="BH198">
+        <v>3.6</v>
+      </c>
+      <c r="BI198">
+        <v>1.44</v>
+      </c>
+      <c r="BJ198">
+        <v>2.58</v>
+      </c>
+      <c r="BK198">
+        <v>1.74</v>
+      </c>
+      <c r="BL198">
+        <v>2.02</v>
+      </c>
+      <c r="BM198">
+        <v>2.19</v>
+      </c>
+      <c r="BN198">
+        <v>1.63</v>
+      </c>
+      <c r="BO198">
+        <v>2.77</v>
+      </c>
+      <c r="BP198">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -40821,13 +40821,13 @@
         <v>13</v>
       </c>
       <c r="BA192">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BB192">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BC192">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="BD192">
         <v>1.69</v>
@@ -41027,13 +41027,13 @@
         <v>8</v>
       </c>
       <c r="BA193">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BB193">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC193">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD193">
         <v>1.59</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="313">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -658,6 +658,9 @@
     <t>['6', '20', '34', '52', '61']</t>
   </si>
   <si>
+    <t>['80']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -920,9 +923,6 @@
   </si>
   <si>
     <t>['25', '36']</t>
-  </si>
-  <si>
-    <t>['80']</t>
   </si>
   <si>
     <t>['7', '64']</t>
@@ -1314,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP198"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1570,7 +1570,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1776,7 +1776,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1982,7 +1982,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2394,7 +2394,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2600,7 +2600,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3012,7 +3012,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ9">
         <v>1.27</v>
@@ -3424,7 +3424,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3836,7 +3836,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4042,7 +4042,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4248,7 +4248,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4329,7 +4329,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ15">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4454,7 +4454,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -5072,7 +5072,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5278,7 +5278,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5356,7 +5356,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ20">
         <v>1.45</v>
@@ -5896,7 +5896,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6308,7 +6308,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6720,7 +6720,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7132,7 +7132,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7213,7 +7213,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR29">
         <v>1.08</v>
@@ -7338,7 +7338,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7750,7 +7750,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8162,7 +8162,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8368,7 +8368,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8574,7 +8574,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8986,7 +8986,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9192,7 +9192,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9604,7 +9604,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9810,7 +9810,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10222,7 +10222,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10428,7 +10428,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10840,7 +10840,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11046,7 +11046,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11252,7 +11252,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11539,7 +11539,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ50">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR50">
         <v>1.2</v>
@@ -11664,7 +11664,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12282,7 +12282,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12360,7 +12360,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ54">
         <v>1.25</v>
@@ -12694,7 +12694,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12900,7 +12900,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -12981,7 +12981,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ57">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR57">
         <v>1.67</v>
@@ -13312,7 +13312,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -14548,7 +14548,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14626,7 +14626,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ65">
         <v>1.09</v>
@@ -14960,7 +14960,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15166,7 +15166,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -16196,7 +16196,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16277,7 +16277,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ73">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR73">
         <v>1.18</v>
@@ -16402,7 +16402,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16608,7 +16608,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16814,7 +16814,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17226,7 +17226,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -18256,7 +18256,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18874,7 +18874,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19158,7 +19158,7 @@
         <v>1.25</v>
       </c>
       <c r="AP87">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ87">
         <v>0.64</v>
@@ -19286,7 +19286,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19698,7 +19698,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19904,7 +19904,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20110,7 +20110,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20316,7 +20316,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20397,7 +20397,7 @@
         <v>1</v>
       </c>
       <c r="AQ93">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR93">
         <v>1.22</v>
@@ -20522,7 +20522,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20728,7 +20728,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21140,7 +21140,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21346,7 +21346,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21552,7 +21552,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22376,7 +22376,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22660,7 +22660,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ104">
         <v>1.18</v>
@@ -22788,7 +22788,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22994,7 +22994,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23200,7 +23200,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23406,7 +23406,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23612,7 +23612,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24311,7 +24311,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ112">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR112">
         <v>1.41</v>
@@ -24436,7 +24436,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24642,7 +24642,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25054,7 +25054,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25260,7 +25260,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25466,7 +25466,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25956,7 +25956,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ120">
         <v>1.4</v>
@@ -26290,7 +26290,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26702,7 +26702,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27114,7 +27114,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27526,7 +27526,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27938,7 +27938,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28225,7 +28225,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ131">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -28350,7 +28350,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28556,7 +28556,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28762,7 +28762,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29380,7 +29380,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29792,7 +29792,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30204,7 +30204,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30616,7 +30616,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30822,7 +30822,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31234,7 +31234,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31440,7 +31440,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31521,7 +31521,7 @@
         <v>1</v>
       </c>
       <c r="AQ147">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR147">
         <v>1.68</v>
@@ -31646,7 +31646,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32264,7 +32264,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32470,7 +32470,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32754,7 +32754,7 @@
         <v>1.63</v>
       </c>
       <c r="AP153">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ153">
         <v>1.45</v>
@@ -32882,7 +32882,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33375,7 +33375,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ156">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR156">
         <v>1.49</v>
@@ -33706,7 +33706,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34324,7 +34324,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34736,7 +34736,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34942,7 +34942,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35148,7 +35148,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35560,7 +35560,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -36256,7 +36256,7 @@
         <v>1.33</v>
       </c>
       <c r="AP170">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ170">
         <v>1.09</v>
@@ -36384,7 +36384,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36590,7 +36590,7 @@
         <v>199</v>
       </c>
       <c r="P172" t="s">
-        <v>302</v>
+        <v>214</v>
       </c>
       <c r="Q172">
         <v>3.1</v>
@@ -37701,7 +37701,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ177">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR177">
         <v>1.06</v>
@@ -38238,7 +38238,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38650,7 +38650,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -40170,7 +40170,7 @@
         <v>0.3</v>
       </c>
       <c r="AP189">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ189">
         <v>0.36</v>
@@ -41439,13 +41439,13 @@
         <v>11</v>
       </c>
       <c r="BA195">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="BB195">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC195">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="BD195">
         <v>1.45</v>
@@ -41645,13 +41645,13 @@
         <v>15</v>
       </c>
       <c r="BA196">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB196">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC196">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BD196">
         <v>2.1</v>
@@ -41851,13 +41851,13 @@
         <v>11</v>
       </c>
       <c r="BA197">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB197">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC197">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD197">
         <v>1.51</v>
@@ -42057,13 +42057,13 @@
         <v>13</v>
       </c>
       <c r="BA198">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB198">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BC198">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD198">
         <v>2.1</v>
@@ -42103,6 +42103,212 @@
       </c>
       <c r="BP198">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7502798</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45705.625</v>
+      </c>
+      <c r="F199">
+        <v>22</v>
+      </c>
+      <c r="G199" t="s">
+        <v>77</v>
+      </c>
+      <c r="H199" t="s">
+        <v>73</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>1</v>
+      </c>
+      <c r="K199">
+        <v>1</v>
+      </c>
+      <c r="L199">
+        <v>1</v>
+      </c>
+      <c r="M199">
+        <v>1</v>
+      </c>
+      <c r="N199">
+        <v>2</v>
+      </c>
+      <c r="O199" t="s">
+        <v>214</v>
+      </c>
+      <c r="P199" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q199">
+        <v>2.75</v>
+      </c>
+      <c r="R199">
+        <v>2.05</v>
+      </c>
+      <c r="S199">
+        <v>4.33</v>
+      </c>
+      <c r="T199">
+        <v>1.44</v>
+      </c>
+      <c r="U199">
+        <v>2.63</v>
+      </c>
+      <c r="V199">
+        <v>3.25</v>
+      </c>
+      <c r="W199">
+        <v>1.33</v>
+      </c>
+      <c r="X199">
+        <v>10</v>
+      </c>
+      <c r="Y199">
+        <v>1.06</v>
+      </c>
+      <c r="Z199">
+        <v>2.05</v>
+      </c>
+      <c r="AA199">
+        <v>3.1</v>
+      </c>
+      <c r="AB199">
+        <v>3.6</v>
+      </c>
+      <c r="AC199">
+        <v>1.02</v>
+      </c>
+      <c r="AD199">
+        <v>7.9</v>
+      </c>
+      <c r="AE199">
+        <v>1.37</v>
+      </c>
+      <c r="AF199">
+        <v>2.8</v>
+      </c>
+      <c r="AG199">
+        <v>2.05</v>
+      </c>
+      <c r="AH199">
+        <v>1.65</v>
+      </c>
+      <c r="AI199">
+        <v>1.91</v>
+      </c>
+      <c r="AJ199">
+        <v>1.8</v>
+      </c>
+      <c r="AK199">
+        <v>1.28</v>
+      </c>
+      <c r="AL199">
+        <v>1.29</v>
+      </c>
+      <c r="AM199">
+        <v>1.72</v>
+      </c>
+      <c r="AN199">
+        <v>1.3</v>
+      </c>
+      <c r="AO199">
+        <v>1.09</v>
+      </c>
+      <c r="AP199">
+        <v>1.27</v>
+      </c>
+      <c r="AQ199">
+        <v>1.08</v>
+      </c>
+      <c r="AR199">
+        <v>1.7</v>
+      </c>
+      <c r="AS199">
+        <v>1.31</v>
+      </c>
+      <c r="AT199">
+        <v>3.01</v>
+      </c>
+      <c r="AU199">
+        <v>4</v>
+      </c>
+      <c r="AV199">
+        <v>3</v>
+      </c>
+      <c r="AW199">
+        <v>4</v>
+      </c>
+      <c r="AX199">
+        <v>5</v>
+      </c>
+      <c r="AY199">
+        <v>8</v>
+      </c>
+      <c r="AZ199">
+        <v>8</v>
+      </c>
+      <c r="BA199">
+        <v>3</v>
+      </c>
+      <c r="BB199">
+        <v>0</v>
+      </c>
+      <c r="BC199">
+        <v>3</v>
+      </c>
+      <c r="BD199">
+        <v>1.69</v>
+      </c>
+      <c r="BE199">
+        <v>8.5</v>
+      </c>
+      <c r="BF199">
+        <v>2.53</v>
+      </c>
+      <c r="BG199">
+        <v>1.12</v>
+      </c>
+      <c r="BH199">
+        <v>4.65</v>
+      </c>
+      <c r="BI199">
+        <v>1.27</v>
+      </c>
+      <c r="BJ199">
+        <v>3.14</v>
+      </c>
+      <c r="BK199">
+        <v>1.51</v>
+      </c>
+      <c r="BL199">
+        <v>2.32</v>
+      </c>
+      <c r="BM199">
+        <v>1.95</v>
+      </c>
+      <c r="BN199">
+        <v>1.85</v>
+      </c>
+      <c r="BO199">
+        <v>2.4</v>
+      </c>
+      <c r="BP199">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="314">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -659,6 +659,9 @@
   </si>
   <si>
     <t>['80']</t>
+  </si>
+  <si>
+    <t>['5', '26', '45+3']</t>
   </si>
   <si>
     <t>['24', '27']</t>
@@ -1314,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1570,7 +1573,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1776,7 +1779,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1982,7 +1985,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2394,7 +2397,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2472,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ6">
         <v>0.9</v>
@@ -2600,7 +2603,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3012,7 +3015,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3299,7 +3302,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ10">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3424,7 +3427,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3836,7 +3839,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4042,7 +4045,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4248,7 +4251,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4454,7 +4457,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -5072,7 +5075,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5278,7 +5281,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5896,7 +5899,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6308,7 +6311,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6386,7 +6389,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ25">
         <v>1.45</v>
@@ -6720,7 +6723,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -6801,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>1.33</v>
@@ -7132,7 +7135,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7338,7 +7341,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7750,7 +7753,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8162,7 +8165,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8368,7 +8371,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8574,7 +8577,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8986,7 +8989,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9067,7 +9070,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ38">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>1.5</v>
@@ -9192,7 +9195,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9604,7 +9607,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9810,7 +9813,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10094,7 +10097,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ43">
         <v>0.36</v>
@@ -10222,7 +10225,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10428,7 +10431,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10840,7 +10843,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11046,7 +11049,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11252,7 +11255,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11664,7 +11667,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12282,7 +12285,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12694,7 +12697,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12900,7 +12903,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13312,7 +13315,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13599,7 +13602,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ60">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>1.51</v>
@@ -14008,7 +14011,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ62">
         <v>1.45</v>
@@ -14548,7 +14551,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14960,7 +14963,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15166,7 +15169,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -16196,7 +16199,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16274,7 +16277,7 @@
         <v>1.25</v>
       </c>
       <c r="AP73">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ73">
         <v>1.08</v>
@@ -16402,7 +16405,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16608,7 +16611,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16689,7 +16692,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ75">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR75">
         <v>1.62</v>
@@ -16814,7 +16817,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17226,7 +17229,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -18256,7 +18259,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18874,7 +18877,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19286,7 +19289,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19698,7 +19701,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19904,7 +19907,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -19982,7 +19985,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ91">
         <v>1.09</v>
@@ -20110,7 +20113,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20191,7 +20194,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ92">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR92">
         <v>1.19</v>
@@ -20316,7 +20319,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20522,7 +20525,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20728,7 +20731,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21140,7 +21143,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21346,7 +21349,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21552,7 +21555,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22376,7 +22379,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22788,7 +22791,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22994,7 +22997,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23200,7 +23203,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23278,7 +23281,7 @@
         <v>1</v>
       </c>
       <c r="AP107">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ107">
         <v>0.55</v>
@@ -23406,7 +23409,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23612,7 +23615,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24436,7 +24439,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24642,7 +24645,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -24929,7 +24932,7 @@
         <v>1</v>
       </c>
       <c r="AQ115">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR115">
         <v>1.59</v>
@@ -25054,7 +25057,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25260,7 +25263,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25466,7 +25469,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -26290,7 +26293,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26368,7 +26371,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ122">
         <v>0.64</v>
@@ -26702,7 +26705,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -26989,7 +26992,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ125">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR125">
         <v>1.63</v>
@@ -27114,7 +27117,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27526,7 +27529,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27938,7 +27941,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28350,7 +28353,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28556,7 +28559,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28762,7 +28765,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29380,7 +29383,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29458,7 +29461,7 @@
         <v>1.57</v>
       </c>
       <c r="AP137">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ137">
         <v>1.18</v>
@@ -29792,7 +29795,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30204,7 +30207,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30616,7 +30619,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30822,7 +30825,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31234,7 +31237,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31440,7 +31443,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31646,7 +31649,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32264,7 +32267,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32345,7 +32348,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ151">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR151">
         <v>1.02</v>
@@ -32470,7 +32473,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32882,7 +32885,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33706,7 +33709,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34324,7 +34327,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34736,7 +34739,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34942,7 +34945,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35148,7 +35151,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35560,7 +35563,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -35844,7 +35847,7 @@
         <v>1.11</v>
       </c>
       <c r="AP168">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ168">
         <v>1.27</v>
@@ -36259,7 +36262,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ170">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR170">
         <v>1.53</v>
@@ -36384,7 +36387,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -37002,7 +37005,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37620,7 +37623,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -38238,7 +38241,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38650,7 +38653,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38856,7 +38859,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39349,7 +39352,7 @@
         <v>1</v>
       </c>
       <c r="AQ185">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR185">
         <v>1.68</v>
@@ -39474,7 +39477,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39552,7 +39555,7 @@
         <v>1.22</v>
       </c>
       <c r="AP186">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ186">
         <v>1.4</v>
@@ -39886,7 +39889,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40298,7 +40301,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40710,7 +40713,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41122,7 +41125,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41534,7 +41537,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41740,7 +41743,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -42152,7 +42155,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42309,6 +42312,212 @@
       </c>
       <c r="BP199">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7502804</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45709.625</v>
+      </c>
+      <c r="F200">
+        <v>23</v>
+      </c>
+      <c r="G200" t="s">
+        <v>74</v>
+      </c>
+      <c r="H200" t="s">
+        <v>81</v>
+      </c>
+      <c r="I200">
+        <v>3</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>3</v>
+      </c>
+      <c r="L200">
+        <v>3</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="N200">
+        <v>3</v>
+      </c>
+      <c r="O200" t="s">
+        <v>215</v>
+      </c>
+      <c r="P200" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q200">
+        <v>2.95</v>
+      </c>
+      <c r="R200">
+        <v>2.14</v>
+      </c>
+      <c r="S200">
+        <v>3.65</v>
+      </c>
+      <c r="T200">
+        <v>1.42</v>
+      </c>
+      <c r="U200">
+        <v>2.7</v>
+      </c>
+      <c r="V200">
+        <v>2.8</v>
+      </c>
+      <c r="W200">
+        <v>1.39</v>
+      </c>
+      <c r="X200">
+        <v>8</v>
+      </c>
+      <c r="Y200">
+        <v>1.03</v>
+      </c>
+      <c r="Z200">
+        <v>2.25</v>
+      </c>
+      <c r="AA200">
+        <v>3.1</v>
+      </c>
+      <c r="AB200">
+        <v>3</v>
+      </c>
+      <c r="AC200">
+        <v>1.01</v>
+      </c>
+      <c r="AD200">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE200">
+        <v>1.31</v>
+      </c>
+      <c r="AF200">
+        <v>3.15</v>
+      </c>
+      <c r="AG200">
+        <v>1.91</v>
+      </c>
+      <c r="AH200">
+        <v>1.75</v>
+      </c>
+      <c r="AI200">
+        <v>1.74</v>
+      </c>
+      <c r="AJ200">
+        <v>1.99</v>
+      </c>
+      <c r="AK200">
+        <v>1.37</v>
+      </c>
+      <c r="AL200">
+        <v>1.31</v>
+      </c>
+      <c r="AM200">
+        <v>1.56</v>
+      </c>
+      <c r="AN200">
+        <v>1.55</v>
+      </c>
+      <c r="AO200">
+        <v>1.09</v>
+      </c>
+      <c r="AP200">
+        <v>1.67</v>
+      </c>
+      <c r="AQ200">
+        <v>1</v>
+      </c>
+      <c r="AR200">
+        <v>1.24</v>
+      </c>
+      <c r="AS200">
+        <v>1.19</v>
+      </c>
+      <c r="AT200">
+        <v>2.43</v>
+      </c>
+      <c r="AU200">
+        <v>8</v>
+      </c>
+      <c r="AV200">
+        <v>3</v>
+      </c>
+      <c r="AW200">
+        <v>4</v>
+      </c>
+      <c r="AX200">
+        <v>5</v>
+      </c>
+      <c r="AY200">
+        <v>12</v>
+      </c>
+      <c r="AZ200">
+        <v>8</v>
+      </c>
+      <c r="BA200">
+        <v>2</v>
+      </c>
+      <c r="BB200">
+        <v>5</v>
+      </c>
+      <c r="BC200">
+        <v>7</v>
+      </c>
+      <c r="BD200">
+        <v>1.7</v>
+      </c>
+      <c r="BE200">
+        <v>6.2</v>
+      </c>
+      <c r="BF200">
+        <v>2.65</v>
+      </c>
+      <c r="BG200">
+        <v>1.12</v>
+      </c>
+      <c r="BH200">
+        <v>4.75</v>
+      </c>
+      <c r="BI200">
+        <v>1.25</v>
+      </c>
+      <c r="BJ200">
+        <v>3.5</v>
+      </c>
+      <c r="BK200">
+        <v>1.48</v>
+      </c>
+      <c r="BL200">
+        <v>2.42</v>
+      </c>
+      <c r="BM200">
+        <v>1.82</v>
+      </c>
+      <c r="BN200">
+        <v>1.82</v>
+      </c>
+      <c r="BO200">
+        <v>2.42</v>
+      </c>
+      <c r="BP200">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -664,6 +664,12 @@
     <t>['5', '26', '45+3']</t>
   </si>
   <si>
+    <t>['8']</t>
+  </si>
+  <si>
+    <t>['41', '68', '90']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -956,6 +962,12 @@
   </si>
   <si>
     <t>['69', '90+8']</t>
+  </si>
+  <si>
+    <t>['4', '12', '45+1', '89']</t>
+  </si>
+  <si>
+    <t>['46', '67']</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1573,7 +1585,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1651,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ2">
         <v>1.45</v>
@@ -1779,7 +1791,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1857,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ3">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1985,7 +1997,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2397,7 +2409,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2478,7 +2490,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ6">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2603,7 +2615,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3015,7 +3027,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3096,7 +3108,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ9">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3299,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3427,7 +3439,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3839,7 +3851,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3920,7 +3932,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ13">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4045,7 +4057,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4251,7 +4263,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4329,7 +4341,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ15">
         <v>1.08</v>
@@ -4457,7 +4469,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4947,7 +4959,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ18">
         <v>1.45</v>
@@ -5075,7 +5087,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5156,7 +5168,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ19">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5281,7 +5293,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5565,7 +5577,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21">
         <v>1.18</v>
@@ -5774,7 +5786,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ22">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR22">
         <v>1.3</v>
@@ -5899,7 +5911,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -5980,7 +5992,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR23">
         <v>1.93</v>
@@ -6186,7 +6198,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ24">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR24">
         <v>1.31</v>
@@ -6311,7 +6323,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6595,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ26">
         <v>1.45</v>
@@ -6723,7 +6735,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -6801,7 +6813,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7007,10 +7019,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ28">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR28">
         <v>1.62</v>
@@ -7135,7 +7147,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7341,7 +7353,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7753,7 +7765,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8165,7 +8177,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8243,7 +8255,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ34">
         <v>1.18</v>
@@ -8371,7 +8383,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8577,7 +8589,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8864,7 +8876,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ37">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR37">
         <v>0.82</v>
@@ -8989,7 +9001,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9195,7 +9207,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9273,7 +9285,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ39">
         <v>1.45</v>
@@ -9482,7 +9494,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ40">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR40">
         <v>1.4</v>
@@ -9607,7 +9619,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9685,7 +9697,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ41">
         <v>1.45</v>
@@ -9813,7 +9825,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9891,7 +9903,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ42">
         <v>1.45</v>
@@ -10100,7 +10112,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ43">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR43">
         <v>1.55</v>
@@ -10225,7 +10237,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10303,10 +10315,10 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ44">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR44">
         <v>1.61</v>
@@ -10431,7 +10443,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10512,7 +10524,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ45">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR45">
         <v>1.58</v>
@@ -10715,10 +10727,10 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ46">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR46">
         <v>1.7</v>
@@ -10843,7 +10855,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11049,7 +11061,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11255,7 +11267,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11667,7 +11679,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12285,7 +12297,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12697,7 +12709,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12903,7 +12915,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -12981,7 +12993,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ57">
         <v>1.08</v>
@@ -13187,10 +13199,10 @@
         <v>0.67</v>
       </c>
       <c r="AP58">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ58">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR58">
         <v>1.6</v>
@@ -13315,7 +13327,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13396,7 +13408,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ59">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR59">
         <v>1.13</v>
@@ -13805,10 +13817,10 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ61">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR61">
         <v>1.62</v>
@@ -14014,7 +14026,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ62">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR62">
         <v>1.41</v>
@@ -14217,7 +14229,7 @@
         <v>1.67</v>
       </c>
       <c r="AP63">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ63">
         <v>1.45</v>
@@ -14423,7 +14435,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ64">
         <v>1.45</v>
@@ -14551,7 +14563,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14963,7 +14975,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15169,7 +15181,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -16074,7 +16086,7 @@
         <v>1</v>
       </c>
       <c r="AQ72">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR72">
         <v>1.62</v>
@@ -16199,7 +16211,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16405,7 +16417,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16611,7 +16623,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16689,7 +16701,7 @@
         <v>0.5</v>
       </c>
       <c r="AP75">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -16817,7 +16829,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -16895,7 +16907,7 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ76">
         <v>1.45</v>
@@ -17229,7 +17241,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17307,7 +17319,7 @@
         <v>1.75</v>
       </c>
       <c r="AP78">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ78">
         <v>1.25</v>
@@ -17516,7 +17528,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ79">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR79">
         <v>1.3</v>
@@ -17719,10 +17731,10 @@
         <v>1.75</v>
       </c>
       <c r="AP80">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ80">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR80">
         <v>1.09</v>
@@ -18134,7 +18146,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ82">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR82">
         <v>1.36</v>
@@ -18259,7 +18271,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18337,7 +18349,7 @@
         <v>2.5</v>
       </c>
       <c r="AP83">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ83">
         <v>1.82</v>
@@ -18546,7 +18558,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ84">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR84">
         <v>1.48</v>
@@ -18877,7 +18889,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -18955,7 +18967,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ86">
         <v>0.55</v>
@@ -19289,7 +19301,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19576,7 +19588,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ89">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR89">
         <v>1.48</v>
@@ -19701,7 +19713,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19907,7 +19919,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20113,7 +20125,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20319,7 +20331,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20397,7 +20409,7 @@
         <v>1.6</v>
       </c>
       <c r="AP93">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ93">
         <v>1.08</v>
@@ -20525,7 +20537,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20603,7 +20615,7 @@
         <v>2.2</v>
       </c>
       <c r="AP94">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ94">
         <v>1.45</v>
@@ -20731,7 +20743,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -20812,7 +20824,7 @@
         <v>1</v>
       </c>
       <c r="AQ95">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR95">
         <v>1.56</v>
@@ -21143,7 +21155,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21221,7 +21233,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ97">
         <v>1.45</v>
@@ -21349,7 +21361,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21430,7 +21442,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ98">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21555,7 +21567,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -21839,7 +21851,7 @@
         <v>1.67</v>
       </c>
       <c r="AP100">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ100">
         <v>1.25</v>
@@ -22048,7 +22060,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ101">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR101">
         <v>1.6</v>
@@ -22379,7 +22391,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22457,7 +22469,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ103">
         <v>1.45</v>
@@ -22791,7 +22803,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22997,7 +23009,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23078,7 +23090,7 @@
         <v>2</v>
       </c>
       <c r="AQ106">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR106">
         <v>1.65</v>
@@ -23203,7 +23215,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23409,7 +23421,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23490,7 +23502,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ108">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR108">
         <v>1.57</v>
@@ -23615,7 +23627,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -23696,7 +23708,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ109">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR109">
         <v>1.09</v>
@@ -23899,7 +23911,7 @@
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ110">
         <v>1.18</v>
@@ -24105,7 +24117,7 @@
         <v>2.6</v>
       </c>
       <c r="AP111">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ111">
         <v>1.82</v>
@@ -24439,7 +24451,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24517,10 +24529,10 @@
         <v>1.17</v>
       </c>
       <c r="AP113">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ113">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24645,7 +24657,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25057,7 +25069,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25263,7 +25275,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25341,7 +25353,7 @@
         <v>1.43</v>
       </c>
       <c r="AP117">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ117">
         <v>1.25</v>
@@ -25469,7 +25481,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25550,7 +25562,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ118">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR118">
         <v>1.48</v>
@@ -25962,7 +25974,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ120">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR120">
         <v>1.47</v>
@@ -26293,7 +26305,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26577,7 +26589,7 @@
         <v>1.83</v>
       </c>
       <c r="AP123">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ123">
         <v>1.18</v>
@@ -26705,7 +26717,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -26783,10 +26795,10 @@
         <v>1.29</v>
       </c>
       <c r="AP124">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ124">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR124">
         <v>1.69</v>
@@ -27117,7 +27129,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27195,7 +27207,7 @@
         <v>1.17</v>
       </c>
       <c r="AP126">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ126">
         <v>1.45</v>
@@ -27529,7 +27541,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27610,7 +27622,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ128">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR128">
         <v>1.46</v>
@@ -27941,7 +27953,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28022,7 +28034,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ130">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR130">
         <v>1.55</v>
@@ -28353,7 +28365,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28559,7 +28571,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28765,7 +28777,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -28846,7 +28858,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ134">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR134">
         <v>1.14</v>
@@ -29255,7 +29267,7 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ136">
         <v>1.09</v>
@@ -29383,7 +29395,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29667,7 +29679,7 @@
         <v>0.86</v>
       </c>
       <c r="AP138">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ138">
         <v>1.18</v>
@@ -29795,7 +29807,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -29873,10 +29885,10 @@
         <v>0.29</v>
       </c>
       <c r="AP139">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ139">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR139">
         <v>1.54</v>
@@ -30207,7 +30219,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30491,7 +30503,7 @@
         <v>0.71</v>
       </c>
       <c r="AP142">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ142">
         <v>0.64</v>
@@ -30619,7 +30631,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30700,7 +30712,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ143">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR143">
         <v>1.64</v>
@@ -30825,7 +30837,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31237,7 +31249,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31443,7 +31455,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31649,7 +31661,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -31727,10 +31739,10 @@
         <v>0.38</v>
       </c>
       <c r="AP148">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ148">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR148">
         <v>1.62</v>
@@ -31936,7 +31948,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ149">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR149">
         <v>1.55</v>
@@ -32139,10 +32151,10 @@
         <v>1.43</v>
       </c>
       <c r="AP150">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ150">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR150">
         <v>1.63</v>
@@ -32267,7 +32279,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32473,7 +32485,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32885,7 +32897,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33169,7 +33181,7 @@
         <v>0.63</v>
       </c>
       <c r="AP155">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ155">
         <v>0.64</v>
@@ -33584,7 +33596,7 @@
         <v>2</v>
       </c>
       <c r="AQ157">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR157">
         <v>1.59</v>
@@ -33709,7 +33721,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -33993,7 +34005,7 @@
         <v>1.38</v>
       </c>
       <c r="AP159">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ159">
         <v>1.45</v>
@@ -34202,7 +34214,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ160">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR160">
         <v>1.7</v>
@@ -34327,7 +34339,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34739,7 +34751,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34945,7 +34957,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35151,7 +35163,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35229,7 +35241,7 @@
         <v>1.33</v>
       </c>
       <c r="AP165">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ165">
         <v>1.45</v>
@@ -35563,7 +35575,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -35641,10 +35653,10 @@
         <v>1.25</v>
       </c>
       <c r="AP167">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ167">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR167">
         <v>1.71</v>
@@ -35850,7 +35862,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ168">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR168">
         <v>1.2</v>
@@ -36053,10 +36065,10 @@
         <v>0.63</v>
       </c>
       <c r="AP169">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ169">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR169">
         <v>1.26</v>
@@ -36387,7 +36399,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -37005,7 +37017,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37083,7 +37095,7 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ174">
         <v>1.09</v>
@@ -37623,7 +37635,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -38241,7 +38253,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38528,7 +38540,7 @@
         <v>2</v>
       </c>
       <c r="AQ181">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR181">
         <v>1.63</v>
@@ -38653,7 +38665,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38731,7 +38743,7 @@
         <v>0.78</v>
       </c>
       <c r="AP182">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ182">
         <v>1.18</v>
@@ -38859,7 +38871,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -38940,7 +38952,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ183">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR183">
         <v>1.33</v>
@@ -39143,7 +39155,7 @@
         <v>1.6</v>
       </c>
       <c r="AP184">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ184">
         <v>1.45</v>
@@ -39349,7 +39361,7 @@
         <v>1.2</v>
       </c>
       <c r="AP185">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ185">
         <v>1</v>
@@ -39477,7 +39489,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39558,7 +39570,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ186">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR186">
         <v>1.18</v>
@@ -39761,7 +39773,7 @@
         <v>1.5</v>
       </c>
       <c r="AP187">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ187">
         <v>1.45</v>
@@ -39889,7 +39901,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40176,7 +40188,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ189">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AR189">
         <v>1.67</v>
@@ -40301,7 +40313,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40382,7 +40394,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ190">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR190">
         <v>1.31</v>
@@ -40713,7 +40725,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41125,7 +41137,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41537,7 +41549,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41743,7 +41755,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -42155,7 +42167,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42518,6 +42530,1036 @@
       </c>
       <c r="BP200">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7502803</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45710.33333333334</v>
+      </c>
+      <c r="F201">
+        <v>23</v>
+      </c>
+      <c r="G201" t="s">
+        <v>78</v>
+      </c>
+      <c r="H201" t="s">
+        <v>76</v>
+      </c>
+      <c r="I201">
+        <v>1</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>1</v>
+      </c>
+      <c r="L201">
+        <v>1</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
+      </c>
+      <c r="N201">
+        <v>1</v>
+      </c>
+      <c r="O201" t="s">
+        <v>216</v>
+      </c>
+      <c r="P201" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q201">
+        <v>2.6</v>
+      </c>
+      <c r="R201">
+        <v>2.15</v>
+      </c>
+      <c r="S201">
+        <v>4.2</v>
+      </c>
+      <c r="T201">
+        <v>1.42</v>
+      </c>
+      <c r="U201">
+        <v>2.65</v>
+      </c>
+      <c r="V201">
+        <v>2.85</v>
+      </c>
+      <c r="W201">
+        <v>1.38</v>
+      </c>
+      <c r="X201">
+        <v>7.3</v>
+      </c>
+      <c r="Y201">
+        <v>1.04</v>
+      </c>
+      <c r="Z201">
+        <v>1.91</v>
+      </c>
+      <c r="AA201">
+        <v>3.4</v>
+      </c>
+      <c r="AB201">
+        <v>3.8</v>
+      </c>
+      <c r="AC201">
+        <v>1.01</v>
+      </c>
+      <c r="AD201">
+        <v>8.9</v>
+      </c>
+      <c r="AE201">
+        <v>1.32</v>
+      </c>
+      <c r="AF201">
+        <v>3.1</v>
+      </c>
+      <c r="AG201">
+        <v>1.91</v>
+      </c>
+      <c r="AH201">
+        <v>1.73</v>
+      </c>
+      <c r="AI201">
+        <v>1.8</v>
+      </c>
+      <c r="AJ201">
+        <v>1.91</v>
+      </c>
+      <c r="AK201">
+        <v>1.27</v>
+      </c>
+      <c r="AL201">
+        <v>1.29</v>
+      </c>
+      <c r="AM201">
+        <v>1.73</v>
+      </c>
+      <c r="AN201">
+        <v>1.18</v>
+      </c>
+      <c r="AO201">
+        <v>0.36</v>
+      </c>
+      <c r="AP201">
+        <v>1.33</v>
+      </c>
+      <c r="AQ201">
+        <v>0.33</v>
+      </c>
+      <c r="AR201">
+        <v>1.53</v>
+      </c>
+      <c r="AS201">
+        <v>1.56</v>
+      </c>
+      <c r="AT201">
+        <v>3.09</v>
+      </c>
+      <c r="AU201">
+        <v>4</v>
+      </c>
+      <c r="AV201">
+        <v>3</v>
+      </c>
+      <c r="AW201">
+        <v>5</v>
+      </c>
+      <c r="AX201">
+        <v>4</v>
+      </c>
+      <c r="AY201">
+        <v>9</v>
+      </c>
+      <c r="AZ201">
+        <v>7</v>
+      </c>
+      <c r="BA201">
+        <v>5</v>
+      </c>
+      <c r="BB201">
+        <v>3</v>
+      </c>
+      <c r="BC201">
+        <v>8</v>
+      </c>
+      <c r="BD201">
+        <v>1.69</v>
+      </c>
+      <c r="BE201">
+        <v>8</v>
+      </c>
+      <c r="BF201">
+        <v>2.54</v>
+      </c>
+      <c r="BG201">
+        <v>1.2</v>
+      </c>
+      <c r="BH201">
+        <v>3.82</v>
+      </c>
+      <c r="BI201">
+        <v>1.4</v>
+      </c>
+      <c r="BJ201">
+        <v>2.72</v>
+      </c>
+      <c r="BK201">
+        <v>1.68</v>
+      </c>
+      <c r="BL201">
+        <v>2.11</v>
+      </c>
+      <c r="BM201">
+        <v>2.09</v>
+      </c>
+      <c r="BN201">
+        <v>1.69</v>
+      </c>
+      <c r="BO201">
+        <v>2.63</v>
+      </c>
+      <c r="BP201">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7502802</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45710.45833333334</v>
+      </c>
+      <c r="F202">
+        <v>23</v>
+      </c>
+      <c r="G202" t="s">
+        <v>71</v>
+      </c>
+      <c r="H202" t="s">
+        <v>84</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>3</v>
+      </c>
+      <c r="K202">
+        <v>3</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="M202">
+        <v>4</v>
+      </c>
+      <c r="N202">
+        <v>5</v>
+      </c>
+      <c r="O202" t="s">
+        <v>123</v>
+      </c>
+      <c r="P202" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q202">
+        <v>4.3</v>
+      </c>
+      <c r="R202">
+        <v>2.05</v>
+      </c>
+      <c r="S202">
+        <v>2.75</v>
+      </c>
+      <c r="T202">
+        <v>1.48</v>
+      </c>
+      <c r="U202">
+        <v>2.45</v>
+      </c>
+      <c r="V202">
+        <v>3.1</v>
+      </c>
+      <c r="W202">
+        <v>1.32</v>
+      </c>
+      <c r="X202">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y202">
+        <v>1.01</v>
+      </c>
+      <c r="Z202">
+        <v>3.75</v>
+      </c>
+      <c r="AA202">
+        <v>3.2</v>
+      </c>
+      <c r="AB202">
+        <v>2</v>
+      </c>
+      <c r="AC202">
+        <v>1.06</v>
+      </c>
+      <c r="AD202">
+        <v>7.5</v>
+      </c>
+      <c r="AE202">
+        <v>1.39</v>
+      </c>
+      <c r="AF202">
+        <v>2.75</v>
+      </c>
+      <c r="AG202">
+        <v>2.1</v>
+      </c>
+      <c r="AH202">
+        <v>1.6</v>
+      </c>
+      <c r="AI202">
+        <v>1.91</v>
+      </c>
+      <c r="AJ202">
+        <v>1.8</v>
+      </c>
+      <c r="AK202">
+        <v>1.67</v>
+      </c>
+      <c r="AL202">
+        <v>1.32</v>
+      </c>
+      <c r="AM202">
+        <v>1.28</v>
+      </c>
+      <c r="AN202">
+        <v>1</v>
+      </c>
+      <c r="AO202">
+        <v>1.27</v>
+      </c>
+      <c r="AP202">
+        <v>0.92</v>
+      </c>
+      <c r="AQ202">
+        <v>1.42</v>
+      </c>
+      <c r="AR202">
+        <v>1.26</v>
+      </c>
+      <c r="AS202">
+        <v>1.44</v>
+      </c>
+      <c r="AT202">
+        <v>2.7</v>
+      </c>
+      <c r="AU202">
+        <v>5</v>
+      </c>
+      <c r="AV202">
+        <v>9</v>
+      </c>
+      <c r="AW202">
+        <v>5</v>
+      </c>
+      <c r="AX202">
+        <v>7</v>
+      </c>
+      <c r="AY202">
+        <v>10</v>
+      </c>
+      <c r="AZ202">
+        <v>16</v>
+      </c>
+      <c r="BA202">
+        <v>-1</v>
+      </c>
+      <c r="BB202">
+        <v>-1</v>
+      </c>
+      <c r="BC202">
+        <v>-1</v>
+      </c>
+      <c r="BD202">
+        <v>2.44</v>
+      </c>
+      <c r="BE202">
+        <v>8</v>
+      </c>
+      <c r="BF202">
+        <v>1.75</v>
+      </c>
+      <c r="BG202">
+        <v>1.39</v>
+      </c>
+      <c r="BH202">
+        <v>2.77</v>
+      </c>
+      <c r="BI202">
+        <v>1.68</v>
+      </c>
+      <c r="BJ202">
+        <v>2.12</v>
+      </c>
+      <c r="BK202">
+        <v>2.11</v>
+      </c>
+      <c r="BL202">
+        <v>1.68</v>
+      </c>
+      <c r="BM202">
+        <v>2.7</v>
+      </c>
+      <c r="BN202">
+        <v>1.41</v>
+      </c>
+      <c r="BO202">
+        <v>3.65</v>
+      </c>
+      <c r="BP202">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7502806</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45710.45833333334</v>
+      </c>
+      <c r="F203">
+        <v>23</v>
+      </c>
+      <c r="G203" t="s">
+        <v>86</v>
+      </c>
+      <c r="H203" t="s">
+        <v>82</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>0</v>
+      </c>
+      <c r="O203" t="s">
+        <v>89</v>
+      </c>
+      <c r="P203" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q203">
+        <v>2.6</v>
+      </c>
+      <c r="R203">
+        <v>2.19</v>
+      </c>
+      <c r="S203">
+        <v>4.1</v>
+      </c>
+      <c r="T203">
+        <v>1.39</v>
+      </c>
+      <c r="U203">
+        <v>2.8</v>
+      </c>
+      <c r="V203">
+        <v>2.7</v>
+      </c>
+      <c r="W203">
+        <v>1.41</v>
+      </c>
+      <c r="X203">
+        <v>7.6</v>
+      </c>
+      <c r="Y203">
+        <v>1.03</v>
+      </c>
+      <c r="Z203">
+        <v>2.05</v>
+      </c>
+      <c r="AA203">
+        <v>3.4</v>
+      </c>
+      <c r="AB203">
+        <v>3.3</v>
+      </c>
+      <c r="AC203">
+        <v>1.03</v>
+      </c>
+      <c r="AD203">
+        <v>9</v>
+      </c>
+      <c r="AE203">
+        <v>1.28</v>
+      </c>
+      <c r="AF203">
+        <v>3.3</v>
+      </c>
+      <c r="AG203">
+        <v>1.83</v>
+      </c>
+      <c r="AH203">
+        <v>1.8</v>
+      </c>
+      <c r="AI203">
+        <v>1.73</v>
+      </c>
+      <c r="AJ203">
+        <v>2</v>
+      </c>
+      <c r="AK203">
+        <v>1.29</v>
+      </c>
+      <c r="AL203">
+        <v>1.28</v>
+      </c>
+      <c r="AM203">
+        <v>1.72</v>
+      </c>
+      <c r="AN203">
+        <v>2</v>
+      </c>
+      <c r="AO203">
+        <v>1.4</v>
+      </c>
+      <c r="AP203">
+        <v>1.92</v>
+      </c>
+      <c r="AQ203">
+        <v>1.36</v>
+      </c>
+      <c r="AR203">
+        <v>1.53</v>
+      </c>
+      <c r="AS203">
+        <v>1.32</v>
+      </c>
+      <c r="AT203">
+        <v>2.85</v>
+      </c>
+      <c r="AU203">
+        <v>5</v>
+      </c>
+      <c r="AV203">
+        <v>4</v>
+      </c>
+      <c r="AW203">
+        <v>11</v>
+      </c>
+      <c r="AX203">
+        <v>9</v>
+      </c>
+      <c r="AY203">
+        <v>16</v>
+      </c>
+      <c r="AZ203">
+        <v>13</v>
+      </c>
+      <c r="BA203">
+        <v>-1</v>
+      </c>
+      <c r="BB203">
+        <v>-1</v>
+      </c>
+      <c r="BC203">
+        <v>-1</v>
+      </c>
+      <c r="BD203">
+        <v>1.82</v>
+      </c>
+      <c r="BE203">
+        <v>8</v>
+      </c>
+      <c r="BF203">
+        <v>2.33</v>
+      </c>
+      <c r="BG203">
+        <v>1.26</v>
+      </c>
+      <c r="BH203">
+        <v>3.38</v>
+      </c>
+      <c r="BI203">
+        <v>1.48</v>
+      </c>
+      <c r="BJ203">
+        <v>2.45</v>
+      </c>
+      <c r="BK203">
+        <v>1.82</v>
+      </c>
+      <c r="BL203">
+        <v>1.93</v>
+      </c>
+      <c r="BM203">
+        <v>2.3</v>
+      </c>
+      <c r="BN203">
+        <v>1.57</v>
+      </c>
+      <c r="BO203">
+        <v>2.93</v>
+      </c>
+      <c r="BP203">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7502810</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45710.52083333334</v>
+      </c>
+      <c r="F204">
+        <v>23</v>
+      </c>
+      <c r="G204" t="s">
+        <v>70</v>
+      </c>
+      <c r="H204" t="s">
+        <v>77</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204">
+        <v>2</v>
+      </c>
+      <c r="N204">
+        <v>3</v>
+      </c>
+      <c r="O204" t="s">
+        <v>117</v>
+      </c>
+      <c r="P204" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q204">
+        <v>3.1</v>
+      </c>
+      <c r="R204">
+        <v>2.05</v>
+      </c>
+      <c r="S204">
+        <v>3.75</v>
+      </c>
+      <c r="T204">
+        <v>1.44</v>
+      </c>
+      <c r="U204">
+        <v>2.63</v>
+      </c>
+      <c r="V204">
+        <v>3.4</v>
+      </c>
+      <c r="W204">
+        <v>1.3</v>
+      </c>
+      <c r="X204">
+        <v>10</v>
+      </c>
+      <c r="Y204">
+        <v>1.06</v>
+      </c>
+      <c r="Z204">
+        <v>2.25</v>
+      </c>
+      <c r="AA204">
+        <v>3.2</v>
+      </c>
+      <c r="AB204">
+        <v>3</v>
+      </c>
+      <c r="AC204">
+        <v>1.06</v>
+      </c>
+      <c r="AD204">
+        <v>8</v>
+      </c>
+      <c r="AE204">
+        <v>1.37</v>
+      </c>
+      <c r="AF204">
+        <v>2.8</v>
+      </c>
+      <c r="AG204">
+        <v>2.05</v>
+      </c>
+      <c r="AH204">
+        <v>1.61</v>
+      </c>
+      <c r="AI204">
+        <v>1.83</v>
+      </c>
+      <c r="AJ204">
+        <v>1.83</v>
+      </c>
+      <c r="AK204">
+        <v>1.38</v>
+      </c>
+      <c r="AL204">
+        <v>1.32</v>
+      </c>
+      <c r="AM204">
+        <v>1.57</v>
+      </c>
+      <c r="AN204">
+        <v>1</v>
+      </c>
+      <c r="AO204">
+        <v>1.45</v>
+      </c>
+      <c r="AP204">
+        <v>0.91</v>
+      </c>
+      <c r="AQ204">
+        <v>1.58</v>
+      </c>
+      <c r="AR204">
+        <v>1.68</v>
+      </c>
+      <c r="AS204">
+        <v>1.4</v>
+      </c>
+      <c r="AT204">
+        <v>3.08</v>
+      </c>
+      <c r="AU204">
+        <v>3</v>
+      </c>
+      <c r="AV204">
+        <v>8</v>
+      </c>
+      <c r="AW204">
+        <v>11</v>
+      </c>
+      <c r="AX204">
+        <v>6</v>
+      </c>
+      <c r="AY204">
+        <v>14</v>
+      </c>
+      <c r="AZ204">
+        <v>14</v>
+      </c>
+      <c r="BA204">
+        <v>-1</v>
+      </c>
+      <c r="BB204">
+        <v>-1</v>
+      </c>
+      <c r="BC204">
+        <v>-1</v>
+      </c>
+      <c r="BD204">
+        <v>1.75</v>
+      </c>
+      <c r="BE204">
+        <v>8</v>
+      </c>
+      <c r="BF204">
+        <v>2.44</v>
+      </c>
+      <c r="BG204">
+        <v>1.23</v>
+      </c>
+      <c r="BH204">
+        <v>3.6</v>
+      </c>
+      <c r="BI204">
+        <v>1.44</v>
+      </c>
+      <c r="BJ204">
+        <v>2.58</v>
+      </c>
+      <c r="BK204">
+        <v>1.74</v>
+      </c>
+      <c r="BL204">
+        <v>2.02</v>
+      </c>
+      <c r="BM204">
+        <v>2.19</v>
+      </c>
+      <c r="BN204">
+        <v>1.63</v>
+      </c>
+      <c r="BO204">
+        <v>2.77</v>
+      </c>
+      <c r="BP204">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7502805</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45710.625</v>
+      </c>
+      <c r="F205">
+        <v>23</v>
+      </c>
+      <c r="G205" t="s">
+        <v>83</v>
+      </c>
+      <c r="H205" t="s">
+        <v>80</v>
+      </c>
+      <c r="I205">
+        <v>1</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>1</v>
+      </c>
+      <c r="L205">
+        <v>3</v>
+      </c>
+      <c r="M205">
+        <v>1</v>
+      </c>
+      <c r="N205">
+        <v>4</v>
+      </c>
+      <c r="O205" t="s">
+        <v>217</v>
+      </c>
+      <c r="P205" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q205">
+        <v>2.6</v>
+      </c>
+      <c r="R205">
+        <v>2.11</v>
+      </c>
+      <c r="S205">
+        <v>4.4</v>
+      </c>
+      <c r="T205">
+        <v>1.45</v>
+      </c>
+      <c r="U205">
+        <v>2.6</v>
+      </c>
+      <c r="V205">
+        <v>2.95</v>
+      </c>
+      <c r="W205">
+        <v>1.35</v>
+      </c>
+      <c r="X205">
+        <v>7.3</v>
+      </c>
+      <c r="Y205">
+        <v>1.04</v>
+      </c>
+      <c r="Z205">
+        <v>1.91</v>
+      </c>
+      <c r="AA205">
+        <v>3.3</v>
+      </c>
+      <c r="AB205">
+        <v>3.8</v>
+      </c>
+      <c r="AC205">
+        <v>1.02</v>
+      </c>
+      <c r="AD205">
+        <v>7.9</v>
+      </c>
+      <c r="AE205">
+        <v>1.35</v>
+      </c>
+      <c r="AF205">
+        <v>2.95</v>
+      </c>
+      <c r="AG205">
+        <v>2</v>
+      </c>
+      <c r="AH205">
+        <v>1.67</v>
+      </c>
+      <c r="AI205">
+        <v>1.86</v>
+      </c>
+      <c r="AJ205">
+        <v>1.85</v>
+      </c>
+      <c r="AK205">
+        <v>1.26</v>
+      </c>
+      <c r="AL205">
+        <v>1.3</v>
+      </c>
+      <c r="AM205">
+        <v>1.75</v>
+      </c>
+      <c r="AN205">
+        <v>1.82</v>
+      </c>
+      <c r="AO205">
+        <v>0.9</v>
+      </c>
+      <c r="AP205">
+        <v>1.92</v>
+      </c>
+      <c r="AQ205">
+        <v>0.82</v>
+      </c>
+      <c r="AR205">
+        <v>1.71</v>
+      </c>
+      <c r="AS205">
+        <v>1.13</v>
+      </c>
+      <c r="AT205">
+        <v>2.84</v>
+      </c>
+      <c r="AU205">
+        <v>5</v>
+      </c>
+      <c r="AV205">
+        <v>3</v>
+      </c>
+      <c r="AW205">
+        <v>11</v>
+      </c>
+      <c r="AX205">
+        <v>5</v>
+      </c>
+      <c r="AY205">
+        <v>16</v>
+      </c>
+      <c r="AZ205">
+        <v>8</v>
+      </c>
+      <c r="BA205">
+        <v>-1</v>
+      </c>
+      <c r="BB205">
+        <v>-1</v>
+      </c>
+      <c r="BC205">
+        <v>-1</v>
+      </c>
+      <c r="BD205">
+        <v>1.85</v>
+      </c>
+      <c r="BE205">
+        <v>8.5</v>
+      </c>
+      <c r="BF205">
+        <v>2.27</v>
+      </c>
+      <c r="BG205">
+        <v>1.15</v>
+      </c>
+      <c r="BH205">
+        <v>4.45</v>
+      </c>
+      <c r="BI205">
+        <v>1.29</v>
+      </c>
+      <c r="BJ205">
+        <v>3.12</v>
+      </c>
+      <c r="BK205">
+        <v>1.53</v>
+      </c>
+      <c r="BL205">
+        <v>2.34</v>
+      </c>
+      <c r="BM205">
+        <v>1.87</v>
+      </c>
+      <c r="BN205">
+        <v>1.87</v>
+      </c>
+      <c r="BO205">
+        <v>2.35</v>
+      </c>
+      <c r="BP205">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="320">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -670,6 +670,9 @@
     <t>['41', '68', '90']</t>
   </si>
   <si>
+    <t>['83']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -968,6 +971,9 @@
   </si>
   <si>
     <t>['46', '67']</t>
+  </si>
+  <si>
+    <t>['18', '37']</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1585,7 +1591,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1666,7 +1672,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ2">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1791,7 +1797,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1997,7 +2003,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2075,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4">
         <v>1.18</v>
@@ -2281,10 +2287,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ5">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2409,7 +2415,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2615,7 +2621,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2693,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ7">
         <v>1.18</v>
@@ -2902,7 +2908,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ8">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3027,7 +3033,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3439,7 +3445,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3851,7 +3857,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4057,7 +4063,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4263,7 +4269,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4469,7 +4475,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -5087,7 +5093,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5293,7 +5299,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5374,7 +5380,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ20">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR20">
         <v>1.01</v>
@@ -5783,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ22">
         <v>0.82</v>
@@ -5911,7 +5917,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -5989,7 +5995,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ23">
         <v>1.36</v>
@@ -6195,7 +6201,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ24">
         <v>0.33</v>
@@ -6323,7 +6329,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6404,7 +6410,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ25">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR25">
         <v>1.23</v>
@@ -6610,7 +6616,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ26">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR26">
         <v>1.66</v>
@@ -6735,7 +6741,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7147,7 +7153,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7353,7 +7359,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7765,7 +7771,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8177,7 +8183,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8383,7 +8389,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8589,7 +8595,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -9001,7 +9007,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9079,7 +9085,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -9207,7 +9213,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9288,7 +9294,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ39">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR39">
         <v>1.92</v>
@@ -9491,7 +9497,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ40">
         <v>1.58</v>
@@ -9619,7 +9625,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9700,7 +9706,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ41">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR41">
         <v>1.49</v>
@@ -9825,7 +9831,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9906,7 +9912,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ42">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR42">
         <v>1.42</v>
@@ -10237,7 +10243,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10443,7 +10449,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10521,7 +10527,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ45">
         <v>1.42</v>
@@ -10855,7 +10861,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11061,7 +11067,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11267,7 +11273,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11679,7 +11685,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12297,7 +12303,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12709,7 +12715,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12787,10 +12793,10 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ56">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR56">
         <v>1.67</v>
@@ -12915,7 +12921,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13327,7 +13333,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13611,7 +13617,7 @@
         <v>0.67</v>
       </c>
       <c r="AP60">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -14232,7 +14238,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ63">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR63">
         <v>1.24</v>
@@ -14438,7 +14444,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ64">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR64">
         <v>1.67</v>
@@ -14563,7 +14569,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14975,7 +14981,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15181,7 +15187,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15259,7 +15265,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ68">
         <v>1.25</v>
@@ -16211,7 +16217,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16417,7 +16423,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16498,7 +16504,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ74">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR74">
         <v>1.25</v>
@@ -16623,7 +16629,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16829,7 +16835,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -16910,7 +16916,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ76">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR76">
         <v>1.55</v>
@@ -17113,10 +17119,10 @@
         <v>1.5</v>
       </c>
       <c r="AP77">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ77">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR77">
         <v>1.55</v>
@@ -17241,7 +17247,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17525,7 +17531,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ79">
         <v>0.33</v>
@@ -18271,7 +18277,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18761,7 +18767,7 @@
         <v>2</v>
       </c>
       <c r="AP85">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ85">
         <v>1.18</v>
@@ -18889,7 +18895,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19301,7 +19307,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19713,7 +19719,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19794,7 +19800,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ90">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR90">
         <v>1.65</v>
@@ -19919,7 +19925,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20125,7 +20131,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20331,7 +20337,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20537,7 +20543,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20618,7 +20624,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ94">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR94">
         <v>1.74</v>
@@ -20743,7 +20749,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21027,7 +21033,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ96">
         <v>1.25</v>
@@ -21155,7 +21161,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21236,7 +21242,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ97">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR97">
         <v>1.52</v>
@@ -21361,7 +21367,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21439,7 +21445,7 @@
         <v>1.4</v>
       </c>
       <c r="AP98">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ98">
         <v>1.58</v>
@@ -21567,7 +21573,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22263,7 +22269,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ102">
         <v>0.64</v>
@@ -22391,7 +22397,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22803,7 +22809,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22884,7 +22890,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ105">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR105">
         <v>1.39</v>
@@ -23009,7 +23015,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23215,7 +23221,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23421,7 +23427,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23627,7 +23633,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24323,7 +24329,7 @@
         <v>1.83</v>
       </c>
       <c r="AP112">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ112">
         <v>1.08</v>
@@ -24451,7 +24457,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24657,7 +24663,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -24735,7 +24741,7 @@
         <v>1.6</v>
       </c>
       <c r="AP114">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ114">
         <v>1.09</v>
@@ -25069,7 +25075,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25150,7 +25156,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ116">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR116">
         <v>1.1</v>
@@ -25275,7 +25281,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25481,7 +25487,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25768,7 +25774,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ119">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR119">
         <v>1.64</v>
@@ -26180,7 +26186,7 @@
         <v>2</v>
       </c>
       <c r="AQ121">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR121">
         <v>1.6</v>
@@ -26305,7 +26311,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26717,7 +26723,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27129,7 +27135,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27541,7 +27547,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27619,7 +27625,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ128">
         <v>0.82</v>
@@ -27825,7 +27831,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ129">
         <v>0.55</v>
@@ -27953,7 +27959,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28365,7 +28371,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28446,7 +28452,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ132">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR132">
         <v>1.39</v>
@@ -28571,7 +28577,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28652,7 +28658,7 @@
         <v>1</v>
       </c>
       <c r="AQ133">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR133">
         <v>1.63</v>
@@ -28777,7 +28783,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29061,7 +29067,7 @@
         <v>2.17</v>
       </c>
       <c r="AP135">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ135">
         <v>1.82</v>
@@ -29395,7 +29401,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29807,7 +29813,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30094,7 +30100,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ140">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR140">
         <v>1.48</v>
@@ -30219,7 +30225,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30631,7 +30637,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30837,7 +30843,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31121,7 +31127,7 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ145">
         <v>0.55</v>
@@ -31249,7 +31255,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31455,7 +31461,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31661,7 +31667,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -31945,7 +31951,7 @@
         <v>1.13</v>
       </c>
       <c r="AP149">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ149">
         <v>1.42</v>
@@ -32279,7 +32285,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32485,7 +32491,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32563,7 +32569,7 @@
         <v>1.43</v>
       </c>
       <c r="AP152">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ152">
         <v>1.45</v>
@@ -32772,7 +32778,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ153">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR153">
         <v>1.48</v>
@@ -32897,7 +32903,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -32978,7 +32984,7 @@
         <v>2</v>
       </c>
       <c r="AQ154">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR154">
         <v>1.58</v>
@@ -33721,7 +33727,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34339,7 +34345,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34751,7 +34757,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34957,7 +34963,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35035,7 +35041,7 @@
         <v>0.88</v>
       </c>
       <c r="AP164">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ164">
         <v>1.18</v>
@@ -35163,7 +35169,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35244,7 +35250,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ165">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR165">
         <v>1.57</v>
@@ -35447,10 +35453,10 @@
         <v>1.56</v>
       </c>
       <c r="AP166">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ166">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR166">
         <v>1.36</v>
@@ -35575,7 +35581,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -36399,7 +36405,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36480,7 +36486,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ171">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR171">
         <v>1.04</v>
@@ -36683,7 +36689,7 @@
         <v>1.5</v>
       </c>
       <c r="AP172">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ172">
         <v>1.18</v>
@@ -37017,7 +37023,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37635,7 +37641,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -38253,7 +38259,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38665,7 +38671,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38871,7 +38877,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -38949,7 +38955,7 @@
         <v>0.67</v>
       </c>
       <c r="AP183">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ183">
         <v>0.82</v>
@@ -39158,7 +39164,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ184">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR184">
         <v>1.54</v>
@@ -39489,7 +39495,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39776,7 +39782,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ187">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AR187">
         <v>1.28</v>
@@ -39901,7 +39907,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -39979,10 +39985,10 @@
         <v>1.5</v>
       </c>
       <c r="AP188">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ188">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR188">
         <v>1.43</v>
@@ -40313,7 +40319,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40391,7 +40397,7 @@
         <v>1.1</v>
       </c>
       <c r="AP190">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ190">
         <v>1.42</v>
@@ -40725,7 +40731,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41137,7 +41143,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41549,7 +41555,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41755,7 +41761,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -42167,7 +42173,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42785,7 +42791,7 @@
         <v>123</v>
       </c>
       <c r="P202" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q202">
         <v>4.3</v>
@@ -42896,13 +42902,13 @@
         <v>16</v>
       </c>
       <c r="BA202">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB202">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC202">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BD202">
         <v>2.44</v>
@@ -43102,13 +43108,13 @@
         <v>13</v>
       </c>
       <c r="BA203">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB203">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BC203">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD203">
         <v>1.82</v>
@@ -43197,7 +43203,7 @@
         <v>117</v>
       </c>
       <c r="P204" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q204">
         <v>3.1</v>
@@ -43308,13 +43314,13 @@
         <v>14</v>
       </c>
       <c r="BA204">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BB204">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC204">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="BD204">
         <v>1.75</v>
@@ -43514,13 +43520,13 @@
         <v>8</v>
       </c>
       <c r="BA205">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB205">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC205">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD205">
         <v>1.85</v>
@@ -43560,6 +43566,624 @@
       </c>
       <c r="BP205">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7502808</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45711.33333333334</v>
+      </c>
+      <c r="F206">
+        <v>23</v>
+      </c>
+      <c r="G206" t="s">
+        <v>75</v>
+      </c>
+      <c r="H206" t="s">
+        <v>85</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>2</v>
+      </c>
+      <c r="K206">
+        <v>2</v>
+      </c>
+      <c r="L206">
+        <v>1</v>
+      </c>
+      <c r="M206">
+        <v>2</v>
+      </c>
+      <c r="N206">
+        <v>3</v>
+      </c>
+      <c r="O206" t="s">
+        <v>218</v>
+      </c>
+      <c r="P206" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q206">
+        <v>3.65</v>
+      </c>
+      <c r="R206">
+        <v>1.98</v>
+      </c>
+      <c r="S206">
+        <v>3.35</v>
+      </c>
+      <c r="T206">
+        <v>1.53</v>
+      </c>
+      <c r="U206">
+        <v>2.37</v>
+      </c>
+      <c r="V206">
+        <v>3.35</v>
+      </c>
+      <c r="W206">
+        <v>1.29</v>
+      </c>
+      <c r="X206">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y206">
+        <v>1.01</v>
+      </c>
+      <c r="Z206">
+        <v>2.88</v>
+      </c>
+      <c r="AA206">
+        <v>2.9</v>
+      </c>
+      <c r="AB206">
+        <v>2.5</v>
+      </c>
+      <c r="AC206">
+        <v>1.04</v>
+      </c>
+      <c r="AD206">
+        <v>6.85</v>
+      </c>
+      <c r="AE206">
+        <v>1.44</v>
+      </c>
+      <c r="AF206">
+        <v>2.55</v>
+      </c>
+      <c r="AG206">
+        <v>2.25</v>
+      </c>
+      <c r="AH206">
+        <v>1.5</v>
+      </c>
+      <c r="AI206">
+        <v>1.97</v>
+      </c>
+      <c r="AJ206">
+        <v>1.75</v>
+      </c>
+      <c r="AK206">
+        <v>1.47</v>
+      </c>
+      <c r="AL206">
+        <v>1.34</v>
+      </c>
+      <c r="AM206">
+        <v>1.4</v>
+      </c>
+      <c r="AN206">
+        <v>1.73</v>
+      </c>
+      <c r="AO206">
+        <v>1.45</v>
+      </c>
+      <c r="AP206">
+        <v>1.58</v>
+      </c>
+      <c r="AQ206">
+        <v>1.58</v>
+      </c>
+      <c r="AR206">
+        <v>1.34</v>
+      </c>
+      <c r="AS206">
+        <v>1.46</v>
+      </c>
+      <c r="AT206">
+        <v>2.8</v>
+      </c>
+      <c r="AU206">
+        <v>8</v>
+      </c>
+      <c r="AV206">
+        <v>8</v>
+      </c>
+      <c r="AW206">
+        <v>11</v>
+      </c>
+      <c r="AX206">
+        <v>2</v>
+      </c>
+      <c r="AY206">
+        <v>19</v>
+      </c>
+      <c r="AZ206">
+        <v>10</v>
+      </c>
+      <c r="BA206">
+        <v>-1</v>
+      </c>
+      <c r="BB206">
+        <v>-1</v>
+      </c>
+      <c r="BC206">
+        <v>-1</v>
+      </c>
+      <c r="BD206">
+        <v>2.2</v>
+      </c>
+      <c r="BE206">
+        <v>8</v>
+      </c>
+      <c r="BF206">
+        <v>1.83</v>
+      </c>
+      <c r="BG206">
+        <v>1.19</v>
+      </c>
+      <c r="BH206">
+        <v>3.98</v>
+      </c>
+      <c r="BI206">
+        <v>1.38</v>
+      </c>
+      <c r="BJ206">
+        <v>2.82</v>
+      </c>
+      <c r="BK206">
+        <v>1.63</v>
+      </c>
+      <c r="BL206">
+        <v>2.18</v>
+      </c>
+      <c r="BM206">
+        <v>2.02</v>
+      </c>
+      <c r="BN206">
+        <v>1.74</v>
+      </c>
+      <c r="BO206">
+        <v>2.53</v>
+      </c>
+      <c r="BP206">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7502809</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45711.45833333334</v>
+      </c>
+      <c r="F207">
+        <v>23</v>
+      </c>
+      <c r="G207" t="s">
+        <v>72</v>
+      </c>
+      <c r="H207" t="s">
+        <v>79</v>
+      </c>
+      <c r="I207">
+        <v>1</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>1</v>
+      </c>
+      <c r="L207">
+        <v>1</v>
+      </c>
+      <c r="M207">
+        <v>1</v>
+      </c>
+      <c r="N207">
+        <v>2</v>
+      </c>
+      <c r="O207" t="s">
+        <v>156</v>
+      </c>
+      <c r="P207" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q207">
+        <v>3.45</v>
+      </c>
+      <c r="R207">
+        <v>1.95</v>
+      </c>
+      <c r="S207">
+        <v>3.6</v>
+      </c>
+      <c r="T207">
+        <v>1.55</v>
+      </c>
+      <c r="U207">
+        <v>2.33</v>
+      </c>
+      <c r="V207">
+        <v>3.4</v>
+      </c>
+      <c r="W207">
+        <v>1.28</v>
+      </c>
+      <c r="X207">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y207">
+        <v>1.01</v>
+      </c>
+      <c r="Z207">
+        <v>2.8</v>
+      </c>
+      <c r="AA207">
+        <v>2.9</v>
+      </c>
+      <c r="AB207">
+        <v>2.62</v>
+      </c>
+      <c r="AC207">
+        <v>1.06</v>
+      </c>
+      <c r="AD207">
+        <v>6.05</v>
+      </c>
+      <c r="AE207">
+        <v>1.46</v>
+      </c>
+      <c r="AF207">
+        <v>2.47</v>
+      </c>
+      <c r="AG207">
+        <v>2.3</v>
+      </c>
+      <c r="AH207">
+        <v>1.5</v>
+      </c>
+      <c r="AI207">
+        <v>2</v>
+      </c>
+      <c r="AJ207">
+        <v>1.73</v>
+      </c>
+      <c r="AK207">
+        <v>1.41</v>
+      </c>
+      <c r="AL207">
+        <v>1.36</v>
+      </c>
+      <c r="AM207">
+        <v>1.44</v>
+      </c>
+      <c r="AN207">
+        <v>1.73</v>
+      </c>
+      <c r="AO207">
+        <v>1.45</v>
+      </c>
+      <c r="AP207">
+        <v>1.67</v>
+      </c>
+      <c r="AQ207">
+        <v>1.42</v>
+      </c>
+      <c r="AR207">
+        <v>1.41</v>
+      </c>
+      <c r="AS207">
+        <v>1.18</v>
+      </c>
+      <c r="AT207">
+        <v>2.59</v>
+      </c>
+      <c r="AU207">
+        <v>3</v>
+      </c>
+      <c r="AV207">
+        <v>5</v>
+      </c>
+      <c r="AW207">
+        <v>3</v>
+      </c>
+      <c r="AX207">
+        <v>8</v>
+      </c>
+      <c r="AY207">
+        <v>6</v>
+      </c>
+      <c r="AZ207">
+        <v>13</v>
+      </c>
+      <c r="BA207">
+        <v>-1</v>
+      </c>
+      <c r="BB207">
+        <v>-1</v>
+      </c>
+      <c r="BC207">
+        <v>-1</v>
+      </c>
+      <c r="BD207">
+        <v>1.83</v>
+      </c>
+      <c r="BE207">
+        <v>8</v>
+      </c>
+      <c r="BF207">
+        <v>2.2</v>
+      </c>
+      <c r="BG207">
+        <v>1.2</v>
+      </c>
+      <c r="BH207">
+        <v>3.82</v>
+      </c>
+      <c r="BI207">
+        <v>1.4</v>
+      </c>
+      <c r="BJ207">
+        <v>2.72</v>
+      </c>
+      <c r="BK207">
+        <v>1.68</v>
+      </c>
+      <c r="BL207">
+        <v>2.11</v>
+      </c>
+      <c r="BM207">
+        <v>2.09</v>
+      </c>
+      <c r="BN207">
+        <v>1.69</v>
+      </c>
+      <c r="BO207">
+        <v>2.63</v>
+      </c>
+      <c r="BP207">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7502807</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45711.52083333334</v>
+      </c>
+      <c r="F208">
+        <v>23</v>
+      </c>
+      <c r="G208" t="s">
+        <v>73</v>
+      </c>
+      <c r="H208" t="s">
+        <v>87</v>
+      </c>
+      <c r="I208">
+        <v>1</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>1</v>
+      </c>
+      <c r="L208">
+        <v>1</v>
+      </c>
+      <c r="M208">
+        <v>1</v>
+      </c>
+      <c r="N208">
+        <v>2</v>
+      </c>
+      <c r="O208" t="s">
+        <v>197</v>
+      </c>
+      <c r="P208" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q208">
+        <v>3.5</v>
+      </c>
+      <c r="R208">
+        <v>1.95</v>
+      </c>
+      <c r="S208">
+        <v>3.4</v>
+      </c>
+      <c r="T208">
+        <v>1.53</v>
+      </c>
+      <c r="U208">
+        <v>2.38</v>
+      </c>
+      <c r="V208">
+        <v>3.5</v>
+      </c>
+      <c r="W208">
+        <v>1.29</v>
+      </c>
+      <c r="X208">
+        <v>11</v>
+      </c>
+      <c r="Y208">
+        <v>1.05</v>
+      </c>
+      <c r="Z208">
+        <v>2.7</v>
+      </c>
+      <c r="AA208">
+        <v>3</v>
+      </c>
+      <c r="AB208">
+        <v>2.62</v>
+      </c>
+      <c r="AC208">
+        <v>1.09</v>
+      </c>
+      <c r="AD208">
+        <v>6.5</v>
+      </c>
+      <c r="AE208">
+        <v>1.43</v>
+      </c>
+      <c r="AF208">
+        <v>2.6</v>
+      </c>
+      <c r="AG208">
+        <v>2.3</v>
+      </c>
+      <c r="AH208">
+        <v>1.5</v>
+      </c>
+      <c r="AI208">
+        <v>2</v>
+      </c>
+      <c r="AJ208">
+        <v>1.73</v>
+      </c>
+      <c r="AK208">
+        <v>1.47</v>
+      </c>
+      <c r="AL208">
+        <v>1.35</v>
+      </c>
+      <c r="AM208">
+        <v>1.43</v>
+      </c>
+      <c r="AN208">
+        <v>1.8</v>
+      </c>
+      <c r="AO208">
+        <v>1.45</v>
+      </c>
+      <c r="AP208">
+        <v>1.73</v>
+      </c>
+      <c r="AQ208">
+        <v>1.42</v>
+      </c>
+      <c r="AR208">
+        <v>1.4</v>
+      </c>
+      <c r="AS208">
+        <v>1.36</v>
+      </c>
+      <c r="AT208">
+        <v>2.76</v>
+      </c>
+      <c r="AU208">
+        <v>2</v>
+      </c>
+      <c r="AV208">
+        <v>3</v>
+      </c>
+      <c r="AW208">
+        <v>2</v>
+      </c>
+      <c r="AX208">
+        <v>4</v>
+      </c>
+      <c r="AY208">
+        <v>4</v>
+      </c>
+      <c r="AZ208">
+        <v>7</v>
+      </c>
+      <c r="BA208">
+        <v>-1</v>
+      </c>
+      <c r="BB208">
+        <v>-1</v>
+      </c>
+      <c r="BC208">
+        <v>-1</v>
+      </c>
+      <c r="BD208">
+        <v>2.05</v>
+      </c>
+      <c r="BE208">
+        <v>8</v>
+      </c>
+      <c r="BF208">
+        <v>1.95</v>
+      </c>
+      <c r="BG208">
+        <v>1.21</v>
+      </c>
+      <c r="BH208">
+        <v>3.75</v>
+      </c>
+      <c r="BI208">
+        <v>1.41</v>
+      </c>
+      <c r="BJ208">
+        <v>2.68</v>
+      </c>
+      <c r="BK208">
+        <v>1.69</v>
+      </c>
+      <c r="BL208">
+        <v>2.09</v>
+      </c>
+      <c r="BM208">
+        <v>2.11</v>
+      </c>
+      <c r="BN208">
+        <v>1.68</v>
+      </c>
+      <c r="BO208">
+        <v>2.67</v>
+      </c>
+      <c r="BP208">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -43726,13 +43726,13 @@
         <v>10</v>
       </c>
       <c r="BA206">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB206">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC206">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD206">
         <v>2.2</v>
@@ -43932,13 +43932,13 @@
         <v>13</v>
       </c>
       <c r="BA207">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB207">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BC207">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="BD207">
         <v>1.83</v>
@@ -44138,13 +44138,13 @@
         <v>7</v>
       </c>
       <c r="BA208">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BB208">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC208">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD208">
         <v>2.05</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="321">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -975,6 +975,9 @@
   <si>
     <t>['18', '37']</t>
   </si>
+  <si>
+    <t>['50', '74']</t>
+  </si>
 </sst>
 </file>
 
@@ -1335,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2084,7 +2087,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ4">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -4759,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ17">
         <v>0.64</v>
@@ -8264,7 +8267,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ34">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR34">
         <v>1.57</v>
@@ -8673,7 +8676,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ36">
         <v>0.55</v>
@@ -10939,7 +10942,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ47">
         <v>1.45</v>
@@ -11148,7 +11151,7 @@
         <v>1</v>
       </c>
       <c r="AQ48">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR48">
         <v>1.74</v>
@@ -15677,7 +15680,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ70">
         <v>1.18</v>
@@ -18561,7 +18564,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ84">
         <v>1.36</v>
@@ -18770,7 +18773,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ85">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -21654,7 +21657,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ99">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR99">
         <v>1.34</v>
@@ -23920,7 +23923,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ110">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR110">
         <v>1.51</v>
@@ -25565,7 +25568,7 @@
         <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ118">
         <v>0.33</v>
@@ -26598,7 +26601,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ123">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR123">
         <v>1.21</v>
@@ -28449,7 +28452,7 @@
         <v>1.86</v>
       </c>
       <c r="AP132">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ132">
         <v>1.42</v>
@@ -29482,7 +29485,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ137">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR137">
         <v>1.18</v>
@@ -30303,7 +30306,7 @@
         <v>2.29</v>
       </c>
       <c r="AP141">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ141">
         <v>1.82</v>
@@ -33393,7 +33396,7 @@
         <v>1.33</v>
       </c>
       <c r="AP156">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ156">
         <v>1.08</v>
@@ -36692,7 +36695,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ172">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR172">
         <v>1.3</v>
@@ -37516,7 +37519,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ176">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR176">
         <v>1.68</v>
@@ -38337,7 +38340,7 @@
         <v>1.4</v>
       </c>
       <c r="AP180">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ180">
         <v>1.25</v>
@@ -40603,7 +40606,7 @@
         <v>1.2</v>
       </c>
       <c r="AP191">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ191">
         <v>1.09</v>
@@ -41224,7 +41227,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ194">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR194">
         <v>1.3</v>
@@ -44184,6 +44187,212 @@
       </c>
       <c r="BP208">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7502816</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45716.71875</v>
+      </c>
+      <c r="F209">
+        <v>24</v>
+      </c>
+      <c r="G209" t="s">
+        <v>85</v>
+      </c>
+      <c r="H209" t="s">
+        <v>86</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>1</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209">
+        <v>2</v>
+      </c>
+      <c r="N209">
+        <v>3</v>
+      </c>
+      <c r="O209" t="s">
+        <v>129</v>
+      </c>
+      <c r="P209" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q209">
+        <v>2.4</v>
+      </c>
+      <c r="R209">
+        <v>2.2</v>
+      </c>
+      <c r="S209">
+        <v>4.7</v>
+      </c>
+      <c r="T209">
+        <v>1.4</v>
+      </c>
+      <c r="U209">
+        <v>2.75</v>
+      </c>
+      <c r="V209">
+        <v>2.75</v>
+      </c>
+      <c r="W209">
+        <v>1.4</v>
+      </c>
+      <c r="X209">
+        <v>7.1</v>
+      </c>
+      <c r="Y209">
+        <v>1.04</v>
+      </c>
+      <c r="Z209">
+        <v>1.8</v>
+      </c>
+      <c r="AA209">
+        <v>3.4</v>
+      </c>
+      <c r="AB209">
+        <v>4.2</v>
+      </c>
+      <c r="AC209">
+        <v>1</v>
+      </c>
+      <c r="AD209">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE209">
+        <v>1.3</v>
+      </c>
+      <c r="AF209">
+        <v>3.2</v>
+      </c>
+      <c r="AG209">
+        <v>1.85</v>
+      </c>
+      <c r="AH209">
+        <v>1.75</v>
+      </c>
+      <c r="AI209">
+        <v>1.81</v>
+      </c>
+      <c r="AJ209">
+        <v>1.9</v>
+      </c>
+      <c r="AK209">
+        <v>1.22</v>
+      </c>
+      <c r="AL209">
+        <v>1.27</v>
+      </c>
+      <c r="AM209">
+        <v>1.88</v>
+      </c>
+      <c r="AN209">
+        <v>1.73</v>
+      </c>
+      <c r="AO209">
+        <v>1.18</v>
+      </c>
+      <c r="AP209">
+        <v>1.58</v>
+      </c>
+      <c r="AQ209">
+        <v>1.33</v>
+      </c>
+      <c r="AR209">
+        <v>1.53</v>
+      </c>
+      <c r="AS209">
+        <v>1.48</v>
+      </c>
+      <c r="AT209">
+        <v>3.01</v>
+      </c>
+      <c r="AU209">
+        <v>7</v>
+      </c>
+      <c r="AV209">
+        <v>6</v>
+      </c>
+      <c r="AW209">
+        <v>10</v>
+      </c>
+      <c r="AX209">
+        <v>7</v>
+      </c>
+      <c r="AY209">
+        <v>17</v>
+      </c>
+      <c r="AZ209">
+        <v>13</v>
+      </c>
+      <c r="BA209">
+        <v>3</v>
+      </c>
+      <c r="BB209">
+        <v>6</v>
+      </c>
+      <c r="BC209">
+        <v>9</v>
+      </c>
+      <c r="BD209">
+        <v>1.61</v>
+      </c>
+      <c r="BE209">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF209">
+        <v>2.71</v>
+      </c>
+      <c r="BG209">
+        <v>1.18</v>
+      </c>
+      <c r="BH209">
+        <v>3.85</v>
+      </c>
+      <c r="BI209">
+        <v>1.38</v>
+      </c>
+      <c r="BJ209">
+        <v>2.71</v>
+      </c>
+      <c r="BK209">
+        <v>1.69</v>
+      </c>
+      <c r="BL209">
+        <v>2.04</v>
+      </c>
+      <c r="BM209">
+        <v>2.12</v>
+      </c>
+      <c r="BN209">
+        <v>1.61</v>
+      </c>
+      <c r="BO209">
+        <v>2.74</v>
+      </c>
+      <c r="BP209">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="324">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -673,6 +673,12 @@
     <t>['83']</t>
   </si>
   <si>
+    <t>['21', '90+5']</t>
+  </si>
+  <si>
+    <t>['25', '51']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -977,6 +983,9 @@
   </si>
   <si>
     <t>['50', '74']</t>
+  </si>
+  <si>
+    <t>['50', '90']</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP209"/>
+  <dimension ref="A1:BP212"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1594,7 +1603,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1800,7 +1809,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -2006,7 +2015,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2290,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ5">
         <v>1.58</v>
@@ -2418,7 +2427,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2624,7 +2633,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3036,7 +3045,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3448,7 +3457,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3526,10 +3535,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ11">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3735,7 +3744,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ12">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3860,7 +3869,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4066,7 +4075,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4272,7 +4281,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4478,7 +4487,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4971,7 +4980,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ18">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5096,7 +5105,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5174,7 +5183,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ19">
         <v>0.33</v>
@@ -5302,7 +5311,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5920,7 +5929,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6204,7 +6213,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ24">
         <v>0.33</v>
@@ -6332,7 +6341,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6744,7 +6753,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7156,7 +7165,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7234,7 +7243,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ29">
         <v>1.08</v>
@@ -7362,7 +7371,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7646,10 +7655,10 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ31">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR31">
         <v>1.31</v>
@@ -7774,7 +7783,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7855,7 +7864,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ32">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR32">
         <v>2.27</v>
@@ -8186,7 +8195,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8392,7 +8401,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8598,7 +8607,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8679,7 +8688,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ36">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR36">
         <v>0.91</v>
@@ -9010,7 +9019,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9216,7 +9225,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9500,7 +9509,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ40">
         <v>1.58</v>
@@ -9628,7 +9637,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9834,7 +9843,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10246,7 +10255,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10452,7 +10461,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10864,7 +10873,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10945,7 +10954,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ47">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR47">
         <v>1.36</v>
@@ -11070,7 +11079,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11276,7 +11285,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11560,7 +11569,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ50">
         <v>1.08</v>
@@ -11688,7 +11697,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -11769,7 +11778,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ51">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR51">
         <v>1.12</v>
@@ -12178,7 +12187,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ53">
         <v>0.64</v>
@@ -12306,7 +12315,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12593,7 +12602,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ55">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR55">
         <v>1.78</v>
@@ -12718,7 +12727,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12924,7 +12933,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13336,7 +13345,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -14572,7 +14581,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14653,7 +14662,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ65">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR65">
         <v>1.18</v>
@@ -14856,7 +14865,7 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ66">
         <v>0.64</v>
@@ -14984,7 +14993,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15062,7 +15071,7 @@
         <v>3</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ67">
         <v>1.82</v>
@@ -15190,7 +15199,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15268,7 +15277,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ68">
         <v>1.25</v>
@@ -15477,7 +15486,7 @@
         <v>1</v>
       </c>
       <c r="AQ69">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR69">
         <v>1.69</v>
@@ -15889,7 +15898,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ71">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR71">
         <v>0.8</v>
@@ -16220,7 +16229,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16426,7 +16435,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16632,7 +16641,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16838,7 +16847,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17250,7 +17259,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17946,7 +17955,7 @@
         <v>1.25</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ81">
         <v>1.18</v>
@@ -18280,7 +18289,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18770,7 +18779,7 @@
         <v>2</v>
       </c>
       <c r="AP85">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ85">
         <v>1.33</v>
@@ -18898,7 +18907,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -18979,7 +18988,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ86">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR86">
         <v>1.78</v>
@@ -19310,7 +19319,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19391,7 +19400,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ88">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR88">
         <v>1.05</v>
@@ -19594,7 +19603,7 @@
         <v>0.33</v>
       </c>
       <c r="AP89">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ89">
         <v>0.82</v>
@@ -19722,7 +19731,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19928,7 +19937,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20009,7 +20018,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ91">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR91">
         <v>1.19</v>
@@ -20134,7 +20143,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20340,7 +20349,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20546,7 +20555,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20752,7 +20761,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21164,7 +21173,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21370,7 +21379,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21576,7 +21585,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22272,7 +22281,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ102">
         <v>0.64</v>
@@ -22400,7 +22409,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22481,7 +22490,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ103">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR103">
         <v>1.71</v>
@@ -22812,7 +22821,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -23018,7 +23027,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23096,7 +23105,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ106">
         <v>1.42</v>
@@ -23224,7 +23233,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23305,7 +23314,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ107">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR107">
         <v>1.21</v>
@@ -23430,7 +23439,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23508,7 +23517,7 @@
         <v>1.4</v>
       </c>
       <c r="AP108">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ108">
         <v>1.36</v>
@@ -23636,7 +23645,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24460,7 +24469,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24666,7 +24675,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -24747,7 +24756,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ114">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR114">
         <v>1.37</v>
@@ -25078,7 +25087,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25284,7 +25293,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25490,7 +25499,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -26186,7 +26195,7 @@
         <v>1.86</v>
       </c>
       <c r="AP121">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ121">
         <v>1.58</v>
@@ -26314,7 +26323,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26726,7 +26735,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27010,7 +27019,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -27138,7 +27147,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27219,7 +27228,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ126">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -27550,7 +27559,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27628,7 +27637,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ128">
         <v>0.82</v>
@@ -27837,7 +27846,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ129">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR129">
         <v>1.3</v>
@@ -27962,7 +27971,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28374,7 +28383,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28580,7 +28589,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28786,7 +28795,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29279,7 +29288,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ136">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR136">
         <v>1.47</v>
@@ -29404,7 +29413,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29816,7 +29825,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30228,7 +30237,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30640,7 +30649,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30718,7 +30727,7 @@
         <v>1.63</v>
       </c>
       <c r="AP143">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ143">
         <v>1.58</v>
@@ -30846,7 +30855,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -30927,7 +30936,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ144">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR144">
         <v>1.17</v>
@@ -31133,7 +31142,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ145">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR145">
         <v>1.33</v>
@@ -31258,7 +31267,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31464,7 +31473,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31670,7 +31679,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -31954,7 +31963,7 @@
         <v>1.13</v>
       </c>
       <c r="AP149">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ149">
         <v>1.42</v>
@@ -32288,7 +32297,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32494,7 +32503,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32575,7 +32584,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ152">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR152">
         <v>1.34</v>
@@ -32906,7 +32915,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -32984,7 +32993,7 @@
         <v>1.75</v>
       </c>
       <c r="AP154">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ154">
         <v>1.42</v>
@@ -33602,7 +33611,7 @@
         <v>0.33</v>
       </c>
       <c r="AP157">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ157">
         <v>0.33</v>
@@ -33730,7 +33739,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -33811,7 +33820,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ158">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR158">
         <v>1.37</v>
@@ -34017,7 +34026,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ159">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR159">
         <v>1.72</v>
@@ -34348,7 +34357,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34429,7 +34438,7 @@
         <v>1</v>
       </c>
       <c r="AQ161">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR161">
         <v>1.7</v>
@@ -34632,7 +34641,7 @@
         <v>1.44</v>
       </c>
       <c r="AP162">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ162">
         <v>1.25</v>
@@ -34760,7 +34769,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34966,7 +34975,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35044,7 +35053,7 @@
         <v>0.88</v>
       </c>
       <c r="AP164">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ164">
         <v>1.18</v>
@@ -35172,7 +35181,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35584,7 +35593,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -36408,7 +36417,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -37026,7 +37035,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37107,7 +37116,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ174">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR174">
         <v>1.73</v>
@@ -37310,7 +37319,7 @@
         <v>2.22</v>
       </c>
       <c r="AP175">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ175">
         <v>1.82</v>
@@ -37644,7 +37653,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -37931,7 +37940,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ178">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR178">
         <v>1.35</v>
@@ -38137,7 +38146,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ179">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR179">
         <v>1.25</v>
@@ -38262,7 +38271,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38546,7 +38555,7 @@
         <v>1.6</v>
       </c>
       <c r="AP181">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ181">
         <v>1.58</v>
@@ -38674,7 +38683,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38880,7 +38889,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39498,7 +39507,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39910,7 +39919,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -39988,7 +39997,7 @@
         <v>1.5</v>
       </c>
       <c r="AP188">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ188">
         <v>1.42</v>
@@ -40322,7 +40331,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40609,7 +40618,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ191">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR191">
         <v>1.47</v>
@@ -40734,7 +40743,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41018,10 +41027,10 @@
         <v>0.6</v>
       </c>
       <c r="AP193">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ193">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR193">
         <v>1.6</v>
@@ -41146,7 +41155,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41558,7 +41567,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41639,7 +41648,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ196">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR196">
         <v>1.34</v>
@@ -41764,7 +41773,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -42048,7 +42057,7 @@
         <v>1.36</v>
       </c>
       <c r="AP198">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ198">
         <v>1.25</v>
@@ -42176,7 +42185,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42794,7 +42803,7 @@
         <v>123</v>
       </c>
       <c r="P202" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q202">
         <v>4.3</v>
@@ -43206,7 +43215,7 @@
         <v>117</v>
       </c>
       <c r="P204" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q204">
         <v>3.1</v>
@@ -43618,7 +43627,7 @@
         <v>218</v>
       </c>
       <c r="P206" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q206">
         <v>3.65</v>
@@ -43824,7 +43833,7 @@
         <v>156</v>
       </c>
       <c r="P207" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q207">
         <v>3.45</v>
@@ -44030,7 +44039,7 @@
         <v>197</v>
       </c>
       <c r="P208" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q208">
         <v>3.5</v>
@@ -44108,7 +44117,7 @@
         <v>1.45</v>
       </c>
       <c r="AP208">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ208">
         <v>1.42</v>
@@ -44236,7 +44245,7 @@
         <v>129</v>
       </c>
       <c r="P209" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q209">
         <v>2.4</v>
@@ -44393,6 +44402,624 @@
       </c>
       <c r="BP209">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7502811</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45717.33333333334</v>
+      </c>
+      <c r="F210">
+        <v>24</v>
+      </c>
+      <c r="G210" t="s">
+        <v>73</v>
+      </c>
+      <c r="H210" t="s">
+        <v>78</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="M210">
+        <v>0</v>
+      </c>
+      <c r="N210">
+        <v>0</v>
+      </c>
+      <c r="O210" t="s">
+        <v>89</v>
+      </c>
+      <c r="P210" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q210">
+        <v>3.2</v>
+      </c>
+      <c r="R210">
+        <v>2.02</v>
+      </c>
+      <c r="S210">
+        <v>3.65</v>
+      </c>
+      <c r="T210">
+        <v>1.5</v>
+      </c>
+      <c r="U210">
+        <v>2.45</v>
+      </c>
+      <c r="V210">
+        <v>3.15</v>
+      </c>
+      <c r="W210">
+        <v>1.31</v>
+      </c>
+      <c r="X210">
+        <v>8.9</v>
+      </c>
+      <c r="Y210">
+        <v>1.01</v>
+      </c>
+      <c r="Z210">
+        <v>2.5</v>
+      </c>
+      <c r="AA210">
+        <v>3</v>
+      </c>
+      <c r="AB210">
+        <v>2.8</v>
+      </c>
+      <c r="AC210">
+        <v>1.02</v>
+      </c>
+      <c r="AD210">
+        <v>7.9</v>
+      </c>
+      <c r="AE210">
+        <v>1.4</v>
+      </c>
+      <c r="AF210">
+        <v>2.7</v>
+      </c>
+      <c r="AG210">
+        <v>2.1</v>
+      </c>
+      <c r="AH210">
+        <v>1.6</v>
+      </c>
+      <c r="AI210">
+        <v>1.9</v>
+      </c>
+      <c r="AJ210">
+        <v>1.81</v>
+      </c>
+      <c r="AK210">
+        <v>1.4</v>
+      </c>
+      <c r="AL210">
+        <v>1.32</v>
+      </c>
+      <c r="AM210">
+        <v>1.51</v>
+      </c>
+      <c r="AN210">
+        <v>1.73</v>
+      </c>
+      <c r="AO210">
+        <v>1.09</v>
+      </c>
+      <c r="AP210">
+        <v>1.67</v>
+      </c>
+      <c r="AQ210">
+        <v>1.08</v>
+      </c>
+      <c r="AR210">
+        <v>1.34</v>
+      </c>
+      <c r="AS210">
+        <v>1.52</v>
+      </c>
+      <c r="AT210">
+        <v>2.86</v>
+      </c>
+      <c r="AU210">
+        <v>0</v>
+      </c>
+      <c r="AV210">
+        <v>6</v>
+      </c>
+      <c r="AW210">
+        <v>4</v>
+      </c>
+      <c r="AX210">
+        <v>6</v>
+      </c>
+      <c r="AY210">
+        <v>4</v>
+      </c>
+      <c r="AZ210">
+        <v>12</v>
+      </c>
+      <c r="BA210">
+        <v>-1</v>
+      </c>
+      <c r="BB210">
+        <v>-1</v>
+      </c>
+      <c r="BC210">
+        <v>-1</v>
+      </c>
+      <c r="BD210">
+        <v>2.13</v>
+      </c>
+      <c r="BE210">
+        <v>6.55</v>
+      </c>
+      <c r="BF210">
+        <v>2.07</v>
+      </c>
+      <c r="BG210">
+        <v>1.16</v>
+      </c>
+      <c r="BH210">
+        <v>4.2</v>
+      </c>
+      <c r="BI210">
+        <v>1.32</v>
+      </c>
+      <c r="BJ210">
+        <v>2.88</v>
+      </c>
+      <c r="BK210">
+        <v>1.6</v>
+      </c>
+      <c r="BL210">
+        <v>2.14</v>
+      </c>
+      <c r="BM210">
+        <v>2.02</v>
+      </c>
+      <c r="BN210">
+        <v>1.71</v>
+      </c>
+      <c r="BO210">
+        <v>2.6</v>
+      </c>
+      <c r="BP210">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7502812</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45717.45833333334</v>
+      </c>
+      <c r="F211">
+        <v>24</v>
+      </c>
+      <c r="G211" t="s">
+        <v>79</v>
+      </c>
+      <c r="H211" t="s">
+        <v>71</v>
+      </c>
+      <c r="I211">
+        <v>1</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>1</v>
+      </c>
+      <c r="L211">
+        <v>2</v>
+      </c>
+      <c r="M211">
+        <v>0</v>
+      </c>
+      <c r="N211">
+        <v>2</v>
+      </c>
+      <c r="O211" t="s">
+        <v>219</v>
+      </c>
+      <c r="P211" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q211">
+        <v>2.42</v>
+      </c>
+      <c r="R211">
+        <v>2.1</v>
+      </c>
+      <c r="S211">
+        <v>5</v>
+      </c>
+      <c r="T211">
+        <v>1.46</v>
+      </c>
+      <c r="U211">
+        <v>2.55</v>
+      </c>
+      <c r="V211">
+        <v>3.05</v>
+      </c>
+      <c r="W211">
+        <v>1.33</v>
+      </c>
+      <c r="X211">
+        <v>8.1</v>
+      </c>
+      <c r="Y211">
+        <v>1.02</v>
+      </c>
+      <c r="Z211">
+        <v>1.73</v>
+      </c>
+      <c r="AA211">
+        <v>3.4</v>
+      </c>
+      <c r="AB211">
+        <v>4.6</v>
+      </c>
+      <c r="AC211">
+        <v>1.02</v>
+      </c>
+      <c r="AD211">
+        <v>7.9</v>
+      </c>
+      <c r="AE211">
+        <v>1.38</v>
+      </c>
+      <c r="AF211">
+        <v>2.8</v>
+      </c>
+      <c r="AG211">
+        <v>2.05</v>
+      </c>
+      <c r="AH211">
+        <v>1.61</v>
+      </c>
+      <c r="AI211">
+        <v>2</v>
+      </c>
+      <c r="AJ211">
+        <v>1.73</v>
+      </c>
+      <c r="AK211">
+        <v>1.2</v>
+      </c>
+      <c r="AL211">
+        <v>1.27</v>
+      </c>
+      <c r="AM211">
+        <v>1.91</v>
+      </c>
+      <c r="AN211">
+        <v>2</v>
+      </c>
+      <c r="AO211">
+        <v>0.55</v>
+      </c>
+      <c r="AP211">
+        <v>2.08</v>
+      </c>
+      <c r="AQ211">
+        <v>0.5</v>
+      </c>
+      <c r="AR211">
+        <v>1.57</v>
+      </c>
+      <c r="AS211">
+        <v>1.21</v>
+      </c>
+      <c r="AT211">
+        <v>2.78</v>
+      </c>
+      <c r="AU211">
+        <v>3</v>
+      </c>
+      <c r="AV211">
+        <v>7</v>
+      </c>
+      <c r="AW211">
+        <v>4</v>
+      </c>
+      <c r="AX211">
+        <v>6</v>
+      </c>
+      <c r="AY211">
+        <v>7</v>
+      </c>
+      <c r="AZ211">
+        <v>13</v>
+      </c>
+      <c r="BA211">
+        <v>-1</v>
+      </c>
+      <c r="BB211">
+        <v>-1</v>
+      </c>
+      <c r="BC211">
+        <v>-1</v>
+      </c>
+      <c r="BD211">
+        <v>1.5</v>
+      </c>
+      <c r="BE211">
+        <v>7.1</v>
+      </c>
+      <c r="BF211">
+        <v>3.35</v>
+      </c>
+      <c r="BG211">
+        <v>1.16</v>
+      </c>
+      <c r="BH211">
+        <v>4.15</v>
+      </c>
+      <c r="BI211">
+        <v>1.33</v>
+      </c>
+      <c r="BJ211">
+        <v>2.83</v>
+      </c>
+      <c r="BK211">
+        <v>1.61</v>
+      </c>
+      <c r="BL211">
+        <v>2.12</v>
+      </c>
+      <c r="BM211">
+        <v>2.03</v>
+      </c>
+      <c r="BN211">
+        <v>1.7</v>
+      </c>
+      <c r="BO211">
+        <v>2.64</v>
+      </c>
+      <c r="BP211">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7502813</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45717.52083333334</v>
+      </c>
+      <c r="F212">
+        <v>24</v>
+      </c>
+      <c r="G212" t="s">
+        <v>87</v>
+      </c>
+      <c r="H212" t="s">
+        <v>75</v>
+      </c>
+      <c r="I212">
+        <v>1</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212">
+        <v>2</v>
+      </c>
+      <c r="M212">
+        <v>2</v>
+      </c>
+      <c r="N212">
+        <v>4</v>
+      </c>
+      <c r="O212" t="s">
+        <v>220</v>
+      </c>
+      <c r="P212" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q212">
+        <v>2.43</v>
+      </c>
+      <c r="R212">
+        <v>2.04</v>
+      </c>
+      <c r="S212">
+        <v>4.95</v>
+      </c>
+      <c r="T212">
+        <v>1.46</v>
+      </c>
+      <c r="U212">
+        <v>2.56</v>
+      </c>
+      <c r="V212">
+        <v>3.15</v>
+      </c>
+      <c r="W212">
+        <v>1.32</v>
+      </c>
+      <c r="X212">
+        <v>7.8</v>
+      </c>
+      <c r="Y212">
+        <v>1.03</v>
+      </c>
+      <c r="Z212">
+        <v>1.87</v>
+      </c>
+      <c r="AA212">
+        <v>3.25</v>
+      </c>
+      <c r="AB212">
+        <v>4</v>
+      </c>
+      <c r="AC212">
+        <v>1.03</v>
+      </c>
+      <c r="AD212">
+        <v>7.4</v>
+      </c>
+      <c r="AE212">
+        <v>1.35</v>
+      </c>
+      <c r="AF212">
+        <v>2.75</v>
+      </c>
+      <c r="AG212">
+        <v>2.1</v>
+      </c>
+      <c r="AH212">
+        <v>1.61</v>
+      </c>
+      <c r="AI212">
+        <v>1.99</v>
+      </c>
+      <c r="AJ212">
+        <v>1.73</v>
+      </c>
+      <c r="AK212">
+        <v>1.2</v>
+      </c>
+      <c r="AL212">
+        <v>1.28</v>
+      </c>
+      <c r="AM212">
+        <v>1.92</v>
+      </c>
+      <c r="AN212">
+        <v>2.18</v>
+      </c>
+      <c r="AO212">
+        <v>1.45</v>
+      </c>
+      <c r="AP212">
+        <v>2.08</v>
+      </c>
+      <c r="AQ212">
+        <v>1.42</v>
+      </c>
+      <c r="AR212">
+        <v>1.61</v>
+      </c>
+      <c r="AS212">
+        <v>1.39</v>
+      </c>
+      <c r="AT212">
+        <v>3</v>
+      </c>
+      <c r="AU212">
+        <v>3</v>
+      </c>
+      <c r="AV212">
+        <v>5</v>
+      </c>
+      <c r="AW212">
+        <v>6</v>
+      </c>
+      <c r="AX212">
+        <v>4</v>
+      </c>
+      <c r="AY212">
+        <v>9</v>
+      </c>
+      <c r="AZ212">
+        <v>9</v>
+      </c>
+      <c r="BA212">
+        <v>-1</v>
+      </c>
+      <c r="BB212">
+        <v>-1</v>
+      </c>
+      <c r="BC212">
+        <v>-1</v>
+      </c>
+      <c r="BD212">
+        <v>1.41</v>
+      </c>
+      <c r="BE212">
+        <v>7.4</v>
+      </c>
+      <c r="BF212">
+        <v>3.82</v>
+      </c>
+      <c r="BG212">
+        <v>1.17</v>
+      </c>
+      <c r="BH212">
+        <v>4.05</v>
+      </c>
+      <c r="BI212">
+        <v>1.34</v>
+      </c>
+      <c r="BJ212">
+        <v>2.78</v>
+      </c>
+      <c r="BK212">
+        <v>1.63</v>
+      </c>
+      <c r="BL212">
+        <v>2.09</v>
+      </c>
+      <c r="BM212">
+        <v>2.07</v>
+      </c>
+      <c r="BN212">
+        <v>1.67</v>
+      </c>
+      <c r="BO212">
+        <v>2.67</v>
+      </c>
+      <c r="BP212">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="326">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -679,6 +679,9 @@
     <t>['25', '51']</t>
   </si>
   <si>
+    <t>['87', '90+3']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -986,6 +989,9 @@
   </si>
   <si>
     <t>['50', '90']</t>
+  </si>
+  <si>
+    <t>['29']</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP212"/>
+  <dimension ref="A1:BP213"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1603,7 +1609,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1809,7 +1815,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -2015,7 +2021,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2427,7 +2433,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2633,7 +2639,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3045,7 +3051,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3457,7 +3463,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3869,7 +3875,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3947,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ13">
         <v>1.58</v>
@@ -4075,7 +4081,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4281,7 +4287,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4487,7 +4493,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4774,7 +4780,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ17">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5105,7 +5111,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5311,7 +5317,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5929,7 +5935,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6341,7 +6347,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6753,7 +6759,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7165,7 +7171,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7371,7 +7377,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7452,7 +7458,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ30">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR30">
         <v>1.33</v>
@@ -7783,7 +7789,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8067,7 +8073,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ33">
         <v>1.25</v>
@@ -8195,7 +8201,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8401,7 +8407,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8607,7 +8613,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -9019,7 +9025,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9225,7 +9231,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9637,7 +9643,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9843,7 +9849,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10255,7 +10261,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10461,7 +10467,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10873,7 +10879,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11079,7 +11085,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11285,7 +11291,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11363,7 +11369,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ49">
         <v>1.82</v>
@@ -11697,7 +11703,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12190,7 +12196,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ53">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR53">
         <v>1.6</v>
@@ -12315,7 +12321,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12727,7 +12733,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12933,7 +12939,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13345,7 +13351,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -14581,7 +14587,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14868,7 +14874,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ66">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR66">
         <v>1.24</v>
@@ -14993,7 +14999,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15199,7 +15205,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -16229,7 +16235,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16435,7 +16441,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16641,7 +16647,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16847,7 +16853,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17259,7 +17265,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -18161,7 +18167,7 @@
         <v>1.6</v>
       </c>
       <c r="AP82">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ82">
         <v>1.42</v>
@@ -18289,7 +18295,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18907,7 +18913,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19194,7 +19200,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ87">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR87">
         <v>1.38</v>
@@ -19319,7 +19325,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19731,7 +19737,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19937,7 +19943,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20143,7 +20149,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20349,7 +20355,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20555,7 +20561,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20761,7 +20767,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21173,7 +21179,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21379,7 +21385,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21585,7 +21591,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -21663,7 +21669,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ99">
         <v>1.33</v>
@@ -22284,7 +22290,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ102">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR102">
         <v>1.5</v>
@@ -22409,7 +22415,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22821,7 +22827,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22899,7 +22905,7 @@
         <v>1.67</v>
       </c>
       <c r="AP105">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ105">
         <v>1.58</v>
@@ -23027,7 +23033,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23233,7 +23239,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23439,7 +23445,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23645,7 +23651,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24469,7 +24475,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24675,7 +24681,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25087,7 +25093,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25293,7 +25299,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25499,7 +25505,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -26323,7 +26329,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26404,7 +26410,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ122">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR122">
         <v>1.24</v>
@@ -26735,7 +26741,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27147,7 +27153,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27559,7 +27565,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27971,7 +27977,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28255,7 +28261,7 @@
         <v>1.57</v>
       </c>
       <c r="AP131">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ131">
         <v>1.08</v>
@@ -28383,7 +28389,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28589,7 +28595,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28795,7 +28801,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29413,7 +29419,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29825,7 +29831,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30109,7 +30115,7 @@
         <v>1.5</v>
       </c>
       <c r="AP140">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ140">
         <v>1.42</v>
@@ -30237,7 +30243,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30524,7 +30530,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ142">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR142">
         <v>1.66</v>
@@ -30649,7 +30655,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30855,7 +30861,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31267,7 +31273,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31473,7 +31479,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31679,7 +31685,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32297,7 +32303,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32503,7 +32509,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32915,7 +32921,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33202,7 +33208,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ155">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR155">
         <v>1.55</v>
@@ -33739,7 +33745,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -33817,7 +33823,7 @@
         <v>1.5</v>
       </c>
       <c r="AP158">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ158">
         <v>1.08</v>
@@ -34357,7 +34363,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34769,7 +34775,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34975,7 +34981,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35181,7 +35187,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35593,7 +35599,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -36417,7 +36423,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36910,7 +36916,7 @@
         <v>1</v>
       </c>
       <c r="AQ173">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR173">
         <v>1.71</v>
@@ -37035,7 +37041,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37653,7 +37659,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -37937,7 +37943,7 @@
         <v>0.67</v>
       </c>
       <c r="AP178">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ178">
         <v>0.5</v>
@@ -38271,7 +38277,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38683,7 +38689,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38889,7 +38895,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39507,7 +39513,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39919,7 +39925,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40331,7 +40337,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40743,7 +40749,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41155,7 +41161,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41442,7 +41448,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ195">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR195">
         <v>1.64</v>
@@ -41567,7 +41573,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41645,7 +41651,7 @@
         <v>1.3</v>
       </c>
       <c r="AP196">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ196">
         <v>1.42</v>
@@ -41773,7 +41779,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -42185,7 +42191,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42803,7 +42809,7 @@
         <v>123</v>
       </c>
       <c r="P202" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q202">
         <v>4.3</v>
@@ -43215,7 +43221,7 @@
         <v>117</v>
       </c>
       <c r="P204" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q204">
         <v>3.1</v>
@@ -43627,7 +43633,7 @@
         <v>218</v>
       </c>
       <c r="P206" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q206">
         <v>3.65</v>
@@ -43833,7 +43839,7 @@
         <v>156</v>
       </c>
       <c r="P207" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q207">
         <v>3.45</v>
@@ -44039,7 +44045,7 @@
         <v>197</v>
       </c>
       <c r="P208" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q208">
         <v>3.5</v>
@@ -44245,7 +44251,7 @@
         <v>129</v>
       </c>
       <c r="P209" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q209">
         <v>2.4</v>
@@ -44863,7 +44869,7 @@
         <v>220</v>
       </c>
       <c r="P212" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q212">
         <v>2.43</v>
@@ -45020,6 +45026,212 @@
       </c>
       <c r="BP212">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7502817</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45718.33333333334</v>
+      </c>
+      <c r="F213">
+        <v>24</v>
+      </c>
+      <c r="G213" t="s">
+        <v>81</v>
+      </c>
+      <c r="H213" t="s">
+        <v>72</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>1</v>
+      </c>
+      <c r="K213">
+        <v>1</v>
+      </c>
+      <c r="L213">
+        <v>2</v>
+      </c>
+      <c r="M213">
+        <v>1</v>
+      </c>
+      <c r="N213">
+        <v>3</v>
+      </c>
+      <c r="O213" t="s">
+        <v>221</v>
+      </c>
+      <c r="P213" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q213">
+        <v>3.15</v>
+      </c>
+      <c r="R213">
+        <v>2.04</v>
+      </c>
+      <c r="S213">
+        <v>3.7</v>
+      </c>
+      <c r="T213">
+        <v>1.49</v>
+      </c>
+      <c r="U213">
+        <v>2.45</v>
+      </c>
+      <c r="V213">
+        <v>3.1</v>
+      </c>
+      <c r="W213">
+        <v>1.32</v>
+      </c>
+      <c r="X213">
+        <v>9</v>
+      </c>
+      <c r="Y213">
+        <v>1.06</v>
+      </c>
+      <c r="Z213">
+        <v>2.4</v>
+      </c>
+      <c r="AA213">
+        <v>3</v>
+      </c>
+      <c r="AB213">
+        <v>2.9</v>
+      </c>
+      <c r="AC213">
+        <v>1.03</v>
+      </c>
+      <c r="AD213">
+        <v>7.3</v>
+      </c>
+      <c r="AE213">
+        <v>1.38</v>
+      </c>
+      <c r="AF213">
+        <v>2.75</v>
+      </c>
+      <c r="AG213">
+        <v>2.1</v>
+      </c>
+      <c r="AH213">
+        <v>1.6</v>
+      </c>
+      <c r="AI213">
+        <v>1.88</v>
+      </c>
+      <c r="AJ213">
+        <v>1.83</v>
+      </c>
+      <c r="AK213">
+        <v>1.38</v>
+      </c>
+      <c r="AL213">
+        <v>1.32</v>
+      </c>
+      <c r="AM213">
+        <v>1.52</v>
+      </c>
+      <c r="AN213">
+        <v>1.27</v>
+      </c>
+      <c r="AO213">
+        <v>0.64</v>
+      </c>
+      <c r="AP213">
+        <v>1.42</v>
+      </c>
+      <c r="AQ213">
+        <v>0.58</v>
+      </c>
+      <c r="AR213">
+        <v>1.4</v>
+      </c>
+      <c r="AS213">
+        <v>1.24</v>
+      </c>
+      <c r="AT213">
+        <v>2.64</v>
+      </c>
+      <c r="AU213">
+        <v>10</v>
+      </c>
+      <c r="AV213">
+        <v>3</v>
+      </c>
+      <c r="AW213">
+        <v>10</v>
+      </c>
+      <c r="AX213">
+        <v>13</v>
+      </c>
+      <c r="AY213">
+        <v>20</v>
+      </c>
+      <c r="AZ213">
+        <v>16</v>
+      </c>
+      <c r="BA213">
+        <v>-1</v>
+      </c>
+      <c r="BB213">
+        <v>-1</v>
+      </c>
+      <c r="BC213">
+        <v>-1</v>
+      </c>
+      <c r="BD213">
+        <v>2.12</v>
+      </c>
+      <c r="BE213">
+        <v>6.55</v>
+      </c>
+      <c r="BF213">
+        <v>2.08</v>
+      </c>
+      <c r="BG213">
+        <v>1.14</v>
+      </c>
+      <c r="BH213">
+        <v>4.45</v>
+      </c>
+      <c r="BI213">
+        <v>1.29</v>
+      </c>
+      <c r="BJ213">
+        <v>3.04</v>
+      </c>
+      <c r="BK213">
+        <v>1.55</v>
+      </c>
+      <c r="BL213">
+        <v>2.23</v>
+      </c>
+      <c r="BM213">
+        <v>1.93</v>
+      </c>
+      <c r="BN213">
+        <v>1.78</v>
+      </c>
+      <c r="BO213">
+        <v>2.48</v>
+      </c>
+      <c r="BP213">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="327">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -680,6 +680,9 @@
   </si>
   <si>
     <t>['87', '90+3']</t>
+  </si>
+  <si>
+    <t>['39']</t>
   </si>
   <si>
     <t>['24', '27']</t>
@@ -1353,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP213"/>
+  <dimension ref="A1:BP215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1609,7 +1612,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1815,7 +1818,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -2021,7 +2024,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2433,7 +2436,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2639,7 +2642,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2923,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ8">
         <v>1.42</v>
@@ -3051,7 +3054,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3129,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ9">
         <v>1.42</v>
@@ -3463,7 +3466,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3875,7 +3878,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4081,7 +4084,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4162,7 +4165,7 @@
         <v>1</v>
       </c>
       <c r="AQ14">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4287,7 +4290,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4493,7 +4496,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4574,7 +4577,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ16">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5111,7 +5114,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5317,7 +5320,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5395,7 +5398,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ20">
         <v>1.42</v>
@@ -5935,7 +5938,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6347,7 +6350,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6759,7 +6762,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7171,7 +7174,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7377,7 +7380,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7789,7 +7792,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8076,7 +8079,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ33">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR33">
         <v>1.04</v>
@@ -8201,7 +8204,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8407,7 +8410,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8488,7 +8491,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR35">
         <v>1.95</v>
@@ -8613,7 +8616,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8897,7 +8900,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ37">
         <v>1.58</v>
@@ -9025,7 +9028,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9231,7 +9234,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9643,7 +9646,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9849,7 +9852,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10261,7 +10264,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10467,7 +10470,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10879,7 +10882,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11085,7 +11088,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11291,7 +11294,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11372,7 +11375,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ49">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR49">
         <v>1.23</v>
@@ -11703,7 +11706,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -11781,7 +11784,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ51">
         <v>1.08</v>
@@ -12321,7 +12324,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12399,10 +12402,10 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ54">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR54">
         <v>1.11</v>
@@ -12733,7 +12736,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12939,7 +12942,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13351,7 +13354,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -14587,7 +14590,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14665,7 +14668,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ65">
         <v>1.08</v>
@@ -14999,7 +15002,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15080,7 +15083,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ67">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR67">
         <v>1.38</v>
@@ -15205,7 +15208,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15286,7 +15289,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ68">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR68">
         <v>1.55</v>
@@ -15901,7 +15904,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ71">
         <v>0.5</v>
@@ -16235,7 +16238,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16441,7 +16444,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16647,7 +16650,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16853,7 +16856,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17265,7 +17268,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17346,7 +17349,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ78">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR78">
         <v>1.7</v>
@@ -18295,7 +18298,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18376,7 +18379,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ83">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR83">
         <v>1.45</v>
@@ -18913,7 +18916,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19197,7 +19200,7 @@
         <v>1.25</v>
       </c>
       <c r="AP87">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ87">
         <v>0.58</v>
@@ -19325,7 +19328,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19403,7 +19406,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ88">
         <v>1.42</v>
@@ -19737,7 +19740,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19943,7 +19946,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20149,7 +20152,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20355,7 +20358,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20561,7 +20564,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20767,7 +20770,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21054,7 +21057,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ96">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR96">
         <v>1.37</v>
@@ -21179,7 +21182,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21385,7 +21388,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21591,7 +21594,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -21878,7 +21881,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ100">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR100">
         <v>1.7</v>
@@ -22415,7 +22418,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22699,7 +22702,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ104">
         <v>1.18</v>
@@ -22827,7 +22830,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -23033,7 +23036,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23239,7 +23242,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23445,7 +23448,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23651,7 +23654,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -23729,7 +23732,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ109">
         <v>0.82</v>
@@ -24144,7 +24147,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ111">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR111">
         <v>1.61</v>
@@ -24475,7 +24478,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24681,7 +24684,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25093,7 +25096,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25299,7 +25302,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25380,7 +25383,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ117">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR117">
         <v>1.26</v>
@@ -25505,7 +25508,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25995,7 +25998,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ120">
         <v>1.36</v>
@@ -26329,7 +26332,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26741,7 +26744,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27153,7 +27156,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27437,7 +27440,7 @@
         <v>0.83</v>
       </c>
       <c r="AP127">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ127">
         <v>1.18</v>
@@ -27565,7 +27568,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27977,7 +27980,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28389,7 +28392,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28595,7 +28598,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28801,7 +28804,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29088,7 +29091,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ135">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR135">
         <v>1.3</v>
@@ -29419,7 +29422,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29831,7 +29834,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30243,7 +30246,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30324,7 +30327,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ141">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR141">
         <v>1.36</v>
@@ -30655,7 +30658,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30861,7 +30864,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31273,7 +31276,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31354,7 +31357,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ146">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR146">
         <v>1.64</v>
@@ -31479,7 +31482,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31685,7 +31688,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32303,7 +32306,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32381,7 +32384,7 @@
         <v>1.13</v>
       </c>
       <c r="AP151">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ151">
         <v>1</v>
@@ -32509,7 +32512,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32793,7 +32796,7 @@
         <v>1.63</v>
       </c>
       <c r="AP153">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ153">
         <v>1.58</v>
@@ -32921,7 +32924,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33745,7 +33748,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34363,7 +34366,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34650,7 +34653,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ162">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR162">
         <v>1.69</v>
@@ -34775,7 +34778,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34856,7 +34859,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ163">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR163">
         <v>1.12</v>
@@ -34981,7 +34984,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35187,7 +35190,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35599,7 +35602,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -36295,7 +36298,7 @@
         <v>1.33</v>
       </c>
       <c r="AP170">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36423,7 +36426,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36501,7 +36504,7 @@
         <v>1.67</v>
       </c>
       <c r="AP171">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ171">
         <v>1.42</v>
@@ -37041,7 +37044,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37328,7 +37331,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ175">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR175">
         <v>1.61</v>
@@ -37659,7 +37662,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -37737,7 +37740,7 @@
         <v>1.2</v>
       </c>
       <c r="AP177">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ177">
         <v>1.08</v>
@@ -38277,7 +38280,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38358,7 +38361,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ180">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR180">
         <v>1.51</v>
@@ -38689,7 +38692,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38895,7 +38898,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39513,7 +39516,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39925,7 +39928,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40209,7 +40212,7 @@
         <v>0.3</v>
       </c>
       <c r="AP189">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ189">
         <v>0.33</v>
@@ -40337,7 +40340,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40749,7 +40752,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41161,7 +41164,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41573,7 +41576,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41779,7 +41782,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -41857,10 +41860,10 @@
         <v>2</v>
       </c>
       <c r="AP197">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ197">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR197">
         <v>1.07</v>
@@ -42066,7 +42069,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ198">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR198">
         <v>1.61</v>
@@ -42191,7 +42194,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42269,7 +42272,7 @@
         <v>1.09</v>
       </c>
       <c r="AP199">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ199">
         <v>1.08</v>
@@ -42809,7 +42812,7 @@
         <v>123</v>
       </c>
       <c r="P202" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q202">
         <v>4.3</v>
@@ -43221,7 +43224,7 @@
         <v>117</v>
       </c>
       <c r="P204" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q204">
         <v>3.1</v>
@@ -43633,7 +43636,7 @@
         <v>218</v>
       </c>
       <c r="P206" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q206">
         <v>3.65</v>
@@ -43839,7 +43842,7 @@
         <v>156</v>
       </c>
       <c r="P207" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q207">
         <v>3.45</v>
@@ -44045,7 +44048,7 @@
         <v>197</v>
       </c>
       <c r="P208" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q208">
         <v>3.5</v>
@@ -44251,7 +44254,7 @@
         <v>129</v>
       </c>
       <c r="P209" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q209">
         <v>2.4</v>
@@ -44869,7 +44872,7 @@
         <v>220</v>
       </c>
       <c r="P212" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q212">
         <v>2.43</v>
@@ -45075,7 +45078,7 @@
         <v>221</v>
       </c>
       <c r="P213" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q213">
         <v>3.15</v>
@@ -45232,6 +45235,418 @@
       </c>
       <c r="BP213">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7502819</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45718.45833333334</v>
+      </c>
+      <c r="F214">
+        <v>24</v>
+      </c>
+      <c r="G214" t="s">
+        <v>76</v>
+      </c>
+      <c r="H214" t="s">
+        <v>70</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="M214">
+        <v>1</v>
+      </c>
+      <c r="N214">
+        <v>1</v>
+      </c>
+      <c r="O214" t="s">
+        <v>89</v>
+      </c>
+      <c r="P214" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q214">
+        <v>3.15</v>
+      </c>
+      <c r="R214">
+        <v>2.1</v>
+      </c>
+      <c r="S214">
+        <v>3.5</v>
+      </c>
+      <c r="T214">
+        <v>1.44</v>
+      </c>
+      <c r="U214">
+        <v>2.6</v>
+      </c>
+      <c r="V214">
+        <v>2.9</v>
+      </c>
+      <c r="W214">
+        <v>1.36</v>
+      </c>
+      <c r="X214">
+        <v>8</v>
+      </c>
+      <c r="Y214">
+        <v>1.08</v>
+      </c>
+      <c r="Z214">
+        <v>2.6</v>
+      </c>
+      <c r="AA214">
+        <v>3.2</v>
+      </c>
+      <c r="AB214">
+        <v>2.6</v>
+      </c>
+      <c r="AC214">
+        <v>1.05</v>
+      </c>
+      <c r="AD214">
+        <v>8</v>
+      </c>
+      <c r="AE214">
+        <v>1.33</v>
+      </c>
+      <c r="AF214">
+        <v>3</v>
+      </c>
+      <c r="AG214">
+        <v>1.95</v>
+      </c>
+      <c r="AH214">
+        <v>1.7</v>
+      </c>
+      <c r="AI214">
+        <v>1.78</v>
+      </c>
+      <c r="AJ214">
+        <v>1.94</v>
+      </c>
+      <c r="AK214">
+        <v>1.41</v>
+      </c>
+      <c r="AL214">
+        <v>1.31</v>
+      </c>
+      <c r="AM214">
+        <v>1.51</v>
+      </c>
+      <c r="AN214">
+        <v>1.55</v>
+      </c>
+      <c r="AO214">
+        <v>1.25</v>
+      </c>
+      <c r="AP214">
+        <v>1.42</v>
+      </c>
+      <c r="AQ214">
+        <v>1.38</v>
+      </c>
+      <c r="AR214">
+        <v>1.15</v>
+      </c>
+      <c r="AS214">
+        <v>1.39</v>
+      </c>
+      <c r="AT214">
+        <v>2.54</v>
+      </c>
+      <c r="AU214">
+        <v>2</v>
+      </c>
+      <c r="AV214">
+        <v>6</v>
+      </c>
+      <c r="AW214">
+        <v>6</v>
+      </c>
+      <c r="AX214">
+        <v>8</v>
+      </c>
+      <c r="AY214">
+        <v>8</v>
+      </c>
+      <c r="AZ214">
+        <v>14</v>
+      </c>
+      <c r="BA214">
+        <v>4</v>
+      </c>
+      <c r="BB214">
+        <v>9</v>
+      </c>
+      <c r="BC214">
+        <v>13</v>
+      </c>
+      <c r="BD214">
+        <v>1.99</v>
+      </c>
+      <c r="BE214">
+        <v>6.45</v>
+      </c>
+      <c r="BF214">
+        <v>2.23</v>
+      </c>
+      <c r="BG214">
+        <v>1.2</v>
+      </c>
+      <c r="BH214">
+        <v>3.72</v>
+      </c>
+      <c r="BI214">
+        <v>1.41</v>
+      </c>
+      <c r="BJ214">
+        <v>2.6</v>
+      </c>
+      <c r="BK214">
+        <v>1.73</v>
+      </c>
+      <c r="BL214">
+        <v>1.99</v>
+      </c>
+      <c r="BM214">
+        <v>2.17</v>
+      </c>
+      <c r="BN214">
+        <v>1.58</v>
+      </c>
+      <c r="BO214">
+        <v>2.88</v>
+      </c>
+      <c r="BP214">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7502815</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45718.45833333334</v>
+      </c>
+      <c r="F215">
+        <v>24</v>
+      </c>
+      <c r="G215" t="s">
+        <v>77</v>
+      </c>
+      <c r="H215" t="s">
+        <v>74</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>1</v>
+      </c>
+      <c r="L215">
+        <v>1</v>
+      </c>
+      <c r="M215">
+        <v>0</v>
+      </c>
+      <c r="N215">
+        <v>1</v>
+      </c>
+      <c r="O215" t="s">
+        <v>222</v>
+      </c>
+      <c r="P215" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q215">
+        <v>2.55</v>
+      </c>
+      <c r="R215">
+        <v>2.17</v>
+      </c>
+      <c r="S215">
+        <v>4.3</v>
+      </c>
+      <c r="T215">
+        <v>1.42</v>
+      </c>
+      <c r="U215">
+        <v>2.7</v>
+      </c>
+      <c r="V215">
+        <v>2.8</v>
+      </c>
+      <c r="W215">
+        <v>1.39</v>
+      </c>
+      <c r="X215">
+        <v>8</v>
+      </c>
+      <c r="Y215">
+        <v>1.08</v>
+      </c>
+      <c r="Z215">
+        <v>1.8</v>
+      </c>
+      <c r="AA215">
+        <v>3.5</v>
+      </c>
+      <c r="AB215">
+        <v>4</v>
+      </c>
+      <c r="AC215">
+        <v>1.01</v>
+      </c>
+      <c r="AD215">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE215">
+        <v>1.31</v>
+      </c>
+      <c r="AF215">
+        <v>3.15</v>
+      </c>
+      <c r="AG215">
+        <v>1.91</v>
+      </c>
+      <c r="AH215">
+        <v>1.73</v>
+      </c>
+      <c r="AI215">
+        <v>1.79</v>
+      </c>
+      <c r="AJ215">
+        <v>1.92</v>
+      </c>
+      <c r="AK215">
+        <v>1.26</v>
+      </c>
+      <c r="AL215">
+        <v>1.28</v>
+      </c>
+      <c r="AM215">
+        <v>1.77</v>
+      </c>
+      <c r="AN215">
+        <v>1.27</v>
+      </c>
+      <c r="AO215">
+        <v>1.82</v>
+      </c>
+      <c r="AP215">
+        <v>1.42</v>
+      </c>
+      <c r="AQ215">
+        <v>1.67</v>
+      </c>
+      <c r="AR215">
+        <v>1.65</v>
+      </c>
+      <c r="AS215">
+        <v>1.35</v>
+      </c>
+      <c r="AT215">
+        <v>3</v>
+      </c>
+      <c r="AU215">
+        <v>5</v>
+      </c>
+      <c r="AV215">
+        <v>2</v>
+      </c>
+      <c r="AW215">
+        <v>6</v>
+      </c>
+      <c r="AX215">
+        <v>7</v>
+      </c>
+      <c r="AY215">
+        <v>11</v>
+      </c>
+      <c r="AZ215">
+        <v>9</v>
+      </c>
+      <c r="BA215">
+        <v>-1</v>
+      </c>
+      <c r="BB215">
+        <v>-1</v>
+      </c>
+      <c r="BC215">
+        <v>-1</v>
+      </c>
+      <c r="BD215">
+        <v>1.37</v>
+      </c>
+      <c r="BE215">
+        <v>7.6</v>
+      </c>
+      <c r="BF215">
+        <v>4.1</v>
+      </c>
+      <c r="BG215">
+        <v>1.13</v>
+      </c>
+      <c r="BH215">
+        <v>4.6</v>
+      </c>
+      <c r="BI215">
+        <v>1.28</v>
+      </c>
+      <c r="BJ215">
+        <v>3.08</v>
+      </c>
+      <c r="BK215">
+        <v>1.52</v>
+      </c>
+      <c r="BL215">
+        <v>2.3</v>
+      </c>
+      <c r="BM215">
+        <v>1.88</v>
+      </c>
+      <c r="BN215">
+        <v>1.82</v>
+      </c>
+      <c r="BO215">
+        <v>2.4</v>
+      </c>
+      <c r="BP215">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="328">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -683,6 +683,9 @@
   </si>
   <si>
     <t>['39']</t>
+  </si>
+  <si>
+    <t>['12', '22', '40', '56', '65']</t>
   </si>
   <si>
     <t>['24', '27']</t>
@@ -1356,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP215"/>
+  <dimension ref="A1:BP216"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1612,7 +1615,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1818,7 +1821,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -2024,7 +2027,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2436,7 +2439,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2642,7 +2645,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2723,7 +2726,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ7">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3054,7 +3057,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3466,7 +3469,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3878,7 +3881,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4084,7 +4087,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4290,7 +4293,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4496,7 +4499,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4574,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ16">
         <v>1.67</v>
@@ -5114,7 +5117,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5320,7 +5323,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5607,7 +5610,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ21">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR21">
         <v>1.84</v>
@@ -5938,7 +5941,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6350,7 +6353,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6762,7 +6765,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7174,7 +7177,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7380,7 +7383,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7792,7 +7795,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7870,7 +7873,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ32">
         <v>1.42</v>
@@ -8204,7 +8207,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8410,7 +8413,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8616,7 +8619,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -9028,7 +9031,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9234,7 +9237,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9646,7 +9649,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9852,7 +9855,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10264,7 +10267,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10470,7 +10473,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10882,7 +10885,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11088,7 +11091,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11294,7 +11297,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11706,7 +11709,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -11993,7 +11996,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ52">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR52">
         <v>1.2</v>
@@ -12324,7 +12327,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12608,7 +12611,7 @@
         <v>2</v>
       </c>
       <c r="AP55">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ55">
         <v>0.5</v>
@@ -12736,7 +12739,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12942,7 +12945,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13354,7 +13357,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -14590,7 +14593,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -15002,7 +15005,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15208,7 +15211,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15701,7 +15704,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ70">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR70">
         <v>1.47</v>
@@ -16238,7 +16241,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16444,7 +16447,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16650,7 +16653,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16856,7 +16859,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17268,7 +17271,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17967,7 +17970,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ81">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -18298,7 +18301,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18916,7 +18919,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19328,7 +19331,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19740,7 +19743,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19818,7 +19821,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ90">
         <v>1.58</v>
@@ -19946,7 +19949,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20152,7 +20155,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20358,7 +20361,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20564,7 +20567,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20770,7 +20773,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21182,7 +21185,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21388,7 +21391,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21594,7 +21597,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22084,7 +22087,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ101">
         <v>0.82</v>
@@ -22418,7 +22421,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22705,7 +22708,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ104">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR104">
         <v>1.44</v>
@@ -22830,7 +22833,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -23036,7 +23039,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23242,7 +23245,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23448,7 +23451,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23654,7 +23657,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24478,7 +24481,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24684,7 +24687,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25096,7 +25099,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25302,7 +25305,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25508,7 +25511,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25792,7 +25795,7 @@
         <v>2</v>
       </c>
       <c r="AP119">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ119">
         <v>1.42</v>
@@ -26332,7 +26335,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26744,7 +26747,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27156,7 +27159,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27443,7 +27446,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ127">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR127">
         <v>0.99</v>
@@ -27568,7 +27571,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27980,7 +27983,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28058,7 +28061,7 @@
         <v>0.43</v>
       </c>
       <c r="AP130">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ130">
         <v>0.33</v>
@@ -28392,7 +28395,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28598,7 +28601,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28804,7 +28807,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29422,7 +29425,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29709,7 +29712,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ138">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR138">
         <v>1.22</v>
@@ -29834,7 +29837,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30246,7 +30249,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30658,7 +30661,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30864,7 +30867,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31276,7 +31279,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31354,7 +31357,7 @@
         <v>1.63</v>
       </c>
       <c r="AP146">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ146">
         <v>1.38</v>
@@ -31482,7 +31485,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31688,7 +31691,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32306,7 +32309,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32512,7 +32515,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32924,7 +32927,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33748,7 +33751,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34238,7 +34241,7 @@
         <v>1.78</v>
       </c>
       <c r="AP160">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ160">
         <v>1.58</v>
@@ -34366,7 +34369,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34778,7 +34781,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34984,7 +34987,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35065,7 +35068,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ164">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR164">
         <v>1.48</v>
@@ -35190,7 +35193,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35602,7 +35605,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -36426,7 +36429,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -37044,7 +37047,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37534,7 +37537,7 @@
         <v>1.44</v>
       </c>
       <c r="AP176">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ176">
         <v>1.33</v>
@@ -37662,7 +37665,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -38280,7 +38283,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38692,7 +38695,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38773,7 +38776,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ182">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR182">
         <v>1.54</v>
@@ -38898,7 +38901,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39516,7 +39519,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39928,7 +39931,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40340,7 +40343,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40752,7 +40755,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40833,7 +40836,7 @@
         <v>1</v>
       </c>
       <c r="AQ192">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR192">
         <v>1.73</v>
@@ -41164,7 +41167,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41448,7 +41451,7 @@
         <v>0.6</v>
       </c>
       <c r="AP195">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ195">
         <v>0.58</v>
@@ -41576,7 +41579,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41782,7 +41785,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -42194,7 +42197,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42812,7 +42815,7 @@
         <v>123</v>
       </c>
       <c r="P202" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q202">
         <v>4.3</v>
@@ -43224,7 +43227,7 @@
         <v>117</v>
       </c>
       <c r="P204" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q204">
         <v>3.1</v>
@@ -43636,7 +43639,7 @@
         <v>218</v>
       </c>
       <c r="P206" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q206">
         <v>3.65</v>
@@ -43842,7 +43845,7 @@
         <v>156</v>
       </c>
       <c r="P207" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q207">
         <v>3.45</v>
@@ -44048,7 +44051,7 @@
         <v>197</v>
       </c>
       <c r="P208" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q208">
         <v>3.5</v>
@@ -44254,7 +44257,7 @@
         <v>129</v>
       </c>
       <c r="P209" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q209">
         <v>2.4</v>
@@ -44872,7 +44875,7 @@
         <v>220</v>
       </c>
       <c r="P212" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q212">
         <v>2.43</v>
@@ -45078,7 +45081,7 @@
         <v>221</v>
       </c>
       <c r="P213" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q213">
         <v>3.15</v>
@@ -45647,6 +45650,212 @@
       </c>
       <c r="BP215">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7502818</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45718.625</v>
+      </c>
+      <c r="F216">
+        <v>24</v>
+      </c>
+      <c r="G216" t="s">
+        <v>84</v>
+      </c>
+      <c r="H216" t="s">
+        <v>83</v>
+      </c>
+      <c r="I216">
+        <v>3</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>3</v>
+      </c>
+      <c r="L216">
+        <v>5</v>
+      </c>
+      <c r="M216">
+        <v>0</v>
+      </c>
+      <c r="N216">
+        <v>5</v>
+      </c>
+      <c r="O216" t="s">
+        <v>223</v>
+      </c>
+      <c r="P216" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q216">
+        <v>2.26</v>
+      </c>
+      <c r="R216">
+        <v>2.18</v>
+      </c>
+      <c r="S216">
+        <v>5.4</v>
+      </c>
+      <c r="T216">
+        <v>1.43</v>
+      </c>
+      <c r="U216">
+        <v>2.65</v>
+      </c>
+      <c r="V216">
+        <v>2.9</v>
+      </c>
+      <c r="W216">
+        <v>1.36</v>
+      </c>
+      <c r="X216">
+        <v>8.5</v>
+      </c>
+      <c r="Y216">
+        <v>1.07</v>
+      </c>
+      <c r="Z216">
+        <v>1.62</v>
+      </c>
+      <c r="AA216">
+        <v>3.5</v>
+      </c>
+      <c r="AB216">
+        <v>5.5</v>
+      </c>
+      <c r="AC216">
+        <v>1.01</v>
+      </c>
+      <c r="AD216">
+        <v>8.5</v>
+      </c>
+      <c r="AE216">
+        <v>1.35</v>
+      </c>
+      <c r="AF216">
+        <v>2.95</v>
+      </c>
+      <c r="AG216">
+        <v>1.95</v>
+      </c>
+      <c r="AH216">
+        <v>1.7</v>
+      </c>
+      <c r="AI216">
+        <v>1.98</v>
+      </c>
+      <c r="AJ216">
+        <v>1.74</v>
+      </c>
+      <c r="AK216">
+        <v>1.17</v>
+      </c>
+      <c r="AL216">
+        <v>1.26</v>
+      </c>
+      <c r="AM216">
+        <v>2.05</v>
+      </c>
+      <c r="AN216">
+        <v>1.64</v>
+      </c>
+      <c r="AO216">
+        <v>1.18</v>
+      </c>
+      <c r="AP216">
+        <v>1.75</v>
+      </c>
+      <c r="AQ216">
+        <v>1.08</v>
+      </c>
+      <c r="AR216">
+        <v>1.76</v>
+      </c>
+      <c r="AS216">
+        <v>1.38</v>
+      </c>
+      <c r="AT216">
+        <v>3.14</v>
+      </c>
+      <c r="AU216">
+        <v>8</v>
+      </c>
+      <c r="AV216">
+        <v>6</v>
+      </c>
+      <c r="AW216">
+        <v>7</v>
+      </c>
+      <c r="AX216">
+        <v>5</v>
+      </c>
+      <c r="AY216">
+        <v>15</v>
+      </c>
+      <c r="AZ216">
+        <v>11</v>
+      </c>
+      <c r="BA216">
+        <v>-1</v>
+      </c>
+      <c r="BB216">
+        <v>-1</v>
+      </c>
+      <c r="BC216">
+        <v>-1</v>
+      </c>
+      <c r="BD216">
+        <v>1.3</v>
+      </c>
+      <c r="BE216">
+        <v>8</v>
+      </c>
+      <c r="BF216">
+        <v>4.75</v>
+      </c>
+      <c r="BG216">
+        <v>1.15</v>
+      </c>
+      <c r="BH216">
+        <v>4.2</v>
+      </c>
+      <c r="BI216">
+        <v>1.32</v>
+      </c>
+      <c r="BJ216">
+        <v>2.88</v>
+      </c>
+      <c r="BK216">
+        <v>1.59</v>
+      </c>
+      <c r="BL216">
+        <v>2.16</v>
+      </c>
+      <c r="BM216">
+        <v>2</v>
+      </c>
+      <c r="BN216">
+        <v>1.72</v>
+      </c>
+      <c r="BO216">
+        <v>2.6</v>
+      </c>
+      <c r="BP216">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -44574,13 +44574,13 @@
         <v>12</v>
       </c>
       <c r="BA210">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB210">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC210">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BD210">
         <v>2.13</v>
@@ -44780,13 +44780,13 @@
         <v>13</v>
       </c>
       <c r="BA211">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB211">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC211">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD211">
         <v>1.5</v>
@@ -44986,13 +44986,13 @@
         <v>9</v>
       </c>
       <c r="BA212">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB212">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC212">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD212">
         <v>1.41</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="329">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -999,6 +999,9 @@
   <si>
     <t>['29']</t>
   </si>
+  <si>
+    <t>['75']</t>
+  </si>
 </sst>
 </file>
 
@@ -1359,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP216"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2520,7 +2523,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ6">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -4165,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ14">
         <v>1.38</v>
@@ -5816,7 +5819,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ22">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>1.3</v>
@@ -8491,7 +8494,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ35">
         <v>1.67</v>
@@ -10348,7 +10351,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ44">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR44">
         <v>1.61</v>
@@ -11169,7 +11172,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ48">
         <v>1.33</v>
@@ -15495,7 +15498,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ69">
         <v>1.42</v>
@@ -16113,7 +16116,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ72">
         <v>1.42</v>
@@ -19618,7 +19621,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ89">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR89">
         <v>1.48</v>
@@ -20851,7 +20854,7 @@
         <v>0.4</v>
       </c>
       <c r="AP95">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ95">
         <v>0.33</v>
@@ -22090,7 +22093,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ101">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR101">
         <v>1.6</v>
@@ -23738,7 +23741,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ109">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR109">
         <v>1.09</v>
@@ -24971,7 +24974,7 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ115">
         <v>1</v>
@@ -27652,7 +27655,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ128">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR128">
         <v>1.46</v>
@@ -28679,7 +28682,7 @@
         <v>1.29</v>
       </c>
       <c r="AP133">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ133">
         <v>1.42</v>
@@ -29918,7 +29921,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ139">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR139">
         <v>1.54</v>
@@ -31563,7 +31566,7 @@
         <v>1.5</v>
       </c>
       <c r="AP147">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ147">
         <v>1.08</v>
@@ -34447,7 +34450,7 @@
         <v>0.75</v>
       </c>
       <c r="AP161">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ161">
         <v>0.5</v>
@@ -36098,7 +36101,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ169">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR169">
         <v>1.26</v>
@@ -36919,7 +36922,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP173">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ173">
         <v>0.58</v>
@@ -38982,7 +38985,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ183">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR183">
         <v>1.33</v>
@@ -40833,7 +40836,7 @@
         <v>1</v>
       </c>
       <c r="AP192">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ192">
         <v>1.08</v>
@@ -43514,7 +43517,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ205">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR205">
         <v>1.71</v>
@@ -45174,10 +45177,10 @@
         <v>2.64</v>
       </c>
       <c r="AU213">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AV213">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW213">
         <v>10</v>
@@ -45186,19 +45189,19 @@
         <v>13</v>
       </c>
       <c r="AY213">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ213">
+        <v>15</v>
+      </c>
+      <c r="BA213">
+        <v>9</v>
+      </c>
+      <c r="BB213">
+        <v>7</v>
+      </c>
+      <c r="BC213">
         <v>16</v>
-      </c>
-      <c r="BA213">
-        <v>-1</v>
-      </c>
-      <c r="BB213">
-        <v>-1</v>
-      </c>
-      <c r="BC213">
-        <v>-1</v>
       </c>
       <c r="BD213">
         <v>2.12</v>
@@ -45586,31 +45589,31 @@
         <v>3</v>
       </c>
       <c r="AU215">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV215">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW215">
         <v>6</v>
       </c>
       <c r="AX215">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY215">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ215">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA215">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB215">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC215">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD215">
         <v>1.37</v>
@@ -45856,6 +45859,212 @@
       </c>
       <c r="BP216">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7502814</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45719.625</v>
+      </c>
+      <c r="F217">
+        <v>24</v>
+      </c>
+      <c r="G217" t="s">
+        <v>82</v>
+      </c>
+      <c r="H217" t="s">
+        <v>80</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+      <c r="M217">
+        <v>1</v>
+      </c>
+      <c r="N217">
+        <v>1</v>
+      </c>
+      <c r="O217" t="s">
+        <v>89</v>
+      </c>
+      <c r="P217" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q217">
+        <v>2.5</v>
+      </c>
+      <c r="R217">
+        <v>2.2</v>
+      </c>
+      <c r="S217">
+        <v>4.5</v>
+      </c>
+      <c r="T217">
+        <v>1.4</v>
+      </c>
+      <c r="U217">
+        <v>2.75</v>
+      </c>
+      <c r="V217">
+        <v>2.75</v>
+      </c>
+      <c r="W217">
+        <v>1.4</v>
+      </c>
+      <c r="X217">
+        <v>8</v>
+      </c>
+      <c r="Y217">
+        <v>1.08</v>
+      </c>
+      <c r="Z217">
+        <v>1.8</v>
+      </c>
+      <c r="AA217">
+        <v>3.7</v>
+      </c>
+      <c r="AB217">
+        <v>3.8</v>
+      </c>
+      <c r="AC217">
+        <v>1.01</v>
+      </c>
+      <c r="AD217">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE217">
+        <v>1.29</v>
+      </c>
+      <c r="AF217">
+        <v>3.3</v>
+      </c>
+      <c r="AG217">
+        <v>1.83</v>
+      </c>
+      <c r="AH217">
+        <v>1.8</v>
+      </c>
+      <c r="AI217">
+        <v>1.8</v>
+      </c>
+      <c r="AJ217">
+        <v>1.91</v>
+      </c>
+      <c r="AK217">
+        <v>1.23</v>
+      </c>
+      <c r="AL217">
+        <v>1.26</v>
+      </c>
+      <c r="AM217">
+        <v>1.88</v>
+      </c>
+      <c r="AN217">
+        <v>1</v>
+      </c>
+      <c r="AO217">
+        <v>0.82</v>
+      </c>
+      <c r="AP217">
+        <v>0.92</v>
+      </c>
+      <c r="AQ217">
+        <v>1</v>
+      </c>
+      <c r="AR217">
+        <v>1.78</v>
+      </c>
+      <c r="AS217">
+        <v>1.12</v>
+      </c>
+      <c r="AT217">
+        <v>2.9</v>
+      </c>
+      <c r="AU217">
+        <v>3</v>
+      </c>
+      <c r="AV217">
+        <v>5</v>
+      </c>
+      <c r="AW217">
+        <v>7</v>
+      </c>
+      <c r="AX217">
+        <v>8</v>
+      </c>
+      <c r="AY217">
+        <v>10</v>
+      </c>
+      <c r="AZ217">
+        <v>13</v>
+      </c>
+      <c r="BA217">
+        <v>5</v>
+      </c>
+      <c r="BB217">
+        <v>4</v>
+      </c>
+      <c r="BC217">
+        <v>9</v>
+      </c>
+      <c r="BD217">
+        <v>1.55</v>
+      </c>
+      <c r="BE217">
+        <v>8.5</v>
+      </c>
+      <c r="BF217">
+        <v>2.91</v>
+      </c>
+      <c r="BG217">
+        <v>1.14</v>
+      </c>
+      <c r="BH217">
+        <v>4.65</v>
+      </c>
+      <c r="BI217">
+        <v>1.27</v>
+      </c>
+      <c r="BJ217">
+        <v>3.25</v>
+      </c>
+      <c r="BK217">
+        <v>1.5</v>
+      </c>
+      <c r="BL217">
+        <v>2.42</v>
+      </c>
+      <c r="BM217">
+        <v>1.82</v>
+      </c>
+      <c r="BN217">
+        <v>1.93</v>
+      </c>
+      <c r="BO217">
+        <v>2.27</v>
+      </c>
+      <c r="BP217">
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -45813,13 +45813,13 @@
         <v>11</v>
       </c>
       <c r="BA216">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB216">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC216">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD216">
         <v>1.3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -45177,10 +45177,10 @@
         <v>2.64</v>
       </c>
       <c r="AU213">
+        <v>10</v>
+      </c>
+      <c r="AV213">
         <v>3</v>
-      </c>
-      <c r="AV213">
-        <v>2</v>
       </c>
       <c r="AW213">
         <v>10</v>
@@ -45189,10 +45189,10 @@
         <v>13</v>
       </c>
       <c r="AY213">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AZ213">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA213">
         <v>9</v>
@@ -45589,22 +45589,22 @@
         <v>3</v>
       </c>
       <c r="AU215">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV215">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW215">
         <v>6</v>
       </c>
       <c r="AX215">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY215">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ215">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA215">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="334">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -688,6 +688,15 @@
     <t>['12', '22', '40', '56', '65']</t>
   </si>
   <si>
+    <t>['3', '42', '79']</t>
+  </si>
+  <si>
+    <t>['58', '85']</t>
+  </si>
+  <si>
+    <t>['9', '37', '83']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -1001,6 +1010,12 @@
   </si>
   <si>
     <t>['75']</t>
+  </si>
+  <si>
+    <t>['12', '45+2']</t>
+  </si>
+  <si>
+    <t>['31', '74']</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1618,7 +1633,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1824,7 +1839,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1905,7 +1920,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ3">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2030,7 +2045,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2317,7 +2332,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ5">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2442,7 +2457,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2520,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ6">
         <v>1</v>
@@ -2648,7 +2663,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2726,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ7">
         <v>1.08</v>
@@ -2935,7 +2950,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ8">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3060,7 +3075,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3344,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3472,7 +3487,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3884,7 +3899,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -3965,7 +3980,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ13">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4090,7 +4105,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4296,7 +4311,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4374,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ15">
         <v>1.08</v>
@@ -4502,7 +4517,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -5120,7 +5135,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5326,7 +5341,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5407,7 +5422,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ20">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR20">
         <v>1.01</v>
@@ -5610,7 +5625,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ21">
         <v>1.08</v>
@@ -5816,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -5944,7 +5959,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6025,7 +6040,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ23">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR23">
         <v>1.93</v>
@@ -6356,7 +6371,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6434,7 +6449,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ25">
         <v>1.42</v>
@@ -6643,7 +6658,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ26">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR26">
         <v>1.66</v>
@@ -6768,7 +6783,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7180,7 +7195,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7386,7 +7401,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7798,7 +7813,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8210,7 +8225,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8288,7 +8303,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ34">
         <v>1.33</v>
@@ -8416,7 +8431,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8622,7 +8637,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8909,7 +8924,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ37">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR37">
         <v>0.82</v>
@@ -9034,7 +9049,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9112,7 +9127,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -9240,7 +9255,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9318,10 +9333,10 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ39">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR39">
         <v>1.92</v>
@@ -9527,7 +9542,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ40">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR40">
         <v>1.4</v>
@@ -9652,7 +9667,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9733,7 +9748,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ41">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR41">
         <v>1.49</v>
@@ -9858,7 +9873,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10142,7 +10157,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ43">
         <v>0.33</v>
@@ -10270,7 +10285,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10476,7 +10491,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10760,10 +10775,10 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ46">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR46">
         <v>1.7</v>
@@ -10888,7 +10903,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11094,7 +11109,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11300,7 +11315,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11712,7 +11727,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12330,7 +12345,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12742,7 +12757,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12820,7 +12835,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ56">
         <v>1.42</v>
@@ -12948,7 +12963,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13026,7 +13041,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ57">
         <v>1.08</v>
@@ -13360,7 +13375,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13441,7 +13456,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ59">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR59">
         <v>1.13</v>
@@ -13850,7 +13865,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ61">
         <v>1.42</v>
@@ -14056,10 +14071,10 @@
         <v>2.33</v>
       </c>
       <c r="AP62">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ62">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR62">
         <v>1.41</v>
@@ -14265,7 +14280,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ63">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR63">
         <v>1.24</v>
@@ -14471,7 +14486,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ64">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR64">
         <v>1.67</v>
@@ -14596,7 +14611,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -15008,7 +15023,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15214,7 +15229,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -16244,7 +16259,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16322,7 +16337,7 @@
         <v>1.25</v>
       </c>
       <c r="AP73">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ73">
         <v>1.08</v>
@@ -16450,7 +16465,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16531,7 +16546,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ74">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR74">
         <v>1.25</v>
@@ -16656,7 +16671,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16734,7 +16749,7 @@
         <v>0.5</v>
       </c>
       <c r="AP75">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -16862,7 +16877,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17146,10 +17161,10 @@
         <v>1.5</v>
       </c>
       <c r="AP77">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ77">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR77">
         <v>1.55</v>
@@ -17274,7 +17289,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17352,7 +17367,7 @@
         <v>1.75</v>
       </c>
       <c r="AP78">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ78">
         <v>1.38</v>
@@ -17767,7 +17782,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ80">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR80">
         <v>1.09</v>
@@ -18304,7 +18319,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18591,7 +18606,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ84">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR84">
         <v>1.48</v>
@@ -18922,7 +18937,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19000,7 +19015,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ86">
         <v>0.5</v>
@@ -19334,7 +19349,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19746,7 +19761,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19827,7 +19842,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ90">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR90">
         <v>1.65</v>
@@ -19952,7 +19967,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20030,7 +20045,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ91">
         <v>1.08</v>
@@ -20158,7 +20173,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20364,7 +20379,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20570,7 +20585,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20648,7 +20663,7 @@
         <v>2.2</v>
       </c>
       <c r="AP94">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ94">
         <v>1.42</v>
@@ -20776,7 +20791,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21188,7 +21203,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21269,7 +21284,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ97">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR97">
         <v>1.52</v>
@@ -21394,7 +21409,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21472,10 +21487,10 @@
         <v>1.4</v>
       </c>
       <c r="AP98">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ98">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21600,7 +21615,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -21884,7 +21899,7 @@
         <v>1.67</v>
       </c>
       <c r="AP100">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ100">
         <v>1.38</v>
@@ -22424,7 +22439,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22502,7 +22517,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ103">
         <v>1.42</v>
@@ -22836,7 +22851,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22917,7 +22932,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ105">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR105">
         <v>1.39</v>
@@ -23042,7 +23057,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23248,7 +23263,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23326,7 +23341,7 @@
         <v>1</v>
       </c>
       <c r="AP107">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ107">
         <v>0.5</v>
@@ -23454,7 +23469,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23535,7 +23550,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ108">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR108">
         <v>1.57</v>
@@ -23660,7 +23675,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24150,7 +24165,7 @@
         <v>2.6</v>
       </c>
       <c r="AP111">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ111">
         <v>1.67</v>
@@ -24356,7 +24371,7 @@
         <v>1.83</v>
       </c>
       <c r="AP112">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ112">
         <v>1.08</v>
@@ -24484,7 +24499,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24565,7 +24580,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ113">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24690,7 +24705,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25102,7 +25117,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25183,7 +25198,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ116">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR116">
         <v>1.1</v>
@@ -25308,7 +25323,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25514,7 +25529,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -26007,7 +26022,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ120">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR120">
         <v>1.47</v>
@@ -26213,7 +26228,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ121">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR121">
         <v>1.6</v>
@@ -26338,7 +26353,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26416,7 +26431,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ122">
         <v>0.58</v>
@@ -26750,7 +26765,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -26828,7 +26843,7 @@
         <v>1.29</v>
       </c>
       <c r="AP124">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ124">
         <v>1.42</v>
@@ -27162,7 +27177,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27574,7 +27589,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27986,7 +28001,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28398,7 +28413,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28604,7 +28619,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28685,7 +28700,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ133">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR133">
         <v>1.63</v>
@@ -28810,7 +28825,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -28891,7 +28906,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ134">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR134">
         <v>1.14</v>
@@ -29094,7 +29109,7 @@
         <v>2.17</v>
       </c>
       <c r="AP135">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ135">
         <v>1.67</v>
@@ -29428,7 +29443,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29506,7 +29521,7 @@
         <v>1.57</v>
       </c>
       <c r="AP137">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ137">
         <v>1.33</v>
@@ -29840,7 +29855,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30127,7 +30142,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ140">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR140">
         <v>1.48</v>
@@ -30252,7 +30267,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30536,7 +30551,7 @@
         <v>0.71</v>
       </c>
       <c r="AP142">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ142">
         <v>0.58</v>
@@ -30664,7 +30679,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30745,7 +30760,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ143">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR143">
         <v>1.64</v>
@@ -30870,7 +30885,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31154,7 +31169,7 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ145">
         <v>0.5</v>
@@ -31282,7 +31297,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31488,7 +31503,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31694,7 +31709,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32184,10 +32199,10 @@
         <v>1.43</v>
       </c>
       <c r="AP150">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ150">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR150">
         <v>1.63</v>
@@ -32312,7 +32327,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32518,7 +32533,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32805,7 +32820,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ153">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR153">
         <v>1.48</v>
@@ -32930,7 +32945,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33754,7 +33769,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34038,7 +34053,7 @@
         <v>1.38</v>
       </c>
       <c r="AP159">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ159">
         <v>1.42</v>
@@ -34247,7 +34262,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ160">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR160">
         <v>1.7</v>
@@ -34372,7 +34387,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34784,7 +34799,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34990,7 +35005,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35196,7 +35211,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35274,10 +35289,10 @@
         <v>1.33</v>
       </c>
       <c r="AP165">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ165">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR165">
         <v>1.57</v>
@@ -35483,7 +35498,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ166">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR166">
         <v>1.36</v>
@@ -35608,7 +35623,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -35689,7 +35704,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ167">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR167">
         <v>1.71</v>
@@ -35892,7 +35907,7 @@
         <v>1.11</v>
       </c>
       <c r="AP168">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ168">
         <v>1.42</v>
@@ -36432,7 +36447,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36716,7 +36731,7 @@
         <v>1.5</v>
       </c>
       <c r="AP172">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ172">
         <v>1.33</v>
@@ -37050,7 +37065,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37128,7 +37143,7 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ174">
         <v>1.08</v>
@@ -37668,7 +37683,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -38286,7 +38301,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38573,7 +38588,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ181">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR181">
         <v>1.63</v>
@@ -38698,7 +38713,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38904,7 +38919,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39188,7 +39203,7 @@
         <v>1.6</v>
       </c>
       <c r="AP184">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ184">
         <v>1.42</v>
@@ -39522,7 +39537,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39600,10 +39615,10 @@
         <v>1.22</v>
       </c>
       <c r="AP186">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ186">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR186">
         <v>1.18</v>
@@ -39809,7 +39824,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ187">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR187">
         <v>1.28</v>
@@ -39934,7 +39949,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40015,7 +40030,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ188">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR188">
         <v>1.43</v>
@@ -40346,7 +40361,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40424,7 +40439,7 @@
         <v>1.1</v>
       </c>
       <c r="AP190">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ190">
         <v>1.42</v>
@@ -40758,7 +40773,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41170,7 +41185,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41582,7 +41597,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41788,7 +41803,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -42200,7 +42215,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42484,7 +42499,7 @@
         <v>1.09</v>
       </c>
       <c r="AP200">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ200">
         <v>1</v>
@@ -42690,7 +42705,7 @@
         <v>0.36</v>
       </c>
       <c r="AP201">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ201">
         <v>0.33</v>
@@ -42818,7 +42833,7 @@
         <v>123</v>
       </c>
       <c r="P202" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q202">
         <v>4.3</v>
@@ -43105,7 +43120,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ203">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR203">
         <v>1.53</v>
@@ -43230,7 +43245,7 @@
         <v>117</v>
       </c>
       <c r="P204" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q204">
         <v>3.1</v>
@@ -43311,7 +43326,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ204">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AR204">
         <v>1.68</v>
@@ -43514,7 +43529,7 @@
         <v>0.9</v>
       </c>
       <c r="AP205">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ205">
         <v>1</v>
@@ -43642,7 +43657,7 @@
         <v>218</v>
       </c>
       <c r="P206" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q206">
         <v>3.65</v>
@@ -43720,10 +43735,10 @@
         <v>1.45</v>
       </c>
       <c r="AP206">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ206">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR206">
         <v>1.34</v>
@@ -43848,7 +43863,7 @@
         <v>156</v>
       </c>
       <c r="P207" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q207">
         <v>3.45</v>
@@ -43929,7 +43944,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ207">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR207">
         <v>1.41</v>
@@ -44054,7 +44069,7 @@
         <v>197</v>
       </c>
       <c r="P208" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q208">
         <v>3.5</v>
@@ -44260,7 +44275,7 @@
         <v>129</v>
       </c>
       <c r="P209" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q209">
         <v>2.4</v>
@@ -44878,7 +44893,7 @@
         <v>220</v>
       </c>
       <c r="P212" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q212">
         <v>2.43</v>
@@ -45084,7 +45099,7 @@
         <v>221</v>
       </c>
       <c r="P213" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q213">
         <v>3.15</v>
@@ -45908,7 +45923,7 @@
         <v>89</v>
       </c>
       <c r="P217" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q217">
         <v>2.5</v>
@@ -46065,6 +46080,830 @@
       </c>
       <c r="BP217">
         <v>1.59</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7502825</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45723.625</v>
+      </c>
+      <c r="F218">
+        <v>25</v>
+      </c>
+      <c r="G218" t="s">
+        <v>83</v>
+      </c>
+      <c r="H218" t="s">
+        <v>85</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>1</v>
+      </c>
+      <c r="K218">
+        <v>1</v>
+      </c>
+      <c r="L218">
+        <v>0</v>
+      </c>
+      <c r="M218">
+        <v>1</v>
+      </c>
+      <c r="N218">
+        <v>1</v>
+      </c>
+      <c r="O218" t="s">
+        <v>89</v>
+      </c>
+      <c r="P218" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q218">
+        <v>3.6</v>
+      </c>
+      <c r="R218">
+        <v>1.93</v>
+      </c>
+      <c r="S218">
+        <v>3</v>
+      </c>
+      <c r="T218">
+        <v>1.49</v>
+      </c>
+      <c r="U218">
+        <v>2.4</v>
+      </c>
+      <c r="V218">
+        <v>3.25</v>
+      </c>
+      <c r="W218">
+        <v>1.29</v>
+      </c>
+      <c r="X218">
+        <v>9.25</v>
+      </c>
+      <c r="Y218">
+        <v>1.05</v>
+      </c>
+      <c r="Z218">
+        <v>2.95</v>
+      </c>
+      <c r="AA218">
+        <v>2.8</v>
+      </c>
+      <c r="AB218">
+        <v>2.6</v>
+      </c>
+      <c r="AC218">
+        <v>1.09</v>
+      </c>
+      <c r="AD218">
+        <v>6.5</v>
+      </c>
+      <c r="AE218">
+        <v>1.44</v>
+      </c>
+      <c r="AF218">
+        <v>2.65</v>
+      </c>
+      <c r="AG218">
+        <v>2.15</v>
+      </c>
+      <c r="AH218">
+        <v>1.57</v>
+      </c>
+      <c r="AI218">
+        <v>2</v>
+      </c>
+      <c r="AJ218">
+        <v>1.7</v>
+      </c>
+      <c r="AK218">
+        <v>1.55</v>
+      </c>
+      <c r="AL218">
+        <v>1.35</v>
+      </c>
+      <c r="AM218">
+        <v>1.36</v>
+      </c>
+      <c r="AN218">
+        <v>1.92</v>
+      </c>
+      <c r="AO218">
+        <v>1.58</v>
+      </c>
+      <c r="AP218">
+        <v>1.77</v>
+      </c>
+      <c r="AQ218">
+        <v>1.69</v>
+      </c>
+      <c r="AR218">
+        <v>1.7</v>
+      </c>
+      <c r="AS218">
+        <v>1.46</v>
+      </c>
+      <c r="AT218">
+        <v>3.16</v>
+      </c>
+      <c r="AU218">
+        <v>3</v>
+      </c>
+      <c r="AV218">
+        <v>2</v>
+      </c>
+      <c r="AW218">
+        <v>10</v>
+      </c>
+      <c r="AX218">
+        <v>6</v>
+      </c>
+      <c r="AY218">
+        <v>13</v>
+      </c>
+      <c r="AZ218">
+        <v>8</v>
+      </c>
+      <c r="BA218">
+        <v>-1</v>
+      </c>
+      <c r="BB218">
+        <v>-1</v>
+      </c>
+      <c r="BC218">
+        <v>-1</v>
+      </c>
+      <c r="BD218">
+        <v>0</v>
+      </c>
+      <c r="BE218">
+        <v>0</v>
+      </c>
+      <c r="BF218">
+        <v>0</v>
+      </c>
+      <c r="BG218">
+        <v>0</v>
+      </c>
+      <c r="BH218">
+        <v>0</v>
+      </c>
+      <c r="BI218">
+        <v>0</v>
+      </c>
+      <c r="BJ218">
+        <v>0</v>
+      </c>
+      <c r="BK218">
+        <v>0</v>
+      </c>
+      <c r="BL218">
+        <v>0</v>
+      </c>
+      <c r="BM218">
+        <v>0</v>
+      </c>
+      <c r="BN218">
+        <v>0</v>
+      </c>
+      <c r="BO218">
+        <v>0</v>
+      </c>
+      <c r="BP218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7502826</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45724.33333333334</v>
+      </c>
+      <c r="F219">
+        <v>25</v>
+      </c>
+      <c r="G219" t="s">
+        <v>74</v>
+      </c>
+      <c r="H219" t="s">
+        <v>79</v>
+      </c>
+      <c r="I219">
+        <v>2</v>
+      </c>
+      <c r="J219">
+        <v>2</v>
+      </c>
+      <c r="K219">
+        <v>4</v>
+      </c>
+      <c r="L219">
+        <v>3</v>
+      </c>
+      <c r="M219">
+        <v>2</v>
+      </c>
+      <c r="N219">
+        <v>5</v>
+      </c>
+      <c r="O219" t="s">
+        <v>224</v>
+      </c>
+      <c r="P219" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q219">
+        <v>3.78</v>
+      </c>
+      <c r="R219">
+        <v>2.01</v>
+      </c>
+      <c r="S219">
+        <v>2.92</v>
+      </c>
+      <c r="T219">
+        <v>1.44</v>
+      </c>
+      <c r="U219">
+        <v>2.61</v>
+      </c>
+      <c r="V219">
+        <v>3.15</v>
+      </c>
+      <c r="W219">
+        <v>1.32</v>
+      </c>
+      <c r="X219">
+        <v>8.1</v>
+      </c>
+      <c r="Y219">
+        <v>1.03</v>
+      </c>
+      <c r="Z219">
+        <v>3.05</v>
+      </c>
+      <c r="AA219">
+        <v>3.1</v>
+      </c>
+      <c r="AB219">
+        <v>2.3</v>
+      </c>
+      <c r="AC219">
+        <v>1.02</v>
+      </c>
+      <c r="AD219">
+        <v>8</v>
+      </c>
+      <c r="AE219">
+        <v>1.33</v>
+      </c>
+      <c r="AF219">
+        <v>2.84</v>
+      </c>
+      <c r="AG219">
+        <v>2.1</v>
+      </c>
+      <c r="AH219">
+        <v>1.61</v>
+      </c>
+      <c r="AI219">
+        <v>1.86</v>
+      </c>
+      <c r="AJ219">
+        <v>1.84</v>
+      </c>
+      <c r="AK219">
+        <v>1.59</v>
+      </c>
+      <c r="AL219">
+        <v>1.32</v>
+      </c>
+      <c r="AM219">
+        <v>1.35</v>
+      </c>
+      <c r="AN219">
+        <v>1.67</v>
+      </c>
+      <c r="AO219">
+        <v>1.42</v>
+      </c>
+      <c r="AP219">
+        <v>1.77</v>
+      </c>
+      <c r="AQ219">
+        <v>1.31</v>
+      </c>
+      <c r="AR219">
+        <v>1.28</v>
+      </c>
+      <c r="AS219">
+        <v>1.22</v>
+      </c>
+      <c r="AT219">
+        <v>2.5</v>
+      </c>
+      <c r="AU219">
+        <v>5</v>
+      </c>
+      <c r="AV219">
+        <v>3</v>
+      </c>
+      <c r="AW219">
+        <v>14</v>
+      </c>
+      <c r="AX219">
+        <v>1</v>
+      </c>
+      <c r="AY219">
+        <v>19</v>
+      </c>
+      <c r="AZ219">
+        <v>4</v>
+      </c>
+      <c r="BA219">
+        <v>12</v>
+      </c>
+      <c r="BB219">
+        <v>2</v>
+      </c>
+      <c r="BC219">
+        <v>14</v>
+      </c>
+      <c r="BD219">
+        <v>0</v>
+      </c>
+      <c r="BE219">
+        <v>0</v>
+      </c>
+      <c r="BF219">
+        <v>0</v>
+      </c>
+      <c r="BG219">
+        <v>0</v>
+      </c>
+      <c r="BH219">
+        <v>0</v>
+      </c>
+      <c r="BI219">
+        <v>0</v>
+      </c>
+      <c r="BJ219">
+        <v>0</v>
+      </c>
+      <c r="BK219">
+        <v>0</v>
+      </c>
+      <c r="BL219">
+        <v>0</v>
+      </c>
+      <c r="BM219">
+        <v>0</v>
+      </c>
+      <c r="BN219">
+        <v>0</v>
+      </c>
+      <c r="BO219">
+        <v>0</v>
+      </c>
+      <c r="BP219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7502820</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45724.45833333334</v>
+      </c>
+      <c r="F220">
+        <v>25</v>
+      </c>
+      <c r="G220" t="s">
+        <v>78</v>
+      </c>
+      <c r="H220" t="s">
+        <v>77</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+      <c r="J220">
+        <v>1</v>
+      </c>
+      <c r="K220">
+        <v>1</v>
+      </c>
+      <c r="L220">
+        <v>2</v>
+      </c>
+      <c r="M220">
+        <v>2</v>
+      </c>
+      <c r="N220">
+        <v>4</v>
+      </c>
+      <c r="O220" t="s">
+        <v>225</v>
+      </c>
+      <c r="P220" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q220">
+        <v>3.26</v>
+      </c>
+      <c r="R220">
+        <v>1.96</v>
+      </c>
+      <c r="S220">
+        <v>3.48</v>
+      </c>
+      <c r="T220">
+        <v>1.46</v>
+      </c>
+      <c r="U220">
+        <v>2.56</v>
+      </c>
+      <c r="V220">
+        <v>3.34</v>
+      </c>
+      <c r="W220">
+        <v>1.29</v>
+      </c>
+      <c r="X220">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y220">
+        <v>1</v>
+      </c>
+      <c r="Z220">
+        <v>2.6</v>
+      </c>
+      <c r="AA220">
+        <v>2.9</v>
+      </c>
+      <c r="AB220">
+        <v>2.8</v>
+      </c>
+      <c r="AC220">
+        <v>1.01</v>
+      </c>
+      <c r="AD220">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE220">
+        <v>1.34</v>
+      </c>
+      <c r="AF220">
+        <v>2.79</v>
+      </c>
+      <c r="AG220">
+        <v>2.15</v>
+      </c>
+      <c r="AH220">
+        <v>1.57</v>
+      </c>
+      <c r="AI220">
+        <v>1.89</v>
+      </c>
+      <c r="AJ220">
+        <v>1.81</v>
+      </c>
+      <c r="AK220">
+        <v>1.42</v>
+      </c>
+      <c r="AL220">
+        <v>1.33</v>
+      </c>
+      <c r="AM220">
+        <v>1.48</v>
+      </c>
+      <c r="AN220">
+        <v>1.33</v>
+      </c>
+      <c r="AO220">
+        <v>1.58</v>
+      </c>
+      <c r="AP220">
+        <v>1.31</v>
+      </c>
+      <c r="AQ220">
+        <v>1.54</v>
+      </c>
+      <c r="AR220">
+        <v>1.51</v>
+      </c>
+      <c r="AS220">
+        <v>1.43</v>
+      </c>
+      <c r="AT220">
+        <v>2.94</v>
+      </c>
+      <c r="AU220">
+        <v>9</v>
+      </c>
+      <c r="AV220">
+        <v>6</v>
+      </c>
+      <c r="AW220">
+        <v>13</v>
+      </c>
+      <c r="AX220">
+        <v>5</v>
+      </c>
+      <c r="AY220">
+        <v>22</v>
+      </c>
+      <c r="AZ220">
+        <v>11</v>
+      </c>
+      <c r="BA220">
+        <v>5</v>
+      </c>
+      <c r="BB220">
+        <v>4</v>
+      </c>
+      <c r="BC220">
+        <v>9</v>
+      </c>
+      <c r="BD220">
+        <v>0</v>
+      </c>
+      <c r="BE220">
+        <v>0</v>
+      </c>
+      <c r="BF220">
+        <v>0</v>
+      </c>
+      <c r="BG220">
+        <v>0</v>
+      </c>
+      <c r="BH220">
+        <v>0</v>
+      </c>
+      <c r="BI220">
+        <v>0</v>
+      </c>
+      <c r="BJ220">
+        <v>0</v>
+      </c>
+      <c r="BK220">
+        <v>0</v>
+      </c>
+      <c r="BL220">
+        <v>0</v>
+      </c>
+      <c r="BM220">
+        <v>0</v>
+      </c>
+      <c r="BN220">
+        <v>0</v>
+      </c>
+      <c r="BO220">
+        <v>0</v>
+      </c>
+      <c r="BP220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7502828</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45724.52083333334</v>
+      </c>
+      <c r="F221">
+        <v>25</v>
+      </c>
+      <c r="G221" t="s">
+        <v>75</v>
+      </c>
+      <c r="H221" t="s">
+        <v>82</v>
+      </c>
+      <c r="I221">
+        <v>2</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>2</v>
+      </c>
+      <c r="L221">
+        <v>3</v>
+      </c>
+      <c r="M221">
+        <v>0</v>
+      </c>
+      <c r="N221">
+        <v>3</v>
+      </c>
+      <c r="O221" t="s">
+        <v>226</v>
+      </c>
+      <c r="P221" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q221">
+        <v>3.05</v>
+      </c>
+      <c r="R221">
+        <v>2.12</v>
+      </c>
+      <c r="S221">
+        <v>3.81</v>
+      </c>
+      <c r="T221">
+        <v>1.45</v>
+      </c>
+      <c r="U221">
+        <v>2.8</v>
+      </c>
+      <c r="V221">
+        <v>3.26</v>
+      </c>
+      <c r="W221">
+        <v>1.35</v>
+      </c>
+      <c r="X221">
+        <v>10</v>
+      </c>
+      <c r="Y221">
+        <v>1.06</v>
+      </c>
+      <c r="Z221">
+        <v>2.35</v>
+      </c>
+      <c r="AA221">
+        <v>3.1</v>
+      </c>
+      <c r="AB221">
+        <v>3</v>
+      </c>
+      <c r="AC221">
+        <v>0</v>
+      </c>
+      <c r="AD221">
+        <v>0</v>
+      </c>
+      <c r="AE221">
+        <v>0</v>
+      </c>
+      <c r="AF221">
+        <v>0</v>
+      </c>
+      <c r="AG221">
+        <v>2.05</v>
+      </c>
+      <c r="AH221">
+        <v>1.61</v>
+      </c>
+      <c r="AI221">
+        <v>1.83</v>
+      </c>
+      <c r="AJ221">
+        <v>1.83</v>
+      </c>
+      <c r="AK221">
+        <v>0</v>
+      </c>
+      <c r="AL221">
+        <v>0</v>
+      </c>
+      <c r="AM221">
+        <v>0</v>
+      </c>
+      <c r="AN221">
+        <v>1.58</v>
+      </c>
+      <c r="AO221">
+        <v>1.36</v>
+      </c>
+      <c r="AP221">
+        <v>1.69</v>
+      </c>
+      <c r="AQ221">
+        <v>1.25</v>
+      </c>
+      <c r="AR221">
+        <v>1.41</v>
+      </c>
+      <c r="AS221">
+        <v>1.35</v>
+      </c>
+      <c r="AT221">
+        <v>2.76</v>
+      </c>
+      <c r="AU221">
+        <v>5</v>
+      </c>
+      <c r="AV221">
+        <v>4</v>
+      </c>
+      <c r="AW221">
+        <v>13</v>
+      </c>
+      <c r="AX221">
+        <v>4</v>
+      </c>
+      <c r="AY221">
+        <v>18</v>
+      </c>
+      <c r="AZ221">
+        <v>8</v>
+      </c>
+      <c r="BA221">
+        <v>-1</v>
+      </c>
+      <c r="BB221">
+        <v>-1</v>
+      </c>
+      <c r="BC221">
+        <v>-1</v>
+      </c>
+      <c r="BD221">
+        <v>0</v>
+      </c>
+      <c r="BE221">
+        <v>0</v>
+      </c>
+      <c r="BF221">
+        <v>0</v>
+      </c>
+      <c r="BG221">
+        <v>0</v>
+      </c>
+      <c r="BH221">
+        <v>0</v>
+      </c>
+      <c r="BI221">
+        <v>0</v>
+      </c>
+      <c r="BJ221">
+        <v>0</v>
+      </c>
+      <c r="BK221">
+        <v>0</v>
+      </c>
+      <c r="BL221">
+        <v>0</v>
+      </c>
+      <c r="BM221">
+        <v>0</v>
+      </c>
+      <c r="BN221">
+        <v>0</v>
+      </c>
+      <c r="BO221">
+        <v>0</v>
+      </c>
+      <c r="BP221">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -46240,13 +46240,13 @@
         <v>8</v>
       </c>
       <c r="BA218">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB218">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC218">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD218">
         <v>0</v>
@@ -46302,7 +46302,7 @@
         <v>69</v>
       </c>
       <c r="E219" s="2">
-        <v>45724.33333333334</v>
+        <v>45724.375</v>
       </c>
       <c r="F219">
         <v>25</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="335">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -697,6 +697,9 @@
     <t>['9', '37', '83']</t>
   </si>
   <si>
+    <t>['75']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -1009,13 +1012,13 @@
     <t>['29']</t>
   </si>
   <si>
-    <t>['75']</t>
-  </si>
-  <si>
     <t>['12', '45+2']</t>
   </si>
   <si>
     <t>['31', '74']</t>
+  </si>
+  <si>
+    <t>['62']</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP221"/>
+  <dimension ref="A1:BP225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1633,7 +1636,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1711,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ2">
         <v>1.42</v>
@@ -1839,7 +1842,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -2045,7 +2048,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2457,7 +2460,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2663,7 +2666,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3075,7 +3078,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3156,7 +3159,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ9">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3487,7 +3490,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3771,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ12">
         <v>0.5</v>
@@ -3899,7 +3902,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4105,7 +4108,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4311,7 +4314,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4517,7 +4520,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -5007,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ18">
         <v>1.42</v>
@@ -5135,7 +5138,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5216,7 +5219,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ19">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5341,7 +5344,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5959,7 +5962,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6246,7 +6249,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ24">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR24">
         <v>1.31</v>
@@ -6371,7 +6374,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6655,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ26">
         <v>1.69</v>
@@ -6783,7 +6786,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7067,10 +7070,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ28">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR28">
         <v>1.62</v>
@@ -7195,7 +7198,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7401,7 +7404,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7479,7 +7482,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ30">
         <v>0.58</v>
@@ -7813,7 +7816,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8225,7 +8228,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8431,7 +8434,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8637,7 +8640,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -9049,7 +9052,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9255,7 +9258,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9667,7 +9670,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9745,7 +9748,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ41">
         <v>1.31</v>
@@ -9873,7 +9876,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10160,7 +10163,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ43">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR43">
         <v>1.55</v>
@@ -10285,7 +10288,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10363,7 +10366,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10491,7 +10494,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10572,7 +10575,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ45">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR45">
         <v>1.58</v>
@@ -10903,7 +10906,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11109,7 +11112,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11315,7 +11318,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11727,7 +11730,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12011,7 +12014,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ52">
         <v>1.08</v>
@@ -12345,7 +12348,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12757,7 +12760,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12963,7 +12966,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13247,10 +13250,10 @@
         <v>0.67</v>
       </c>
       <c r="AP58">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ58">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR58">
         <v>1.6</v>
@@ -13375,7 +13378,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13453,7 +13456,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ59">
         <v>1.25</v>
@@ -13868,7 +13871,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ61">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR61">
         <v>1.62</v>
@@ -14483,7 +14486,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ64">
         <v>1.69</v>
@@ -14611,7 +14614,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -15023,7 +15026,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15229,7 +15232,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -16134,7 +16137,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ72">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR72">
         <v>1.62</v>
@@ -16259,7 +16262,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16465,7 +16468,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16543,7 +16546,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ74">
         <v>1.69</v>
@@ -16671,7 +16674,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16877,7 +16880,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -16955,7 +16958,7 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ76">
         <v>1.42</v>
@@ -17289,7 +17292,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17576,7 +17579,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ79">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR79">
         <v>1.3</v>
@@ -18194,7 +18197,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ82">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR82">
         <v>1.36</v>
@@ -18319,7 +18322,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18397,7 +18400,7 @@
         <v>2.5</v>
       </c>
       <c r="AP83">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ83">
         <v>1.67</v>
@@ -18937,7 +18940,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19349,7 +19352,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19761,7 +19764,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19967,7 +19970,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20173,7 +20176,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20251,7 +20254,7 @@
         <v>0.6</v>
       </c>
       <c r="AP92">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20379,7 +20382,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20585,7 +20588,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20791,7 +20794,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -20872,7 +20875,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ95">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR95">
         <v>1.56</v>
@@ -21203,7 +21206,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21281,7 +21284,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ97">
         <v>1.31</v>
@@ -21409,7 +21412,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21615,7 +21618,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22439,7 +22442,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22851,7 +22854,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -23057,7 +23060,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23138,7 +23141,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ106">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR106">
         <v>1.65</v>
@@ -23263,7 +23266,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23469,7 +23472,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23675,7 +23678,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -23959,7 +23962,7 @@
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ110">
         <v>1.33</v>
@@ -24499,7 +24502,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24577,7 +24580,7 @@
         <v>1.17</v>
       </c>
       <c r="AP113">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ113">
         <v>1.54</v>
@@ -24705,7 +24708,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25117,7 +25120,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25195,7 +25198,7 @@
         <v>1</v>
       </c>
       <c r="AP116">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ116">
         <v>1.31</v>
@@ -25323,7 +25326,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25529,7 +25532,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25610,7 +25613,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ118">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR118">
         <v>1.48</v>
@@ -26353,7 +26356,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26765,7 +26768,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -26846,7 +26849,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ124">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR124">
         <v>1.69</v>
@@ -27177,7 +27180,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27255,7 +27258,7 @@
         <v>1.17</v>
       </c>
       <c r="AP126">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ126">
         <v>1.42</v>
@@ -27589,7 +27592,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -28001,7 +28004,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28082,7 +28085,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ130">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR130">
         <v>1.55</v>
@@ -28413,7 +28416,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28619,7 +28622,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28825,7 +28828,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -28903,7 +28906,7 @@
         <v>1.43</v>
       </c>
       <c r="AP134">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ134">
         <v>1.54</v>
@@ -29315,7 +29318,7 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ136">
         <v>1.08</v>
@@ -29443,7 +29446,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29855,7 +29858,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -29933,7 +29936,7 @@
         <v>0.29</v>
       </c>
       <c r="AP139">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ139">
         <v>1</v>
@@ -30267,7 +30270,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30679,7 +30682,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30885,7 +30888,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -30963,7 +30966,7 @@
         <v>1.29</v>
       </c>
       <c r="AP144">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ144">
         <v>1.08</v>
@@ -31297,7 +31300,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31503,7 +31506,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31709,7 +31712,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -31787,10 +31790,10 @@
         <v>0.38</v>
       </c>
       <c r="AP148">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ148">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR148">
         <v>1.62</v>
@@ -31996,7 +31999,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ149">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR149">
         <v>1.55</v>
@@ -32327,7 +32330,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32533,7 +32536,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32945,7 +32948,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33229,7 +33232,7 @@
         <v>0.63</v>
       </c>
       <c r="AP155">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ155">
         <v>0.58</v>
@@ -33644,7 +33647,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ157">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR157">
         <v>1.59</v>
@@ -33769,7 +33772,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34387,7 +34390,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34799,7 +34802,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34877,7 +34880,7 @@
         <v>2.38</v>
       </c>
       <c r="AP163">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ163">
         <v>1.67</v>
@@ -35005,7 +35008,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35211,7 +35214,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35623,7 +35626,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -35701,7 +35704,7 @@
         <v>1.25</v>
       </c>
       <c r="AP167">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ167">
         <v>1.25</v>
@@ -35910,7 +35913,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ168">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR168">
         <v>1.2</v>
@@ -36447,7 +36450,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -37065,7 +37068,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37683,7 +37686,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -38173,7 +38176,7 @@
         <v>1.33</v>
       </c>
       <c r="AP179">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ179">
         <v>1.42</v>
@@ -38301,7 +38304,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38713,7 +38716,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38791,7 +38794,7 @@
         <v>0.78</v>
       </c>
       <c r="AP182">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ182">
         <v>1.08</v>
@@ -38919,7 +38922,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39409,7 +39412,7 @@
         <v>1.2</v>
       </c>
       <c r="AP185">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ185">
         <v>1</v>
@@ -39537,7 +39540,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39949,7 +39952,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40236,7 +40239,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ189">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR189">
         <v>1.67</v>
@@ -40361,7 +40364,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40442,7 +40445,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ190">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR190">
         <v>1.31</v>
@@ -40773,7 +40776,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41185,7 +41188,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41263,7 +41266,7 @@
         <v>1.3</v>
       </c>
       <c r="AP194">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ194">
         <v>1.33</v>
@@ -41597,7 +41600,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41803,7 +41806,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -42215,7 +42218,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42708,7 +42711,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ201">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AR201">
         <v>1.53</v>
@@ -42833,7 +42836,7 @@
         <v>123</v>
       </c>
       <c r="P202" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q202">
         <v>4.3</v>
@@ -42914,7 +42917,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ202">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR202">
         <v>1.26</v>
@@ -43117,7 +43120,7 @@
         <v>1.4</v>
       </c>
       <c r="AP203">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ203">
         <v>1.25</v>
@@ -43245,7 +43248,7 @@
         <v>117</v>
       </c>
       <c r="P204" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q204">
         <v>3.1</v>
@@ -43323,7 +43326,7 @@
         <v>1.45</v>
       </c>
       <c r="AP204">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ204">
         <v>1.54</v>
@@ -43657,7 +43660,7 @@
         <v>218</v>
       </c>
       <c r="P206" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q206">
         <v>3.65</v>
@@ -43863,7 +43866,7 @@
         <v>156</v>
       </c>
       <c r="P207" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q207">
         <v>3.45</v>
@@ -44069,7 +44072,7 @@
         <v>197</v>
       </c>
       <c r="P208" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q208">
         <v>3.5</v>
@@ -44275,7 +44278,7 @@
         <v>129</v>
       </c>
       <c r="P209" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q209">
         <v>2.4</v>
@@ -44893,7 +44896,7 @@
         <v>220</v>
       </c>
       <c r="P212" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q212">
         <v>2.43</v>
@@ -45099,7 +45102,7 @@
         <v>221</v>
       </c>
       <c r="P213" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q213">
         <v>3.15</v>
@@ -45923,7 +45926,7 @@
         <v>89</v>
       </c>
       <c r="P217" t="s">
-        <v>331</v>
+        <v>227</v>
       </c>
       <c r="Q217">
         <v>2.5</v>
@@ -46129,7 +46132,7 @@
         <v>89</v>
       </c>
       <c r="P218" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q218">
         <v>3.6</v>
@@ -46904,6 +46907,830 @@
       </c>
       <c r="BP221">
         <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7502824</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45725.33333333334</v>
+      </c>
+      <c r="F222">
+        <v>25</v>
+      </c>
+      <c r="G222" t="s">
+        <v>71</v>
+      </c>
+      <c r="H222" t="s">
+        <v>76</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+      <c r="M222">
+        <v>0</v>
+      </c>
+      <c r="N222">
+        <v>0</v>
+      </c>
+      <c r="O222" t="s">
+        <v>89</v>
+      </c>
+      <c r="P222" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q222">
+        <v>2.8</v>
+      </c>
+      <c r="R222">
+        <v>2.03</v>
+      </c>
+      <c r="S222">
+        <v>3.92</v>
+      </c>
+      <c r="T222">
+        <v>1.42</v>
+      </c>
+      <c r="U222">
+        <v>2.7</v>
+      </c>
+      <c r="V222">
+        <v>3.1</v>
+      </c>
+      <c r="W222">
+        <v>1.33</v>
+      </c>
+      <c r="X222">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y222">
+        <v>1.02</v>
+      </c>
+      <c r="Z222">
+        <v>2.2</v>
+      </c>
+      <c r="AA222">
+        <v>3.2</v>
+      </c>
+      <c r="AB222">
+        <v>3.25</v>
+      </c>
+      <c r="AC222">
+        <v>1.01</v>
+      </c>
+      <c r="AD222">
+        <v>8.9</v>
+      </c>
+      <c r="AE222">
+        <v>1.31</v>
+      </c>
+      <c r="AF222">
+        <v>2.93</v>
+      </c>
+      <c r="AG222">
+        <v>2</v>
+      </c>
+      <c r="AH222">
+        <v>1.65</v>
+      </c>
+      <c r="AI222">
+        <v>1.84</v>
+      </c>
+      <c r="AJ222">
+        <v>1.86</v>
+      </c>
+      <c r="AK222">
+        <v>1.31</v>
+      </c>
+      <c r="AL222">
+        <v>1.31</v>
+      </c>
+      <c r="AM222">
+        <v>1.65</v>
+      </c>
+      <c r="AN222">
+        <v>0.92</v>
+      </c>
+      <c r="AO222">
+        <v>0.33</v>
+      </c>
+      <c r="AP222">
+        <v>0.92</v>
+      </c>
+      <c r="AQ222">
+        <v>0.38</v>
+      </c>
+      <c r="AR222">
+        <v>1.27</v>
+      </c>
+      <c r="AS222">
+        <v>1.52</v>
+      </c>
+      <c r="AT222">
+        <v>2.79</v>
+      </c>
+      <c r="AU222">
+        <v>4</v>
+      </c>
+      <c r="AV222">
+        <v>7</v>
+      </c>
+      <c r="AW222">
+        <v>10</v>
+      </c>
+      <c r="AX222">
+        <v>3</v>
+      </c>
+      <c r="AY222">
+        <v>14</v>
+      </c>
+      <c r="AZ222">
+        <v>10</v>
+      </c>
+      <c r="BA222">
+        <v>2</v>
+      </c>
+      <c r="BB222">
+        <v>3</v>
+      </c>
+      <c r="BC222">
+        <v>5</v>
+      </c>
+      <c r="BD222">
+        <v>0</v>
+      </c>
+      <c r="BE222">
+        <v>0</v>
+      </c>
+      <c r="BF222">
+        <v>0</v>
+      </c>
+      <c r="BG222">
+        <v>0</v>
+      </c>
+      <c r="BH222">
+        <v>0</v>
+      </c>
+      <c r="BI222">
+        <v>0</v>
+      </c>
+      <c r="BJ222">
+        <v>0</v>
+      </c>
+      <c r="BK222">
+        <v>0</v>
+      </c>
+      <c r="BL222">
+        <v>0</v>
+      </c>
+      <c r="BM222">
+        <v>0</v>
+      </c>
+      <c r="BN222">
+        <v>0</v>
+      </c>
+      <c r="BO222">
+        <v>0</v>
+      </c>
+      <c r="BP222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7502827</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45725.45833333334</v>
+      </c>
+      <c r="F223">
+        <v>25</v>
+      </c>
+      <c r="G223" t="s">
+        <v>70</v>
+      </c>
+      <c r="H223" t="s">
+        <v>73</v>
+      </c>
+      <c r="I223">
+        <v>0</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>0</v>
+      </c>
+      <c r="L223">
+        <v>1</v>
+      </c>
+      <c r="M223">
+        <v>1</v>
+      </c>
+      <c r="N223">
+        <v>2</v>
+      </c>
+      <c r="O223" t="s">
+        <v>227</v>
+      </c>
+      <c r="P223" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q223">
+        <v>2.73</v>
+      </c>
+      <c r="R223">
+        <v>1.99</v>
+      </c>
+      <c r="S223">
+        <v>4.25</v>
+      </c>
+      <c r="T223">
+        <v>1.44</v>
+      </c>
+      <c r="U223">
+        <v>2.62</v>
+      </c>
+      <c r="V223">
+        <v>3.22</v>
+      </c>
+      <c r="W223">
+        <v>1.31</v>
+      </c>
+      <c r="X223">
+        <v>9.4</v>
+      </c>
+      <c r="Y223">
+        <v>1.01</v>
+      </c>
+      <c r="Z223">
+        <v>2.1</v>
+      </c>
+      <c r="AA223">
+        <v>3.2</v>
+      </c>
+      <c r="AB223">
+        <v>3.5</v>
+      </c>
+      <c r="AC223">
+        <v>1.01</v>
+      </c>
+      <c r="AD223">
+        <v>9</v>
+      </c>
+      <c r="AE223">
+        <v>1.33</v>
+      </c>
+      <c r="AF223">
+        <v>2.84</v>
+      </c>
+      <c r="AG223">
+        <v>2.2</v>
+      </c>
+      <c r="AH223">
+        <v>1.55</v>
+      </c>
+      <c r="AI223">
+        <v>1.9</v>
+      </c>
+      <c r="AJ223">
+        <v>1.8</v>
+      </c>
+      <c r="AK223">
+        <v>1.28</v>
+      </c>
+      <c r="AL223">
+        <v>1.31</v>
+      </c>
+      <c r="AM223">
+        <v>1.71</v>
+      </c>
+      <c r="AN223">
+        <v>0.91</v>
+      </c>
+      <c r="AO223">
+        <v>1.08</v>
+      </c>
+      <c r="AP223">
+        <v>0.92</v>
+      </c>
+      <c r="AQ223">
+        <v>1.08</v>
+      </c>
+      <c r="AR223">
+        <v>1.66</v>
+      </c>
+      <c r="AS223">
+        <v>1.28</v>
+      </c>
+      <c r="AT223">
+        <v>2.94</v>
+      </c>
+      <c r="AU223">
+        <v>3</v>
+      </c>
+      <c r="AV223">
+        <v>7</v>
+      </c>
+      <c r="AW223">
+        <v>5</v>
+      </c>
+      <c r="AX223">
+        <v>8</v>
+      </c>
+      <c r="AY223">
+        <v>8</v>
+      </c>
+      <c r="AZ223">
+        <v>15</v>
+      </c>
+      <c r="BA223">
+        <v>-1</v>
+      </c>
+      <c r="BB223">
+        <v>-1</v>
+      </c>
+      <c r="BC223">
+        <v>-1</v>
+      </c>
+      <c r="BD223">
+        <v>0</v>
+      </c>
+      <c r="BE223">
+        <v>0</v>
+      </c>
+      <c r="BF223">
+        <v>0</v>
+      </c>
+      <c r="BG223">
+        <v>0</v>
+      </c>
+      <c r="BH223">
+        <v>0</v>
+      </c>
+      <c r="BI223">
+        <v>0</v>
+      </c>
+      <c r="BJ223">
+        <v>0</v>
+      </c>
+      <c r="BK223">
+        <v>0</v>
+      </c>
+      <c r="BL223">
+        <v>0</v>
+      </c>
+      <c r="BM223">
+        <v>0</v>
+      </c>
+      <c r="BN223">
+        <v>0</v>
+      </c>
+      <c r="BO223">
+        <v>0</v>
+      </c>
+      <c r="BP223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7502823</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45725.52083333334</v>
+      </c>
+      <c r="F224">
+        <v>25</v>
+      </c>
+      <c r="G224" t="s">
+        <v>80</v>
+      </c>
+      <c r="H224" t="s">
+        <v>84</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>0</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+      <c r="M224">
+        <v>1</v>
+      </c>
+      <c r="N224">
+        <v>1</v>
+      </c>
+      <c r="O224" t="s">
+        <v>89</v>
+      </c>
+      <c r="P224" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q224">
+        <v>5.44</v>
+      </c>
+      <c r="R224">
+        <v>2.31</v>
+      </c>
+      <c r="S224">
+        <v>2.24</v>
+      </c>
+      <c r="T224">
+        <v>1.37</v>
+      </c>
+      <c r="U224">
+        <v>3.03</v>
+      </c>
+      <c r="V224">
+        <v>2.87</v>
+      </c>
+      <c r="W224">
+        <v>1.41</v>
+      </c>
+      <c r="X224">
+        <v>7</v>
+      </c>
+      <c r="Y224">
+        <v>1.1</v>
+      </c>
+      <c r="Z224">
+        <v>4.8</v>
+      </c>
+      <c r="AA224">
+        <v>3.7</v>
+      </c>
+      <c r="AB224">
+        <v>1.66</v>
+      </c>
+      <c r="AC224">
+        <v>0</v>
+      </c>
+      <c r="AD224">
+        <v>0</v>
+      </c>
+      <c r="AE224">
+        <v>2.53</v>
+      </c>
+      <c r="AF224">
+        <v>1.51</v>
+      </c>
+      <c r="AG224">
+        <v>1.85</v>
+      </c>
+      <c r="AH224">
+        <v>1.75</v>
+      </c>
+      <c r="AI224">
+        <v>1.8</v>
+      </c>
+      <c r="AJ224">
+        <v>1.91</v>
+      </c>
+      <c r="AK224">
+        <v>0</v>
+      </c>
+      <c r="AL224">
+        <v>0</v>
+      </c>
+      <c r="AM224">
+        <v>0</v>
+      </c>
+      <c r="AN224">
+        <v>0.75</v>
+      </c>
+      <c r="AO224">
+        <v>1.42</v>
+      </c>
+      <c r="AP224">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ224">
+        <v>1.54</v>
+      </c>
+      <c r="AR224">
+        <v>1.35</v>
+      </c>
+      <c r="AS224">
+        <v>1.49</v>
+      </c>
+      <c r="AT224">
+        <v>2.84</v>
+      </c>
+      <c r="AU224">
+        <v>7</v>
+      </c>
+      <c r="AV224">
+        <v>4</v>
+      </c>
+      <c r="AW224">
+        <v>8</v>
+      </c>
+      <c r="AX224">
+        <v>11</v>
+      </c>
+      <c r="AY224">
+        <v>15</v>
+      </c>
+      <c r="AZ224">
+        <v>15</v>
+      </c>
+      <c r="BA224">
+        <v>-1</v>
+      </c>
+      <c r="BB224">
+        <v>-1</v>
+      </c>
+      <c r="BC224">
+        <v>-1</v>
+      </c>
+      <c r="BD224">
+        <v>0</v>
+      </c>
+      <c r="BE224">
+        <v>0</v>
+      </c>
+      <c r="BF224">
+        <v>0</v>
+      </c>
+      <c r="BG224">
+        <v>0</v>
+      </c>
+      <c r="BH224">
+        <v>0</v>
+      </c>
+      <c r="BI224">
+        <v>0</v>
+      </c>
+      <c r="BJ224">
+        <v>0</v>
+      </c>
+      <c r="BK224">
+        <v>0</v>
+      </c>
+      <c r="BL224">
+        <v>0</v>
+      </c>
+      <c r="BM224">
+        <v>0</v>
+      </c>
+      <c r="BN224">
+        <v>0</v>
+      </c>
+      <c r="BO224">
+        <v>0</v>
+      </c>
+      <c r="BP224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7502822</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45725.625</v>
+      </c>
+      <c r="F225">
+        <v>25</v>
+      </c>
+      <c r="G225" t="s">
+        <v>86</v>
+      </c>
+      <c r="H225" t="s">
+        <v>81</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>0</v>
+      </c>
+      <c r="L225">
+        <v>0</v>
+      </c>
+      <c r="M225">
+        <v>0</v>
+      </c>
+      <c r="N225">
+        <v>0</v>
+      </c>
+      <c r="O225" t="s">
+        <v>89</v>
+      </c>
+      <c r="P225" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q225">
+        <v>2.62</v>
+      </c>
+      <c r="R225">
+        <v>2.16</v>
+      </c>
+      <c r="S225">
+        <v>3.82</v>
+      </c>
+      <c r="T225">
+        <v>1.36</v>
+      </c>
+      <c r="U225">
+        <v>2.94</v>
+      </c>
+      <c r="V225">
+        <v>2.7</v>
+      </c>
+      <c r="W225">
+        <v>1.42</v>
+      </c>
+      <c r="X225">
+        <v>6.2</v>
+      </c>
+      <c r="Y225">
+        <v>1.07</v>
+      </c>
+      <c r="Z225">
+        <v>1.95</v>
+      </c>
+      <c r="AA225">
+        <v>3.4</v>
+      </c>
+      <c r="AB225">
+        <v>3.5</v>
+      </c>
+      <c r="AC225">
+        <v>1</v>
+      </c>
+      <c r="AD225">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE225">
+        <v>1.23</v>
+      </c>
+      <c r="AF225">
+        <v>3.44</v>
+      </c>
+      <c r="AG225">
+        <v>1.75</v>
+      </c>
+      <c r="AH225">
+        <v>1.85</v>
+      </c>
+      <c r="AI225">
+        <v>1.68</v>
+      </c>
+      <c r="AJ225">
+        <v>2.06</v>
+      </c>
+      <c r="AK225">
+        <v>1.31</v>
+      </c>
+      <c r="AL225">
+        <v>1.28</v>
+      </c>
+      <c r="AM225">
+        <v>1.7</v>
+      </c>
+      <c r="AN225">
+        <v>1.92</v>
+      </c>
+      <c r="AO225">
+        <v>1</v>
+      </c>
+      <c r="AP225">
+        <v>1.85</v>
+      </c>
+      <c r="AQ225">
+        <v>1</v>
+      </c>
+      <c r="AR225">
+        <v>1.56</v>
+      </c>
+      <c r="AS225">
+        <v>1.18</v>
+      </c>
+      <c r="AT225">
+        <v>2.74</v>
+      </c>
+      <c r="AU225">
+        <v>5</v>
+      </c>
+      <c r="AV225">
+        <v>2</v>
+      </c>
+      <c r="AW225">
+        <v>8</v>
+      </c>
+      <c r="AX225">
+        <v>2</v>
+      </c>
+      <c r="AY225">
+        <v>13</v>
+      </c>
+      <c r="AZ225">
+        <v>4</v>
+      </c>
+      <c r="BA225">
+        <v>12</v>
+      </c>
+      <c r="BB225">
+        <v>1</v>
+      </c>
+      <c r="BC225">
+        <v>13</v>
+      </c>
+      <c r="BD225">
+        <v>1.63</v>
+      </c>
+      <c r="BE225">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF225">
+        <v>2.65</v>
+      </c>
+      <c r="BG225">
+        <v>1.16</v>
+      </c>
+      <c r="BH225">
+        <v>4.15</v>
+      </c>
+      <c r="BI225">
+        <v>1.34</v>
+      </c>
+      <c r="BJ225">
+        <v>2.88</v>
+      </c>
+      <c r="BK225">
+        <v>1.73</v>
+      </c>
+      <c r="BL225">
+        <v>2</v>
+      </c>
+      <c r="BM225">
+        <v>2</v>
+      </c>
+      <c r="BN225">
+        <v>1.69</v>
+      </c>
+      <c r="BO225">
+        <v>2.56</v>
+      </c>
+      <c r="BP225">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -46861,13 +46861,13 @@
         <v>8</v>
       </c>
       <c r="BA221">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB221">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC221">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BD221">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="335">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1380,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP225"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1717,7 +1717,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ2">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2126,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ4">
         <v>1.33</v>
@@ -6040,7 +6040,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ23">
         <v>1.25</v>
@@ -6455,7 +6455,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ25">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR25">
         <v>1.23</v>
@@ -9957,7 +9957,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ42">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR42">
         <v>1.42</v>
@@ -10572,7 +10572,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ45">
         <v>1.54</v>
@@ -12841,7 +12841,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ56">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR56">
         <v>1.67</v>
@@ -13662,7 +13662,7 @@
         <v>0.67</v>
       </c>
       <c r="AP60">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -16961,7 +16961,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ76">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR76">
         <v>1.55</v>
@@ -17576,7 +17576,7 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ79">
         <v>0.38</v>
@@ -20669,7 +20669,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ94">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR94">
         <v>1.74</v>
@@ -21078,7 +21078,7 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ96">
         <v>1.38</v>
@@ -24786,7 +24786,7 @@
         <v>1.6</v>
       </c>
       <c r="AP114">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ114">
         <v>1.08</v>
@@ -25819,7 +25819,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ119">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR119">
         <v>1.64</v>
@@ -27876,7 +27876,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ129">
         <v>0.5</v>
@@ -28497,7 +28497,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ132">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR132">
         <v>1.39</v>
@@ -32614,7 +32614,7 @@
         <v>1.43</v>
       </c>
       <c r="AP152">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ152">
         <v>1.42</v>
@@ -33029,7 +33029,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ154">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR154">
         <v>1.58</v>
@@ -35498,7 +35498,7 @@
         <v>1.56</v>
       </c>
       <c r="AP166">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ166">
         <v>1.69</v>
@@ -36531,7 +36531,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ171">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR171">
         <v>1.04</v>
@@ -39000,7 +39000,7 @@
         <v>0.67</v>
       </c>
       <c r="AP183">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ183">
         <v>1</v>
@@ -39209,7 +39209,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ184">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR184">
         <v>1.54</v>
@@ -43944,7 +43944,7 @@
         <v>1.45</v>
       </c>
       <c r="AP207">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AQ207">
         <v>1.31</v>
@@ -44153,7 +44153,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ208">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR208">
         <v>1.4</v>
@@ -47273,13 +47273,13 @@
         <v>15</v>
       </c>
       <c r="BA223">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB223">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC223">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD223">
         <v>0</v>
@@ -47479,13 +47479,13 @@
         <v>15</v>
       </c>
       <c r="BA224">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB224">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BC224">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="BD224">
         <v>0</v>
@@ -47731,6 +47731,212 @@
       </c>
       <c r="BP225">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7502821</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45726.625</v>
+      </c>
+      <c r="F226">
+        <v>25</v>
+      </c>
+      <c r="G226" t="s">
+        <v>72</v>
+      </c>
+      <c r="H226" t="s">
+        <v>87</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>1</v>
+      </c>
+      <c r="K226">
+        <v>1</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+      <c r="N226">
+        <v>1</v>
+      </c>
+      <c r="O226" t="s">
+        <v>89</v>
+      </c>
+      <c r="P226" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q226">
+        <v>4</v>
+      </c>
+      <c r="R226">
+        <v>1.91</v>
+      </c>
+      <c r="S226">
+        <v>3.25</v>
+      </c>
+      <c r="T226">
+        <v>1.57</v>
+      </c>
+      <c r="U226">
+        <v>2.25</v>
+      </c>
+      <c r="V226">
+        <v>3.75</v>
+      </c>
+      <c r="W226">
+        <v>1.25</v>
+      </c>
+      <c r="X226">
+        <v>11</v>
+      </c>
+      <c r="Y226">
+        <v>1.05</v>
+      </c>
+      <c r="Z226">
+        <v>3.1</v>
+      </c>
+      <c r="AA226">
+        <v>2.95</v>
+      </c>
+      <c r="AB226">
+        <v>2.4</v>
+      </c>
+      <c r="AC226">
+        <v>1.09</v>
+      </c>
+      <c r="AD226">
+        <v>6.5</v>
+      </c>
+      <c r="AE226">
+        <v>1.5</v>
+      </c>
+      <c r="AF226">
+        <v>2.5</v>
+      </c>
+      <c r="AG226">
+        <v>2.37</v>
+      </c>
+      <c r="AH226">
+        <v>1.48</v>
+      </c>
+      <c r="AI226">
+        <v>2.1</v>
+      </c>
+      <c r="AJ226">
+        <v>1.67</v>
+      </c>
+      <c r="AK226">
+        <v>1.55</v>
+      </c>
+      <c r="AL226">
+        <v>1.35</v>
+      </c>
+      <c r="AM226">
+        <v>1.35</v>
+      </c>
+      <c r="AN226">
+        <v>1.67</v>
+      </c>
+      <c r="AO226">
+        <v>1.42</v>
+      </c>
+      <c r="AP226">
+        <v>1.54</v>
+      </c>
+      <c r="AQ226">
+        <v>1.54</v>
+      </c>
+      <c r="AR226">
+        <v>1.36</v>
+      </c>
+      <c r="AS226">
+        <v>1.34</v>
+      </c>
+      <c r="AT226">
+        <v>2.7</v>
+      </c>
+      <c r="AU226">
+        <v>5</v>
+      </c>
+      <c r="AV226">
+        <v>5</v>
+      </c>
+      <c r="AW226">
+        <v>5</v>
+      </c>
+      <c r="AX226">
+        <v>9</v>
+      </c>
+      <c r="AY226">
+        <v>10</v>
+      </c>
+      <c r="AZ226">
+        <v>14</v>
+      </c>
+      <c r="BA226">
+        <v>5</v>
+      </c>
+      <c r="BB226">
+        <v>8</v>
+      </c>
+      <c r="BC226">
+        <v>13</v>
+      </c>
+      <c r="BD226">
+        <v>2.24</v>
+      </c>
+      <c r="BE226">
+        <v>6.5</v>
+      </c>
+      <c r="BF226">
+        <v>1.98</v>
+      </c>
+      <c r="BG226">
+        <v>1.17</v>
+      </c>
+      <c r="BH226">
+        <v>4.05</v>
+      </c>
+      <c r="BI226">
+        <v>1.34</v>
+      </c>
+      <c r="BJ226">
+        <v>2.78</v>
+      </c>
+      <c r="BK226">
+        <v>1.63</v>
+      </c>
+      <c r="BL226">
+        <v>2.09</v>
+      </c>
+      <c r="BM226">
+        <v>2</v>
+      </c>
+      <c r="BN226">
+        <v>1.73</v>
+      </c>
+      <c r="BO226">
+        <v>2.67</v>
+      </c>
+      <c r="BP226">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="336">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1020,6 +1020,9 @@
   <si>
     <t>['62']</t>
   </si>
+  <si>
+    <t>['28', '48']</t>
+  </si>
 </sst>
 </file>
 
@@ -1380,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP227"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2747,7 +2750,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ7">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3980,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ13">
         <v>1.54</v>
@@ -5631,7 +5634,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ21">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR21">
         <v>1.84</v>
@@ -8100,7 +8103,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ33">
         <v>1.38</v>
@@ -11396,7 +11399,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ49">
         <v>1.67</v>
@@ -12017,7 +12020,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ52">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR52">
         <v>1.2</v>
@@ -15725,7 +15728,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ70">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR70">
         <v>1.47</v>
@@ -17991,7 +17994,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ81">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -18194,7 +18197,7 @@
         <v>1.6</v>
       </c>
       <c r="AP82">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ82">
         <v>1.54</v>
@@ -21696,7 +21699,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ99">
         <v>1.33</v>
@@ -22729,7 +22732,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ104">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR104">
         <v>1.44</v>
@@ -22932,7 +22935,7 @@
         <v>1.67</v>
       </c>
       <c r="AP105">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ105">
         <v>1.69</v>
@@ -27467,7 +27470,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ127">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR127">
         <v>0.99</v>
@@ -28288,7 +28291,7 @@
         <v>1.57</v>
       </c>
       <c r="AP131">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ131">
         <v>1.08</v>
@@ -29733,7 +29736,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ138">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR138">
         <v>1.22</v>
@@ -30142,7 +30145,7 @@
         <v>1.5</v>
       </c>
       <c r="AP140">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ140">
         <v>1.31</v>
@@ -33850,7 +33853,7 @@
         <v>1.5</v>
       </c>
       <c r="AP158">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ158">
         <v>1.08</v>
@@ -35089,7 +35092,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ164">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR164">
         <v>1.48</v>
@@ -37970,7 +37973,7 @@
         <v>0.67</v>
       </c>
       <c r="AP178">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ178">
         <v>0.5</v>
@@ -38797,7 +38800,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ182">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR182">
         <v>1.54</v>
@@ -40857,7 +40860,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ192">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR192">
         <v>1.73</v>
@@ -41678,7 +41681,7 @@
         <v>1.3</v>
       </c>
       <c r="AP196">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ196">
         <v>1.42</v>
@@ -45180,7 +45183,7 @@
         <v>0.64</v>
       </c>
       <c r="AP213">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ213">
         <v>0.58</v>
@@ -45801,7 +45804,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ216">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR216">
         <v>1.76</v>
@@ -47937,6 +47940,212 @@
       </c>
       <c r="BP226">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7502836</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45730.65625</v>
+      </c>
+      <c r="F227">
+        <v>26</v>
+      </c>
+      <c r="G227" t="s">
+        <v>81</v>
+      </c>
+      <c r="H227" t="s">
+        <v>83</v>
+      </c>
+      <c r="I227">
+        <v>1</v>
+      </c>
+      <c r="J227">
+        <v>1</v>
+      </c>
+      <c r="K227">
+        <v>2</v>
+      </c>
+      <c r="L227">
+        <v>1</v>
+      </c>
+      <c r="M227">
+        <v>2</v>
+      </c>
+      <c r="N227">
+        <v>3</v>
+      </c>
+      <c r="O227" t="s">
+        <v>156</v>
+      </c>
+      <c r="P227" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q227">
+        <v>2.9</v>
+      </c>
+      <c r="R227">
+        <v>2</v>
+      </c>
+      <c r="S227">
+        <v>3.6</v>
+      </c>
+      <c r="T227">
+        <v>1.44</v>
+      </c>
+      <c r="U227">
+        <v>2.55</v>
+      </c>
+      <c r="V227">
+        <v>3</v>
+      </c>
+      <c r="W227">
+        <v>1.33</v>
+      </c>
+      <c r="X227">
+        <v>8.25</v>
+      </c>
+      <c r="Y227">
+        <v>1.06</v>
+      </c>
+      <c r="Z227">
+        <v>2.25</v>
+      </c>
+      <c r="AA227">
+        <v>3.15</v>
+      </c>
+      <c r="AB227">
+        <v>3.1</v>
+      </c>
+      <c r="AC227">
+        <v>1.07</v>
+      </c>
+      <c r="AD227">
+        <v>7.5</v>
+      </c>
+      <c r="AE227">
+        <v>1.38</v>
+      </c>
+      <c r="AF227">
+        <v>2.9</v>
+      </c>
+      <c r="AG227">
+        <v>2.05</v>
+      </c>
+      <c r="AH227">
+        <v>1.65</v>
+      </c>
+      <c r="AI227">
+        <v>1.87</v>
+      </c>
+      <c r="AJ227">
+        <v>1.82</v>
+      </c>
+      <c r="AK227">
+        <v>1.35</v>
+      </c>
+      <c r="AL227">
+        <v>1.32</v>
+      </c>
+      <c r="AM227">
+        <v>1.58</v>
+      </c>
+      <c r="AN227">
+        <v>1.42</v>
+      </c>
+      <c r="AO227">
+        <v>1.08</v>
+      </c>
+      <c r="AP227">
+        <v>1.31</v>
+      </c>
+      <c r="AQ227">
+        <v>1.23</v>
+      </c>
+      <c r="AR227">
+        <v>1.49</v>
+      </c>
+      <c r="AS227">
+        <v>1.39</v>
+      </c>
+      <c r="AT227">
+        <v>2.88</v>
+      </c>
+      <c r="AU227">
+        <v>5</v>
+      </c>
+      <c r="AV227">
+        <v>3</v>
+      </c>
+      <c r="AW227">
+        <v>6</v>
+      </c>
+      <c r="AX227">
+        <v>8</v>
+      </c>
+      <c r="AY227">
+        <v>11</v>
+      </c>
+      <c r="AZ227">
+        <v>11</v>
+      </c>
+      <c r="BA227">
+        <v>6</v>
+      </c>
+      <c r="BB227">
+        <v>2</v>
+      </c>
+      <c r="BC227">
+        <v>8</v>
+      </c>
+      <c r="BD227">
+        <v>1.95</v>
+      </c>
+      <c r="BE227">
+        <v>8</v>
+      </c>
+      <c r="BF227">
+        <v>2.1</v>
+      </c>
+      <c r="BG227">
+        <v>1.15</v>
+      </c>
+      <c r="BH227">
+        <v>4.45</v>
+      </c>
+      <c r="BI227">
+        <v>1.29</v>
+      </c>
+      <c r="BJ227">
+        <v>3.12</v>
+      </c>
+      <c r="BK227">
+        <v>1.53</v>
+      </c>
+      <c r="BL227">
+        <v>2.34</v>
+      </c>
+      <c r="BM227">
+        <v>1.87</v>
+      </c>
+      <c r="BN227">
+        <v>1.87</v>
+      </c>
+      <c r="BO227">
+        <v>2.35</v>
+      </c>
+      <c r="BP227">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="339">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -700,6 +700,12 @@
     <t>['75']</t>
   </si>
   <si>
+    <t>['14', '25']</t>
+  </si>
+  <si>
+    <t>['11', '50', '56', '90+2']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -1022,6 +1028,9 @@
   </si>
   <si>
     <t>['28', '48']</t>
+  </si>
+  <si>
+    <t>['33', '62']</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP227"/>
+  <dimension ref="A1:BP231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1639,7 +1648,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1845,7 +1854,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -2051,7 +2060,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2335,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ5">
         <v>1.69</v>
@@ -2463,7 +2472,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2544,7 +2553,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2669,7 +2678,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3081,7 +3090,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3493,7 +3502,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3571,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>1.08</v>
@@ -3905,7 +3914,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4111,7 +4120,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4317,7 +4326,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4523,7 +4532,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4604,7 +4613,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ16">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4807,7 +4816,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ17">
         <v>0.58</v>
@@ -5016,7 +5025,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ18">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5141,7 +5150,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5347,7 +5356,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5840,7 +5849,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ22">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR22">
         <v>1.3</v>
@@ -5965,7 +5974,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6249,7 +6258,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ24">
         <v>0.38</v>
@@ -6377,7 +6386,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6789,7 +6798,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7201,7 +7210,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7279,7 +7288,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
         <v>1.08</v>
@@ -7407,7 +7416,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7819,7 +7828,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7900,7 +7909,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ32">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR32">
         <v>2.27</v>
@@ -8231,7 +8240,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8437,7 +8446,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8518,7 +8527,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ35">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR35">
         <v>1.95</v>
@@ -8643,7 +8652,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8721,7 +8730,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ36">
         <v>0.5</v>
@@ -9055,7 +9064,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9261,7 +9270,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9545,7 +9554,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ40">
         <v>1.54</v>
@@ -9673,7 +9682,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9879,7 +9888,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10291,7 +10300,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10372,7 +10381,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR44">
         <v>1.61</v>
@@ -10497,7 +10506,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10909,7 +10918,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10987,10 +10996,10 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ47">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR47">
         <v>1.36</v>
@@ -11115,7 +11124,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11321,7 +11330,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11402,7 +11411,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ49">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR49">
         <v>1.23</v>
@@ -11733,7 +11742,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12223,7 +12232,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ53">
         <v>0.58</v>
@@ -12351,7 +12360,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12763,7 +12772,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12969,7 +12978,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13381,7 +13390,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -14617,7 +14626,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -15029,7 +15038,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15107,10 +15116,10 @@
         <v>3</v>
       </c>
       <c r="AP67">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR67">
         <v>1.38</v>
@@ -15235,7 +15244,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15313,7 +15322,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ68">
         <v>1.38</v>
@@ -15522,7 +15531,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ69">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR69">
         <v>1.69</v>
@@ -15725,7 +15734,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ70">
         <v>1.23</v>
@@ -16265,7 +16274,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16471,7 +16480,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16677,7 +16686,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16883,7 +16892,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17295,7 +17304,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17991,7 +18000,7 @@
         <v>1.25</v>
       </c>
       <c r="AP81">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ81">
         <v>1.23</v>
@@ -18325,7 +18334,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18406,7 +18415,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ83">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR83">
         <v>1.45</v>
@@ -18609,7 +18618,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ84">
         <v>1.25</v>
@@ -18815,7 +18824,7 @@
         <v>2</v>
       </c>
       <c r="AP85">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ85">
         <v>1.33</v>
@@ -18943,7 +18952,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19355,7 +19364,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19436,7 +19445,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ88">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR88">
         <v>1.05</v>
@@ -19642,7 +19651,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR89">
         <v>1.48</v>
@@ -19767,7 +19776,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19973,7 +19982,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20179,7 +20188,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20385,7 +20394,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20591,7 +20600,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20797,7 +20806,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21209,7 +21218,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21415,7 +21424,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21621,7 +21630,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22114,7 +22123,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ101">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR101">
         <v>1.6</v>
@@ -22317,7 +22326,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ102">
         <v>0.58</v>
@@ -22445,7 +22454,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22526,7 +22535,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ103">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR103">
         <v>1.71</v>
@@ -22857,7 +22866,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -23063,7 +23072,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23141,7 +23150,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
         <v>1.54</v>
@@ -23269,7 +23278,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23475,7 +23484,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23681,7 +23690,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -23762,7 +23771,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR109">
         <v>1.09</v>
@@ -24174,7 +24183,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ111">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR111">
         <v>1.61</v>
@@ -24505,7 +24514,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24711,7 +24720,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25123,7 +25132,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25329,7 +25338,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25535,7 +25544,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25613,7 +25622,7 @@
         <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ118">
         <v>0.38</v>
@@ -26231,7 +26240,7 @@
         <v>1.86</v>
       </c>
       <c r="AP121">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ121">
         <v>1.69</v>
@@ -26359,7 +26368,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26771,7 +26780,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27183,7 +27192,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27264,7 +27273,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ126">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -27595,7 +27604,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27673,10 +27682,10 @@
         <v>0.33</v>
       </c>
       <c r="AP128">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ128">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR128">
         <v>1.46</v>
@@ -28007,7 +28016,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28419,7 +28428,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28497,7 +28506,7 @@
         <v>1.86</v>
       </c>
       <c r="AP132">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ132">
         <v>1.54</v>
@@ -28625,7 +28634,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28831,7 +28840,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29118,7 +29127,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ135">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR135">
         <v>1.3</v>
@@ -29449,7 +29458,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29861,7 +29870,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -29942,7 +29951,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ139">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR139">
         <v>1.54</v>
@@ -30273,7 +30282,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30351,10 +30360,10 @@
         <v>2.29</v>
       </c>
       <c r="AP141">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ141">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR141">
         <v>1.36</v>
@@ -30685,7 +30694,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30891,7 +30900,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31303,7 +31312,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31509,7 +31518,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31715,7 +31724,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -31999,7 +32008,7 @@
         <v>1.13</v>
       </c>
       <c r="AP149">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ149">
         <v>1.54</v>
@@ -32333,7 +32342,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32539,7 +32548,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32620,7 +32629,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ152">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR152">
         <v>1.34</v>
@@ -32951,7 +32960,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33029,7 +33038,7 @@
         <v>1.75</v>
       </c>
       <c r="AP154">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ154">
         <v>1.54</v>
@@ -33441,7 +33450,7 @@
         <v>1.33</v>
       </c>
       <c r="AP156">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ156">
         <v>1.08</v>
@@ -33647,7 +33656,7 @@
         <v>0.33</v>
       </c>
       <c r="AP157">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ157">
         <v>0.38</v>
@@ -33775,7 +33784,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34062,7 +34071,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ159">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR159">
         <v>1.72</v>
@@ -34393,7 +34402,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34805,7 +34814,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34886,7 +34895,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ163">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR163">
         <v>1.12</v>
@@ -35011,7 +35020,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35089,7 +35098,7 @@
         <v>0.88</v>
       </c>
       <c r="AP164">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ164">
         <v>1.23</v>
@@ -35217,7 +35226,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35629,7 +35638,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -36122,7 +36131,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ169">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR169">
         <v>1.26</v>
@@ -36453,7 +36462,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -37071,7 +37080,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37358,7 +37367,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ175">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR175">
         <v>1.61</v>
@@ -37689,7 +37698,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -38182,7 +38191,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ179">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR179">
         <v>1.25</v>
@@ -38307,7 +38316,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38385,7 +38394,7 @@
         <v>1.4</v>
       </c>
       <c r="AP180">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ180">
         <v>1.38</v>
@@ -38591,7 +38600,7 @@
         <v>1.6</v>
       </c>
       <c r="AP181">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ181">
         <v>1.54</v>
@@ -38719,7 +38728,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38925,7 +38934,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39006,7 +39015,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ183">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR183">
         <v>1.33</v>
@@ -39543,7 +39552,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39955,7 +39964,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40033,7 +40042,7 @@
         <v>1.5</v>
       </c>
       <c r="AP188">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ188">
         <v>1.31</v>
@@ -40367,7 +40376,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40651,7 +40660,7 @@
         <v>1.2</v>
       </c>
       <c r="AP191">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ191">
         <v>1.08</v>
@@ -40779,7 +40788,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41191,7 +41200,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41603,7 +41612,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41684,7 +41693,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ196">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR196">
         <v>1.34</v>
@@ -41809,7 +41818,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -41890,7 +41899,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ197">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR197">
         <v>1.07</v>
@@ -42093,7 +42102,7 @@
         <v>1.36</v>
       </c>
       <c r="AP198">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ198">
         <v>1.38</v>
@@ -42221,7 +42230,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42839,7 +42848,7 @@
         <v>123</v>
       </c>
       <c r="P202" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q202">
         <v>4.3</v>
@@ -43251,7 +43260,7 @@
         <v>117</v>
       </c>
       <c r="P204" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q204">
         <v>3.1</v>
@@ -43538,7 +43547,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ205">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR205">
         <v>1.71</v>
@@ -43663,7 +43672,7 @@
         <v>218</v>
       </c>
       <c r="P206" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q206">
         <v>3.65</v>
@@ -43869,7 +43878,7 @@
         <v>156</v>
       </c>
       <c r="P207" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q207">
         <v>3.45</v>
@@ -44075,7 +44084,7 @@
         <v>197</v>
       </c>
       <c r="P208" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q208">
         <v>3.5</v>
@@ -44153,7 +44162,7 @@
         <v>1.45</v>
       </c>
       <c r="AP208">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ208">
         <v>1.54</v>
@@ -44281,7 +44290,7 @@
         <v>129</v>
       </c>
       <c r="P209" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q209">
         <v>2.4</v>
@@ -44359,7 +44368,7 @@
         <v>1.18</v>
       </c>
       <c r="AP209">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ209">
         <v>1.33</v>
@@ -44565,7 +44574,7 @@
         <v>1.09</v>
       </c>
       <c r="AP210">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ210">
         <v>1.08</v>
@@ -44771,7 +44780,7 @@
         <v>0.55</v>
       </c>
       <c r="AP211">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ211">
         <v>0.5</v>
@@ -44899,7 +44908,7 @@
         <v>220</v>
       </c>
       <c r="P212" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q212">
         <v>2.43</v>
@@ -44980,7 +44989,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ212">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR212">
         <v>1.61</v>
@@ -45105,7 +45114,7 @@
         <v>221</v>
       </c>
       <c r="P213" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q213">
         <v>3.15</v>
@@ -45598,7 +45607,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ215">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR215">
         <v>1.65</v>
@@ -46010,7 +46019,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ217">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR217">
         <v>1.78</v>
@@ -46135,7 +46144,7 @@
         <v>89</v>
       </c>
       <c r="P218" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q218">
         <v>3.6</v>
@@ -46341,7 +46350,7 @@
         <v>224</v>
       </c>
       <c r="P219" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q219">
         <v>3.78</v>
@@ -46547,7 +46556,7 @@
         <v>225</v>
       </c>
       <c r="P220" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q220">
         <v>3.26</v>
@@ -47371,7 +47380,7 @@
         <v>89</v>
       </c>
       <c r="P224" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q224">
         <v>5.44</v>
@@ -47989,7 +47998,7 @@
         <v>156</v>
       </c>
       <c r="P227" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q227">
         <v>2.9</v>
@@ -48146,6 +48155,830 @@
       </c>
       <c r="BP227">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7502829</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45730.73958333334</v>
+      </c>
+      <c r="F228">
+        <v>26</v>
+      </c>
+      <c r="G228" t="s">
+        <v>79</v>
+      </c>
+      <c r="H228" t="s">
+        <v>75</v>
+      </c>
+      <c r="I228">
+        <v>2</v>
+      </c>
+      <c r="J228">
+        <v>1</v>
+      </c>
+      <c r="K228">
+        <v>3</v>
+      </c>
+      <c r="L228">
+        <v>2</v>
+      </c>
+      <c r="M228">
+        <v>2</v>
+      </c>
+      <c r="N228">
+        <v>4</v>
+      </c>
+      <c r="O228" t="s">
+        <v>228</v>
+      </c>
+      <c r="P228" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q228">
+        <v>2.6</v>
+      </c>
+      <c r="R228">
+        <v>2</v>
+      </c>
+      <c r="S228">
+        <v>4</v>
+      </c>
+      <c r="T228">
+        <v>1.44</v>
+      </c>
+      <c r="U228">
+        <v>2.55</v>
+      </c>
+      <c r="V228">
+        <v>3.1</v>
+      </c>
+      <c r="W228">
+        <v>1.32</v>
+      </c>
+      <c r="X228">
+        <v>8.5</v>
+      </c>
+      <c r="Y228">
+        <v>1.06</v>
+      </c>
+      <c r="Z228">
+        <v>1.95</v>
+      </c>
+      <c r="AA228">
+        <v>3.25</v>
+      </c>
+      <c r="AB228">
+        <v>3.8</v>
+      </c>
+      <c r="AC228">
+        <v>1.07</v>
+      </c>
+      <c r="AD228">
+        <v>7.5</v>
+      </c>
+      <c r="AE228">
+        <v>1.38</v>
+      </c>
+      <c r="AF228">
+        <v>2.9</v>
+      </c>
+      <c r="AG228">
+        <v>2.05</v>
+      </c>
+      <c r="AH228">
+        <v>1.61</v>
+      </c>
+      <c r="AI228">
+        <v>1.95</v>
+      </c>
+      <c r="AJ228">
+        <v>1.73</v>
+      </c>
+      <c r="AK228">
+        <v>1.27</v>
+      </c>
+      <c r="AL228">
+        <v>1.3</v>
+      </c>
+      <c r="AM228">
+        <v>1.75</v>
+      </c>
+      <c r="AN228">
+        <v>2.08</v>
+      </c>
+      <c r="AO228">
+        <v>1.42</v>
+      </c>
+      <c r="AP228">
+        <v>2</v>
+      </c>
+      <c r="AQ228">
+        <v>1.38</v>
+      </c>
+      <c r="AR228">
+        <v>1.52</v>
+      </c>
+      <c r="AS228">
+        <v>1.39</v>
+      </c>
+      <c r="AT228">
+        <v>2.91</v>
+      </c>
+      <c r="AU228">
+        <v>6</v>
+      </c>
+      <c r="AV228">
+        <v>6</v>
+      </c>
+      <c r="AW228">
+        <v>6</v>
+      </c>
+      <c r="AX228">
+        <v>1</v>
+      </c>
+      <c r="AY228">
+        <v>12</v>
+      </c>
+      <c r="AZ228">
+        <v>7</v>
+      </c>
+      <c r="BA228">
+        <v>-1</v>
+      </c>
+      <c r="BB228">
+        <v>-1</v>
+      </c>
+      <c r="BC228">
+        <v>-1</v>
+      </c>
+      <c r="BD228">
+        <v>1.75</v>
+      </c>
+      <c r="BE228">
+        <v>8</v>
+      </c>
+      <c r="BF228">
+        <v>2.44</v>
+      </c>
+      <c r="BG228">
+        <v>1.21</v>
+      </c>
+      <c r="BH228">
+        <v>3.75</v>
+      </c>
+      <c r="BI228">
+        <v>1.41</v>
+      </c>
+      <c r="BJ228">
+        <v>2.68</v>
+      </c>
+      <c r="BK228">
+        <v>1.69</v>
+      </c>
+      <c r="BL228">
+        <v>2.09</v>
+      </c>
+      <c r="BM228">
+        <v>2.11</v>
+      </c>
+      <c r="BN228">
+        <v>1.68</v>
+      </c>
+      <c r="BO228">
+        <v>2.67</v>
+      </c>
+      <c r="BP228">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7502830</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45731.33333333334</v>
+      </c>
+      <c r="F229">
+        <v>26</v>
+      </c>
+      <c r="G229" t="s">
+        <v>73</v>
+      </c>
+      <c r="H229" t="s">
+        <v>74</v>
+      </c>
+      <c r="I229">
+        <v>1</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>1</v>
+      </c>
+      <c r="L229">
+        <v>1</v>
+      </c>
+      <c r="M229">
+        <v>0</v>
+      </c>
+      <c r="N229">
+        <v>1</v>
+      </c>
+      <c r="O229" t="s">
+        <v>197</v>
+      </c>
+      <c r="P229" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q229">
+        <v>2.63</v>
+      </c>
+      <c r="R229">
+        <v>2.05</v>
+      </c>
+      <c r="S229">
+        <v>4.5</v>
+      </c>
+      <c r="T229">
+        <v>1.5</v>
+      </c>
+      <c r="U229">
+        <v>2.5</v>
+      </c>
+      <c r="V229">
+        <v>3.4</v>
+      </c>
+      <c r="W229">
+        <v>1.3</v>
+      </c>
+      <c r="X229">
+        <v>10</v>
+      </c>
+      <c r="Y229">
+        <v>1.06</v>
+      </c>
+      <c r="Z229">
+        <v>2</v>
+      </c>
+      <c r="AA229">
+        <v>3.25</v>
+      </c>
+      <c r="AB229">
+        <v>3.6</v>
+      </c>
+      <c r="AC229">
+        <v>1.07</v>
+      </c>
+      <c r="AD229">
+        <v>7.5</v>
+      </c>
+      <c r="AE229">
+        <v>1.4</v>
+      </c>
+      <c r="AF229">
+        <v>2.8</v>
+      </c>
+      <c r="AG229">
+        <v>2.1</v>
+      </c>
+      <c r="AH229">
+        <v>1.61</v>
+      </c>
+      <c r="AI229">
+        <v>1.91</v>
+      </c>
+      <c r="AJ229">
+        <v>1.8</v>
+      </c>
+      <c r="AK229">
+        <v>1.25</v>
+      </c>
+      <c r="AL229">
+        <v>1.28</v>
+      </c>
+      <c r="AM229">
+        <v>1.73</v>
+      </c>
+      <c r="AN229">
+        <v>1.67</v>
+      </c>
+      <c r="AO229">
+        <v>1.67</v>
+      </c>
+      <c r="AP229">
+        <v>1.77</v>
+      </c>
+      <c r="AQ229">
+        <v>1.54</v>
+      </c>
+      <c r="AR229">
+        <v>1.27</v>
+      </c>
+      <c r="AS229">
+        <v>1.33</v>
+      </c>
+      <c r="AT229">
+        <v>2.6</v>
+      </c>
+      <c r="AU229">
+        <v>3</v>
+      </c>
+      <c r="AV229">
+        <v>3</v>
+      </c>
+      <c r="AW229">
+        <v>5</v>
+      </c>
+      <c r="AX229">
+        <v>13</v>
+      </c>
+      <c r="AY229">
+        <v>8</v>
+      </c>
+      <c r="AZ229">
+        <v>16</v>
+      </c>
+      <c r="BA229">
+        <v>-1</v>
+      </c>
+      <c r="BB229">
+        <v>-1</v>
+      </c>
+      <c r="BC229">
+        <v>-1</v>
+      </c>
+      <c r="BD229">
+        <v>1.49</v>
+      </c>
+      <c r="BE229">
+        <v>7.1</v>
+      </c>
+      <c r="BF229">
+        <v>3.4</v>
+      </c>
+      <c r="BG229">
+        <v>1.14</v>
+      </c>
+      <c r="BH229">
+        <v>4.4</v>
+      </c>
+      <c r="BI229">
+        <v>1.3</v>
+      </c>
+      <c r="BJ229">
+        <v>2.97</v>
+      </c>
+      <c r="BK229">
+        <v>1.56</v>
+      </c>
+      <c r="BL229">
+        <v>2.21</v>
+      </c>
+      <c r="BM229">
+        <v>2</v>
+      </c>
+      <c r="BN229">
+        <v>1.73</v>
+      </c>
+      <c r="BO229">
+        <v>2.51</v>
+      </c>
+      <c r="BP229">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7502835</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45731.45833333334</v>
+      </c>
+      <c r="F230">
+        <v>26</v>
+      </c>
+      <c r="G230" t="s">
+        <v>70</v>
+      </c>
+      <c r="H230" t="s">
+        <v>78</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>0</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
+      </c>
+      <c r="N230">
+        <v>0</v>
+      </c>
+      <c r="O230" t="s">
+        <v>89</v>
+      </c>
+      <c r="P230" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q230">
+        <v>3</v>
+      </c>
+      <c r="R230">
+        <v>2</v>
+      </c>
+      <c r="S230">
+        <v>4</v>
+      </c>
+      <c r="T230">
+        <v>1.5</v>
+      </c>
+      <c r="U230">
+        <v>2.5</v>
+      </c>
+      <c r="V230">
+        <v>3.4</v>
+      </c>
+      <c r="W230">
+        <v>1.3</v>
+      </c>
+      <c r="X230">
+        <v>10</v>
+      </c>
+      <c r="Y230">
+        <v>1.06</v>
+      </c>
+      <c r="Z230">
+        <v>2.2</v>
+      </c>
+      <c r="AA230">
+        <v>3.3</v>
+      </c>
+      <c r="AB230">
+        <v>3.05</v>
+      </c>
+      <c r="AC230">
+        <v>1.07</v>
+      </c>
+      <c r="AD230">
+        <v>7.5</v>
+      </c>
+      <c r="AE230">
+        <v>1.42</v>
+      </c>
+      <c r="AF230">
+        <v>2.7</v>
+      </c>
+      <c r="AG230">
+        <v>2.05</v>
+      </c>
+      <c r="AH230">
+        <v>1.65</v>
+      </c>
+      <c r="AI230">
+        <v>2</v>
+      </c>
+      <c r="AJ230">
+        <v>1.73</v>
+      </c>
+      <c r="AK230">
+        <v>1.35</v>
+      </c>
+      <c r="AL230">
+        <v>1.28</v>
+      </c>
+      <c r="AM230">
+        <v>1.6</v>
+      </c>
+      <c r="AN230">
+        <v>0.92</v>
+      </c>
+      <c r="AO230">
+        <v>1.08</v>
+      </c>
+      <c r="AP230">
+        <v>0.92</v>
+      </c>
+      <c r="AQ230">
+        <v>1.08</v>
+      </c>
+      <c r="AR230">
+        <v>1.63</v>
+      </c>
+      <c r="AS230">
+        <v>1.51</v>
+      </c>
+      <c r="AT230">
+        <v>3.14</v>
+      </c>
+      <c r="AU230">
+        <v>6</v>
+      </c>
+      <c r="AV230">
+        <v>2</v>
+      </c>
+      <c r="AW230">
+        <v>4</v>
+      </c>
+      <c r="AX230">
+        <v>6</v>
+      </c>
+      <c r="AY230">
+        <v>10</v>
+      </c>
+      <c r="AZ230">
+        <v>8</v>
+      </c>
+      <c r="BA230">
+        <v>-1</v>
+      </c>
+      <c r="BB230">
+        <v>-1</v>
+      </c>
+      <c r="BC230">
+        <v>-1</v>
+      </c>
+      <c r="BD230">
+        <v>1.93</v>
+      </c>
+      <c r="BE230">
+        <v>6.45</v>
+      </c>
+      <c r="BF230">
+        <v>2.31</v>
+      </c>
+      <c r="BG230">
+        <v>1.19</v>
+      </c>
+      <c r="BH230">
+        <v>3.82</v>
+      </c>
+      <c r="BI230">
+        <v>1.39</v>
+      </c>
+      <c r="BJ230">
+        <v>2.67</v>
+      </c>
+      <c r="BK230">
+        <v>1.7</v>
+      </c>
+      <c r="BL230">
+        <v>2.03</v>
+      </c>
+      <c r="BM230">
+        <v>2.05</v>
+      </c>
+      <c r="BN230">
+        <v>1.7</v>
+      </c>
+      <c r="BO230">
+        <v>2.78</v>
+      </c>
+      <c r="BP230">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7502831</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45731.52083333334</v>
+      </c>
+      <c r="F231">
+        <v>26</v>
+      </c>
+      <c r="G231" t="s">
+        <v>85</v>
+      </c>
+      <c r="H231" t="s">
+        <v>80</v>
+      </c>
+      <c r="I231">
+        <v>1</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>1</v>
+      </c>
+      <c r="L231">
+        <v>4</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>4</v>
+      </c>
+      <c r="O231" t="s">
+        <v>229</v>
+      </c>
+      <c r="P231" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q231">
+        <v>2.2</v>
+      </c>
+      <c r="R231">
+        <v>2.25</v>
+      </c>
+      <c r="S231">
+        <v>5.5</v>
+      </c>
+      <c r="T231">
+        <v>1.36</v>
+      </c>
+      <c r="U231">
+        <v>3</v>
+      </c>
+      <c r="V231">
+        <v>2.75</v>
+      </c>
+      <c r="W231">
+        <v>1.4</v>
+      </c>
+      <c r="X231">
+        <v>8</v>
+      </c>
+      <c r="Y231">
+        <v>1.08</v>
+      </c>
+      <c r="Z231">
+        <v>1.54</v>
+      </c>
+      <c r="AA231">
+        <v>4</v>
+      </c>
+      <c r="AB231">
+        <v>5.5</v>
+      </c>
+      <c r="AC231">
+        <v>1.04</v>
+      </c>
+      <c r="AD231">
+        <v>9</v>
+      </c>
+      <c r="AE231">
+        <v>1.28</v>
+      </c>
+      <c r="AF231">
+        <v>3.55</v>
+      </c>
+      <c r="AG231">
+        <v>1.8</v>
+      </c>
+      <c r="AH231">
+        <v>1.83</v>
+      </c>
+      <c r="AI231">
+        <v>1.91</v>
+      </c>
+      <c r="AJ231">
+        <v>1.8</v>
+      </c>
+      <c r="AK231">
+        <v>1.11</v>
+      </c>
+      <c r="AL231">
+        <v>1.2</v>
+      </c>
+      <c r="AM231">
+        <v>2.3</v>
+      </c>
+      <c r="AN231">
+        <v>1.58</v>
+      </c>
+      <c r="AO231">
+        <v>1</v>
+      </c>
+      <c r="AP231">
+        <v>1.69</v>
+      </c>
+      <c r="AQ231">
+        <v>0.92</v>
+      </c>
+      <c r="AR231">
+        <v>1.57</v>
+      </c>
+      <c r="AS231">
+        <v>1.15</v>
+      </c>
+      <c r="AT231">
+        <v>2.72</v>
+      </c>
+      <c r="AU231">
+        <v>4</v>
+      </c>
+      <c r="AV231">
+        <v>6</v>
+      </c>
+      <c r="AW231">
+        <v>6</v>
+      </c>
+      <c r="AX231">
+        <v>6</v>
+      </c>
+      <c r="AY231">
+        <v>10</v>
+      </c>
+      <c r="AZ231">
+        <v>12</v>
+      </c>
+      <c r="BA231">
+        <v>-1</v>
+      </c>
+      <c r="BB231">
+        <v>-1</v>
+      </c>
+      <c r="BC231">
+        <v>-1</v>
+      </c>
+      <c r="BD231">
+        <v>1.42</v>
+      </c>
+      <c r="BE231">
+        <v>9.5</v>
+      </c>
+      <c r="BF231">
+        <v>3.38</v>
+      </c>
+      <c r="BG231">
+        <v>1.12</v>
+      </c>
+      <c r="BH231">
+        <v>4.7</v>
+      </c>
+      <c r="BI231">
+        <v>1.27</v>
+      </c>
+      <c r="BJ231">
+        <v>3.14</v>
+      </c>
+      <c r="BK231">
+        <v>1.5</v>
+      </c>
+      <c r="BL231">
+        <v>2.35</v>
+      </c>
+      <c r="BM231">
+        <v>1.91</v>
+      </c>
+      <c r="BN231">
+        <v>1.8</v>
+      </c>
+      <c r="BO231">
+        <v>2.34</v>
+      </c>
+      <c r="BP231">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -48315,13 +48315,13 @@
         <v>7</v>
       </c>
       <c r="BA228">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB228">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC228">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD228">
         <v>1.75</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="342">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -706,6 +706,15 @@
     <t>['11', '50', '56', '90+2']</t>
   </si>
   <si>
+    <t>['20', '88']</t>
+  </si>
+  <si>
+    <t>['17', '79', '90+1']</t>
+  </si>
+  <si>
+    <t>['45', '56']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -1392,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP231"/>
+  <dimension ref="A1:BP235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1648,7 +1657,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1854,7 +1863,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1935,7 +1944,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ3">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2060,7 +2069,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2141,7 +2150,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ4">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2472,7 +2481,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2678,7 +2687,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2962,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ8">
         <v>1.31</v>
@@ -3090,7 +3099,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3168,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ9">
         <v>1.54</v>
@@ -3502,7 +3511,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3789,7 +3798,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ12">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3914,7 +3923,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4120,7 +4129,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4326,7 +4335,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4532,7 +4541,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4610,7 +4619,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ16">
         <v>1.54</v>
@@ -4819,7 +4828,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ17">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5150,7 +5159,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5228,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ19">
         <v>0.38</v>
@@ -5356,7 +5365,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5434,7 +5443,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ20">
         <v>1.31</v>
@@ -5974,7 +5983,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6055,7 +6064,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ23">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR23">
         <v>1.93</v>
@@ -6386,7 +6395,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6798,7 +6807,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7210,7 +7219,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7416,7 +7425,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7497,7 +7506,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ30">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR30">
         <v>1.33</v>
@@ -7700,7 +7709,7 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ31">
         <v>1.08</v>
@@ -7828,7 +7837,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7906,7 +7915,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ32">
         <v>1.38</v>
@@ -8240,7 +8249,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8321,7 +8330,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR34">
         <v>1.57</v>
@@ -8446,7 +8455,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8652,7 +8661,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8733,7 +8742,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ36">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR36">
         <v>0.91</v>
@@ -8936,7 +8945,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ37">
         <v>1.54</v>
@@ -9064,7 +9073,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9270,7 +9279,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9682,7 +9691,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9888,7 +9897,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10300,7 +10309,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10506,7 +10515,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10793,7 +10802,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ46">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR46">
         <v>1.7</v>
@@ -10918,7 +10927,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11124,7 +11133,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11205,7 +11214,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR48">
         <v>1.74</v>
@@ -11330,7 +11339,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11614,7 +11623,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ50">
         <v>1.08</v>
@@ -11742,7 +11751,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -11820,7 +11829,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ51">
         <v>1.08</v>
@@ -12235,7 +12244,7 @@
         <v>2</v>
       </c>
       <c r="AQ53">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR53">
         <v>1.6</v>
@@ -12360,7 +12369,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12438,7 +12447,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ54">
         <v>1.38</v>
@@ -12644,10 +12653,10 @@
         <v>2</v>
       </c>
       <c r="AP55">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ55">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR55">
         <v>1.78</v>
@@ -12772,7 +12781,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12978,7 +12987,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13390,7 +13399,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13471,7 +13480,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ59">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR59">
         <v>1.13</v>
@@ -14626,7 +14635,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14704,7 +14713,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ65">
         <v>1.08</v>
@@ -14910,10 +14919,10 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ66">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR66">
         <v>1.24</v>
@@ -15038,7 +15047,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15244,7 +15253,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15940,10 +15949,10 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ71">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR71">
         <v>0.8</v>
@@ -16274,7 +16283,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16480,7 +16489,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16686,7 +16695,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16892,7 +16901,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17304,7 +17313,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -18334,7 +18343,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18621,7 +18630,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ84">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR84">
         <v>1.48</v>
@@ -18827,7 +18836,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ85">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18952,7 +18961,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19033,7 +19042,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ86">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR86">
         <v>1.78</v>
@@ -19236,10 +19245,10 @@
         <v>1.25</v>
       </c>
       <c r="AP87">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ87">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR87">
         <v>1.38</v>
@@ -19364,7 +19373,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19442,7 +19451,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ88">
         <v>1.38</v>
@@ -19648,7 +19657,7 @@
         <v>0.33</v>
       </c>
       <c r="AP89">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ89">
         <v>0.92</v>
@@ -19776,7 +19785,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19854,7 +19863,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ90">
         <v>1.69</v>
@@ -19982,7 +19991,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20188,7 +20197,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20394,7 +20403,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20600,7 +20609,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20806,7 +20815,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21218,7 +21227,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21424,7 +21433,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21630,7 +21639,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -21711,7 +21720,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ99">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR99">
         <v>1.34</v>
@@ -22120,7 +22129,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ101">
         <v>0.92</v>
@@ -22329,7 +22338,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ102">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR102">
         <v>1.5</v>
@@ -22454,7 +22463,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22738,7 +22747,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ104">
         <v>1.23</v>
@@ -22866,7 +22875,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -23072,7 +23081,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23278,7 +23287,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23359,7 +23368,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ107">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR107">
         <v>1.21</v>
@@ -23484,7 +23493,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23562,10 +23571,10 @@
         <v>1.4</v>
       </c>
       <c r="AP108">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ108">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR108">
         <v>1.57</v>
@@ -23690,7 +23699,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -23768,7 +23777,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ109">
         <v>0.92</v>
@@ -23977,7 +23986,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ110">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR110">
         <v>1.51</v>
@@ -24514,7 +24523,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24720,7 +24729,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25132,7 +25141,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25338,7 +25347,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25544,7 +25553,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25828,7 +25837,7 @@
         <v>2</v>
       </c>
       <c r="AP119">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ119">
         <v>1.54</v>
@@ -26034,10 +26043,10 @@
         <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ120">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR120">
         <v>1.47</v>
@@ -26368,7 +26377,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26449,7 +26458,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ122">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR122">
         <v>1.24</v>
@@ -26655,7 +26664,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ123">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR123">
         <v>1.21</v>
@@ -26780,7 +26789,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27064,7 +27073,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -27192,7 +27201,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27476,7 +27485,7 @@
         <v>0.83</v>
       </c>
       <c r="AP127">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ127">
         <v>1.23</v>
@@ -27604,7 +27613,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27891,7 +27900,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ129">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR129">
         <v>1.3</v>
@@ -28016,7 +28025,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28094,7 +28103,7 @@
         <v>0.43</v>
       </c>
       <c r="AP130">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ130">
         <v>0.38</v>
@@ -28428,7 +28437,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28634,7 +28643,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28840,7 +28849,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29458,7 +29467,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29539,7 +29548,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ137">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR137">
         <v>1.18</v>
@@ -29870,7 +29879,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30282,7 +30291,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30569,7 +30578,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ142">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR142">
         <v>1.66</v>
@@ -30694,7 +30703,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30772,7 +30781,7 @@
         <v>1.63</v>
       </c>
       <c r="AP143">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ143">
         <v>1.54</v>
@@ -30900,7 +30909,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31187,7 +31196,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ145">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR145">
         <v>1.33</v>
@@ -31312,7 +31321,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31390,7 +31399,7 @@
         <v>1.63</v>
       </c>
       <c r="AP146">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ146">
         <v>1.38</v>
@@ -31518,7 +31527,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31724,7 +31733,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32217,7 +32226,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ150">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR150">
         <v>1.63</v>
@@ -32342,7 +32351,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32420,7 +32429,7 @@
         <v>1.13</v>
       </c>
       <c r="AP151">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ151">
         <v>1</v>
@@ -32548,7 +32557,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32832,7 +32841,7 @@
         <v>1.63</v>
       </c>
       <c r="AP153">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ153">
         <v>1.69</v>
@@ -32960,7 +32969,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33247,7 +33256,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ155">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR155">
         <v>1.55</v>
@@ -33784,7 +33793,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34274,7 +34283,7 @@
         <v>1.78</v>
       </c>
       <c r="AP160">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ160">
         <v>1.54</v>
@@ -34402,7 +34411,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34483,7 +34492,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ161">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR161">
         <v>1.7</v>
@@ -34686,7 +34695,7 @@
         <v>1.44</v>
       </c>
       <c r="AP162">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ162">
         <v>1.38</v>
@@ -34814,7 +34823,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -35020,7 +35029,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35226,7 +35235,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35638,7 +35647,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -35719,7 +35728,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ167">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR167">
         <v>1.71</v>
@@ -36334,7 +36343,7 @@
         <v>1.33</v>
       </c>
       <c r="AP170">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36462,7 +36471,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36540,7 +36549,7 @@
         <v>1.67</v>
       </c>
       <c r="AP171">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ171">
         <v>1.54</v>
@@ -36749,7 +36758,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ172">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR172">
         <v>1.3</v>
@@ -36955,7 +36964,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ173">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR173">
         <v>1.71</v>
@@ -37080,7 +37089,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37364,7 +37373,7 @@
         <v>2.22</v>
       </c>
       <c r="AP175">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ175">
         <v>1.54</v>
@@ -37570,10 +37579,10 @@
         <v>1.44</v>
       </c>
       <c r="AP176">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ176">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR176">
         <v>1.68</v>
@@ -37698,7 +37707,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -37776,7 +37785,7 @@
         <v>1.2</v>
       </c>
       <c r="AP177">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ177">
         <v>1.08</v>
@@ -37985,7 +37994,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ178">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR178">
         <v>1.35</v>
@@ -38316,7 +38325,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38728,7 +38737,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38934,7 +38943,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39552,7 +39561,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39633,7 +39642,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ186">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR186">
         <v>1.18</v>
@@ -39964,7 +39973,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40248,7 +40257,7 @@
         <v>0.3</v>
       </c>
       <c r="AP189">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ189">
         <v>0.38</v>
@@ -40376,7 +40385,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40788,7 +40797,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41072,10 +41081,10 @@
         <v>0.6</v>
       </c>
       <c r="AP193">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ193">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR193">
         <v>1.6</v>
@@ -41200,7 +41209,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41281,7 +41290,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ194">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR194">
         <v>1.3</v>
@@ -41484,10 +41493,10 @@
         <v>0.6</v>
       </c>
       <c r="AP195">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ195">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR195">
         <v>1.64</v>
@@ -41612,7 +41621,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41818,7 +41827,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -41896,7 +41905,7 @@
         <v>2</v>
       </c>
       <c r="AP197">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ197">
         <v>1.54</v>
@@ -42230,7 +42239,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42308,7 +42317,7 @@
         <v>1.09</v>
       </c>
       <c r="AP199">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ199">
         <v>1.08</v>
@@ -42848,7 +42857,7 @@
         <v>123</v>
       </c>
       <c r="P202" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q202">
         <v>4.3</v>
@@ -43135,7 +43144,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ203">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR203">
         <v>1.53</v>
@@ -43260,7 +43269,7 @@
         <v>117</v>
       </c>
       <c r="P204" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q204">
         <v>3.1</v>
@@ -43672,7 +43681,7 @@
         <v>218</v>
       </c>
       <c r="P206" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q206">
         <v>3.65</v>
@@ -43878,7 +43887,7 @@
         <v>156</v>
       </c>
       <c r="P207" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q207">
         <v>3.45</v>
@@ -44084,7 +44093,7 @@
         <v>197</v>
       </c>
       <c r="P208" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q208">
         <v>3.5</v>
@@ -44290,7 +44299,7 @@
         <v>129</v>
       </c>
       <c r="P209" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q209">
         <v>2.4</v>
@@ -44371,7 +44380,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ209">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR209">
         <v>1.53</v>
@@ -44783,7 +44792,7 @@
         <v>2</v>
       </c>
       <c r="AQ211">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR211">
         <v>1.57</v>
@@ -44908,7 +44917,7 @@
         <v>220</v>
       </c>
       <c r="P212" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q212">
         <v>2.43</v>
@@ -44986,7 +44995,7 @@
         <v>1.45</v>
       </c>
       <c r="AP212">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ212">
         <v>1.38</v>
@@ -45114,7 +45123,7 @@
         <v>221</v>
       </c>
       <c r="P213" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q213">
         <v>3.15</v>
@@ -45195,7 +45204,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ213">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR213">
         <v>1.4</v>
@@ -45398,7 +45407,7 @@
         <v>1.25</v>
       </c>
       <c r="AP214">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ214">
         <v>1.38</v>
@@ -45604,7 +45613,7 @@
         <v>1.82</v>
       </c>
       <c r="AP215">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ215">
         <v>1.54</v>
@@ -45810,7 +45819,7 @@
         <v>1.18</v>
       </c>
       <c r="AP216">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ216">
         <v>1.23</v>
@@ -46144,7 +46153,7 @@
         <v>89</v>
       </c>
       <c r="P218" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q218">
         <v>3.6</v>
@@ -46350,7 +46359,7 @@
         <v>224</v>
       </c>
       <c r="P219" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q219">
         <v>3.78</v>
@@ -46556,7 +46565,7 @@
         <v>225</v>
       </c>
       <c r="P220" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q220">
         <v>3.26</v>
@@ -46843,7 +46852,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ221">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR221">
         <v>1.41</v>
@@ -47380,7 +47389,7 @@
         <v>89</v>
       </c>
       <c r="P224" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q224">
         <v>5.44</v>
@@ -47998,7 +48007,7 @@
         <v>156</v>
       </c>
       <c r="P227" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q227">
         <v>2.9</v>
@@ -48204,7 +48213,7 @@
         <v>228</v>
       </c>
       <c r="P228" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q228">
         <v>2.6</v>
@@ -48979,6 +48988,830 @@
       </c>
       <c r="BP231">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7502834</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45732.33333333334</v>
+      </c>
+      <c r="F232">
+        <v>26</v>
+      </c>
+      <c r="G232" t="s">
+        <v>87</v>
+      </c>
+      <c r="H232" t="s">
+        <v>86</v>
+      </c>
+      <c r="I232">
+        <v>1</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>1</v>
+      </c>
+      <c r="L232">
+        <v>2</v>
+      </c>
+      <c r="M232">
+        <v>1</v>
+      </c>
+      <c r="N232">
+        <v>3</v>
+      </c>
+      <c r="O232" t="s">
+        <v>230</v>
+      </c>
+      <c r="P232" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q232">
+        <v>2.75</v>
+      </c>
+      <c r="R232">
+        <v>2.1</v>
+      </c>
+      <c r="S232">
+        <v>4.33</v>
+      </c>
+      <c r="T232">
+        <v>1.44</v>
+      </c>
+      <c r="U232">
+        <v>2.63</v>
+      </c>
+      <c r="V232">
+        <v>3.25</v>
+      </c>
+      <c r="W232">
+        <v>1.33</v>
+      </c>
+      <c r="X232">
+        <v>9</v>
+      </c>
+      <c r="Y232">
+        <v>1.07</v>
+      </c>
+      <c r="Z232">
+        <v>2</v>
+      </c>
+      <c r="AA232">
+        <v>3.3</v>
+      </c>
+      <c r="AB232">
+        <v>3.65</v>
+      </c>
+      <c r="AC232">
+        <v>1.06</v>
+      </c>
+      <c r="AD232">
+        <v>8</v>
+      </c>
+      <c r="AE232">
+        <v>1.35</v>
+      </c>
+      <c r="AF232">
+        <v>3</v>
+      </c>
+      <c r="AG232">
+        <v>1.95</v>
+      </c>
+      <c r="AH232">
+        <v>1.7</v>
+      </c>
+      <c r="AI232">
+        <v>1.83</v>
+      </c>
+      <c r="AJ232">
+        <v>1.83</v>
+      </c>
+      <c r="AK232">
+        <v>1.25</v>
+      </c>
+      <c r="AL232">
+        <v>1.25</v>
+      </c>
+      <c r="AM232">
+        <v>1.77</v>
+      </c>
+      <c r="AN232">
+        <v>2.08</v>
+      </c>
+      <c r="AO232">
+        <v>1.33</v>
+      </c>
+      <c r="AP232">
+        <v>2.15</v>
+      </c>
+      <c r="AQ232">
+        <v>1.23</v>
+      </c>
+      <c r="AR232">
+        <v>1.59</v>
+      </c>
+      <c r="AS232">
+        <v>1.5</v>
+      </c>
+      <c r="AT232">
+        <v>3.09</v>
+      </c>
+      <c r="AU232">
+        <v>7</v>
+      </c>
+      <c r="AV232">
+        <v>4</v>
+      </c>
+      <c r="AW232">
+        <v>9</v>
+      </c>
+      <c r="AX232">
+        <v>6</v>
+      </c>
+      <c r="AY232">
+        <v>16</v>
+      </c>
+      <c r="AZ232">
+        <v>10</v>
+      </c>
+      <c r="BA232">
+        <v>-1</v>
+      </c>
+      <c r="BB232">
+        <v>-1</v>
+      </c>
+      <c r="BC232">
+        <v>-1</v>
+      </c>
+      <c r="BD232">
+        <v>1.7</v>
+      </c>
+      <c r="BE232">
+        <v>6.7</v>
+      </c>
+      <c r="BF232">
+        <v>2.72</v>
+      </c>
+      <c r="BG232">
+        <v>1.17</v>
+      </c>
+      <c r="BH232">
+        <v>4.05</v>
+      </c>
+      <c r="BI232">
+        <v>1.34</v>
+      </c>
+      <c r="BJ232">
+        <v>2.78</v>
+      </c>
+      <c r="BK232">
+        <v>1.63</v>
+      </c>
+      <c r="BL232">
+        <v>2.09</v>
+      </c>
+      <c r="BM232">
+        <v>2.05</v>
+      </c>
+      <c r="BN232">
+        <v>1.7</v>
+      </c>
+      <c r="BO232">
+        <v>2.67</v>
+      </c>
+      <c r="BP232">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7502832</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45732.45833333334</v>
+      </c>
+      <c r="F233">
+        <v>26</v>
+      </c>
+      <c r="G233" t="s">
+        <v>77</v>
+      </c>
+      <c r="H233" t="s">
+        <v>71</v>
+      </c>
+      <c r="I233">
+        <v>1</v>
+      </c>
+      <c r="J233">
+        <v>1</v>
+      </c>
+      <c r="K233">
+        <v>2</v>
+      </c>
+      <c r="L233">
+        <v>3</v>
+      </c>
+      <c r="M233">
+        <v>1</v>
+      </c>
+      <c r="N233">
+        <v>4</v>
+      </c>
+      <c r="O233" t="s">
+        <v>231</v>
+      </c>
+      <c r="P233" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q233">
+        <v>2.5</v>
+      </c>
+      <c r="R233">
+        <v>2.1</v>
+      </c>
+      <c r="S233">
+        <v>5</v>
+      </c>
+      <c r="T233">
+        <v>1.44</v>
+      </c>
+      <c r="U233">
+        <v>2.63</v>
+      </c>
+      <c r="V233">
+        <v>3.25</v>
+      </c>
+      <c r="W233">
+        <v>1.33</v>
+      </c>
+      <c r="X233">
+        <v>10</v>
+      </c>
+      <c r="Y233">
+        <v>1.06</v>
+      </c>
+      <c r="Z233">
+        <v>1.83</v>
+      </c>
+      <c r="AA233">
+        <v>3.35</v>
+      </c>
+      <c r="AB233">
+        <v>4.2</v>
+      </c>
+      <c r="AC233">
+        <v>1.06</v>
+      </c>
+      <c r="AD233">
+        <v>8</v>
+      </c>
+      <c r="AE233">
+        <v>1.36</v>
+      </c>
+      <c r="AF233">
+        <v>2.95</v>
+      </c>
+      <c r="AG233">
+        <v>2.05</v>
+      </c>
+      <c r="AH233">
+        <v>1.65</v>
+      </c>
+      <c r="AI233">
+        <v>2</v>
+      </c>
+      <c r="AJ233">
+        <v>1.73</v>
+      </c>
+      <c r="AK233">
+        <v>1.18</v>
+      </c>
+      <c r="AL233">
+        <v>1.25</v>
+      </c>
+      <c r="AM233">
+        <v>1.9</v>
+      </c>
+      <c r="AN233">
+        <v>1.42</v>
+      </c>
+      <c r="AO233">
+        <v>0.5</v>
+      </c>
+      <c r="AP233">
+        <v>1.54</v>
+      </c>
+      <c r="AQ233">
+        <v>0.46</v>
+      </c>
+      <c r="AR233">
+        <v>1.65</v>
+      </c>
+      <c r="AS233">
+        <v>1.25</v>
+      </c>
+      <c r="AT233">
+        <v>2.9</v>
+      </c>
+      <c r="AU233">
+        <v>6</v>
+      </c>
+      <c r="AV233">
+        <v>4</v>
+      </c>
+      <c r="AW233">
+        <v>7</v>
+      </c>
+      <c r="AX233">
+        <v>5</v>
+      </c>
+      <c r="AY233">
+        <v>13</v>
+      </c>
+      <c r="AZ233">
+        <v>9</v>
+      </c>
+      <c r="BA233">
+        <v>-1</v>
+      </c>
+      <c r="BB233">
+        <v>-1</v>
+      </c>
+      <c r="BC233">
+        <v>-1</v>
+      </c>
+      <c r="BD233">
+        <v>1.47</v>
+      </c>
+      <c r="BE233">
+        <v>9</v>
+      </c>
+      <c r="BF233">
+        <v>3.18</v>
+      </c>
+      <c r="BG233">
+        <v>1.21</v>
+      </c>
+      <c r="BH233">
+        <v>3.58</v>
+      </c>
+      <c r="BI233">
+        <v>1.43</v>
+      </c>
+      <c r="BJ233">
+        <v>2.54</v>
+      </c>
+      <c r="BK233">
+        <v>1.77</v>
+      </c>
+      <c r="BL233">
+        <v>1.94</v>
+      </c>
+      <c r="BM233">
+        <v>2.05</v>
+      </c>
+      <c r="BN233">
+        <v>1.7</v>
+      </c>
+      <c r="BO233">
+        <v>2.92</v>
+      </c>
+      <c r="BP233">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7502837</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45732.52083333334</v>
+      </c>
+      <c r="F234">
+        <v>26</v>
+      </c>
+      <c r="G234" t="s">
+        <v>76</v>
+      </c>
+      <c r="H234" t="s">
+        <v>72</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+      <c r="J234">
+        <v>1</v>
+      </c>
+      <c r="K234">
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <v>0</v>
+      </c>
+      <c r="M234">
+        <v>1</v>
+      </c>
+      <c r="N234">
+        <v>1</v>
+      </c>
+      <c r="O234" t="s">
+        <v>89</v>
+      </c>
+      <c r="P234" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q234">
+        <v>3.2</v>
+      </c>
+      <c r="R234">
+        <v>2</v>
+      </c>
+      <c r="S234">
+        <v>3.75</v>
+      </c>
+      <c r="T234">
+        <v>1.5</v>
+      </c>
+      <c r="U234">
+        <v>2.5</v>
+      </c>
+      <c r="V234">
+        <v>3.4</v>
+      </c>
+      <c r="W234">
+        <v>1.3</v>
+      </c>
+      <c r="X234">
+        <v>10</v>
+      </c>
+      <c r="Y234">
+        <v>1.06</v>
+      </c>
+      <c r="Z234">
+        <v>2.35</v>
+      </c>
+      <c r="AA234">
+        <v>3.25</v>
+      </c>
+      <c r="AB234">
+        <v>2.9</v>
+      </c>
+      <c r="AC234">
+        <v>1.07</v>
+      </c>
+      <c r="AD234">
+        <v>7.5</v>
+      </c>
+      <c r="AE234">
+        <v>1.4</v>
+      </c>
+      <c r="AF234">
+        <v>2.8</v>
+      </c>
+      <c r="AG234">
+        <v>2.1</v>
+      </c>
+      <c r="AH234">
+        <v>1.61</v>
+      </c>
+      <c r="AI234">
+        <v>1.91</v>
+      </c>
+      <c r="AJ234">
+        <v>1.8</v>
+      </c>
+      <c r="AK234">
+        <v>1.36</v>
+      </c>
+      <c r="AL234">
+        <v>1.3</v>
+      </c>
+      <c r="AM234">
+        <v>1.57</v>
+      </c>
+      <c r="AN234">
+        <v>1.42</v>
+      </c>
+      <c r="AO234">
+        <v>0.58</v>
+      </c>
+      <c r="AP234">
+        <v>1.31</v>
+      </c>
+      <c r="AQ234">
+        <v>0.77</v>
+      </c>
+      <c r="AR234">
+        <v>1.13</v>
+      </c>
+      <c r="AS234">
+        <v>1.27</v>
+      </c>
+      <c r="AT234">
+        <v>2.4</v>
+      </c>
+      <c r="AU234">
+        <v>4</v>
+      </c>
+      <c r="AV234">
+        <v>4</v>
+      </c>
+      <c r="AW234">
+        <v>7</v>
+      </c>
+      <c r="AX234">
+        <v>6</v>
+      </c>
+      <c r="AY234">
+        <v>11</v>
+      </c>
+      <c r="AZ234">
+        <v>10</v>
+      </c>
+      <c r="BA234">
+        <v>-1</v>
+      </c>
+      <c r="BB234">
+        <v>-1</v>
+      </c>
+      <c r="BC234">
+        <v>-1</v>
+      </c>
+      <c r="BD234">
+        <v>1.74</v>
+      </c>
+      <c r="BE234">
+        <v>6.7</v>
+      </c>
+      <c r="BF234">
+        <v>2.62</v>
+      </c>
+      <c r="BG234">
+        <v>1.14</v>
+      </c>
+      <c r="BH234">
+        <v>4.4</v>
+      </c>
+      <c r="BI234">
+        <v>1.3</v>
+      </c>
+      <c r="BJ234">
+        <v>2.97</v>
+      </c>
+      <c r="BK234">
+        <v>1.56</v>
+      </c>
+      <c r="BL234">
+        <v>2.21</v>
+      </c>
+      <c r="BM234">
+        <v>1.91</v>
+      </c>
+      <c r="BN234">
+        <v>1.8</v>
+      </c>
+      <c r="BO234">
+        <v>2.51</v>
+      </c>
+      <c r="BP234">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7502833</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45732.72916666666</v>
+      </c>
+      <c r="F235">
+        <v>26</v>
+      </c>
+      <c r="G235" t="s">
+        <v>84</v>
+      </c>
+      <c r="H235" t="s">
+        <v>82</v>
+      </c>
+      <c r="I235">
+        <v>1</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>1</v>
+      </c>
+      <c r="L235">
+        <v>2</v>
+      </c>
+      <c r="M235">
+        <v>1</v>
+      </c>
+      <c r="N235">
+        <v>3</v>
+      </c>
+      <c r="O235" t="s">
+        <v>232</v>
+      </c>
+      <c r="P235" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q235">
+        <v>2.1</v>
+      </c>
+      <c r="R235">
+        <v>2.25</v>
+      </c>
+      <c r="S235">
+        <v>6</v>
+      </c>
+      <c r="T235">
+        <v>1.36</v>
+      </c>
+      <c r="U235">
+        <v>3</v>
+      </c>
+      <c r="V235">
+        <v>2.75</v>
+      </c>
+      <c r="W235">
+        <v>1.4</v>
+      </c>
+      <c r="X235">
+        <v>7</v>
+      </c>
+      <c r="Y235">
+        <v>1.1</v>
+      </c>
+      <c r="Z235">
+        <v>1.57</v>
+      </c>
+      <c r="AA235">
+        <v>3.9</v>
+      </c>
+      <c r="AB235">
+        <v>5.25</v>
+      </c>
+      <c r="AC235">
+        <v>1.04</v>
+      </c>
+      <c r="AD235">
+        <v>9</v>
+      </c>
+      <c r="AE235">
+        <v>1.28</v>
+      </c>
+      <c r="AF235">
+        <v>3.5</v>
+      </c>
+      <c r="AG235">
+        <v>1.8</v>
+      </c>
+      <c r="AH235">
+        <v>1.83</v>
+      </c>
+      <c r="AI235">
+        <v>1.91</v>
+      </c>
+      <c r="AJ235">
+        <v>1.8</v>
+      </c>
+      <c r="AK235">
+        <v>1.11</v>
+      </c>
+      <c r="AL235">
+        <v>1.2</v>
+      </c>
+      <c r="AM235">
+        <v>2.3</v>
+      </c>
+      <c r="AN235">
+        <v>1.75</v>
+      </c>
+      <c r="AO235">
+        <v>1.25</v>
+      </c>
+      <c r="AP235">
+        <v>1.85</v>
+      </c>
+      <c r="AQ235">
+        <v>1.15</v>
+      </c>
+      <c r="AR235">
+        <v>1.77</v>
+      </c>
+      <c r="AS235">
+        <v>1.33</v>
+      </c>
+      <c r="AT235">
+        <v>3.1</v>
+      </c>
+      <c r="AU235">
+        <v>-1</v>
+      </c>
+      <c r="AV235">
+        <v>-1</v>
+      </c>
+      <c r="AW235">
+        <v>-1</v>
+      </c>
+      <c r="AX235">
+        <v>-1</v>
+      </c>
+      <c r="AY235">
+        <v>-1</v>
+      </c>
+      <c r="AZ235">
+        <v>-1</v>
+      </c>
+      <c r="BA235">
+        <v>-1</v>
+      </c>
+      <c r="BB235">
+        <v>-1</v>
+      </c>
+      <c r="BC235">
+        <v>-1</v>
+      </c>
+      <c r="BD235">
+        <v>1.36</v>
+      </c>
+      <c r="BE235">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF235">
+        <v>3.72</v>
+      </c>
+      <c r="BG235">
+        <v>1.15</v>
+      </c>
+      <c r="BH235">
+        <v>4.25</v>
+      </c>
+      <c r="BI235">
+        <v>1.32</v>
+      </c>
+      <c r="BJ235">
+        <v>2.88</v>
+      </c>
+      <c r="BK235">
+        <v>1.58</v>
+      </c>
+      <c r="BL235">
+        <v>2.17</v>
+      </c>
+      <c r="BM235">
+        <v>1.91</v>
+      </c>
+      <c r="BN235">
+        <v>1.8</v>
+      </c>
+      <c r="BO235">
+        <v>2.54</v>
+      </c>
+      <c r="BP235">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -48530,13 +48530,13 @@
         <v>16</v>
       </c>
       <c r="BA229">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB229">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BC229">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="BD229">
         <v>1.49</v>
@@ -48736,13 +48736,13 @@
         <v>8</v>
       </c>
       <c r="BA230">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB230">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC230">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD230">
         <v>1.93</v>
@@ -48942,13 +48942,13 @@
         <v>12</v>
       </c>
       <c r="BA231">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB231">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BC231">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BD231">
         <v>1.42</v>
@@ -49748,22 +49748,22 @@
         <v>3.1</v>
       </c>
       <c r="AU235">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV235">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW235">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AX235">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AY235">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AZ235">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BA235">
         <v>-1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -49148,13 +49148,13 @@
         <v>10</v>
       </c>
       <c r="BA232">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB232">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC232">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BD232">
         <v>1.7</v>
@@ -49354,13 +49354,13 @@
         <v>9</v>
       </c>
       <c r="BA233">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB233">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC233">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BD233">
         <v>1.47</v>
@@ -49560,13 +49560,13 @@
         <v>10</v>
       </c>
       <c r="BA234">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB234">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC234">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD234">
         <v>1.74</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -49766,13 +49766,13 @@
         <v>6</v>
       </c>
       <c r="BA235">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BB235">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC235">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD235">
         <v>1.36</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="349">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -715,6 +715,15 @@
     <t>['45', '56']</t>
   </si>
   <si>
+    <t>['17', '76', '90+6']</t>
+  </si>
+  <si>
+    <t>['33', '37']</t>
+  </si>
+  <si>
+    <t>['52', '90+6']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -1040,6 +1049,18 @@
   </si>
   <si>
     <t>['33', '62']</t>
+  </si>
+  <si>
+    <t>['21', '89', '90+8']</t>
+  </si>
+  <si>
+    <t>['6', '55']</t>
+  </si>
+  <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
+    <t>['3', '21', '28', '46']</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP235"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1657,7 +1678,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1738,7 +1759,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ2">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1863,7 +1884,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -2069,7 +2090,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2147,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ4">
         <v>1.23</v>
@@ -2356,7 +2377,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ5">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2481,7 +2502,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2559,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ6">
         <v>0.92</v>
@@ -2687,7 +2708,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2765,7 +2786,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ7">
         <v>1.23</v>
@@ -3099,7 +3120,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3386,7 +3407,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3511,7 +3532,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3795,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ12">
         <v>0.46</v>
@@ -3923,7 +3944,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4004,7 +4025,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ13">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4129,7 +4150,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4207,10 +4228,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ14">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4335,7 +4356,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4541,7 +4562,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4619,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ16">
         <v>1.54</v>
@@ -5159,7 +5180,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5240,7 +5261,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ19">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5365,7 +5386,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5855,7 +5876,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ22">
         <v>0.92</v>
@@ -5983,7 +6004,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6061,7 +6082,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ23">
         <v>1.15</v>
@@ -6270,7 +6291,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ24">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR24">
         <v>1.31</v>
@@ -6395,7 +6416,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6473,10 +6494,10 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ25">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR25">
         <v>1.23</v>
@@ -6682,7 +6703,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ26">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR26">
         <v>1.66</v>
@@ -6807,7 +6828,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -6888,7 +6909,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR27">
         <v>1.33</v>
@@ -7219,7 +7240,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7425,7 +7446,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7503,7 +7524,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ30">
         <v>0.77</v>
@@ -7837,7 +7858,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7915,7 +7936,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ32">
         <v>1.38</v>
@@ -8124,7 +8145,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ33">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR33">
         <v>1.04</v>
@@ -8249,7 +8270,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8455,7 +8476,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8533,7 +8554,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ35">
         <v>1.54</v>
@@ -8661,7 +8682,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8948,7 +8969,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ37">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR37">
         <v>0.82</v>
@@ -9073,7 +9094,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9151,10 +9172,10 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR38">
         <v>1.5</v>
@@ -9279,7 +9300,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9360,7 +9381,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ39">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR39">
         <v>1.92</v>
@@ -9566,7 +9587,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ40">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR40">
         <v>1.4</v>
@@ -9691,7 +9712,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9897,7 +9918,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9978,7 +9999,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ42">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR42">
         <v>1.42</v>
@@ -10181,10 +10202,10 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ43">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR43">
         <v>1.55</v>
@@ -10309,7 +10330,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10515,7 +10536,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10593,7 +10614,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ45">
         <v>1.54</v>
@@ -10927,7 +10948,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11133,7 +11154,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11211,7 +11232,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ48">
         <v>1.23</v>
@@ -11339,7 +11360,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11751,7 +11772,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12035,7 +12056,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ52">
         <v>1.23</v>
@@ -12369,7 +12390,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12450,7 +12471,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ54">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR54">
         <v>1.11</v>
@@ -12653,7 +12674,7 @@
         <v>2</v>
       </c>
       <c r="AP55">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ55">
         <v>0.46</v>
@@ -12781,7 +12802,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -12859,10 +12880,10 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ56">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR56">
         <v>1.67</v>
@@ -12987,7 +13008,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13274,7 +13295,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ58">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR58">
         <v>1.6</v>
@@ -13399,7 +13420,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13477,7 +13498,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ59">
         <v>1.15</v>
@@ -13683,10 +13704,10 @@
         <v>0.67</v>
       </c>
       <c r="AP60">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR60">
         <v>1.51</v>
@@ -14095,10 +14116,10 @@
         <v>2.33</v>
       </c>
       <c r="AP62">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ62">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR62">
         <v>1.41</v>
@@ -14510,7 +14531,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ64">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR64">
         <v>1.67</v>
@@ -14635,7 +14656,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -15047,7 +15068,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15253,7 +15274,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15334,7 +15355,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ68">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR68">
         <v>1.55</v>
@@ -15537,7 +15558,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ69">
         <v>1.38</v>
@@ -16155,7 +16176,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ72">
         <v>1.54</v>
@@ -16283,7 +16304,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16361,7 +16382,7 @@
         <v>1.25</v>
       </c>
       <c r="AP73">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ73">
         <v>1.08</v>
@@ -16489,7 +16510,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16567,10 +16588,10 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ74">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR74">
         <v>1.25</v>
@@ -16695,7 +16716,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16776,7 +16797,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR75">
         <v>1.62</v>
@@ -16901,7 +16922,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -16982,7 +17003,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ76">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR76">
         <v>1.55</v>
@@ -17185,7 +17206,7 @@
         <v>1.5</v>
       </c>
       <c r="AP77">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ77">
         <v>1.31</v>
@@ -17313,7 +17334,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17394,7 +17415,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ78">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR78">
         <v>1.7</v>
@@ -17597,10 +17618,10 @@
         <v>0.5</v>
       </c>
       <c r="AP79">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ79">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR79">
         <v>1.3</v>
@@ -17806,7 +17827,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ80">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR80">
         <v>1.09</v>
@@ -18343,7 +18364,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18961,7 +18982,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19373,7 +19394,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19785,7 +19806,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -19863,10 +19884,10 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ90">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR90">
         <v>1.65</v>
@@ -19991,7 +20012,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20069,7 +20090,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ91">
         <v>1.08</v>
@@ -20197,7 +20218,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20275,10 +20296,10 @@
         <v>0.6</v>
       </c>
       <c r="AP92">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR92">
         <v>1.19</v>
@@ -20403,7 +20424,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20609,7 +20630,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20690,7 +20711,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ94">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR94">
         <v>1.74</v>
@@ -20815,7 +20836,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -20893,10 +20914,10 @@
         <v>0.4</v>
       </c>
       <c r="AP95">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ95">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR95">
         <v>1.56</v>
@@ -21099,10 +21120,10 @@
         <v>2</v>
       </c>
       <c r="AP96">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ96">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR96">
         <v>1.37</v>
@@ -21227,7 +21248,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21433,7 +21454,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21511,10 +21532,10 @@
         <v>1.4</v>
       </c>
       <c r="AP98">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ98">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR98">
         <v>1.44</v>
@@ -21639,7 +21660,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -21926,7 +21947,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ100">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR100">
         <v>1.7</v>
@@ -22129,7 +22150,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ101">
         <v>0.92</v>
@@ -22463,7 +22484,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22875,7 +22896,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22956,7 +22977,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ105">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR105">
         <v>1.39</v>
@@ -23081,7 +23102,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23287,7 +23308,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23365,7 +23386,7 @@
         <v>1</v>
       </c>
       <c r="AP107">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ107">
         <v>0.46</v>
@@ -23493,7 +23514,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23699,7 +23720,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24395,7 +24416,7 @@
         <v>1.83</v>
       </c>
       <c r="AP112">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ112">
         <v>1.08</v>
@@ -24523,7 +24544,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24604,7 +24625,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ113">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR113">
         <v>1.52</v>
@@ -24729,7 +24750,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -24807,7 +24828,7 @@
         <v>1.6</v>
       </c>
       <c r="AP114">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ114">
         <v>1.08</v>
@@ -25013,10 +25034,10 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR115">
         <v>1.59</v>
@@ -25141,7 +25162,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25219,7 +25240,7 @@
         <v>1</v>
       </c>
       <c r="AP116">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ116">
         <v>1.31</v>
@@ -25347,7 +25368,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25428,7 +25449,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ117">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR117">
         <v>1.26</v>
@@ -25553,7 +25574,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -25634,7 +25655,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ118">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR118">
         <v>1.48</v>
@@ -25837,10 +25858,10 @@
         <v>2</v>
       </c>
       <c r="AP119">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ119">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR119">
         <v>1.64</v>
@@ -26252,7 +26273,7 @@
         <v>2</v>
       </c>
       <c r="AQ121">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR121">
         <v>1.6</v>
@@ -26377,7 +26398,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26455,7 +26476,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ122">
         <v>0.77</v>
@@ -26789,7 +26810,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27076,7 +27097,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ125">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR125">
         <v>1.63</v>
@@ -27201,7 +27222,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27613,7 +27634,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27897,7 +27918,7 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ129">
         <v>0.46</v>
@@ -28025,7 +28046,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28103,10 +28124,10 @@
         <v>0.43</v>
       </c>
       <c r="AP130">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ130">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR130">
         <v>1.55</v>
@@ -28437,7 +28458,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28518,7 +28539,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ132">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR132">
         <v>1.39</v>
@@ -28643,7 +28664,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28721,7 +28742,7 @@
         <v>1.29</v>
       </c>
       <c r="AP133">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ133">
         <v>1.31</v>
@@ -28849,7 +28870,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -28927,10 +28948,10 @@
         <v>1.43</v>
       </c>
       <c r="AP134">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ134">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR134">
         <v>1.14</v>
@@ -29133,7 +29154,7 @@
         <v>2.17</v>
       </c>
       <c r="AP135">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ135">
         <v>1.54</v>
@@ -29467,7 +29488,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29545,7 +29566,7 @@
         <v>1.57</v>
       </c>
       <c r="AP137">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ137">
         <v>1.23</v>
@@ -29879,7 +29900,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -30291,7 +30312,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30703,7 +30724,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30784,7 +30805,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ143">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR143">
         <v>1.64</v>
@@ -30909,7 +30930,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -30987,7 +31008,7 @@
         <v>1.29</v>
       </c>
       <c r="AP144">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ144">
         <v>1.08</v>
@@ -31193,7 +31214,7 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ145">
         <v>0.46</v>
@@ -31321,7 +31342,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31399,10 +31420,10 @@
         <v>1.63</v>
       </c>
       <c r="AP146">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ146">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR146">
         <v>1.64</v>
@@ -31527,7 +31548,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31605,7 +31626,7 @@
         <v>1.5</v>
       </c>
       <c r="AP147">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ147">
         <v>1.08</v>
@@ -31733,7 +31754,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -31814,7 +31835,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ148">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR148">
         <v>1.62</v>
@@ -32351,7 +32372,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32432,7 +32453,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ151">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR151">
         <v>1.02</v>
@@ -32557,7 +32578,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32635,7 +32656,7 @@
         <v>1.43</v>
       </c>
       <c r="AP152">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ152">
         <v>1.38</v>
@@ -32844,7 +32865,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ153">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR153">
         <v>1.48</v>
@@ -32969,7 +32990,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33050,7 +33071,7 @@
         <v>2</v>
       </c>
       <c r="AQ154">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR154">
         <v>1.58</v>
@@ -33668,7 +33689,7 @@
         <v>2</v>
       </c>
       <c r="AQ157">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR157">
         <v>1.59</v>
@@ -33793,7 +33814,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34283,10 +34304,10 @@
         <v>1.78</v>
       </c>
       <c r="AP160">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ160">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR160">
         <v>1.7</v>
@@ -34411,7 +34432,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34489,7 +34510,7 @@
         <v>0.75</v>
       </c>
       <c r="AP161">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ161">
         <v>0.46</v>
@@ -34698,7 +34719,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ162">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR162">
         <v>1.69</v>
@@ -34823,7 +34844,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34901,7 +34922,7 @@
         <v>2.38</v>
       </c>
       <c r="AP163">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ163">
         <v>1.54</v>
@@ -35029,7 +35050,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35235,7 +35256,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35519,10 +35540,10 @@
         <v>1.56</v>
       </c>
       <c r="AP166">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ166">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR166">
         <v>1.36</v>
@@ -35647,7 +35668,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -35931,7 +35952,7 @@
         <v>1.11</v>
       </c>
       <c r="AP168">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ168">
         <v>1.54</v>
@@ -36346,7 +36367,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ170">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR170">
         <v>1.53</v>
@@ -36471,7 +36492,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36552,7 +36573,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ171">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR171">
         <v>1.04</v>
@@ -36755,7 +36776,7 @@
         <v>1.5</v>
       </c>
       <c r="AP172">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ172">
         <v>1.23</v>
@@ -36961,7 +36982,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP173">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ173">
         <v>0.77</v>
@@ -37089,7 +37110,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37579,7 +37600,7 @@
         <v>1.44</v>
       </c>
       <c r="AP176">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ176">
         <v>1.23</v>
@@ -37707,7 +37728,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -38197,7 +38218,7 @@
         <v>1.33</v>
       </c>
       <c r="AP179">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ179">
         <v>1.38</v>
@@ -38325,7 +38346,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38406,7 +38427,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ180">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR180">
         <v>1.51</v>
@@ -38612,7 +38633,7 @@
         <v>2</v>
       </c>
       <c r="AQ181">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR181">
         <v>1.63</v>
@@ -38737,7 +38758,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38943,7 +38964,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39021,7 +39042,7 @@
         <v>0.67</v>
       </c>
       <c r="AP183">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ183">
         <v>0.92</v>
@@ -39230,7 +39251,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ184">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR184">
         <v>1.54</v>
@@ -39436,7 +39457,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ185">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR185">
         <v>1.68</v>
@@ -39561,7 +39582,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39639,7 +39660,7 @@
         <v>1.22</v>
       </c>
       <c r="AP186">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ186">
         <v>1.15</v>
@@ -39848,7 +39869,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ187">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR187">
         <v>1.28</v>
@@ -39973,7 +39994,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40260,7 +40281,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ189">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR189">
         <v>1.67</v>
@@ -40385,7 +40406,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40463,7 +40484,7 @@
         <v>1.1</v>
       </c>
       <c r="AP190">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ190">
         <v>1.54</v>
@@ -40797,7 +40818,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40875,7 +40896,7 @@
         <v>1</v>
       </c>
       <c r="AP192">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ192">
         <v>1.23</v>
@@ -41209,7 +41230,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41287,7 +41308,7 @@
         <v>1.3</v>
       </c>
       <c r="AP194">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ194">
         <v>1.23</v>
@@ -41493,7 +41514,7 @@
         <v>0.6</v>
       </c>
       <c r="AP195">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ195">
         <v>0.77</v>
@@ -41621,7 +41642,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41827,7 +41848,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -42114,7 +42135,7 @@
         <v>2</v>
       </c>
       <c r="AQ198">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR198">
         <v>1.61</v>
@@ -42239,7 +42260,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42523,10 +42544,10 @@
         <v>1.09</v>
       </c>
       <c r="AP200">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ200">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR200">
         <v>1.24</v>
@@ -42732,7 +42753,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ201">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR201">
         <v>1.53</v>
@@ -42857,7 +42878,7 @@
         <v>123</v>
       </c>
       <c r="P202" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q202">
         <v>4.3</v>
@@ -43269,7 +43290,7 @@
         <v>117</v>
       </c>
       <c r="P204" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q204">
         <v>3.1</v>
@@ -43350,7 +43371,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ204">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR204">
         <v>1.68</v>
@@ -43681,7 +43702,7 @@
         <v>218</v>
       </c>
       <c r="P206" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q206">
         <v>3.65</v>
@@ -43759,10 +43780,10 @@
         <v>1.45</v>
       </c>
       <c r="AP206">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ206">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR206">
         <v>1.34</v>
@@ -43887,7 +43908,7 @@
         <v>156</v>
       </c>
       <c r="P207" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q207">
         <v>3.45</v>
@@ -43965,7 +43986,7 @@
         <v>1.45</v>
       </c>
       <c r="AP207">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ207">
         <v>1.31</v>
@@ -44093,7 +44114,7 @@
         <v>197</v>
       </c>
       <c r="P208" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q208">
         <v>3.5</v>
@@ -44174,7 +44195,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ208">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR208">
         <v>1.4</v>
@@ -44299,7 +44320,7 @@
         <v>129</v>
       </c>
       <c r="P209" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q209">
         <v>2.4</v>
@@ -44917,7 +44938,7 @@
         <v>220</v>
       </c>
       <c r="P212" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q212">
         <v>2.43</v>
@@ -45123,7 +45144,7 @@
         <v>221</v>
       </c>
       <c r="P213" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q213">
         <v>3.15</v>
@@ -45410,7 +45431,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ214">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR214">
         <v>1.15</v>
@@ -45819,7 +45840,7 @@
         <v>1.18</v>
       </c>
       <c r="AP216">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ216">
         <v>1.23</v>
@@ -46025,7 +46046,7 @@
         <v>0.82</v>
       </c>
       <c r="AP217">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ217">
         <v>0.92</v>
@@ -46153,7 +46174,7 @@
         <v>89</v>
       </c>
       <c r="P218" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q218">
         <v>3.6</v>
@@ -46234,7 +46255,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ218">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR218">
         <v>1.7</v>
@@ -46359,7 +46380,7 @@
         <v>224</v>
       </c>
       <c r="P219" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q219">
         <v>3.78</v>
@@ -46437,7 +46458,7 @@
         <v>1.42</v>
       </c>
       <c r="AP219">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ219">
         <v>1.31</v>
@@ -46565,7 +46586,7 @@
         <v>225</v>
       </c>
       <c r="P220" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q220">
         <v>3.26</v>
@@ -46646,7 +46667,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ220">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR220">
         <v>1.51</v>
@@ -46849,7 +46870,7 @@
         <v>1.36</v>
       </c>
       <c r="AP221">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ221">
         <v>1.15</v>
@@ -47058,7 +47079,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ222">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="AR222">
         <v>1.27</v>
@@ -47389,7 +47410,7 @@
         <v>89</v>
       </c>
       <c r="P224" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q224">
         <v>5.44</v>
@@ -47467,7 +47488,7 @@
         <v>1.42</v>
       </c>
       <c r="AP224">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AQ224">
         <v>1.54</v>
@@ -47676,7 +47697,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ225">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR225">
         <v>1.56</v>
@@ -47879,10 +47900,10 @@
         <v>1.42</v>
       </c>
       <c r="AP226">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ226">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR226">
         <v>1.36</v>
@@ -48007,7 +48028,7 @@
         <v>156</v>
       </c>
       <c r="P227" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q227">
         <v>2.9</v>
@@ -48213,7 +48234,7 @@
         <v>228</v>
       </c>
       <c r="P228" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q228">
         <v>2.6</v>
@@ -49037,7 +49058,7 @@
         <v>230</v>
       </c>
       <c r="P232" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q232">
         <v>2.75</v>
@@ -49733,7 +49754,7 @@
         <v>1.25</v>
       </c>
       <c r="AP235">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ235">
         <v>1.15</v>
@@ -49812,6 +49833,1242 @@
       </c>
       <c r="BP235">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7502840</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45745.33333333334</v>
+      </c>
+      <c r="F236">
+        <v>27</v>
+      </c>
+      <c r="G236" t="s">
+        <v>80</v>
+      </c>
+      <c r="H236" t="s">
+        <v>87</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+      <c r="J236">
+        <v>1</v>
+      </c>
+      <c r="K236">
+        <v>1</v>
+      </c>
+      <c r="L236">
+        <v>1</v>
+      </c>
+      <c r="M236">
+        <v>3</v>
+      </c>
+      <c r="N236">
+        <v>4</v>
+      </c>
+      <c r="O236" t="s">
+        <v>128</v>
+      </c>
+      <c r="P236" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q236">
+        <v>4.5</v>
+      </c>
+      <c r="R236">
+        <v>2.1</v>
+      </c>
+      <c r="S236">
+        <v>2.63</v>
+      </c>
+      <c r="T236">
+        <v>1.44</v>
+      </c>
+      <c r="U236">
+        <v>2.63</v>
+      </c>
+      <c r="V236">
+        <v>3.25</v>
+      </c>
+      <c r="W236">
+        <v>1.33</v>
+      </c>
+      <c r="X236">
+        <v>9</v>
+      </c>
+      <c r="Y236">
+        <v>1.07</v>
+      </c>
+      <c r="Z236">
+        <v>3.8</v>
+      </c>
+      <c r="AA236">
+        <v>3.4</v>
+      </c>
+      <c r="AB236">
+        <v>1.9</v>
+      </c>
+      <c r="AC236">
+        <v>0</v>
+      </c>
+      <c r="AD236">
+        <v>0</v>
+      </c>
+      <c r="AE236">
+        <v>3.23</v>
+      </c>
+      <c r="AF236">
+        <v>1.34</v>
+      </c>
+      <c r="AG236">
+        <v>1.95</v>
+      </c>
+      <c r="AH236">
+        <v>1.7</v>
+      </c>
+      <c r="AI236">
+        <v>1.91</v>
+      </c>
+      <c r="AJ236">
+        <v>1.8</v>
+      </c>
+      <c r="AK236">
+        <v>0</v>
+      </c>
+      <c r="AL236">
+        <v>0</v>
+      </c>
+      <c r="AM236">
+        <v>0</v>
+      </c>
+      <c r="AN236">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AO236">
+        <v>1.54</v>
+      </c>
+      <c r="AP236">
+        <v>0.64</v>
+      </c>
+      <c r="AQ236">
+        <v>1.64</v>
+      </c>
+      <c r="AR236">
+        <v>1.38</v>
+      </c>
+      <c r="AS236">
+        <v>1.37</v>
+      </c>
+      <c r="AT236">
+        <v>2.75</v>
+      </c>
+      <c r="AU236">
+        <v>5</v>
+      </c>
+      <c r="AV236">
+        <v>5</v>
+      </c>
+      <c r="AW236">
+        <v>5</v>
+      </c>
+      <c r="AX236">
+        <v>4</v>
+      </c>
+      <c r="AY236">
+        <v>10</v>
+      </c>
+      <c r="AZ236">
+        <v>9</v>
+      </c>
+      <c r="BA236">
+        <v>3</v>
+      </c>
+      <c r="BB236">
+        <v>4</v>
+      </c>
+      <c r="BC236">
+        <v>7</v>
+      </c>
+      <c r="BD236">
+        <v>0</v>
+      </c>
+      <c r="BE236">
+        <v>0</v>
+      </c>
+      <c r="BF236">
+        <v>0</v>
+      </c>
+      <c r="BG236">
+        <v>0</v>
+      </c>
+      <c r="BH236">
+        <v>0</v>
+      </c>
+      <c r="BI236">
+        <v>0</v>
+      </c>
+      <c r="BJ236">
+        <v>0</v>
+      </c>
+      <c r="BK236">
+        <v>0</v>
+      </c>
+      <c r="BL236">
+        <v>0</v>
+      </c>
+      <c r="BM236">
+        <v>0</v>
+      </c>
+      <c r="BN236">
+        <v>0</v>
+      </c>
+      <c r="BO236">
+        <v>0</v>
+      </c>
+      <c r="BP236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7502841</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45745.45833333334</v>
+      </c>
+      <c r="F237">
+        <v>27</v>
+      </c>
+      <c r="G237" t="s">
+        <v>74</v>
+      </c>
+      <c r="H237" t="s">
+        <v>70</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>1</v>
+      </c>
+      <c r="K237">
+        <v>1</v>
+      </c>
+      <c r="L237">
+        <v>0</v>
+      </c>
+      <c r="M237">
+        <v>1</v>
+      </c>
+      <c r="N237">
+        <v>1</v>
+      </c>
+      <c r="O237" t="s">
+        <v>89</v>
+      </c>
+      <c r="P237" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q237">
+        <v>3.5</v>
+      </c>
+      <c r="R237">
+        <v>2.05</v>
+      </c>
+      <c r="S237">
+        <v>3.25</v>
+      </c>
+      <c r="T237">
+        <v>1.44</v>
+      </c>
+      <c r="U237">
+        <v>2.63</v>
+      </c>
+      <c r="V237">
+        <v>3.25</v>
+      </c>
+      <c r="W237">
+        <v>1.33</v>
+      </c>
+      <c r="X237">
+        <v>10</v>
+      </c>
+      <c r="Y237">
+        <v>1.06</v>
+      </c>
+      <c r="Z237">
+        <v>2.7</v>
+      </c>
+      <c r="AA237">
+        <v>3.1</v>
+      </c>
+      <c r="AB237">
+        <v>2.5</v>
+      </c>
+      <c r="AC237">
+        <v>0</v>
+      </c>
+      <c r="AD237">
+        <v>0</v>
+      </c>
+      <c r="AE237">
+        <v>2.26</v>
+      </c>
+      <c r="AF237">
+        <v>1.63</v>
+      </c>
+      <c r="AG237">
+        <v>2.05</v>
+      </c>
+      <c r="AH237">
+        <v>1.65</v>
+      </c>
+      <c r="AI237">
+        <v>1.83</v>
+      </c>
+      <c r="AJ237">
+        <v>1.83</v>
+      </c>
+      <c r="AK237">
+        <v>0</v>
+      </c>
+      <c r="AL237">
+        <v>0</v>
+      </c>
+      <c r="AM237">
+        <v>0</v>
+      </c>
+      <c r="AN237">
+        <v>1.77</v>
+      </c>
+      <c r="AO237">
+        <v>1.38</v>
+      </c>
+      <c r="AP237">
+        <v>1.64</v>
+      </c>
+      <c r="AQ237">
+        <v>1.5</v>
+      </c>
+      <c r="AR237">
+        <v>1.34</v>
+      </c>
+      <c r="AS237">
+        <v>1.43</v>
+      </c>
+      <c r="AT237">
+        <v>2.77</v>
+      </c>
+      <c r="AU237">
+        <v>4</v>
+      </c>
+      <c r="AV237">
+        <v>7</v>
+      </c>
+      <c r="AW237">
+        <v>11</v>
+      </c>
+      <c r="AX237">
+        <v>5</v>
+      </c>
+      <c r="AY237">
+        <v>15</v>
+      </c>
+      <c r="AZ237">
+        <v>12</v>
+      </c>
+      <c r="BA237">
+        <v>-1</v>
+      </c>
+      <c r="BB237">
+        <v>-1</v>
+      </c>
+      <c r="BC237">
+        <v>-1</v>
+      </c>
+      <c r="BD237">
+        <v>0</v>
+      </c>
+      <c r="BE237">
+        <v>0</v>
+      </c>
+      <c r="BF237">
+        <v>0</v>
+      </c>
+      <c r="BG237">
+        <v>0</v>
+      </c>
+      <c r="BH237">
+        <v>0</v>
+      </c>
+      <c r="BI237">
+        <v>0</v>
+      </c>
+      <c r="BJ237">
+        <v>0</v>
+      </c>
+      <c r="BK237">
+        <v>0</v>
+      </c>
+      <c r="BL237">
+        <v>0</v>
+      </c>
+      <c r="BM237">
+        <v>0</v>
+      </c>
+      <c r="BN237">
+        <v>0</v>
+      </c>
+      <c r="BO237">
+        <v>0</v>
+      </c>
+      <c r="BP237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7502838</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45745.52083333334</v>
+      </c>
+      <c r="F238">
+        <v>27</v>
+      </c>
+      <c r="G238" t="s">
+        <v>84</v>
+      </c>
+      <c r="H238" t="s">
+        <v>81</v>
+      </c>
+      <c r="I238">
+        <v>1</v>
+      </c>
+      <c r="J238">
+        <v>1</v>
+      </c>
+      <c r="K238">
+        <v>2</v>
+      </c>
+      <c r="L238">
+        <v>3</v>
+      </c>
+      <c r="M238">
+        <v>2</v>
+      </c>
+      <c r="N238">
+        <v>5</v>
+      </c>
+      <c r="O238" t="s">
+        <v>233</v>
+      </c>
+      <c r="P238" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q238">
+        <v>2.1</v>
+      </c>
+      <c r="R238">
+        <v>2.3</v>
+      </c>
+      <c r="S238">
+        <v>6</v>
+      </c>
+      <c r="T238">
+        <v>1.36</v>
+      </c>
+      <c r="U238">
+        <v>3</v>
+      </c>
+      <c r="V238">
+        <v>2.63</v>
+      </c>
+      <c r="W238">
+        <v>1.44</v>
+      </c>
+      <c r="X238">
+        <v>7</v>
+      </c>
+      <c r="Y238">
+        <v>1.1</v>
+      </c>
+      <c r="Z238">
+        <v>1.54</v>
+      </c>
+      <c r="AA238">
+        <v>3.9</v>
+      </c>
+      <c r="AB238">
+        <v>5.3</v>
+      </c>
+      <c r="AC238">
+        <v>0</v>
+      </c>
+      <c r="AD238">
+        <v>0</v>
+      </c>
+      <c r="AE238">
+        <v>0</v>
+      </c>
+      <c r="AF238">
+        <v>0</v>
+      </c>
+      <c r="AG238">
+        <v>1.75</v>
+      </c>
+      <c r="AH238">
+        <v>1.91</v>
+      </c>
+      <c r="AI238">
+        <v>1.83</v>
+      </c>
+      <c r="AJ238">
+        <v>1.83</v>
+      </c>
+      <c r="AK238">
+        <v>0</v>
+      </c>
+      <c r="AL238">
+        <v>0</v>
+      </c>
+      <c r="AM238">
+        <v>0</v>
+      </c>
+      <c r="AN238">
+        <v>1.85</v>
+      </c>
+      <c r="AO238">
+        <v>1</v>
+      </c>
+      <c r="AP238">
+        <v>1.93</v>
+      </c>
+      <c r="AQ238">
+        <v>0.93</v>
+      </c>
+      <c r="AR238">
+        <v>1.78</v>
+      </c>
+      <c r="AS238">
+        <v>1.14</v>
+      </c>
+      <c r="AT238">
+        <v>2.92</v>
+      </c>
+      <c r="AU238">
+        <v>8</v>
+      </c>
+      <c r="AV238">
+        <v>3</v>
+      </c>
+      <c r="AW238">
+        <v>19</v>
+      </c>
+      <c r="AX238">
+        <v>8</v>
+      </c>
+      <c r="AY238">
+        <v>27</v>
+      </c>
+      <c r="AZ238">
+        <v>11</v>
+      </c>
+      <c r="BA238">
+        <v>-1</v>
+      </c>
+      <c r="BB238">
+        <v>-1</v>
+      </c>
+      <c r="BC238">
+        <v>-1</v>
+      </c>
+      <c r="BD238">
+        <v>0</v>
+      </c>
+      <c r="BE238">
+        <v>0</v>
+      </c>
+      <c r="BF238">
+        <v>0</v>
+      </c>
+      <c r="BG238">
+        <v>0</v>
+      </c>
+      <c r="BH238">
+        <v>0</v>
+      </c>
+      <c r="BI238">
+        <v>0</v>
+      </c>
+      <c r="BJ238">
+        <v>0</v>
+      </c>
+      <c r="BK238">
+        <v>0</v>
+      </c>
+      <c r="BL238">
+        <v>0</v>
+      </c>
+      <c r="BM238">
+        <v>0</v>
+      </c>
+      <c r="BN238">
+        <v>0</v>
+      </c>
+      <c r="BO238">
+        <v>0</v>
+      </c>
+      <c r="BP238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7502839</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45746.29166666666</v>
+      </c>
+      <c r="F239">
+        <v>27</v>
+      </c>
+      <c r="G239" t="s">
+        <v>72</v>
+      </c>
+      <c r="H239" t="s">
+        <v>77</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>0</v>
+      </c>
+      <c r="L239">
+        <v>0</v>
+      </c>
+      <c r="M239">
+        <v>1</v>
+      </c>
+      <c r="N239">
+        <v>1</v>
+      </c>
+      <c r="O239" t="s">
+        <v>89</v>
+      </c>
+      <c r="P239" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q239">
+        <v>3.75</v>
+      </c>
+      <c r="R239">
+        <v>2</v>
+      </c>
+      <c r="S239">
+        <v>3.2</v>
+      </c>
+      <c r="T239">
+        <v>1.5</v>
+      </c>
+      <c r="U239">
+        <v>2.5</v>
+      </c>
+      <c r="V239">
+        <v>3.5</v>
+      </c>
+      <c r="W239">
+        <v>1.29</v>
+      </c>
+      <c r="X239">
+        <v>11</v>
+      </c>
+      <c r="Y239">
+        <v>1.05</v>
+      </c>
+      <c r="Z239">
+        <v>3.05</v>
+      </c>
+      <c r="AA239">
+        <v>3</v>
+      </c>
+      <c r="AB239">
+        <v>2.4</v>
+      </c>
+      <c r="AC239">
+        <v>2.95</v>
+      </c>
+      <c r="AD239">
+        <v>1.39</v>
+      </c>
+      <c r="AE239">
+        <v>0</v>
+      </c>
+      <c r="AF239">
+        <v>0</v>
+      </c>
+      <c r="AG239">
+        <v>2.2</v>
+      </c>
+      <c r="AH239">
+        <v>1.55</v>
+      </c>
+      <c r="AI239">
+        <v>2</v>
+      </c>
+      <c r="AJ239">
+        <v>1.73</v>
+      </c>
+      <c r="AK239">
+        <v>0</v>
+      </c>
+      <c r="AL239">
+        <v>0</v>
+      </c>
+      <c r="AM239">
+        <v>0</v>
+      </c>
+      <c r="AN239">
+        <v>1.54</v>
+      </c>
+      <c r="AO239">
+        <v>1.54</v>
+      </c>
+      <c r="AP239">
+        <v>1.43</v>
+      </c>
+      <c r="AQ239">
+        <v>1.64</v>
+      </c>
+      <c r="AR239">
+        <v>1.37</v>
+      </c>
+      <c r="AS239">
+        <v>1.43</v>
+      </c>
+      <c r="AT239">
+        <v>2.8</v>
+      </c>
+      <c r="AU239">
+        <v>3</v>
+      </c>
+      <c r="AV239">
+        <v>7</v>
+      </c>
+      <c r="AW239">
+        <v>7</v>
+      </c>
+      <c r="AX239">
+        <v>4</v>
+      </c>
+      <c r="AY239">
+        <v>10</v>
+      </c>
+      <c r="AZ239">
+        <v>11</v>
+      </c>
+      <c r="BA239">
+        <v>-1</v>
+      </c>
+      <c r="BB239">
+        <v>-1</v>
+      </c>
+      <c r="BC239">
+        <v>-1</v>
+      </c>
+      <c r="BD239">
+        <v>0</v>
+      </c>
+      <c r="BE239">
+        <v>0</v>
+      </c>
+      <c r="BF239">
+        <v>0</v>
+      </c>
+      <c r="BG239">
+        <v>0</v>
+      </c>
+      <c r="BH239">
+        <v>0</v>
+      </c>
+      <c r="BI239">
+        <v>0</v>
+      </c>
+      <c r="BJ239">
+        <v>0</v>
+      </c>
+      <c r="BK239">
+        <v>0</v>
+      </c>
+      <c r="BL239">
+        <v>0</v>
+      </c>
+      <c r="BM239">
+        <v>0</v>
+      </c>
+      <c r="BN239">
+        <v>0</v>
+      </c>
+      <c r="BO239">
+        <v>0</v>
+      </c>
+      <c r="BP239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7502846</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45746.36458333334</v>
+      </c>
+      <c r="F240">
+        <v>27</v>
+      </c>
+      <c r="G240" t="s">
+        <v>75</v>
+      </c>
+      <c r="H240" t="s">
+        <v>76</v>
+      </c>
+      <c r="I240">
+        <v>2</v>
+      </c>
+      <c r="J240">
+        <v>3</v>
+      </c>
+      <c r="K240">
+        <v>5</v>
+      </c>
+      <c r="L240">
+        <v>2</v>
+      </c>
+      <c r="M240">
+        <v>4</v>
+      </c>
+      <c r="N240">
+        <v>6</v>
+      </c>
+      <c r="O240" t="s">
+        <v>234</v>
+      </c>
+      <c r="P240" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q240">
+        <v>3</v>
+      </c>
+      <c r="R240">
+        <v>2.05</v>
+      </c>
+      <c r="S240">
+        <v>4</v>
+      </c>
+      <c r="T240">
+        <v>1.44</v>
+      </c>
+      <c r="U240">
+        <v>2.63</v>
+      </c>
+      <c r="V240">
+        <v>3.25</v>
+      </c>
+      <c r="W240">
+        <v>1.33</v>
+      </c>
+      <c r="X240">
+        <v>10</v>
+      </c>
+      <c r="Y240">
+        <v>1.06</v>
+      </c>
+      <c r="Z240">
+        <v>2.2</v>
+      </c>
+      <c r="AA240">
+        <v>3.3</v>
+      </c>
+      <c r="AB240">
+        <v>3.1</v>
+      </c>
+      <c r="AC240">
+        <v>0</v>
+      </c>
+      <c r="AD240">
+        <v>0</v>
+      </c>
+      <c r="AE240">
+        <v>0</v>
+      </c>
+      <c r="AF240">
+        <v>0</v>
+      </c>
+      <c r="AG240">
+        <v>2.05</v>
+      </c>
+      <c r="AH240">
+        <v>1.65</v>
+      </c>
+      <c r="AI240">
+        <v>1.83</v>
+      </c>
+      <c r="AJ240">
+        <v>1.83</v>
+      </c>
+      <c r="AK240">
+        <v>0</v>
+      </c>
+      <c r="AL240">
+        <v>0</v>
+      </c>
+      <c r="AM240">
+        <v>0</v>
+      </c>
+      <c r="AN240">
+        <v>1.69</v>
+      </c>
+      <c r="AO240">
+        <v>0.38</v>
+      </c>
+      <c r="AP240">
+        <v>1.57</v>
+      </c>
+      <c r="AQ240">
+        <v>0.57</v>
+      </c>
+      <c r="AR240">
+        <v>1.45</v>
+      </c>
+      <c r="AS240">
+        <v>1.52</v>
+      </c>
+      <c r="AT240">
+        <v>2.97</v>
+      </c>
+      <c r="AU240">
+        <v>9</v>
+      </c>
+      <c r="AV240">
+        <v>9</v>
+      </c>
+      <c r="AW240">
+        <v>11</v>
+      </c>
+      <c r="AX240">
+        <v>2</v>
+      </c>
+      <c r="AY240">
+        <v>20</v>
+      </c>
+      <c r="AZ240">
+        <v>11</v>
+      </c>
+      <c r="BA240">
+        <v>8</v>
+      </c>
+      <c r="BB240">
+        <v>2</v>
+      </c>
+      <c r="BC240">
+        <v>10</v>
+      </c>
+      <c r="BD240">
+        <v>0</v>
+      </c>
+      <c r="BE240">
+        <v>0</v>
+      </c>
+      <c r="BF240">
+        <v>0</v>
+      </c>
+      <c r="BG240">
+        <v>0</v>
+      </c>
+      <c r="BH240">
+        <v>0</v>
+      </c>
+      <c r="BI240">
+        <v>0</v>
+      </c>
+      <c r="BJ240">
+        <v>0</v>
+      </c>
+      <c r="BK240">
+        <v>0</v>
+      </c>
+      <c r="BL240">
+        <v>0</v>
+      </c>
+      <c r="BM240">
+        <v>0</v>
+      </c>
+      <c r="BN240">
+        <v>0</v>
+      </c>
+      <c r="BO240">
+        <v>0</v>
+      </c>
+      <c r="BP240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7502842</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45746.41666666666</v>
+      </c>
+      <c r="F241">
+        <v>27</v>
+      </c>
+      <c r="G241" t="s">
+        <v>82</v>
+      </c>
+      <c r="H241" t="s">
+        <v>85</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>0</v>
+      </c>
+      <c r="L241">
+        <v>2</v>
+      </c>
+      <c r="M241">
+        <v>0</v>
+      </c>
+      <c r="N241">
+        <v>2</v>
+      </c>
+      <c r="O241" t="s">
+        <v>235</v>
+      </c>
+      <c r="P241" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q241">
+        <v>3.75</v>
+      </c>
+      <c r="R241">
+        <v>2.05</v>
+      </c>
+      <c r="S241">
+        <v>3.1</v>
+      </c>
+      <c r="T241">
+        <v>1.44</v>
+      </c>
+      <c r="U241">
+        <v>2.63</v>
+      </c>
+      <c r="V241">
+        <v>3.4</v>
+      </c>
+      <c r="W241">
+        <v>1.3</v>
+      </c>
+      <c r="X241">
+        <v>10</v>
+      </c>
+      <c r="Y241">
+        <v>1.06</v>
+      </c>
+      <c r="Z241">
+        <v>3.1</v>
+      </c>
+      <c r="AA241">
+        <v>3.1</v>
+      </c>
+      <c r="AB241">
+        <v>2.25</v>
+      </c>
+      <c r="AC241">
+        <v>0</v>
+      </c>
+      <c r="AD241">
+        <v>0</v>
+      </c>
+      <c r="AE241">
+        <v>2.56</v>
+      </c>
+      <c r="AF241">
+        <v>1.49</v>
+      </c>
+      <c r="AG241">
+        <v>2.05</v>
+      </c>
+      <c r="AH241">
+        <v>1.61</v>
+      </c>
+      <c r="AI241">
+        <v>1.83</v>
+      </c>
+      <c r="AJ241">
+        <v>1.83</v>
+      </c>
+      <c r="AK241">
+        <v>0</v>
+      </c>
+      <c r="AL241">
+        <v>0</v>
+      </c>
+      <c r="AM241">
+        <v>0</v>
+      </c>
+      <c r="AN241">
+        <v>0.92</v>
+      </c>
+      <c r="AO241">
+        <v>1.69</v>
+      </c>
+      <c r="AP241">
+        <v>1.07</v>
+      </c>
+      <c r="AQ241">
+        <v>1.57</v>
+      </c>
+      <c r="AR241">
+        <v>1.74</v>
+      </c>
+      <c r="AS241">
+        <v>1.42</v>
+      </c>
+      <c r="AT241">
+        <v>3.16</v>
+      </c>
+      <c r="AU241">
+        <v>10</v>
+      </c>
+      <c r="AV241">
+        <v>5</v>
+      </c>
+      <c r="AW241">
+        <v>8</v>
+      </c>
+      <c r="AX241">
+        <v>5</v>
+      </c>
+      <c r="AY241">
+        <v>18</v>
+      </c>
+      <c r="AZ241">
+        <v>10</v>
+      </c>
+      <c r="BA241">
+        <v>-1</v>
+      </c>
+      <c r="BB241">
+        <v>-1</v>
+      </c>
+      <c r="BC241">
+        <v>-1</v>
+      </c>
+      <c r="BD241">
+        <v>0</v>
+      </c>
+      <c r="BE241">
+        <v>0</v>
+      </c>
+      <c r="BF241">
+        <v>0</v>
+      </c>
+      <c r="BG241">
+        <v>0</v>
+      </c>
+      <c r="BH241">
+        <v>0</v>
+      </c>
+      <c r="BI241">
+        <v>0</v>
+      </c>
+      <c r="BJ241">
+        <v>0</v>
+      </c>
+      <c r="BK241">
+        <v>0</v>
+      </c>
+      <c r="BL241">
+        <v>0</v>
+      </c>
+      <c r="BM241">
+        <v>0</v>
+      </c>
+      <c r="BN241">
+        <v>0</v>
+      </c>
+      <c r="BO241">
+        <v>0</v>
+      </c>
+      <c r="BP241">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="349">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1422,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP241"/>
+  <dimension ref="A1:BP242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2995,7 +2995,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ8">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -4434,7 +4434,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ15">
         <v>1.08</v>
@@ -5467,7 +5467,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ20">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR20">
         <v>1.01</v>
@@ -8348,7 +8348,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ34">
         <v>1.23</v>
@@ -9793,7 +9793,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ41">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR41">
         <v>1.49</v>
@@ -10820,7 +10820,7 @@
         <v>2</v>
       </c>
       <c r="AP46">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ46">
         <v>1.15</v>
@@ -13910,7 +13910,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ61">
         <v>1.54</v>
@@ -14325,7 +14325,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ63">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR63">
         <v>1.24</v>
@@ -16794,7 +16794,7 @@
         <v>0.5</v>
       </c>
       <c r="AP75">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ75">
         <v>0.93</v>
@@ -17209,7 +17209,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ77">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR77">
         <v>1.55</v>
@@ -20708,7 +20708,7 @@
         <v>2.2</v>
       </c>
       <c r="AP94">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ94">
         <v>1.64</v>
@@ -21329,7 +21329,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ97">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR97">
         <v>1.52</v>
@@ -21944,7 +21944,7 @@
         <v>1.67</v>
       </c>
       <c r="AP100">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ100">
         <v>1.5</v>
@@ -24210,7 +24210,7 @@
         <v>2.6</v>
       </c>
       <c r="AP111">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ111">
         <v>1.54</v>
@@ -25243,7 +25243,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ116">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR116">
         <v>1.1</v>
@@ -28745,7 +28745,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ133">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR133">
         <v>1.63</v>
@@ -30187,7 +30187,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ140">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR140">
         <v>1.48</v>
@@ -30596,7 +30596,7 @@
         <v>0.71</v>
       </c>
       <c r="AP142">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ142">
         <v>0.77</v>
@@ -34098,7 +34098,7 @@
         <v>1.38</v>
       </c>
       <c r="AP159">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ159">
         <v>1.38</v>
@@ -35337,7 +35337,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ165">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR165">
         <v>1.57</v>
@@ -37188,7 +37188,7 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ174">
         <v>1.08</v>
@@ -40075,7 +40075,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ188">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR188">
         <v>1.43</v>
@@ -43574,7 +43574,7 @@
         <v>0.9</v>
       </c>
       <c r="AP205">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ205">
         <v>0.92</v>
@@ -43989,7 +43989,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ207">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR207">
         <v>1.41</v>
@@ -46252,7 +46252,7 @@
         <v>1.58</v>
       </c>
       <c r="AP218">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ218">
         <v>1.57</v>
@@ -46461,7 +46461,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ219">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR219">
         <v>1.28</v>
@@ -50199,13 +50199,13 @@
         <v>12</v>
       </c>
       <c r="BA237">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BB237">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC237">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD237">
         <v>0</v>
@@ -50405,13 +50405,13 @@
         <v>11</v>
       </c>
       <c r="BA238">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BB238">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC238">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="BD238">
         <v>0</v>
@@ -51068,6 +51068,212 @@
         <v>0</v>
       </c>
       <c r="BP241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7502845</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45746.58333333334</v>
+      </c>
+      <c r="F242">
+        <v>27</v>
+      </c>
+      <c r="G242" t="s">
+        <v>83</v>
+      </c>
+      <c r="H242" t="s">
+        <v>79</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>0</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+      <c r="M242">
+        <v>1</v>
+      </c>
+      <c r="N242">
+        <v>1</v>
+      </c>
+      <c r="O242" t="s">
+        <v>89</v>
+      </c>
+      <c r="P242" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q242">
+        <v>3.6</v>
+      </c>
+      <c r="R242">
+        <v>1.95</v>
+      </c>
+      <c r="S242">
+        <v>3.4</v>
+      </c>
+      <c r="T242">
+        <v>1.53</v>
+      </c>
+      <c r="U242">
+        <v>2.38</v>
+      </c>
+      <c r="V242">
+        <v>3.5</v>
+      </c>
+      <c r="W242">
+        <v>1.29</v>
+      </c>
+      <c r="X242">
+        <v>11</v>
+      </c>
+      <c r="Y242">
+        <v>1.05</v>
+      </c>
+      <c r="Z242">
+        <v>2.8</v>
+      </c>
+      <c r="AA242">
+        <v>2.9</v>
+      </c>
+      <c r="AB242">
+        <v>2.55</v>
+      </c>
+      <c r="AC242">
+        <v>0</v>
+      </c>
+      <c r="AD242">
+        <v>0</v>
+      </c>
+      <c r="AE242">
+        <v>3.37</v>
+      </c>
+      <c r="AF242">
+        <v>1.31</v>
+      </c>
+      <c r="AG242">
+        <v>2.2</v>
+      </c>
+      <c r="AH242">
+        <v>1.55</v>
+      </c>
+      <c r="AI242">
+        <v>1.91</v>
+      </c>
+      <c r="AJ242">
+        <v>1.8</v>
+      </c>
+      <c r="AK242">
+        <v>0</v>
+      </c>
+      <c r="AL242">
+        <v>0</v>
+      </c>
+      <c r="AM242">
+        <v>0</v>
+      </c>
+      <c r="AN242">
+        <v>1.77</v>
+      </c>
+      <c r="AO242">
+        <v>1.31</v>
+      </c>
+      <c r="AP242">
+        <v>1.64</v>
+      </c>
+      <c r="AQ242">
+        <v>1.43</v>
+      </c>
+      <c r="AR242">
+        <v>1.68</v>
+      </c>
+      <c r="AS242">
+        <v>1.19</v>
+      </c>
+      <c r="AT242">
+        <v>2.87</v>
+      </c>
+      <c r="AU242">
+        <v>11</v>
+      </c>
+      <c r="AV242">
+        <v>9</v>
+      </c>
+      <c r="AW242">
+        <v>10</v>
+      </c>
+      <c r="AX242">
+        <v>2</v>
+      </c>
+      <c r="AY242">
+        <v>21</v>
+      </c>
+      <c r="AZ242">
+        <v>11</v>
+      </c>
+      <c r="BA242">
+        <v>-1</v>
+      </c>
+      <c r="BB242">
+        <v>-1</v>
+      </c>
+      <c r="BC242">
+        <v>-1</v>
+      </c>
+      <c r="BD242">
+        <v>0</v>
+      </c>
+      <c r="BE242">
+        <v>0</v>
+      </c>
+      <c r="BF242">
+        <v>0</v>
+      </c>
+      <c r="BG242">
+        <v>0</v>
+      </c>
+      <c r="BH242">
+        <v>0</v>
+      </c>
+      <c r="BI242">
+        <v>0</v>
+      </c>
+      <c r="BJ242">
+        <v>0</v>
+      </c>
+      <c r="BK242">
+        <v>0</v>
+      </c>
+      <c r="BL242">
+        <v>0</v>
+      </c>
+      <c r="BM242">
+        <v>0</v>
+      </c>
+      <c r="BN242">
+        <v>0</v>
+      </c>
+      <c r="BO242">
+        <v>0</v>
+      </c>
+      <c r="BP242">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="349">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -724,6 +724,9 @@
     <t>['52', '90+6']</t>
   </si>
   <si>
+    <t>['78']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -908,9 +911,6 @@
   </si>
   <si>
     <t>['41', '67', '90+2']</t>
-  </si>
-  <si>
-    <t>['78']</t>
   </si>
   <si>
     <t>['71']</t>
@@ -1422,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP242"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1678,7 +1678,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1884,7 +1884,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ3">
         <v>1.15</v>
@@ -2090,7 +2090,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2502,7 +2502,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2708,7 +2708,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3120,7 +3120,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3532,7 +3532,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3613,7 +3613,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4150,7 +4150,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4356,7 +4356,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4437,7 +4437,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ15">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ18">
         <v>1.38</v>
@@ -5180,7 +5180,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5386,7 +5386,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6004,7 +6004,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6416,7 +6416,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6828,7 +6828,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -6906,7 +6906,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ27">
         <v>0.93</v>
@@ -7112,7 +7112,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ28">
         <v>1.54</v>
@@ -7240,7 +7240,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7321,7 +7321,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>1.08</v>
@@ -7446,7 +7446,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7733,7 +7733,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ31">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR31">
         <v>1.31</v>
@@ -7858,7 +7858,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8270,7 +8270,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8476,7 +8476,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8682,7 +8682,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -9094,7 +9094,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9300,7 +9300,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9712,7 +9712,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9918,7 +9918,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9996,7 +9996,7 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ42">
         <v>1.64</v>
@@ -10330,7 +10330,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10408,7 +10408,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ44">
         <v>0.92</v>
@@ -10536,7 +10536,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10948,7 +10948,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11154,7 +11154,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11360,7 +11360,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11647,7 +11647,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ50">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR50">
         <v>1.2</v>
@@ -11772,7 +11772,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -11853,7 +11853,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ51">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.12</v>
@@ -12390,7 +12390,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12802,7 +12802,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -13008,7 +13008,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13089,7 +13089,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ57">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR57">
         <v>1.67</v>
@@ -13420,7 +13420,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -14322,7 +14322,7 @@
         <v>1.67</v>
       </c>
       <c r="AP63">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ63">
         <v>1.43</v>
@@ -14528,7 +14528,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ64">
         <v>1.57</v>
@@ -14656,7 +14656,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14737,7 +14737,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ65">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR65">
         <v>1.18</v>
@@ -15068,7 +15068,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15274,7 +15274,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -16304,7 +16304,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16385,7 +16385,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ73">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR73">
         <v>1.18</v>
@@ -16510,7 +16510,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16716,7 +16716,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16922,7 +16922,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17000,7 +17000,7 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ76">
         <v>1.64</v>
@@ -17334,7 +17334,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17824,7 +17824,7 @@
         <v>1.75</v>
       </c>
       <c r="AP80">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ80">
         <v>1.64</v>
@@ -18364,7 +18364,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18982,7 +18982,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19394,7 +19394,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19806,7 +19806,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -20012,7 +20012,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20093,7 +20093,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ91">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR91">
         <v>1.19</v>
@@ -20218,7 +20218,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20424,7 +20424,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20502,10 +20502,10 @@
         <v>1.6</v>
       </c>
       <c r="AP93">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ93">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>1.22</v>
@@ -20630,7 +20630,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20836,7 +20836,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21248,7 +21248,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21326,7 +21326,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ97">
         <v>1.43</v>
@@ -21454,7 +21454,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21660,7 +21660,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22484,7 +22484,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22896,7 +22896,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -23102,7 +23102,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23308,7 +23308,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23514,7 +23514,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23720,7 +23720,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24419,7 +24419,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ112">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR112">
         <v>1.41</v>
@@ -24544,7 +24544,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24622,7 +24622,7 @@
         <v>1.17</v>
       </c>
       <c r="AP113">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ113">
         <v>1.64</v>
@@ -24750,7 +24750,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -24831,7 +24831,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ114">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR114">
         <v>1.37</v>
@@ -25162,7 +25162,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25368,7 +25368,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25446,7 +25446,7 @@
         <v>1.43</v>
       </c>
       <c r="AP117">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ117">
         <v>1.5</v>
@@ -25574,7 +25574,7 @@
         <v>163</v>
       </c>
       <c r="P118" t="s">
-        <v>298</v>
+        <v>236</v>
       </c>
       <c r="Q118">
         <v>2.38</v>
@@ -26682,7 +26682,7 @@
         <v>1.83</v>
       </c>
       <c r="AP123">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ123">
         <v>1.23</v>
@@ -28333,7 +28333,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ131">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR131">
         <v>1.36</v>
@@ -29360,10 +29360,10 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ136">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR136">
         <v>1.47</v>
@@ -29772,7 +29772,7 @@
         <v>0.86</v>
       </c>
       <c r="AP138">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ138">
         <v>1.23</v>
@@ -31011,7 +31011,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ144">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR144">
         <v>1.17</v>
@@ -31629,7 +31629,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ147">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR147">
         <v>1.68</v>
@@ -31832,7 +31832,7 @@
         <v>0.38</v>
       </c>
       <c r="AP148">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ148">
         <v>0.57</v>
@@ -33274,7 +33274,7 @@
         <v>0.63</v>
       </c>
       <c r="AP155">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ155">
         <v>0.77</v>
@@ -33483,7 +33483,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ156">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR156">
         <v>1.49</v>
@@ -33895,7 +33895,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ158">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR158">
         <v>1.37</v>
@@ -36158,7 +36158,7 @@
         <v>0.63</v>
       </c>
       <c r="AP169">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ169">
         <v>0.92</v>
@@ -37191,7 +37191,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ174">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR174">
         <v>1.73</v>
@@ -37809,7 +37809,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ177">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR177">
         <v>1.06</v>
@@ -38836,7 +38836,7 @@
         <v>0.78</v>
       </c>
       <c r="AP182">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ182">
         <v>1.23</v>
@@ -39866,7 +39866,7 @@
         <v>1.5</v>
       </c>
       <c r="AP187">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ187">
         <v>1.57</v>
@@ -40693,7 +40693,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ191">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR191">
         <v>1.47</v>
@@ -42260,7 +42260,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42341,7 +42341,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ199">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR199">
         <v>1.7</v>
@@ -42956,7 +42956,7 @@
         <v>1.27</v>
       </c>
       <c r="AP202">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ202">
         <v>1.54</v>
@@ -43162,7 +43162,7 @@
         <v>1.4</v>
       </c>
       <c r="AP203">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ203">
         <v>1.15</v>
@@ -43908,7 +43908,7 @@
         <v>156</v>
       </c>
       <c r="P207" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q207">
         <v>3.45</v>
@@ -44607,7 +44607,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ210">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR210">
         <v>1.34</v>
@@ -46174,7 +46174,7 @@
         <v>89</v>
       </c>
       <c r="P218" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q218">
         <v>3.6</v>
@@ -47076,7 +47076,7 @@
         <v>0.33</v>
       </c>
       <c r="AP222">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ222">
         <v>0.57</v>
@@ -47285,7 +47285,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ223">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR223">
         <v>1.66</v>
@@ -47694,7 +47694,7 @@
         <v>1</v>
       </c>
       <c r="AP225">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ225">
         <v>0.93</v>
@@ -48727,7 +48727,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ230">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR230">
         <v>1.63</v>
@@ -49058,7 +49058,7 @@
         <v>230</v>
       </c>
       <c r="P232" t="s">
-        <v>298</v>
+        <v>236</v>
       </c>
       <c r="Q232">
         <v>2.75</v>
@@ -50611,13 +50611,13 @@
         <v>11</v>
       </c>
       <c r="BA239">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB239">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC239">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD239">
         <v>0</v>
@@ -51023,13 +51023,13 @@
         <v>10</v>
       </c>
       <c r="BA241">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB241">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC241">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD241">
         <v>0</v>
@@ -51229,52 +51229,464 @@
         <v>11</v>
       </c>
       <c r="BA242">
+        <v>9</v>
+      </c>
+      <c r="BB242">
+        <v>2</v>
+      </c>
+      <c r="BC242">
+        <v>11</v>
+      </c>
+      <c r="BD242">
+        <v>0</v>
+      </c>
+      <c r="BE242">
+        <v>0</v>
+      </c>
+      <c r="BF242">
+        <v>0</v>
+      </c>
+      <c r="BG242">
+        <v>0</v>
+      </c>
+      <c r="BH242">
+        <v>0</v>
+      </c>
+      <c r="BI242">
+        <v>0</v>
+      </c>
+      <c r="BJ242">
+        <v>0</v>
+      </c>
+      <c r="BK242">
+        <v>0</v>
+      </c>
+      <c r="BL242">
+        <v>0</v>
+      </c>
+      <c r="BM242">
+        <v>0</v>
+      </c>
+      <c r="BN242">
+        <v>0</v>
+      </c>
+      <c r="BO242">
+        <v>0</v>
+      </c>
+      <c r="BP242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7502843</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45747.58333333334</v>
+      </c>
+      <c r="F243">
+        <v>27</v>
+      </c>
+      <c r="G243" t="s">
+        <v>86</v>
+      </c>
+      <c r="H243" t="s">
+        <v>73</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>0</v>
+      </c>
+      <c r="L243">
+        <v>1</v>
+      </c>
+      <c r="M243">
+        <v>0</v>
+      </c>
+      <c r="N243">
+        <v>1</v>
+      </c>
+      <c r="O243" t="s">
+        <v>236</v>
+      </c>
+      <c r="P243" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q243">
+        <v>3</v>
+      </c>
+      <c r="R243">
+        <v>2.05</v>
+      </c>
+      <c r="S243">
+        <v>3.75</v>
+      </c>
+      <c r="T243">
+        <v>1.44</v>
+      </c>
+      <c r="U243">
+        <v>2.63</v>
+      </c>
+      <c r="V243">
+        <v>3.25</v>
+      </c>
+      <c r="W243">
+        <v>1.33</v>
+      </c>
+      <c r="X243">
+        <v>10</v>
+      </c>
+      <c r="Y243">
+        <v>1.06</v>
+      </c>
+      <c r="Z243">
+        <v>2.3</v>
+      </c>
+      <c r="AA243">
+        <v>3.15</v>
+      </c>
+      <c r="AB243">
+        <v>3</v>
+      </c>
+      <c r="AC243">
+        <v>1.07</v>
+      </c>
+      <c r="AD243">
+        <v>7.5</v>
+      </c>
+      <c r="AE243">
+        <v>1.38</v>
+      </c>
+      <c r="AF243">
+        <v>2.9</v>
+      </c>
+      <c r="AG243">
+        <v>2.05</v>
+      </c>
+      <c r="AH243">
+        <v>1.65</v>
+      </c>
+      <c r="AI243">
+        <v>1.83</v>
+      </c>
+      <c r="AJ243">
+        <v>1.83</v>
+      </c>
+      <c r="AK243">
+        <v>1.32</v>
+      </c>
+      <c r="AL243">
+        <v>1.31</v>
+      </c>
+      <c r="AM243">
+        <v>1.65</v>
+      </c>
+      <c r="AN243">
+        <v>1.85</v>
+      </c>
+      <c r="AO243">
+        <v>1.08</v>
+      </c>
+      <c r="AP243">
+        <v>1.93</v>
+      </c>
+      <c r="AQ243">
+        <v>1</v>
+      </c>
+      <c r="AR243">
+        <v>1.58</v>
+      </c>
+      <c r="AS243">
+        <v>1.32</v>
+      </c>
+      <c r="AT243">
+        <v>2.9</v>
+      </c>
+      <c r="AU243">
+        <v>5</v>
+      </c>
+      <c r="AV243">
+        <v>2</v>
+      </c>
+      <c r="AW243">
+        <v>6</v>
+      </c>
+      <c r="AX243">
+        <v>5</v>
+      </c>
+      <c r="AY243">
+        <v>11</v>
+      </c>
+      <c r="AZ243">
+        <v>7</v>
+      </c>
+      <c r="BA243">
         <v>-1</v>
       </c>
-      <c r="BB242">
+      <c r="BB243">
         <v>-1</v>
       </c>
-      <c r="BC242">
+      <c r="BC243">
         <v>-1</v>
       </c>
-      <c r="BD242">
-        <v>0</v>
-      </c>
-      <c r="BE242">
-        <v>0</v>
-      </c>
-      <c r="BF242">
-        <v>0</v>
-      </c>
-      <c r="BG242">
-        <v>0</v>
-      </c>
-      <c r="BH242">
-        <v>0</v>
-      </c>
-      <c r="BI242">
-        <v>0</v>
-      </c>
-      <c r="BJ242">
-        <v>0</v>
-      </c>
-      <c r="BK242">
-        <v>0</v>
-      </c>
-      <c r="BL242">
-        <v>0</v>
-      </c>
-      <c r="BM242">
-        <v>0</v>
-      </c>
-      <c r="BN242">
-        <v>0</v>
-      </c>
-      <c r="BO242">
-        <v>0</v>
-      </c>
-      <c r="BP242">
-        <v>0</v>
+      <c r="BD243">
+        <v>1.87</v>
+      </c>
+      <c r="BE243">
+        <v>6.5</v>
+      </c>
+      <c r="BF243">
+        <v>2.4</v>
+      </c>
+      <c r="BG243">
+        <v>1.18</v>
+      </c>
+      <c r="BH243">
+        <v>3.86</v>
+      </c>
+      <c r="BI243">
+        <v>1.38</v>
+      </c>
+      <c r="BJ243">
+        <v>2.71</v>
+      </c>
+      <c r="BK243">
+        <v>1.69</v>
+      </c>
+      <c r="BL243">
+        <v>2.04</v>
+      </c>
+      <c r="BM243">
+        <v>2.05</v>
+      </c>
+      <c r="BN243">
+        <v>1.7</v>
+      </c>
+      <c r="BO243">
+        <v>2.74</v>
+      </c>
+      <c r="BP243">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7502844</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45747.67708333334</v>
+      </c>
+      <c r="F244">
+        <v>27</v>
+      </c>
+      <c r="G244" t="s">
+        <v>71</v>
+      </c>
+      <c r="H244" t="s">
+        <v>78</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244">
+        <v>0</v>
+      </c>
+      <c r="L244">
+        <v>1</v>
+      </c>
+      <c r="M244">
+        <v>0</v>
+      </c>
+      <c r="N244">
+        <v>1</v>
+      </c>
+      <c r="O244" t="s">
+        <v>108</v>
+      </c>
+      <c r="P244" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q244">
+        <v>3.75</v>
+      </c>
+      <c r="R244">
+        <v>1.95</v>
+      </c>
+      <c r="S244">
+        <v>3.25</v>
+      </c>
+      <c r="T244">
+        <v>1.53</v>
+      </c>
+      <c r="U244">
+        <v>2.38</v>
+      </c>
+      <c r="V244">
+        <v>3.75</v>
+      </c>
+      <c r="W244">
+        <v>1.25</v>
+      </c>
+      <c r="X244">
+        <v>11</v>
+      </c>
+      <c r="Y244">
+        <v>1.05</v>
+      </c>
+      <c r="Z244">
+        <v>2.9</v>
+      </c>
+      <c r="AA244">
+        <v>2.95</v>
+      </c>
+      <c r="AB244">
+        <v>2.5</v>
+      </c>
+      <c r="AC244">
+        <v>1.09</v>
+      </c>
+      <c r="AD244">
+        <v>6.5</v>
+      </c>
+      <c r="AE244">
+        <v>1.45</v>
+      </c>
+      <c r="AF244">
+        <v>2.6</v>
+      </c>
+      <c r="AG244">
+        <v>2.3</v>
+      </c>
+      <c r="AH244">
+        <v>1.5</v>
+      </c>
+      <c r="AI244">
+        <v>2</v>
+      </c>
+      <c r="AJ244">
+        <v>1.73</v>
+      </c>
+      <c r="AK244">
+        <v>1.53</v>
+      </c>
+      <c r="AL244">
+        <v>1.34</v>
+      </c>
+      <c r="AM244">
+        <v>1.38</v>
+      </c>
+      <c r="AN244">
+        <v>0.92</v>
+      </c>
+      <c r="AO244">
+        <v>1.08</v>
+      </c>
+      <c r="AP244">
+        <v>1.07</v>
+      </c>
+      <c r="AQ244">
+        <v>1</v>
+      </c>
+      <c r="AR244">
+        <v>1.29</v>
+      </c>
+      <c r="AS244">
+        <v>1.49</v>
+      </c>
+      <c r="AT244">
+        <v>2.78</v>
+      </c>
+      <c r="AU244">
+        <v>7</v>
+      </c>
+      <c r="AV244">
+        <v>0</v>
+      </c>
+      <c r="AW244">
+        <v>2</v>
+      </c>
+      <c r="AX244">
+        <v>12</v>
+      </c>
+      <c r="AY244">
+        <v>9</v>
+      </c>
+      <c r="AZ244">
+        <v>12</v>
+      </c>
+      <c r="BA244">
+        <v>-1</v>
+      </c>
+      <c r="BB244">
+        <v>-1</v>
+      </c>
+      <c r="BC244">
+        <v>-1</v>
+      </c>
+      <c r="BD244">
+        <v>2.34</v>
+      </c>
+      <c r="BE244">
+        <v>8.4</v>
+      </c>
+      <c r="BF244">
+        <v>1.79</v>
+      </c>
+      <c r="BG244">
+        <v>1.23</v>
+      </c>
+      <c r="BH244">
+        <v>3.42</v>
+      </c>
+      <c r="BI244">
+        <v>1.46</v>
+      </c>
+      <c r="BJ244">
+        <v>2.45</v>
+      </c>
+      <c r="BK244">
+        <v>1.73</v>
+      </c>
+      <c r="BL244">
+        <v>2</v>
+      </c>
+      <c r="BM244">
+        <v>2.32</v>
+      </c>
+      <c r="BN244">
+        <v>1.51</v>
+      </c>
+      <c r="BO244">
+        <v>3.08</v>
+      </c>
+      <c r="BP244">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -51435,13 +51435,13 @@
         <v>7</v>
       </c>
       <c r="BA243">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB243">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC243">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD243">
         <v>1.87</v>
@@ -51641,13 +51641,13 @@
         <v>12</v>
       </c>
       <c r="BA244">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB244">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC244">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD244">
         <v>2.34</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="351">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -727,6 +727,9 @@
     <t>['78']</t>
   </si>
   <si>
+    <t>['84', '90+10']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -1061,6 +1064,9 @@
   </si>
   <si>
     <t>['3', '21', '28', '46']</t>
+  </si>
+  <si>
+    <t>['14', '31']</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP248"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1678,7 +1684,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1756,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ2">
         <v>1.64</v>
@@ -1884,7 +1890,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -2090,7 +2096,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2502,7 +2508,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2708,7 +2714,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2789,7 +2795,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ7">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3120,7 +3126,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3201,7 +3207,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ9">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3404,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ10">
         <v>0.93</v>
@@ -3532,7 +3538,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3944,7 +3950,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4150,7 +4156,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4356,7 +4362,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4562,7 +4568,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -4643,7 +4649,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ16">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4846,10 +4852,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ17">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5180,7 +5186,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5258,7 +5264,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ19">
         <v>0.57</v>
@@ -5386,7 +5392,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5670,10 +5676,10 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ21">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR21">
         <v>1.84</v>
@@ -6004,7 +6010,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6416,7 +6422,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6700,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ26">
         <v>1.57</v>
@@ -6828,7 +6834,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7115,7 +7121,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ28">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR28">
         <v>1.62</v>
@@ -7240,7 +7246,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7446,7 +7452,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7527,7 +7533,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ30">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR30">
         <v>1.33</v>
@@ -7730,7 +7736,7 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -7858,7 +7864,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -8270,7 +8276,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8476,7 +8482,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8557,7 +8563,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ35">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR35">
         <v>1.95</v>
@@ -8682,7 +8688,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8760,7 +8766,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ36">
         <v>0.46</v>
@@ -9094,7 +9100,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9300,7 +9306,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9378,7 +9384,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ39">
         <v>1.57</v>
@@ -9712,7 +9718,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9790,7 +9796,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ41">
         <v>1.43</v>
@@ -9918,7 +9924,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10330,7 +10336,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10536,7 +10542,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10617,7 +10623,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ45">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR45">
         <v>1.58</v>
@@ -10948,7 +10954,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11026,7 +11032,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ47">
         <v>1.38</v>
@@ -11154,7 +11160,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11360,7 +11366,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11441,7 +11447,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ49">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR49">
         <v>1.23</v>
@@ -11644,7 +11650,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11772,7 +11778,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -12059,7 +12065,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ52">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR52">
         <v>1.2</v>
@@ -12265,7 +12271,7 @@
         <v>2</v>
       </c>
       <c r="AQ53">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR53">
         <v>1.6</v>
@@ -12390,7 +12396,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12802,7 +12808,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -13008,7 +13014,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13086,7 +13092,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -13292,7 +13298,7 @@
         <v>0.67</v>
       </c>
       <c r="AP58">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ58">
         <v>0.57</v>
@@ -13420,7 +13426,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13913,7 +13919,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ61">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR61">
         <v>1.62</v>
@@ -14656,7 +14662,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14940,10 +14946,10 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ66">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR66">
         <v>1.24</v>
@@ -15068,7 +15074,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15149,7 +15155,7 @@
         <v>2</v>
       </c>
       <c r="AQ67">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR67">
         <v>1.38</v>
@@ -15274,7 +15280,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15764,10 +15770,10 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ70">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR70">
         <v>1.47</v>
@@ -16179,7 +16185,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ72">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR72">
         <v>1.62</v>
@@ -16304,7 +16310,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16510,7 +16516,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16716,7 +16722,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16922,7 +16928,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17334,7 +17340,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17412,7 +17418,7 @@
         <v>1.75</v>
       </c>
       <c r="AP78">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ78">
         <v>1.5</v>
@@ -18033,7 +18039,7 @@
         <v>2</v>
       </c>
       <c r="AQ81">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -18239,7 +18245,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ82">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR82">
         <v>1.36</v>
@@ -18364,7 +18370,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18442,10 +18448,10 @@
         <v>2.5</v>
       </c>
       <c r="AP83">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ83">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR83">
         <v>1.45</v>
@@ -18648,7 +18654,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ84">
         <v>1.15</v>
@@ -18982,7 +18988,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19060,7 +19066,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ86">
         <v>0.46</v>
@@ -19269,7 +19275,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ87">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR87">
         <v>1.38</v>
@@ -19394,7 +19400,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19678,7 +19684,7 @@
         <v>0.33</v>
       </c>
       <c r="AP89">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ89">
         <v>0.92</v>
@@ -19806,7 +19812,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -20012,7 +20018,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20218,7 +20224,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20424,7 +20430,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20630,7 +20636,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20836,7 +20842,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21248,7 +21254,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21454,7 +21460,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21660,7 +21666,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -22359,7 +22365,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ102">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR102">
         <v>1.5</v>
@@ -22484,7 +22490,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22562,7 +22568,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ103">
         <v>1.38</v>
@@ -22771,7 +22777,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ104">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR104">
         <v>1.44</v>
@@ -22896,7 +22902,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -23102,7 +23108,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23183,7 +23189,7 @@
         <v>2</v>
       </c>
       <c r="AQ106">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR106">
         <v>1.65</v>
@@ -23308,7 +23314,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23514,7 +23520,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23592,7 +23598,7 @@
         <v>1.4</v>
       </c>
       <c r="AP108">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ108">
         <v>1.15</v>
@@ -23720,7 +23726,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -24004,7 +24010,7 @@
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ110">
         <v>1.23</v>
@@ -24213,7 +24219,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ111">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR111">
         <v>1.61</v>
@@ -24544,7 +24550,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24750,7 +24756,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25162,7 +25168,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25368,7 +25374,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -25652,7 +25658,7 @@
         <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ118">
         <v>0.57</v>
@@ -26398,7 +26404,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26479,7 +26485,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ122">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR122">
         <v>1.24</v>
@@ -26810,7 +26816,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -26888,10 +26894,10 @@
         <v>1.29</v>
       </c>
       <c r="AP124">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ124">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR124">
         <v>1.69</v>
@@ -27094,7 +27100,7 @@
         <v>1.29</v>
       </c>
       <c r="AP125">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ125">
         <v>0.93</v>
@@ -27222,7 +27228,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27300,7 +27306,7 @@
         <v>1.17</v>
       </c>
       <c r="AP126">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ126">
         <v>1.38</v>
@@ -27509,7 +27515,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ127">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR127">
         <v>0.99</v>
@@ -27634,7 +27640,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -28046,7 +28052,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28458,7 +28464,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28536,7 +28542,7 @@
         <v>1.86</v>
       </c>
       <c r="AP132">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ132">
         <v>1.64</v>
@@ -28664,7 +28670,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28870,7 +28876,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29157,7 +29163,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ135">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR135">
         <v>1.3</v>
@@ -29488,7 +29494,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29775,7 +29781,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ138">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR138">
         <v>1.22</v>
@@ -29900,7 +29906,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -29978,7 +29984,7 @@
         <v>0.29</v>
       </c>
       <c r="AP139">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ139">
         <v>0.92</v>
@@ -30312,7 +30318,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30390,10 +30396,10 @@
         <v>2.29</v>
       </c>
       <c r="AP141">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ141">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR141">
         <v>1.36</v>
@@ -30599,7 +30605,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ142">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR142">
         <v>1.66</v>
@@ -30724,7 +30730,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30802,7 +30808,7 @@
         <v>1.63</v>
       </c>
       <c r="AP143">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ143">
         <v>1.64</v>
@@ -30930,7 +30936,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31342,7 +31348,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31548,7 +31554,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31754,7 +31760,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32041,7 +32047,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ149">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR149">
         <v>1.55</v>
@@ -32244,7 +32250,7 @@
         <v>1.43</v>
       </c>
       <c r="AP150">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ150">
         <v>1.15</v>
@@ -32372,7 +32378,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32578,7 +32584,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32990,7 +32996,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33277,7 +33283,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ155">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR155">
         <v>1.55</v>
@@ -33480,7 +33486,7 @@
         <v>1.33</v>
       </c>
       <c r="AP156">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ156">
         <v>1</v>
@@ -33814,7 +33820,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -34432,7 +34438,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34716,7 +34722,7 @@
         <v>1.44</v>
       </c>
       <c r="AP162">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ162">
         <v>1.5</v>
@@ -34844,7 +34850,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -34925,7 +34931,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ163">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR163">
         <v>1.12</v>
@@ -35050,7 +35056,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35131,7 +35137,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ164">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR164">
         <v>1.48</v>
@@ -35256,7 +35262,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35334,7 +35340,7 @@
         <v>1.33</v>
       </c>
       <c r="AP165">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ165">
         <v>1.43</v>
@@ -35668,7 +35674,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -35746,7 +35752,7 @@
         <v>1.25</v>
       </c>
       <c r="AP167">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ167">
         <v>1.15</v>
@@ -35955,7 +35961,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ168">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR168">
         <v>1.2</v>
@@ -36492,7 +36498,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36985,7 +36991,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ173">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR173">
         <v>1.71</v>
@@ -37110,7 +37116,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37394,10 +37400,10 @@
         <v>2.22</v>
       </c>
       <c r="AP175">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ175">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR175">
         <v>1.61</v>
@@ -37728,7 +37734,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -38346,7 +38352,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38424,7 +38430,7 @@
         <v>1.4</v>
       </c>
       <c r="AP180">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ180">
         <v>1.5</v>
@@ -38758,7 +38764,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38839,7 +38845,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ182">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR182">
         <v>1.54</v>
@@ -38964,7 +38970,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39248,7 +39254,7 @@
         <v>1.6</v>
       </c>
       <c r="AP184">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ184">
         <v>1.64</v>
@@ -39454,7 +39460,7 @@
         <v>1.2</v>
       </c>
       <c r="AP185">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ185">
         <v>0.93</v>
@@ -39582,7 +39588,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39994,7 +40000,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40406,7 +40412,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40487,7 +40493,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ190">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR190">
         <v>1.31</v>
@@ -40690,7 +40696,7 @@
         <v>1.2</v>
       </c>
       <c r="AP191">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ191">
         <v>1</v>
@@ -40818,7 +40824,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -40899,7 +40905,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ192">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR192">
         <v>1.73</v>
@@ -41102,7 +41108,7 @@
         <v>0.6</v>
       </c>
       <c r="AP193">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ193">
         <v>0.46</v>
@@ -41230,7 +41236,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41517,7 +41523,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ195">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR195">
         <v>1.64</v>
@@ -41642,7 +41648,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41848,7 +41854,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -41929,7 +41935,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ197">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR197">
         <v>1.07</v>
@@ -42260,7 +42266,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42750,7 +42756,7 @@
         <v>0.36</v>
       </c>
       <c r="AP201">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ201">
         <v>0.57</v>
@@ -42878,7 +42884,7 @@
         <v>123</v>
       </c>
       <c r="P202" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q202">
         <v>4.3</v>
@@ -42959,7 +42965,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ202">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR202">
         <v>1.26</v>
@@ -43290,7 +43296,7 @@
         <v>117</v>
       </c>
       <c r="P204" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q204">
         <v>3.1</v>
@@ -43368,7 +43374,7 @@
         <v>1.45</v>
       </c>
       <c r="AP204">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ204">
         <v>1.64</v>
@@ -43702,7 +43708,7 @@
         <v>218</v>
       </c>
       <c r="P206" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q206">
         <v>3.65</v>
@@ -43908,7 +43914,7 @@
         <v>156</v>
       </c>
       <c r="P207" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q207">
         <v>3.45</v>
@@ -44114,7 +44120,7 @@
         <v>197</v>
       </c>
       <c r="P208" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q208">
         <v>3.5</v>
@@ -44320,7 +44326,7 @@
         <v>129</v>
       </c>
       <c r="P209" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q209">
         <v>2.4</v>
@@ -44398,7 +44404,7 @@
         <v>1.18</v>
       </c>
       <c r="AP209">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ209">
         <v>1.23</v>
@@ -44938,7 +44944,7 @@
         <v>220</v>
       </c>
       <c r="P212" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q212">
         <v>2.43</v>
@@ -45016,7 +45022,7 @@
         <v>1.45</v>
       </c>
       <c r="AP212">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ212">
         <v>1.38</v>
@@ -45144,7 +45150,7 @@
         <v>221</v>
       </c>
       <c r="P213" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q213">
         <v>3.15</v>
@@ -45225,7 +45231,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ213">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR213">
         <v>1.4</v>
@@ -45637,7 +45643,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ215">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR215">
         <v>1.65</v>
@@ -45843,7 +45849,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ216">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR216">
         <v>1.76</v>
@@ -46174,7 +46180,7 @@
         <v>89</v>
       </c>
       <c r="P218" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q218">
         <v>3.6</v>
@@ -46380,7 +46386,7 @@
         <v>224</v>
       </c>
       <c r="P219" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q219">
         <v>3.78</v>
@@ -46586,7 +46592,7 @@
         <v>225</v>
       </c>
       <c r="P220" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q220">
         <v>3.26</v>
@@ -46664,7 +46670,7 @@
         <v>1.58</v>
       </c>
       <c r="AP220">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ220">
         <v>1.64</v>
@@ -47282,7 +47288,7 @@
         <v>1.08</v>
       </c>
       <c r="AP223">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ223">
         <v>1</v>
@@ -47410,7 +47416,7 @@
         <v>89</v>
       </c>
       <c r="P224" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q224">
         <v>5.44</v>
@@ -47491,7 +47497,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ224">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR224">
         <v>1.35</v>
@@ -48028,7 +48034,7 @@
         <v>156</v>
       </c>
       <c r="P227" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q227">
         <v>2.9</v>
@@ -48109,7 +48115,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ227">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR227">
         <v>1.49</v>
@@ -48234,7 +48240,7 @@
         <v>228</v>
       </c>
       <c r="P228" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q228">
         <v>2.6</v>
@@ -48521,7 +48527,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ229">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR229">
         <v>1.27</v>
@@ -48724,7 +48730,7 @@
         <v>1.08</v>
       </c>
       <c r="AP230">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ230">
         <v>1</v>
@@ -48930,7 +48936,7 @@
         <v>1</v>
       </c>
       <c r="AP231">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ231">
         <v>0.92</v>
@@ -49136,7 +49142,7 @@
         <v>1.33</v>
       </c>
       <c r="AP232">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ232">
         <v>1.23</v>
@@ -49551,7 +49557,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ234">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR234">
         <v>1.13</v>
@@ -49882,7 +49888,7 @@
         <v>128</v>
       </c>
       <c r="P236" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q236">
         <v>4.5</v>
@@ -50294,7 +50300,7 @@
         <v>233</v>
       </c>
       <c r="P238" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q238">
         <v>2.1</v>
@@ -50500,7 +50506,7 @@
         <v>89</v>
       </c>
       <c r="P239" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q239">
         <v>3.75</v>
@@ -50706,7 +50712,7 @@
         <v>234</v>
       </c>
       <c r="P240" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q240">
         <v>3</v>
@@ -51118,7 +51124,7 @@
         <v>89</v>
       </c>
       <c r="P242" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q242">
         <v>3.6</v>
@@ -51687,6 +51693,830 @@
       </c>
       <c r="BP244">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7502852</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45752.29166666666</v>
+      </c>
+      <c r="F245">
+        <v>28</v>
+      </c>
+      <c r="G245" t="s">
+        <v>87</v>
+      </c>
+      <c r="H245" t="s">
+        <v>83</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+      <c r="J245">
+        <v>1</v>
+      </c>
+      <c r="K245">
+        <v>1</v>
+      </c>
+      <c r="L245">
+        <v>2</v>
+      </c>
+      <c r="M245">
+        <v>1</v>
+      </c>
+      <c r="N245">
+        <v>3</v>
+      </c>
+      <c r="O245" t="s">
+        <v>237</v>
+      </c>
+      <c r="P245" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q245">
+        <v>2.5</v>
+      </c>
+      <c r="R245">
+        <v>2.05</v>
+      </c>
+      <c r="S245">
+        <v>5</v>
+      </c>
+      <c r="T245">
+        <v>1.44</v>
+      </c>
+      <c r="U245">
+        <v>2.63</v>
+      </c>
+      <c r="V245">
+        <v>3.4</v>
+      </c>
+      <c r="W245">
+        <v>1.3</v>
+      </c>
+      <c r="X245">
+        <v>10</v>
+      </c>
+      <c r="Y245">
+        <v>1.06</v>
+      </c>
+      <c r="Z245">
+        <v>1.77</v>
+      </c>
+      <c r="AA245">
+        <v>3.3</v>
+      </c>
+      <c r="AB245">
+        <v>4.5</v>
+      </c>
+      <c r="AC245">
+        <v>1.01</v>
+      </c>
+      <c r="AD245">
+        <v>8.9</v>
+      </c>
+      <c r="AE245">
+        <v>1.33</v>
+      </c>
+      <c r="AF245">
+        <v>2.82</v>
+      </c>
+      <c r="AG245">
+        <v>2.1</v>
+      </c>
+      <c r="AH245">
+        <v>1.61</v>
+      </c>
+      <c r="AI245">
+        <v>2</v>
+      </c>
+      <c r="AJ245">
+        <v>1.73</v>
+      </c>
+      <c r="AK245">
+        <v>1.15</v>
+      </c>
+      <c r="AL245">
+        <v>1.28</v>
+      </c>
+      <c r="AM245">
+        <v>2.11</v>
+      </c>
+      <c r="AN245">
+        <v>2.15</v>
+      </c>
+      <c r="AO245">
+        <v>1.23</v>
+      </c>
+      <c r="AP245">
+        <v>2.21</v>
+      </c>
+      <c r="AQ245">
+        <v>1.14</v>
+      </c>
+      <c r="AR245">
+        <v>1.6</v>
+      </c>
+      <c r="AS245">
+        <v>1.38</v>
+      </c>
+      <c r="AT245">
+        <v>2.98</v>
+      </c>
+      <c r="AU245">
+        <v>5</v>
+      </c>
+      <c r="AV245">
+        <v>2</v>
+      </c>
+      <c r="AW245">
+        <v>13</v>
+      </c>
+      <c r="AX245">
+        <v>4</v>
+      </c>
+      <c r="AY245">
+        <v>18</v>
+      </c>
+      <c r="AZ245">
+        <v>6</v>
+      </c>
+      <c r="BA245">
+        <v>-1</v>
+      </c>
+      <c r="BB245">
+        <v>-1</v>
+      </c>
+      <c r="BC245">
+        <v>-1</v>
+      </c>
+      <c r="BD245">
+        <v>1.46</v>
+      </c>
+      <c r="BE245">
+        <v>7.2</v>
+      </c>
+      <c r="BF245">
+        <v>3.55</v>
+      </c>
+      <c r="BG245">
+        <v>1.19</v>
+      </c>
+      <c r="BH245">
+        <v>3.75</v>
+      </c>
+      <c r="BI245">
+        <v>1.4</v>
+      </c>
+      <c r="BJ245">
+        <v>2.64</v>
+      </c>
+      <c r="BK245">
+        <v>1.72</v>
+      </c>
+      <c r="BL245">
+        <v>2</v>
+      </c>
+      <c r="BM245">
+        <v>2.15</v>
+      </c>
+      <c r="BN245">
+        <v>1.59</v>
+      </c>
+      <c r="BO245">
+        <v>2.83</v>
+      </c>
+      <c r="BP245">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7502847</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45752.41666666666</v>
+      </c>
+      <c r="F246">
+        <v>28</v>
+      </c>
+      <c r="G246" t="s">
+        <v>78</v>
+      </c>
+      <c r="H246" t="s">
+        <v>74</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246">
+        <v>0</v>
+      </c>
+      <c r="L246">
+        <v>1</v>
+      </c>
+      <c r="M246">
+        <v>0</v>
+      </c>
+      <c r="N246">
+        <v>1</v>
+      </c>
+      <c r="O246" t="s">
+        <v>154</v>
+      </c>
+      <c r="P246" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q246">
+        <v>2.88</v>
+      </c>
+      <c r="R246">
+        <v>2.1</v>
+      </c>
+      <c r="S246">
+        <v>4</v>
+      </c>
+      <c r="T246">
+        <v>1.44</v>
+      </c>
+      <c r="U246">
+        <v>2.63</v>
+      </c>
+      <c r="V246">
+        <v>3.25</v>
+      </c>
+      <c r="W246">
+        <v>1.33</v>
+      </c>
+      <c r="X246">
+        <v>9</v>
+      </c>
+      <c r="Y246">
+        <v>1.07</v>
+      </c>
+      <c r="Z246">
+        <v>2.05</v>
+      </c>
+      <c r="AA246">
+        <v>3.3</v>
+      </c>
+      <c r="AB246">
+        <v>3.35</v>
+      </c>
+      <c r="AC246">
+        <v>0</v>
+      </c>
+      <c r="AD246">
+        <v>0</v>
+      </c>
+      <c r="AE246">
+        <v>1.36</v>
+      </c>
+      <c r="AF246">
+        <v>3.22</v>
+      </c>
+      <c r="AG246">
+        <v>2.15</v>
+      </c>
+      <c r="AH246">
+        <v>1.6</v>
+      </c>
+      <c r="AI246">
+        <v>1.83</v>
+      </c>
+      <c r="AJ246">
+        <v>1.83</v>
+      </c>
+      <c r="AK246">
+        <v>1.21</v>
+      </c>
+      <c r="AL246">
+        <v>1.28</v>
+      </c>
+      <c r="AM246">
+        <v>1.95</v>
+      </c>
+      <c r="AN246">
+        <v>1.31</v>
+      </c>
+      <c r="AO246">
+        <v>1.54</v>
+      </c>
+      <c r="AP246">
+        <v>1.43</v>
+      </c>
+      <c r="AQ246">
+        <v>1.43</v>
+      </c>
+      <c r="AR246">
+        <v>1.59</v>
+      </c>
+      <c r="AS246">
+        <v>1.35</v>
+      </c>
+      <c r="AT246">
+        <v>2.94</v>
+      </c>
+      <c r="AU246">
+        <v>5</v>
+      </c>
+      <c r="AV246">
+        <v>4</v>
+      </c>
+      <c r="AW246">
+        <v>9</v>
+      </c>
+      <c r="AX246">
+        <v>0</v>
+      </c>
+      <c r="AY246">
+        <v>14</v>
+      </c>
+      <c r="AZ246">
+        <v>4</v>
+      </c>
+      <c r="BA246">
+        <v>-1</v>
+      </c>
+      <c r="BB246">
+        <v>-1</v>
+      </c>
+      <c r="BC246">
+        <v>-1</v>
+      </c>
+      <c r="BD246">
+        <v>1.39</v>
+      </c>
+      <c r="BE246">
+        <v>9.6</v>
+      </c>
+      <c r="BF246">
+        <v>3.54</v>
+      </c>
+      <c r="BG246">
+        <v>1.14</v>
+      </c>
+      <c r="BH246">
+        <v>4.4</v>
+      </c>
+      <c r="BI246">
+        <v>1.3</v>
+      </c>
+      <c r="BJ246">
+        <v>2.97</v>
+      </c>
+      <c r="BK246">
+        <v>1.56</v>
+      </c>
+      <c r="BL246">
+        <v>2.21</v>
+      </c>
+      <c r="BM246">
+        <v>1.95</v>
+      </c>
+      <c r="BN246">
+        <v>1.76</v>
+      </c>
+      <c r="BO246">
+        <v>2.51</v>
+      </c>
+      <c r="BP246">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7502853</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45752.47916666666</v>
+      </c>
+      <c r="F247">
+        <v>28</v>
+      </c>
+      <c r="G247" t="s">
+        <v>70</v>
+      </c>
+      <c r="H247" t="s">
+        <v>72</v>
+      </c>
+      <c r="I247">
+        <v>0</v>
+      </c>
+      <c r="J247">
+        <v>1</v>
+      </c>
+      <c r="K247">
+        <v>1</v>
+      </c>
+      <c r="L247">
+        <v>1</v>
+      </c>
+      <c r="M247">
+        <v>1</v>
+      </c>
+      <c r="N247">
+        <v>2</v>
+      </c>
+      <c r="O247" t="s">
+        <v>185</v>
+      </c>
+      <c r="P247" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q247">
+        <v>2.63</v>
+      </c>
+      <c r="R247">
+        <v>2.05</v>
+      </c>
+      <c r="S247">
+        <v>4.75</v>
+      </c>
+      <c r="T247">
+        <v>1.5</v>
+      </c>
+      <c r="U247">
+        <v>2.5</v>
+      </c>
+      <c r="V247">
+        <v>3.4</v>
+      </c>
+      <c r="W247">
+        <v>1.3</v>
+      </c>
+      <c r="X247">
+        <v>10</v>
+      </c>
+      <c r="Y247">
+        <v>1.06</v>
+      </c>
+      <c r="Z247">
+        <v>1.87</v>
+      </c>
+      <c r="AA247">
+        <v>3.2</v>
+      </c>
+      <c r="AB247">
+        <v>4.2</v>
+      </c>
+      <c r="AC247">
+        <v>1.03</v>
+      </c>
+      <c r="AD247">
+        <v>7.2</v>
+      </c>
+      <c r="AE247">
+        <v>1.39</v>
+      </c>
+      <c r="AF247">
+        <v>3.07</v>
+      </c>
+      <c r="AG247">
+        <v>2.15</v>
+      </c>
+      <c r="AH247">
+        <v>1.57</v>
+      </c>
+      <c r="AI247">
+        <v>2</v>
+      </c>
+      <c r="AJ247">
+        <v>1.73</v>
+      </c>
+      <c r="AK247">
+        <v>1.22</v>
+      </c>
+      <c r="AL247">
+        <v>1.38</v>
+      </c>
+      <c r="AM247">
+        <v>1.75</v>
+      </c>
+      <c r="AN247">
+        <v>0.92</v>
+      </c>
+      <c r="AO247">
+        <v>0.77</v>
+      </c>
+      <c r="AP247">
+        <v>0.93</v>
+      </c>
+      <c r="AQ247">
+        <v>0.79</v>
+      </c>
+      <c r="AR247">
+        <v>1.63</v>
+      </c>
+      <c r="AS247">
+        <v>1.27</v>
+      </c>
+      <c r="AT247">
+        <v>2.9</v>
+      </c>
+      <c r="AU247">
+        <v>3</v>
+      </c>
+      <c r="AV247">
+        <v>5</v>
+      </c>
+      <c r="AW247">
+        <v>11</v>
+      </c>
+      <c r="AX247">
+        <v>6</v>
+      </c>
+      <c r="AY247">
+        <v>14</v>
+      </c>
+      <c r="AZ247">
+        <v>11</v>
+      </c>
+      <c r="BA247">
+        <v>7</v>
+      </c>
+      <c r="BB247">
+        <v>2</v>
+      </c>
+      <c r="BC247">
+        <v>9</v>
+      </c>
+      <c r="BD247">
+        <v>1.51</v>
+      </c>
+      <c r="BE247">
+        <v>7.1</v>
+      </c>
+      <c r="BF247">
+        <v>3.32</v>
+      </c>
+      <c r="BG247">
+        <v>1.14</v>
+      </c>
+      <c r="BH247">
+        <v>4.45</v>
+      </c>
+      <c r="BI247">
+        <v>1.29</v>
+      </c>
+      <c r="BJ247">
+        <v>3.04</v>
+      </c>
+      <c r="BK247">
+        <v>1.54</v>
+      </c>
+      <c r="BL247">
+        <v>2.25</v>
+      </c>
+      <c r="BM247">
+        <v>1.93</v>
+      </c>
+      <c r="BN247">
+        <v>1.78</v>
+      </c>
+      <c r="BO247">
+        <v>2.48</v>
+      </c>
+      <c r="BP247">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7502848</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45752.58333333334</v>
+      </c>
+      <c r="F248">
+        <v>28</v>
+      </c>
+      <c r="G248" t="s">
+        <v>85</v>
+      </c>
+      <c r="H248" t="s">
+        <v>84</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+      <c r="J248">
+        <v>2</v>
+      </c>
+      <c r="K248">
+        <v>2</v>
+      </c>
+      <c r="L248">
+        <v>1</v>
+      </c>
+      <c r="M248">
+        <v>2</v>
+      </c>
+      <c r="N248">
+        <v>3</v>
+      </c>
+      <c r="O248" t="s">
+        <v>109</v>
+      </c>
+      <c r="P248" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q248">
+        <v>3.6</v>
+      </c>
+      <c r="R248">
+        <v>2.05</v>
+      </c>
+      <c r="S248">
+        <v>3.2</v>
+      </c>
+      <c r="T248">
+        <v>1.44</v>
+      </c>
+      <c r="U248">
+        <v>2.63</v>
+      </c>
+      <c r="V248">
+        <v>3.25</v>
+      </c>
+      <c r="W248">
+        <v>1.33</v>
+      </c>
+      <c r="X248">
+        <v>10</v>
+      </c>
+      <c r="Y248">
+        <v>1.06</v>
+      </c>
+      <c r="Z248">
+        <v>2.85</v>
+      </c>
+      <c r="AA248">
+        <v>3.1</v>
+      </c>
+      <c r="AB248">
+        <v>2.4</v>
+      </c>
+      <c r="AC248">
+        <v>1.04</v>
+      </c>
+      <c r="AD248">
+        <v>6.8</v>
+      </c>
+      <c r="AE248">
+        <v>1.36</v>
+      </c>
+      <c r="AF248">
+        <v>3.2</v>
+      </c>
+      <c r="AG248">
+        <v>2.05</v>
+      </c>
+      <c r="AH248">
+        <v>1.61</v>
+      </c>
+      <c r="AI248">
+        <v>1.83</v>
+      </c>
+      <c r="AJ248">
+        <v>1.83</v>
+      </c>
+      <c r="AK248">
+        <v>1.61</v>
+      </c>
+      <c r="AL248">
+        <v>1.36</v>
+      </c>
+      <c r="AM248">
+        <v>1.31</v>
+      </c>
+      <c r="AN248">
+        <v>1.69</v>
+      </c>
+      <c r="AO248">
+        <v>1.54</v>
+      </c>
+      <c r="AP248">
+        <v>1.57</v>
+      </c>
+      <c r="AQ248">
+        <v>1.64</v>
+      </c>
+      <c r="AR248">
+        <v>1.53</v>
+      </c>
+      <c r="AS248">
+        <v>1.5</v>
+      </c>
+      <c r="AT248">
+        <v>3.03</v>
+      </c>
+      <c r="AU248">
+        <v>11</v>
+      </c>
+      <c r="AV248">
+        <v>7</v>
+      </c>
+      <c r="AW248">
+        <v>7</v>
+      </c>
+      <c r="AX248">
+        <v>5</v>
+      </c>
+      <c r="AY248">
+        <v>18</v>
+      </c>
+      <c r="AZ248">
+        <v>12</v>
+      </c>
+      <c r="BA248">
+        <v>-1</v>
+      </c>
+      <c r="BB248">
+        <v>-1</v>
+      </c>
+      <c r="BC248">
+        <v>-1</v>
+      </c>
+      <c r="BD248">
+        <v>2.28</v>
+      </c>
+      <c r="BE248">
+        <v>6.5</v>
+      </c>
+      <c r="BF248">
+        <v>1.95</v>
+      </c>
+      <c r="BG248">
+        <v>1.18</v>
+      </c>
+      <c r="BH248">
+        <v>3.9</v>
+      </c>
+      <c r="BI248">
+        <v>1.37</v>
+      </c>
+      <c r="BJ248">
+        <v>2.75</v>
+      </c>
+      <c r="BK248">
+        <v>1.68</v>
+      </c>
+      <c r="BL248">
+        <v>2.06</v>
+      </c>
+      <c r="BM248">
+        <v>2.09</v>
+      </c>
+      <c r="BN248">
+        <v>1.63</v>
+      </c>
+      <c r="BO248">
+        <v>2.7</v>
+      </c>
+      <c r="BP248">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="355">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -730,6 +730,12 @@
     <t>['84', '90+10']</t>
   </si>
   <si>
+    <t>['30', '57', '67']</t>
+  </si>
+  <si>
+    <t>['15', '48']</t>
+  </si>
+  <si>
     <t>['24', '27']</t>
   </si>
   <si>
@@ -1067,6 +1073,12 @@
   </si>
   <si>
     <t>['14', '31']</t>
+  </si>
+  <si>
+    <t>['12', '67', '81']</t>
+  </si>
+  <si>
+    <t>['55', '66', '87']</t>
   </si>
 </sst>
 </file>
@@ -1428,7 +1440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP248"/>
+  <dimension ref="A1:BP253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1684,7 +1696,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1890,7 +1902,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -1971,7 +1983,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ3">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2096,7 +2108,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -2177,7 +2189,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ4">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2380,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ5">
         <v>1.57</v>
@@ -2508,7 +2520,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q6">
         <v>2.63</v>
@@ -2589,7 +2601,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ6">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2714,7 +2726,7 @@
         <v>89</v>
       </c>
       <c r="P7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2998,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ8">
         <v>1.43</v>
@@ -3126,7 +3138,7 @@
         <v>89</v>
       </c>
       <c r="P9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
@@ -3204,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ9">
         <v>1.64</v>
@@ -3538,7 +3550,7 @@
         <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -3616,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -3825,7 +3837,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ12">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3950,7 +3962,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -4028,7 +4040,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ13">
         <v>1.64</v>
@@ -4156,7 +4168,7 @@
         <v>95</v>
       </c>
       <c r="P14" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q14">
         <v>3.73</v>
@@ -4362,7 +4374,7 @@
         <v>96</v>
       </c>
       <c r="P15" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q15">
         <v>3.51</v>
@@ -4568,7 +4580,7 @@
         <v>97</v>
       </c>
       <c r="P16" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q16">
         <v>2.38</v>
@@ -5061,7 +5073,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ18">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5186,7 +5198,7 @@
         <v>99</v>
       </c>
       <c r="P19" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q19">
         <v>2.79</v>
@@ -5392,7 +5404,7 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5470,7 +5482,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ20">
         <v>1.43</v>
@@ -5885,7 +5897,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ22">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR22">
         <v>1.3</v>
@@ -6010,7 +6022,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6091,7 +6103,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ23">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR23">
         <v>1.93</v>
@@ -6294,7 +6306,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ24">
         <v>0.57</v>
@@ -6422,7 +6434,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q25">
         <v>2.91</v>
@@ -6834,7 +6846,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q27">
         <v>3.25</v>
@@ -7246,7 +7258,7 @@
         <v>89</v>
       </c>
       <c r="P29" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7324,7 +7336,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7452,7 +7464,7 @@
         <v>89</v>
       </c>
       <c r="P30" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q30">
         <v>3.3</v>
@@ -7864,7 +7876,7 @@
         <v>109</v>
       </c>
       <c r="P32" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7945,7 +7957,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ32">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR32">
         <v>2.27</v>
@@ -8148,7 +8160,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ33">
         <v>1.5</v>
@@ -8276,7 +8288,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q34">
         <v>3.1</v>
@@ -8357,7 +8369,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ34">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR34">
         <v>1.57</v>
@@ -8482,7 +8494,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q35">
         <v>2.57</v>
@@ -8688,7 +8700,7 @@
         <v>89</v>
       </c>
       <c r="P36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8769,7 +8781,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ36">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR36">
         <v>0.91</v>
@@ -8972,7 +8984,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ37">
         <v>1.64</v>
@@ -9100,7 +9112,7 @@
         <v>114</v>
       </c>
       <c r="P38" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9306,7 +9318,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -9590,7 +9602,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ40">
         <v>1.64</v>
@@ -9718,7 +9730,7 @@
         <v>116</v>
       </c>
       <c r="P41" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
@@ -9924,7 +9936,7 @@
         <v>89</v>
       </c>
       <c r="P42" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10336,7 +10348,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -10417,7 +10429,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ44">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR44">
         <v>1.61</v>
@@ -10542,7 +10554,7 @@
         <v>89</v>
       </c>
       <c r="P45" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q45">
         <v>2.85</v>
@@ -10829,7 +10841,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ46">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR46">
         <v>1.7</v>
@@ -10954,7 +10966,7 @@
         <v>120</v>
       </c>
       <c r="P47" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11035,7 +11047,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ47">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR47">
         <v>1.36</v>
@@ -11160,7 +11172,7 @@
         <v>89</v>
       </c>
       <c r="P48" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -11241,7 +11253,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ48">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR48">
         <v>1.74</v>
@@ -11366,7 +11378,7 @@
         <v>89</v>
       </c>
       <c r="P49" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11444,7 +11456,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ49">
         <v>1.43</v>
@@ -11778,7 +11790,7 @@
         <v>89</v>
       </c>
       <c r="P51" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q51">
         <v>3.2</v>
@@ -11856,7 +11868,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -12268,7 +12280,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ53">
         <v>0.79</v>
@@ -12396,7 +12408,7 @@
         <v>123</v>
       </c>
       <c r="P54" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q54">
         <v>3.1</v>
@@ -12474,7 +12486,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ54">
         <v>1.5</v>
@@ -12683,7 +12695,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ55">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR55">
         <v>1.78</v>
@@ -12808,7 +12820,7 @@
         <v>89</v>
       </c>
       <c r="P56" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q56">
         <v>3.08</v>
@@ -13014,7 +13026,7 @@
         <v>109</v>
       </c>
       <c r="P57" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -13426,7 +13438,7 @@
         <v>89</v>
       </c>
       <c r="P59" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13507,7 +13519,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ59">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR59">
         <v>1.13</v>
@@ -14662,7 +14674,7 @@
         <v>129</v>
       </c>
       <c r="P65" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14740,7 +14752,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -15074,7 +15086,7 @@
         <v>131</v>
       </c>
       <c r="P67" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q67">
         <v>3.12</v>
@@ -15152,7 +15164,7 @@
         <v>3</v>
       </c>
       <c r="AP67">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ67">
         <v>1.43</v>
@@ -15280,7 +15292,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q68">
         <v>2.96</v>
@@ -15358,7 +15370,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ68">
         <v>1.5</v>
@@ -15567,7 +15579,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ69">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR69">
         <v>1.69</v>
@@ -15976,10 +15988,10 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ71">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR71">
         <v>0.8</v>
@@ -16310,7 +16322,7 @@
         <v>89</v>
       </c>
       <c r="P73" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q73">
         <v>2.92</v>
@@ -16516,7 +16528,7 @@
         <v>89</v>
       </c>
       <c r="P74" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q74">
         <v>3.6</v>
@@ -16722,7 +16734,7 @@
         <v>97</v>
       </c>
       <c r="P75" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q75">
         <v>3.04</v>
@@ -16928,7 +16940,7 @@
         <v>135</v>
       </c>
       <c r="P76" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q76">
         <v>2.8</v>
@@ -17340,7 +17352,7 @@
         <v>137</v>
       </c>
       <c r="P78" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -18036,7 +18048,7 @@
         <v>1.25</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ81">
         <v>1.14</v>
@@ -18242,7 +18254,7 @@
         <v>1.6</v>
       </c>
       <c r="AP82">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ82">
         <v>1.64</v>
@@ -18370,7 +18382,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q83">
         <v>2.36</v>
@@ -18657,7 +18669,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ84">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR84">
         <v>1.48</v>
@@ -18860,10 +18872,10 @@
         <v>2</v>
       </c>
       <c r="AP85">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ85">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR85">
         <v>1.36</v>
@@ -18988,7 +19000,7 @@
         <v>144</v>
       </c>
       <c r="P86" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q86">
         <v>2.38</v>
@@ -19069,7 +19081,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ86">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR86">
         <v>1.78</v>
@@ -19272,7 +19284,7 @@
         <v>1.25</v>
       </c>
       <c r="AP87">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ87">
         <v>0.79</v>
@@ -19400,7 +19412,7 @@
         <v>127</v>
       </c>
       <c r="P88" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19478,10 +19490,10 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ88">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR88">
         <v>1.05</v>
@@ -19687,7 +19699,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ89">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR89">
         <v>1.48</v>
@@ -19812,7 +19824,7 @@
         <v>89</v>
       </c>
       <c r="P90" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q90">
         <v>3.09</v>
@@ -20018,7 +20030,7 @@
         <v>147</v>
       </c>
       <c r="P91" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q91">
         <v>3.05</v>
@@ -20224,7 +20236,7 @@
         <v>89</v>
       </c>
       <c r="P92" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q92">
         <v>3.5</v>
@@ -20430,7 +20442,7 @@
         <v>89</v>
       </c>
       <c r="P93" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q93">
         <v>3.64</v>
@@ -20636,7 +20648,7 @@
         <v>108</v>
       </c>
       <c r="P94" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q94">
         <v>3.35</v>
@@ -20842,7 +20854,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -21254,7 +21266,7 @@
         <v>150</v>
       </c>
       <c r="P97" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q97">
         <v>2.63</v>
@@ -21460,7 +21472,7 @@
         <v>151</v>
       </c>
       <c r="P98" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q98">
         <v>3.3</v>
@@ -21666,7 +21678,7 @@
         <v>89</v>
       </c>
       <c r="P99" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q99">
         <v>2.99</v>
@@ -21744,10 +21756,10 @@
         <v>1.75</v>
       </c>
       <c r="AP99">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ99">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR99">
         <v>1.34</v>
@@ -22159,7 +22171,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ101">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR101">
         <v>1.6</v>
@@ -22362,7 +22374,7 @@
         <v>1</v>
       </c>
       <c r="AP102">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ102">
         <v>0.79</v>
@@ -22490,7 +22502,7 @@
         <v>153</v>
       </c>
       <c r="P103" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q103">
         <v>2.6</v>
@@ -22571,7 +22583,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ103">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR103">
         <v>1.71</v>
@@ -22774,7 +22786,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ104">
         <v>1.14</v>
@@ -22902,7 +22914,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q105">
         <v>3.3</v>
@@ -22980,7 +22992,7 @@
         <v>1.67</v>
       </c>
       <c r="AP105">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ105">
         <v>1.57</v>
@@ -23108,7 +23120,7 @@
         <v>155</v>
       </c>
       <c r="P106" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q106">
         <v>3.38</v>
@@ -23186,7 +23198,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ106">
         <v>1.64</v>
@@ -23314,7 +23326,7 @@
         <v>156</v>
       </c>
       <c r="P107" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q107">
         <v>2.62</v>
@@ -23395,7 +23407,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ107">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR107">
         <v>1.21</v>
@@ -23520,7 +23532,7 @@
         <v>157</v>
       </c>
       <c r="P108" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q108">
         <v>2.66</v>
@@ -23601,7 +23613,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ108">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR108">
         <v>1.57</v>
@@ -23726,7 +23738,7 @@
         <v>158</v>
       </c>
       <c r="P109" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q109">
         <v>2.29</v>
@@ -23804,10 +23816,10 @@
         <v>0.4</v>
       </c>
       <c r="AP109">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ109">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR109">
         <v>1.09</v>
@@ -24013,7 +24025,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ110">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR110">
         <v>1.51</v>
@@ -24550,7 +24562,7 @@
         <v>89</v>
       </c>
       <c r="P113" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q113">
         <v>2.83</v>
@@ -24756,7 +24768,7 @@
         <v>160</v>
       </c>
       <c r="P114" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q114">
         <v>3</v>
@@ -25168,7 +25180,7 @@
         <v>161</v>
       </c>
       <c r="P116" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q116">
         <v>3.86</v>
@@ -25374,7 +25386,7 @@
         <v>162</v>
       </c>
       <c r="P117" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q117">
         <v>4.05</v>
@@ -26070,10 +26082,10 @@
         <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ120">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR120">
         <v>1.47</v>
@@ -26276,7 +26288,7 @@
         <v>1.86</v>
       </c>
       <c r="AP121">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ121">
         <v>1.57</v>
@@ -26404,7 +26416,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -26691,7 +26703,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ123">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR123">
         <v>1.21</v>
@@ -26816,7 +26828,7 @@
         <v>167</v>
       </c>
       <c r="P124" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q124">
         <v>2.84</v>
@@ -27228,7 +27240,7 @@
         <v>89</v>
       </c>
       <c r="P126" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q126">
         <v>2.41</v>
@@ -27309,7 +27321,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ126">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -27512,7 +27524,7 @@
         <v>0.83</v>
       </c>
       <c r="AP127">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ127">
         <v>1.14</v>
@@ -27640,7 +27652,7 @@
         <v>169</v>
       </c>
       <c r="P128" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q128">
         <v>2.1</v>
@@ -27718,10 +27730,10 @@
         <v>0.33</v>
       </c>
       <c r="AP128">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ128">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR128">
         <v>1.46</v>
@@ -27927,7 +27939,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ129">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR129">
         <v>1.3</v>
@@ -28052,7 +28064,7 @@
         <v>171</v>
       </c>
       <c r="P130" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q130">
         <v>2.49</v>
@@ -28336,7 +28348,7 @@
         <v>1.57</v>
       </c>
       <c r="AP131">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ131">
         <v>1</v>
@@ -28464,7 +28476,7 @@
         <v>173</v>
       </c>
       <c r="P132" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q132">
         <v>2.94</v>
@@ -28670,7 +28682,7 @@
         <v>161</v>
       </c>
       <c r="P133" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28876,7 +28888,7 @@
         <v>174</v>
       </c>
       <c r="P134" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q134">
         <v>4.33</v>
@@ -29494,7 +29506,7 @@
         <v>176</v>
       </c>
       <c r="P137" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q137">
         <v>3.12</v>
@@ -29575,7 +29587,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ137">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR137">
         <v>1.18</v>
@@ -29906,7 +29918,7 @@
         <v>177</v>
       </c>
       <c r="P139" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q139">
         <v>1.99</v>
@@ -29987,7 +29999,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ139">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR139">
         <v>1.54</v>
@@ -30190,7 +30202,7 @@
         <v>1.5</v>
       </c>
       <c r="AP140">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ140">
         <v>1.43</v>
@@ -30318,7 +30330,7 @@
         <v>89</v>
       </c>
       <c r="P141" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q141">
         <v>2.6</v>
@@ -30730,7 +30742,7 @@
         <v>128</v>
       </c>
       <c r="P143" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q143">
         <v>2.65</v>
@@ -30936,7 +30948,7 @@
         <v>89</v>
       </c>
       <c r="P144" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q144">
         <v>4.33</v>
@@ -31223,7 +31235,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ145">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR145">
         <v>1.33</v>
@@ -31348,7 +31360,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -31554,7 +31566,7 @@
         <v>182</v>
       </c>
       <c r="P147" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q147">
         <v>3.25</v>
@@ -31760,7 +31772,7 @@
         <v>183</v>
       </c>
       <c r="P148" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q148">
         <v>2.36</v>
@@ -32044,7 +32056,7 @@
         <v>1.13</v>
       </c>
       <c r="AP149">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ149">
         <v>1.64</v>
@@ -32253,7 +32265,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ150">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR150">
         <v>1.63</v>
@@ -32378,7 +32390,7 @@
         <v>129</v>
       </c>
       <c r="P151" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q151">
         <v>2.78</v>
@@ -32456,7 +32468,7 @@
         <v>1.13</v>
       </c>
       <c r="AP151">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ151">
         <v>0.93</v>
@@ -32584,7 +32596,7 @@
         <v>185</v>
       </c>
       <c r="P152" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q152">
         <v>2.81</v>
@@ -32665,7 +32677,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ152">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR152">
         <v>1.34</v>
@@ -32868,7 +32880,7 @@
         <v>1.63</v>
       </c>
       <c r="AP153">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ153">
         <v>1.57</v>
@@ -32996,7 +33008,7 @@
         <v>186</v>
       </c>
       <c r="P154" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q154">
         <v>3.38</v>
@@ -33074,7 +33086,7 @@
         <v>1.75</v>
       </c>
       <c r="AP154">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ154">
         <v>1.64</v>
@@ -33692,7 +33704,7 @@
         <v>0.33</v>
       </c>
       <c r="AP157">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ157">
         <v>0.57</v>
@@ -33820,7 +33832,7 @@
         <v>190</v>
       </c>
       <c r="P158" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q158">
         <v>3.5</v>
@@ -33898,7 +33910,7 @@
         <v>1.5</v>
       </c>
       <c r="AP158">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ158">
         <v>1</v>
@@ -34107,7 +34119,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ159">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR159">
         <v>1.72</v>
@@ -34438,7 +34450,7 @@
         <v>193</v>
       </c>
       <c r="P161" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34519,7 +34531,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ161">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR161">
         <v>1.7</v>
@@ -34850,7 +34862,7 @@
         <v>194</v>
       </c>
       <c r="P163" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q163">
         <v>4.2</v>
@@ -35056,7 +35068,7 @@
         <v>195</v>
       </c>
       <c r="P164" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q164">
         <v>2.55</v>
@@ -35134,7 +35146,7 @@
         <v>0.88</v>
       </c>
       <c r="AP164">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ164">
         <v>1.14</v>
@@ -35262,7 +35274,7 @@
         <v>89</v>
       </c>
       <c r="P165" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35674,7 +35686,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q167">
         <v>2.45</v>
@@ -35755,7 +35767,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ167">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR167">
         <v>1.71</v>
@@ -36167,7 +36179,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ169">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR169">
         <v>1.26</v>
@@ -36370,7 +36382,7 @@
         <v>1.33</v>
       </c>
       <c r="AP170">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ170">
         <v>0.93</v>
@@ -36498,7 +36510,7 @@
         <v>198</v>
       </c>
       <c r="P171" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q171">
         <v>3.84</v>
@@ -36576,7 +36588,7 @@
         <v>1.67</v>
       </c>
       <c r="AP171">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ171">
         <v>1.64</v>
@@ -36785,7 +36797,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ172">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR172">
         <v>1.3</v>
@@ -37116,7 +37128,7 @@
         <v>200</v>
       </c>
       <c r="P174" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q174">
         <v>3.32</v>
@@ -37609,7 +37621,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ176">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR176">
         <v>1.68</v>
@@ -37734,7 +37746,7 @@
         <v>202</v>
       </c>
       <c r="P177" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q177">
         <v>3.2</v>
@@ -37812,7 +37824,7 @@
         <v>1.2</v>
       </c>
       <c r="AP177">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ177">
         <v>1</v>
@@ -38018,10 +38030,10 @@
         <v>0.67</v>
       </c>
       <c r="AP178">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ178">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR178">
         <v>1.35</v>
@@ -38227,7 +38239,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ179">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR179">
         <v>1.25</v>
@@ -38352,7 +38364,7 @@
         <v>179</v>
       </c>
       <c r="P180" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q180">
         <v>2.97</v>
@@ -38636,7 +38648,7 @@
         <v>1.6</v>
       </c>
       <c r="AP181">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ181">
         <v>1.64</v>
@@ -38764,7 +38776,7 @@
         <v>89</v>
       </c>
       <c r="P182" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q182">
         <v>2.65</v>
@@ -38970,7 +38982,7 @@
         <v>205</v>
       </c>
       <c r="P183" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q183">
         <v>2.27</v>
@@ -39051,7 +39063,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ183">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR183">
         <v>1.33</v>
@@ -39588,7 +39600,7 @@
         <v>141</v>
       </c>
       <c r="P186" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q186">
         <v>3.14</v>
@@ -39669,7 +39681,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ186">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR186">
         <v>1.18</v>
@@ -40000,7 +40012,7 @@
         <v>207</v>
       </c>
       <c r="P188" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40078,7 +40090,7 @@
         <v>1.5</v>
       </c>
       <c r="AP188">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ188">
         <v>1.43</v>
@@ -40284,7 +40296,7 @@
         <v>0.3</v>
       </c>
       <c r="AP189">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ189">
         <v>0.57</v>
@@ -40412,7 +40424,7 @@
         <v>208</v>
       </c>
       <c r="P190" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q190">
         <v>3.6</v>
@@ -40824,7 +40836,7 @@
         <v>123</v>
       </c>
       <c r="P192" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q192">
         <v>2.95</v>
@@ -41111,7 +41123,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ193">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR193">
         <v>1.6</v>
@@ -41236,7 +41248,7 @@
         <v>210</v>
       </c>
       <c r="P194" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q194">
         <v>4.2</v>
@@ -41317,7 +41329,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ194">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR194">
         <v>1.3</v>
@@ -41648,7 +41660,7 @@
         <v>211</v>
       </c>
       <c r="P196" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q196">
         <v>3.2</v>
@@ -41726,10 +41738,10 @@
         <v>1.3</v>
       </c>
       <c r="AP196">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ196">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR196">
         <v>1.34</v>
@@ -41854,7 +41866,7 @@
         <v>212</v>
       </c>
       <c r="P197" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q197">
         <v>3</v>
@@ -41932,7 +41944,7 @@
         <v>2</v>
       </c>
       <c r="AP197">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ197">
         <v>1.43</v>
@@ -42138,7 +42150,7 @@
         <v>1.36</v>
       </c>
       <c r="AP198">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ198">
         <v>1.5</v>
@@ -42266,7 +42278,7 @@
         <v>214</v>
       </c>
       <c r="P199" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q199">
         <v>2.75</v>
@@ -42344,7 +42356,7 @@
         <v>1.09</v>
       </c>
       <c r="AP199">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ199">
         <v>1</v>
@@ -42884,7 +42896,7 @@
         <v>123</v>
       </c>
       <c r="P202" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q202">
         <v>4.3</v>
@@ -43171,7 +43183,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ203">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR203">
         <v>1.53</v>
@@ -43296,7 +43308,7 @@
         <v>117</v>
       </c>
       <c r="P204" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q204">
         <v>3.1</v>
@@ -43583,7 +43595,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ205">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR205">
         <v>1.71</v>
@@ -43708,7 +43720,7 @@
         <v>218</v>
       </c>
       <c r="P206" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q206">
         <v>3.65</v>
@@ -43914,7 +43926,7 @@
         <v>156</v>
       </c>
       <c r="P207" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q207">
         <v>3.45</v>
@@ -44120,7 +44132,7 @@
         <v>197</v>
       </c>
       <c r="P208" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q208">
         <v>3.5</v>
@@ -44198,7 +44210,7 @@
         <v>1.45</v>
       </c>
       <c r="AP208">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ208">
         <v>1.64</v>
@@ -44326,7 +44338,7 @@
         <v>129</v>
       </c>
       <c r="P209" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q209">
         <v>2.4</v>
@@ -44407,7 +44419,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ209">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR209">
         <v>1.53</v>
@@ -44610,7 +44622,7 @@
         <v>1.09</v>
       </c>
       <c r="AP210">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ210">
         <v>1</v>
@@ -44816,10 +44828,10 @@
         <v>0.55</v>
       </c>
       <c r="AP211">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ211">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR211">
         <v>1.57</v>
@@ -44944,7 +44956,7 @@
         <v>220</v>
       </c>
       <c r="P212" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q212">
         <v>2.43</v>
@@ -45025,7 +45037,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ212">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR212">
         <v>1.61</v>
@@ -45150,7 +45162,7 @@
         <v>221</v>
       </c>
       <c r="P213" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q213">
         <v>3.15</v>
@@ -45228,7 +45240,7 @@
         <v>0.64</v>
       </c>
       <c r="AP213">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ213">
         <v>0.79</v>
@@ -45434,7 +45446,7 @@
         <v>1.25</v>
       </c>
       <c r="AP214">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ214">
         <v>1.5</v>
@@ -45640,7 +45652,7 @@
         <v>1.82</v>
       </c>
       <c r="AP215">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ215">
         <v>1.43</v>
@@ -46055,7 +46067,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ217">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR217">
         <v>1.78</v>
@@ -46180,7 +46192,7 @@
         <v>89</v>
       </c>
       <c r="P218" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q218">
         <v>3.6</v>
@@ -46386,7 +46398,7 @@
         <v>224</v>
       </c>
       <c r="P219" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q219">
         <v>3.78</v>
@@ -46592,7 +46604,7 @@
         <v>225</v>
       </c>
       <c r="P220" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q220">
         <v>3.26</v>
@@ -46879,7 +46891,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ221">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR221">
         <v>1.41</v>
@@ -47416,7 +47428,7 @@
         <v>89</v>
       </c>
       <c r="P224" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q224">
         <v>5.44</v>
@@ -48034,7 +48046,7 @@
         <v>156</v>
       </c>
       <c r="P227" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q227">
         <v>2.9</v>
@@ -48112,7 +48124,7 @@
         <v>1.08</v>
       </c>
       <c r="AP227">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ227">
         <v>1.14</v>
@@ -48240,7 +48252,7 @@
         <v>228</v>
       </c>
       <c r="P228" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q228">
         <v>2.6</v>
@@ -48318,10 +48330,10 @@
         <v>1.42</v>
       </c>
       <c r="AP228">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ228">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR228">
         <v>1.52</v>
@@ -48524,7 +48536,7 @@
         <v>1.67</v>
       </c>
       <c r="AP229">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ229">
         <v>1.43</v>
@@ -48939,7 +48951,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ231">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR231">
         <v>1.57</v>
@@ -49145,7 +49157,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ232">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR232">
         <v>1.59</v>
@@ -49348,10 +49360,10 @@
         <v>0.5</v>
       </c>
       <c r="AP233">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ233">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR233">
         <v>1.65</v>
@@ -49554,7 +49566,7 @@
         <v>0.58</v>
       </c>
       <c r="AP234">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ234">
         <v>0.79</v>
@@ -49763,7 +49775,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ235">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR235">
         <v>1.77</v>
@@ -49888,7 +49900,7 @@
         <v>128</v>
       </c>
       <c r="P236" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q236">
         <v>4.5</v>
@@ -50300,7 +50312,7 @@
         <v>233</v>
       </c>
       <c r="P238" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q238">
         <v>2.1</v>
@@ -50506,7 +50518,7 @@
         <v>89</v>
       </c>
       <c r="P239" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q239">
         <v>3.75</v>
@@ -50712,7 +50724,7 @@
         <v>234</v>
       </c>
       <c r="P240" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q240">
         <v>3</v>
@@ -51124,7 +51136,7 @@
         <v>89</v>
       </c>
       <c r="P242" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q242">
         <v>3.6</v>
@@ -52360,7 +52372,7 @@
         <v>109</v>
       </c>
       <c r="P248" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q248">
         <v>3.6</v>
@@ -52517,6 +52529,1036 @@
       </c>
       <c r="BP248">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7502849</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45753.29166666666</v>
+      </c>
+      <c r="F249">
+        <v>28</v>
+      </c>
+      <c r="G249" t="s">
+        <v>77</v>
+      </c>
+      <c r="H249" t="s">
+        <v>75</v>
+      </c>
+      <c r="I249">
+        <v>1</v>
+      </c>
+      <c r="J249">
+        <v>1</v>
+      </c>
+      <c r="K249">
+        <v>2</v>
+      </c>
+      <c r="L249">
+        <v>1</v>
+      </c>
+      <c r="M249">
+        <v>3</v>
+      </c>
+      <c r="N249">
+        <v>4</v>
+      </c>
+      <c r="O249" t="s">
+        <v>199</v>
+      </c>
+      <c r="P249" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q249">
+        <v>2.35</v>
+      </c>
+      <c r="R249">
+        <v>2.09</v>
+      </c>
+      <c r="S249">
+        <v>4.95</v>
+      </c>
+      <c r="T249">
+        <v>1.39</v>
+      </c>
+      <c r="U249">
+        <v>2.77</v>
+      </c>
+      <c r="V249">
+        <v>2.99</v>
+      </c>
+      <c r="W249">
+        <v>1.34</v>
+      </c>
+      <c r="X249">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y249">
+        <v>1.02</v>
+      </c>
+      <c r="Z249">
+        <v>1.91</v>
+      </c>
+      <c r="AA249">
+        <v>3.3</v>
+      </c>
+      <c r="AB249">
+        <v>3.9</v>
+      </c>
+      <c r="AC249">
+        <v>1.02</v>
+      </c>
+      <c r="AD249">
+        <v>7.9</v>
+      </c>
+      <c r="AE249">
+        <v>1.27</v>
+      </c>
+      <c r="AF249">
+        <v>3.15</v>
+      </c>
+      <c r="AG249">
+        <v>1.95</v>
+      </c>
+      <c r="AH249">
+        <v>1.7</v>
+      </c>
+      <c r="AI249">
+        <v>1.89</v>
+      </c>
+      <c r="AJ249">
+        <v>1.81</v>
+      </c>
+      <c r="AK249">
+        <v>1.19</v>
+      </c>
+      <c r="AL249">
+        <v>1.27</v>
+      </c>
+      <c r="AM249">
+        <v>2.01</v>
+      </c>
+      <c r="AN249">
+        <v>1.54</v>
+      </c>
+      <c r="AO249">
+        <v>1.38</v>
+      </c>
+      <c r="AP249">
+        <v>1.43</v>
+      </c>
+      <c r="AQ249">
+        <v>1.5</v>
+      </c>
+      <c r="AR249">
+        <v>1.66</v>
+      </c>
+      <c r="AS249">
+        <v>1.37</v>
+      </c>
+      <c r="AT249">
+        <v>3.03</v>
+      </c>
+      <c r="AU249">
+        <v>4</v>
+      </c>
+      <c r="AV249">
+        <v>6</v>
+      </c>
+      <c r="AW249">
+        <v>8</v>
+      </c>
+      <c r="AX249">
+        <v>7</v>
+      </c>
+      <c r="AY249">
+        <v>12</v>
+      </c>
+      <c r="AZ249">
+        <v>13</v>
+      </c>
+      <c r="BA249">
+        <v>-1</v>
+      </c>
+      <c r="BB249">
+        <v>-1</v>
+      </c>
+      <c r="BC249">
+        <v>-1</v>
+      </c>
+      <c r="BD249">
+        <v>1.62</v>
+      </c>
+      <c r="BE249">
+        <v>6.8</v>
+      </c>
+      <c r="BF249">
+        <v>2.95</v>
+      </c>
+      <c r="BG249">
+        <v>1.29</v>
+      </c>
+      <c r="BH249">
+        <v>3.4</v>
+      </c>
+      <c r="BI249">
+        <v>1.48</v>
+      </c>
+      <c r="BJ249">
+        <v>2.5</v>
+      </c>
+      <c r="BK249">
+        <v>1.77</v>
+      </c>
+      <c r="BL249">
+        <v>2.02</v>
+      </c>
+      <c r="BM249">
+        <v>2.22</v>
+      </c>
+      <c r="BN249">
+        <v>1.63</v>
+      </c>
+      <c r="BO249">
+        <v>2.7</v>
+      </c>
+      <c r="BP249">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7502854</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45753.29166666666</v>
+      </c>
+      <c r="F250">
+        <v>28</v>
+      </c>
+      <c r="G250" t="s">
+        <v>76</v>
+      </c>
+      <c r="H250" t="s">
+        <v>82</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>0</v>
+      </c>
+      <c r="L250">
+        <v>1</v>
+      </c>
+      <c r="M250">
+        <v>0</v>
+      </c>
+      <c r="N250">
+        <v>1</v>
+      </c>
+      <c r="O250" t="s">
+        <v>174</v>
+      </c>
+      <c r="P250" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q250">
+        <v>2.83</v>
+      </c>
+      <c r="R250">
+        <v>2.09</v>
+      </c>
+      <c r="S250">
+        <v>3.66</v>
+      </c>
+      <c r="T250">
+        <v>1.39</v>
+      </c>
+      <c r="U250">
+        <v>2.77</v>
+      </c>
+      <c r="V250">
+        <v>2.77</v>
+      </c>
+      <c r="W250">
+        <v>1.39</v>
+      </c>
+      <c r="X250">
+        <v>6.5</v>
+      </c>
+      <c r="Y250">
+        <v>1.05</v>
+      </c>
+      <c r="Z250">
+        <v>2.2</v>
+      </c>
+      <c r="AA250">
+        <v>3.2</v>
+      </c>
+      <c r="AB250">
+        <v>3.1</v>
+      </c>
+      <c r="AC250">
+        <v>1.01</v>
+      </c>
+      <c r="AD250">
+        <v>8.5</v>
+      </c>
+      <c r="AE250">
+        <v>1.26</v>
+      </c>
+      <c r="AF250">
+        <v>3.22</v>
+      </c>
+      <c r="AG250">
+        <v>1.91</v>
+      </c>
+      <c r="AH250">
+        <v>1.75</v>
+      </c>
+      <c r="AI250">
+        <v>1.71</v>
+      </c>
+      <c r="AJ250">
+        <v>2.02</v>
+      </c>
+      <c r="AK250">
+        <v>1.36</v>
+      </c>
+      <c r="AL250">
+        <v>1.31</v>
+      </c>
+      <c r="AM250">
+        <v>1.61</v>
+      </c>
+      <c r="AN250">
+        <v>1.31</v>
+      </c>
+      <c r="AO250">
+        <v>1.15</v>
+      </c>
+      <c r="AP250">
+        <v>1.43</v>
+      </c>
+      <c r="AQ250">
+        <v>1.07</v>
+      </c>
+      <c r="AR250">
+        <v>1.15</v>
+      </c>
+      <c r="AS250">
+        <v>1.3</v>
+      </c>
+      <c r="AT250">
+        <v>2.45</v>
+      </c>
+      <c r="AU250">
+        <v>3</v>
+      </c>
+      <c r="AV250">
+        <v>3</v>
+      </c>
+      <c r="AW250">
+        <v>9</v>
+      </c>
+      <c r="AX250">
+        <v>1</v>
+      </c>
+      <c r="AY250">
+        <v>12</v>
+      </c>
+      <c r="AZ250">
+        <v>4</v>
+      </c>
+      <c r="BA250">
+        <v>-1</v>
+      </c>
+      <c r="BB250">
+        <v>-1</v>
+      </c>
+      <c r="BC250">
+        <v>-1</v>
+      </c>
+      <c r="BD250">
+        <v>1.93</v>
+      </c>
+      <c r="BE250">
+        <v>6.55</v>
+      </c>
+      <c r="BF250">
+        <v>2.3</v>
+      </c>
+      <c r="BG250">
+        <v>1.14</v>
+      </c>
+      <c r="BH250">
+        <v>4.33</v>
+      </c>
+      <c r="BI250">
+        <v>1.31</v>
+      </c>
+      <c r="BJ250">
+        <v>2.92</v>
+      </c>
+      <c r="BK250">
+        <v>1.57</v>
+      </c>
+      <c r="BL250">
+        <v>2.19</v>
+      </c>
+      <c r="BM250">
+        <v>1.96</v>
+      </c>
+      <c r="BN250">
+        <v>1.75</v>
+      </c>
+      <c r="BO250">
+        <v>2.54</v>
+      </c>
+      <c r="BP250">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7502851</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45753.41666666666</v>
+      </c>
+      <c r="F251">
+        <v>28</v>
+      </c>
+      <c r="G251" t="s">
+        <v>73</v>
+      </c>
+      <c r="H251" t="s">
+        <v>71</v>
+      </c>
+      <c r="I251">
+        <v>1</v>
+      </c>
+      <c r="J251">
+        <v>1</v>
+      </c>
+      <c r="K251">
+        <v>2</v>
+      </c>
+      <c r="L251">
+        <v>3</v>
+      </c>
+      <c r="M251">
+        <v>1</v>
+      </c>
+      <c r="N251">
+        <v>4</v>
+      </c>
+      <c r="O251" t="s">
+        <v>238</v>
+      </c>
+      <c r="P251" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q251">
+        <v>2.75</v>
+      </c>
+      <c r="R251">
+        <v>2.05</v>
+      </c>
+      <c r="S251">
+        <v>4.33</v>
+      </c>
+      <c r="T251">
+        <v>1.5</v>
+      </c>
+      <c r="U251">
+        <v>2.5</v>
+      </c>
+      <c r="V251">
+        <v>3.4</v>
+      </c>
+      <c r="W251">
+        <v>1.3</v>
+      </c>
+      <c r="X251">
+        <v>10</v>
+      </c>
+      <c r="Y251">
+        <v>1.06</v>
+      </c>
+      <c r="Z251">
+        <v>1.77</v>
+      </c>
+      <c r="AA251">
+        <v>3.3</v>
+      </c>
+      <c r="AB251">
+        <v>4.4</v>
+      </c>
+      <c r="AC251">
+        <v>1.02</v>
+      </c>
+      <c r="AD251">
+        <v>7.8</v>
+      </c>
+      <c r="AE251">
+        <v>1.35</v>
+      </c>
+      <c r="AF251">
+        <v>2.75</v>
+      </c>
+      <c r="AG251">
+        <v>2.1</v>
+      </c>
+      <c r="AH251">
+        <v>1.6</v>
+      </c>
+      <c r="AI251">
+        <v>2</v>
+      </c>
+      <c r="AJ251">
+        <v>1.73</v>
+      </c>
+      <c r="AK251">
+        <v>1.26</v>
+      </c>
+      <c r="AL251">
+        <v>1.31</v>
+      </c>
+      <c r="AM251">
+        <v>1.78</v>
+      </c>
+      <c r="AN251">
+        <v>1.77</v>
+      </c>
+      <c r="AO251">
+        <v>0.46</v>
+      </c>
+      <c r="AP251">
+        <v>1.86</v>
+      </c>
+      <c r="AQ251">
+        <v>0.43</v>
+      </c>
+      <c r="AR251">
+        <v>1.25</v>
+      </c>
+      <c r="AS251">
+        <v>1.26</v>
+      </c>
+      <c r="AT251">
+        <v>2.51</v>
+      </c>
+      <c r="AU251">
+        <v>5</v>
+      </c>
+      <c r="AV251">
+        <v>4</v>
+      </c>
+      <c r="AW251">
+        <v>7</v>
+      </c>
+      <c r="AX251">
+        <v>6</v>
+      </c>
+      <c r="AY251">
+        <v>12</v>
+      </c>
+      <c r="AZ251">
+        <v>10</v>
+      </c>
+      <c r="BA251">
+        <v>-1</v>
+      </c>
+      <c r="BB251">
+        <v>-1</v>
+      </c>
+      <c r="BC251">
+        <v>-1</v>
+      </c>
+      <c r="BD251">
+        <v>1.63</v>
+      </c>
+      <c r="BE251">
+        <v>6.7</v>
+      </c>
+      <c r="BF251">
+        <v>2.92</v>
+      </c>
+      <c r="BG251">
+        <v>1.29</v>
+      </c>
+      <c r="BH251">
+        <v>3.3</v>
+      </c>
+      <c r="BI251">
+        <v>1.51</v>
+      </c>
+      <c r="BJ251">
+        <v>2.51</v>
+      </c>
+      <c r="BK251">
+        <v>1.85</v>
+      </c>
+      <c r="BL251">
+        <v>1.94</v>
+      </c>
+      <c r="BM251">
+        <v>2.34</v>
+      </c>
+      <c r="BN251">
+        <v>1.57</v>
+      </c>
+      <c r="BO251">
+        <v>2.9</v>
+      </c>
+      <c r="BP251">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7502855</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45753.47916666666</v>
+      </c>
+      <c r="F252">
+        <v>28</v>
+      </c>
+      <c r="G252" t="s">
+        <v>81</v>
+      </c>
+      <c r="H252" t="s">
+        <v>80</v>
+      </c>
+      <c r="I252">
+        <v>1</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>1</v>
+      </c>
+      <c r="L252">
+        <v>2</v>
+      </c>
+      <c r="M252">
+        <v>3</v>
+      </c>
+      <c r="N252">
+        <v>5</v>
+      </c>
+      <c r="O252" t="s">
+        <v>239</v>
+      </c>
+      <c r="P252" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q252">
+        <v>2.5</v>
+      </c>
+      <c r="R252">
+        <v>2.25</v>
+      </c>
+      <c r="S252">
+        <v>3.9</v>
+      </c>
+      <c r="T252">
+        <v>1.35</v>
+      </c>
+      <c r="U252">
+        <v>3</v>
+      </c>
+      <c r="V252">
+        <v>2.7</v>
+      </c>
+      <c r="W252">
+        <v>1.44</v>
+      </c>
+      <c r="X252">
+        <v>7</v>
+      </c>
+      <c r="Y252">
+        <v>1.1</v>
+      </c>
+      <c r="Z252">
+        <v>1.8</v>
+      </c>
+      <c r="AA252">
+        <v>3.4</v>
+      </c>
+      <c r="AB252">
+        <v>4</v>
+      </c>
+      <c r="AC252">
+        <v>1</v>
+      </c>
+      <c r="AD252">
+        <v>9</v>
+      </c>
+      <c r="AE252">
+        <v>1.23</v>
+      </c>
+      <c r="AF252">
+        <v>3.44</v>
+      </c>
+      <c r="AG252">
+        <v>1.83</v>
+      </c>
+      <c r="AH252">
+        <v>1.8</v>
+      </c>
+      <c r="AI252">
+        <v>1.75</v>
+      </c>
+      <c r="AJ252">
+        <v>2</v>
+      </c>
+      <c r="AK252">
+        <v>1.25</v>
+      </c>
+      <c r="AL252">
+        <v>1.3</v>
+      </c>
+      <c r="AM252">
+        <v>1.85</v>
+      </c>
+      <c r="AN252">
+        <v>1.31</v>
+      </c>
+      <c r="AO252">
+        <v>0.92</v>
+      </c>
+      <c r="AP252">
+        <v>1.21</v>
+      </c>
+      <c r="AQ252">
+        <v>1.07</v>
+      </c>
+      <c r="AR252">
+        <v>1.49</v>
+      </c>
+      <c r="AS252">
+        <v>1.19</v>
+      </c>
+      <c r="AT252">
+        <v>2.68</v>
+      </c>
+      <c r="AU252">
+        <v>5</v>
+      </c>
+      <c r="AV252">
+        <v>6</v>
+      </c>
+      <c r="AW252">
+        <v>7</v>
+      </c>
+      <c r="AX252">
+        <v>10</v>
+      </c>
+      <c r="AY252">
+        <v>12</v>
+      </c>
+      <c r="AZ252">
+        <v>16</v>
+      </c>
+      <c r="BA252">
+        <v>-1</v>
+      </c>
+      <c r="BB252">
+        <v>-1</v>
+      </c>
+      <c r="BC252">
+        <v>-1</v>
+      </c>
+      <c r="BD252">
+        <v>1.9</v>
+      </c>
+      <c r="BE252">
+        <v>6.6</v>
+      </c>
+      <c r="BF252">
+        <v>2.34</v>
+      </c>
+      <c r="BG252">
+        <v>1.2</v>
+      </c>
+      <c r="BH252">
+        <v>4</v>
+      </c>
+      <c r="BI252">
+        <v>1.33</v>
+      </c>
+      <c r="BJ252">
+        <v>3</v>
+      </c>
+      <c r="BK252">
+        <v>1.6</v>
+      </c>
+      <c r="BL252">
+        <v>2.28</v>
+      </c>
+      <c r="BM252">
+        <v>1.94</v>
+      </c>
+      <c r="BN252">
+        <v>1.85</v>
+      </c>
+      <c r="BO252">
+        <v>2.4</v>
+      </c>
+      <c r="BP252">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7502850</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45753.58333333334</v>
+      </c>
+      <c r="F253">
+        <v>28</v>
+      </c>
+      <c r="G253" t="s">
+        <v>79</v>
+      </c>
+      <c r="H253" t="s">
+        <v>86</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253">
+        <v>0</v>
+      </c>
+      <c r="L253">
+        <v>0</v>
+      </c>
+      <c r="M253">
+        <v>0</v>
+      </c>
+      <c r="N253">
+        <v>0</v>
+      </c>
+      <c r="O253" t="s">
+        <v>89</v>
+      </c>
+      <c r="P253" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q253">
+        <v>2.5</v>
+      </c>
+      <c r="R253">
+        <v>2.2</v>
+      </c>
+      <c r="S253">
+        <v>4.33</v>
+      </c>
+      <c r="T253">
+        <v>1.4</v>
+      </c>
+      <c r="U253">
+        <v>2.75</v>
+      </c>
+      <c r="V253">
+        <v>2.75</v>
+      </c>
+      <c r="W253">
+        <v>1.4</v>
+      </c>
+      <c r="X253">
+        <v>8</v>
+      </c>
+      <c r="Y253">
+        <v>1.08</v>
+      </c>
+      <c r="Z253">
+        <v>2.05</v>
+      </c>
+      <c r="AA253">
+        <v>3.4</v>
+      </c>
+      <c r="AB253">
+        <v>3.2</v>
+      </c>
+      <c r="AC253">
+        <v>1.01</v>
+      </c>
+      <c r="AD253">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE253">
+        <v>1.26</v>
+      </c>
+      <c r="AF253">
+        <v>3.22</v>
+      </c>
+      <c r="AG253">
+        <v>1.85</v>
+      </c>
+      <c r="AH253">
+        <v>1.8</v>
+      </c>
+      <c r="AI253">
+        <v>1.8</v>
+      </c>
+      <c r="AJ253">
+        <v>1.91</v>
+      </c>
+      <c r="AK253">
+        <v>1.28</v>
+      </c>
+      <c r="AL253">
+        <v>1.28</v>
+      </c>
+      <c r="AM253">
+        <v>1.79</v>
+      </c>
+      <c r="AN253">
+        <v>2</v>
+      </c>
+      <c r="AO253">
+        <v>1.23</v>
+      </c>
+      <c r="AP253">
+        <v>1.93</v>
+      </c>
+      <c r="AQ253">
+        <v>1.21</v>
+      </c>
+      <c r="AR253">
+        <v>1.52</v>
+      </c>
+      <c r="AS253">
+        <v>1.47</v>
+      </c>
+      <c r="AT253">
+        <v>2.99</v>
+      </c>
+      <c r="AU253">
+        <v>6</v>
+      </c>
+      <c r="AV253">
+        <v>4</v>
+      </c>
+      <c r="AW253">
+        <v>10</v>
+      </c>
+      <c r="AX253">
+        <v>3</v>
+      </c>
+      <c r="AY253">
+        <v>16</v>
+      </c>
+      <c r="AZ253">
+        <v>7</v>
+      </c>
+      <c r="BA253">
+        <v>-1</v>
+      </c>
+      <c r="BB253">
+        <v>-1</v>
+      </c>
+      <c r="BC253">
+        <v>-1</v>
+      </c>
+      <c r="BD253">
+        <v>1.83</v>
+      </c>
+      <c r="BE253">
+        <v>6.5</v>
+      </c>
+      <c r="BF253">
+        <v>2.47</v>
+      </c>
+      <c r="BG253">
+        <v>1.19</v>
+      </c>
+      <c r="BH253">
+        <v>3.82</v>
+      </c>
+      <c r="BI253">
+        <v>1.39</v>
+      </c>
+      <c r="BJ253">
+        <v>2.67</v>
+      </c>
+      <c r="BK253">
+        <v>1.7</v>
+      </c>
+      <c r="BL253">
+        <v>2.03</v>
+      </c>
+      <c r="BM253">
+        <v>2.14</v>
+      </c>
+      <c r="BN253">
+        <v>1.6</v>
+      </c>
+      <c r="BO253">
+        <v>2.78</v>
+      </c>
+      <c r="BP253">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -51865,13 +51865,13 @@
         <v>6</v>
       </c>
       <c r="BA245">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BB245">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BC245">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BD245">
         <v>1.46</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -52071,13 +52071,13 @@
         <v>4</v>
       </c>
       <c r="BA246">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB246">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC246">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD246">
         <v>1.39</v>
@@ -52483,13 +52483,13 @@
         <v>12</v>
       </c>
       <c r="BA248">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB248">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC248">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD248">
         <v>2.28</v>
@@ -52689,13 +52689,13 @@
         <v>13</v>
       </c>
       <c r="BA249">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB249">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC249">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BD249">
         <v>1.62</v>
@@ -52895,13 +52895,13 @@
         <v>4</v>
       </c>
       <c r="BA250">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB250">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC250">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD250">
         <v>1.93</v>
@@ -53101,13 +53101,13 @@
         <v>10</v>
       </c>
       <c r="BA251">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB251">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC251">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD251">
         <v>1.63</v>
@@ -53307,13 +53307,13 @@
         <v>16</v>
       </c>
       <c r="BA252">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB252">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BC252">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD252">
         <v>1.9</v>
@@ -53513,13 +53513,13 @@
         <v>7</v>
       </c>
       <c r="BA253">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB253">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC253">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD253">
         <v>1.83</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -50521,46 +50521,46 @@
         <v>350</v>
       </c>
       <c r="Q239">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R239">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S239">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T239">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U239">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V239">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W239">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X239">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y239">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z239">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA239">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB239">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC239">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD239">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE239">
         <v>0</v>
@@ -50569,16 +50569,16 @@
         <v>0</v>
       </c>
       <c r="AG239">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH239">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI239">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ239">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AK239">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Portugal LigaPro_20242025.xlsx
@@ -1939,7 +1939,7 @@
         <v>11</v>
       </c>
       <c r="AZ2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA2">
         <v>5</v>
@@ -2142,10 +2142,10 @@
         <v>3</v>
       </c>
       <c r="AY3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA3">
         <v>2</v>
@@ -2348,10 +2348,10 @@
         <v>2</v>
       </c>
       <c r="AY4">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AZ4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA4">
         <v>8</v>
@@ -2554,10 +2554,10 @@
         <v>10</v>
       </c>
       <c r="AY5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA5">
         <v>1</v>
@@ -2966,10 +2966,10 @@
         <v>10</v>
       </c>
       <c r="AY7">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AZ7">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="BA7">
         <v>6</v>
@@ -3584,7 +3584,7 @@
         <v>3</v>
       </c>
       <c r="AY10">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ10">
         <v>5</v>
@@ -3790,10 +3790,10 @@
         <v>4</v>
       </c>
       <c r="AY11">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ11">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -3996,10 +3996,10 @@
         <v>6</v>
       </c>
       <c r="AY12">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ12">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA12">
         <v>4</v>
@@ -4202,10 +4202,10 @@
         <v>10</v>
       </c>
       <c r="AY13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ13">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA13">
         <v>6</v>
@@ -4408,10 +4408,10 @@
         <v>11</v>
       </c>
       <c r="AY14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ14">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BA14">
         <v>9</v>
@@ -4614,10 +4614,10 @@
         <v>4</v>
       </c>
       <c r="AY15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA15">
         <v>2</v>
@@ -4820,10 +4820,10 @@
         <v>7</v>
       </c>
       <c r="AY16">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA16">
         <v>12</v>
@@ -5026,7 +5026,7 @@
         <v>3</v>
       </c>
       <c r="AY17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ17">
         <v>8</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="AY18">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ18">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA18">
         <v>6</v>
@@ -5438,10 +5438,10 @@
         <v>7</v>
       </c>
       <c r="AY19">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ19">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA19">
         <v>6</v>
@@ -5644,7 +5644,7 @@
         <v>5</v>
       </c>
       <c r="AY20">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ20">
         <v>13</v>
@@ -5853,7 +5853,7 @@
         <v>14</v>
       </c>
       <c r="AZ21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA21">
         <v>8</v>
@@ -6056,10 +6056,10 @@
         <v>7</v>
       </c>
       <c r="AY22">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ22">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA22">
         <v>5</v>
@@ -6262,10 +6262,10 @@
         <v>5</v>
       </c>
       <c r="AY23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ23">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA23">
         <v>1</v>
@@ -6468,10 +6468,10 @@
         <v>8</v>
       </c>
       <c r="AY24">
+        <v>12</v>
+      </c>
+      <c r="AZ24">
         <v>13</v>
-      </c>
-      <c r="AZ24">
-        <v>17</v>
       </c>
       <c r="BA24">
         <v>3</v>
@@ -6674,10 +6674,10 @@
         <v>7</v>
       </c>
       <c r="AY25">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ25">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA25">
         <v>8</v>
@@ -6880,7 +6880,7 @@
         <v>4</v>
       </c>
       <c r="AY26">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ26">
         <v>8</v>
@@ -7086,7 +7086,7 @@
         <v>4</v>
       </c>
       <c r="AY27">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ27">
         <v>8</v>
@@ -7292,10 +7292,10 @@
         <v>6</v>
       </c>
       <c r="AY28">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA28">
         <v>6</v>
@@ -7498,10 +7498,10 @@
         <v>3</v>
       </c>
       <c r="AY29">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ29">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA29">
         <v>10</v>
@@ -8322,7 +8322,7 @@
         <v>10</v>
       </c>
       <c r="AY33">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ33">
         <v>14</v>
@@ -22536,10 +22536,10 @@
         <v>8</v>
       </c>
       <c r="AY102">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ102">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA102">
         <v>3</v>
@@ -23154,10 +23154,10 @@
         <v>10</v>
       </c>
       <c r="AY105">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ105">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA105">
         <v>2</v>
@@ -23360,10 +23360,10 @@
         <v>8</v>
       </c>
       <c r="AY106">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ106">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA106">
         <v>4</v>
@@ -27480,10 +27480,10 @@
         <v>7</v>
       </c>
       <c r="AY126">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ126">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA126">
         <v>2</v>
@@ -27686,10 +27686,10 @@
         <v>5</v>
       </c>
       <c r="AY127">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ127">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA127">
         <v>4</v>
@@ -27892,10 +27892,10 @@
         <v>7</v>
       </c>
       <c r="AY128">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ128">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA128">
         <v>5</v>
@@ -28304,10 +28304,10 @@
         <v>4</v>
       </c>
       <c r="AY130">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ130">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA130">
         <v>6</v>
@@ -28510,10 +28510,10 @@
         <v>4</v>
       </c>
       <c r="AY131">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ131">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA131">
         <v>7</v>
@@ -28716,10 +28716,10 @@
         <v>4</v>
       </c>
       <c r="AY132">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ132">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA132">
         <v>5</v>
@@ -31600,7 +31600,7 @@
         <v>3</v>
       </c>
       <c r="AY146">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ146">
         <v>8</v>
@@ -31806,10 +31806,10 @@
         <v>4</v>
       </c>
       <c r="AY147">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ147">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA147">
         <v>5</v>
